--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -9700,10 +9700,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="515">
-        <v>2486.976938296959</v>
+        <v>2484.6630678668002</v>
       </c>
       <c r="T9" s="6">
-        <v>46283.22324291667</v>
+        <v>46283.226254189816</v>
       </c>
       <c r="U9" s="6" t="inlineStr">
         <is>
@@ -9766,10 +9766,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="515">
-        <v>336.84317981883305</v>
+        <v>336.6318996179027</v>
       </c>
       <c r="T10" s="6">
-        <v>46283.22293982639</v>
+        <v>46283.225953946756</v>
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
@@ -9832,10 +9832,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="515">
-        <v>2.7222077104531777</v>
+        <v>2.712110021596802</v>
       </c>
       <c r="T11" s="6">
-        <v>46283.22294565973</v>
+        <v>46283.22595894676</v>
       </c>
       <c r="U11" s="6" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
       </c>
       <c r="S12" s="515"/>
       <c r="T12" s="6">
-        <v>46283.22295516204</v>
+        <v>46283.22596384259</v>
       </c>
       <c r="U12" s="6"/>
       <c r="V12" s="6" t="inlineStr">
@@ -9959,7 +9959,7 @@
       </c>
       <c r="S13" s="515"/>
       <c r="T13" s="6">
-        <v>46283.22296072917</v>
+        <v>46283.22596960649</v>
       </c>
       <c r="U13" s="6"/>
       <c r="V13" s="6" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="S14" s="515"/>
       <c r="T14" s="6">
-        <v>46283.22296304398</v>
+        <v>46283.22597613426</v>
       </c>
       <c r="U14" s="6"/>
       <c r="V14" s="6" t="inlineStr">
@@ -10079,7 +10079,7 @@
       </c>
       <c r="S15" s="515"/>
       <c r="T15" s="6">
-        <v>46283.222972222226</v>
+        <v>46283.225981840274</v>
       </c>
       <c r="U15" s="6"/>
       <c r="V15" s="6" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="S16" s="515"/>
       <c r="T16" s="6">
-        <v>46283.22297565972</v>
+        <v>46283.225988101854</v>
       </c>
       <c r="U16" s="6"/>
       <c r="V16" s="6" t="inlineStr">
@@ -10199,7 +10199,7 @@
       </c>
       <c r="S17" s="515"/>
       <c r="T17" s="6">
-        <v>46283.22298041666</v>
+        <v>46283.225993611115</v>
       </c>
       <c r="U17" s="6"/>
       <c r="V17" s="6" t="inlineStr">
@@ -10258,10 +10258,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="515">
-        <v>176.63324956539753</v>
+        <v>176.62741612974895</v>
       </c>
       <c r="T18" s="6">
-        <v>46283.22298625</v>
+        <v>46283.225998622685</v>
       </c>
       <c r="U18" s="6" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
       </c>
       <c r="S19" s="515"/>
       <c r="T19" s="6">
-        <v>46283.22299296296</v>
+        <v>46283.226004375</v>
       </c>
       <c r="U19" s="6"/>
       <c r="V19" s="6" t="inlineStr">
@@ -10384,10 +10384,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="515">
-        <v>86.24994870840253</v>
+        <v>86.24710024398982</v>
       </c>
       <c r="T20" s="6">
-        <v>46283.22299871528</v>
+        <v>46283.226011342595</v>
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
@@ -10451,7 +10451,7 @@
       </c>
       <c r="S21" s="515"/>
       <c r="T21" s="6">
-        <v>46283.22300519676</v>
+        <v>46283.22601709491</v>
       </c>
       <c r="U21" s="6"/>
       <c r="V21" s="6" t="inlineStr">
@@ -10510,10 +10510,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="515">
-        <v>8.767110126312438</v>
+        <v>8.76682058641623</v>
       </c>
       <c r="T22" s="6">
-        <v>46283.22300944444</v>
+        <v>46283.22602296296</v>
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
@@ -10577,7 +10577,7 @@
       </c>
       <c r="S23" s="515"/>
       <c r="T23" s="6">
-        <v>46283.22301515046</v>
+        <v>46283.22602857639</v>
       </c>
       <c r="U23" s="6"/>
       <c r="V23" s="6" t="inlineStr">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="S24" s="515"/>
       <c r="T24" s="6">
-        <v>46283.22302200231</v>
+        <v>46283.226034155094</v>
       </c>
       <c r="U24" s="6"/>
       <c r="V24" s="6" t="inlineStr">
@@ -10696,10 +10696,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="515">
-        <v>403.61733365759636</v>
+        <v>402.5131552347726</v>
       </c>
       <c r="T25" s="6">
-        <v>46283.223027719905</v>
+        <v>46283.226039803245</v>
       </c>
       <c r="U25" s="6" t="inlineStr">
         <is>
@@ -10763,7 +10763,7 @@
       </c>
       <c r="S26" s="515"/>
       <c r="T26" s="6">
-        <v>46283.22303346065</v>
+        <v>46283.22604488426</v>
       </c>
       <c r="U26" s="6"/>
       <c r="V26" s="6" t="inlineStr">
@@ -10822,10 +10822,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="515">
-        <v>349.15316321536767</v>
+        <v>349.1416321898437</v>
       </c>
       <c r="T27" s="6">
-        <v>46283.2230383912</v>
+        <v>46283.22605157407</v>
       </c>
       <c r="U27" s="6" t="inlineStr">
         <is>
@@ -10888,10 +10888,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="515">
-        <v>28.212880646204074</v>
+        <v>28.211948896241275</v>
       </c>
       <c r="T28" s="6">
-        <v>46283.22304478009</v>
+        <v>46283.226056481486</v>
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="S29" s="515"/>
       <c r="T29" s="6">
-        <v>46283.223049976856</v>
+        <v>46283.226063194445</v>
       </c>
       <c r="U29" s="6"/>
       <c r="V29" s="6" t="inlineStr">
@@ -11015,7 +11015,7 @@
       </c>
       <c r="S30" s="515"/>
       <c r="T30" s="6">
-        <v>46283.22305758102</v>
+        <v>46283.22606887731</v>
       </c>
       <c r="U30" s="6"/>
       <c r="V30" s="6" t="inlineStr">
@@ -11075,7 +11075,7 @@
       </c>
       <c r="S31" s="515"/>
       <c r="T31" s="6">
-        <v>46283.223061585646</v>
+        <v>46283.22607498843</v>
       </c>
       <c r="U31" s="6"/>
       <c r="V31" s="6" t="inlineStr">
@@ -11134,10 +11134,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="515">
-        <v>1158.1292428159238</v>
+        <v>1157.4905276304964</v>
       </c>
       <c r="T32" s="6">
-        <v>46283.22306899305</v>
+        <v>46283.22607966435</v>
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
@@ -11201,7 +11201,7 @@
       </c>
       <c r="S33" s="515"/>
       <c r="T33" s="6">
-        <v>46283.22307320602</v>
+        <v>46283.22608563657</v>
       </c>
       <c r="U33" s="6"/>
       <c r="V33" s="6" t="inlineStr">
@@ -11260,10 +11260,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="515">
-        <v>685.4358885055781</v>
+        <v>684.6196340753105</v>
       </c>
       <c r="T34" s="6">
-        <v>46283.22307894676</v>
+        <v>46283.22609211806</v>
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="S35" s="515"/>
       <c r="T35" s="6">
-        <v>46283.22308510417</v>
+        <v>46283.22609819444</v>
       </c>
       <c r="U35" s="6"/>
       <c r="V35" s="6" t="inlineStr">
@@ -11387,7 +11387,7 @@
       </c>
       <c r="S36" s="515"/>
       <c r="T36" s="6">
-        <v>46283.22309461806</v>
+        <v>46283.226103472225</v>
       </c>
       <c r="U36" s="6"/>
       <c r="V36" s="6" t="inlineStr">
@@ -11447,7 +11447,7 @@
       </c>
       <c r="S37" s="515"/>
       <c r="T37" s="6">
-        <v>46283.22309714121</v>
+        <v>46283.226108842595</v>
       </c>
       <c r="U37" s="6"/>
       <c r="V37" s="6" t="inlineStr">
@@ -11506,10 +11506,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="515">
-        <v>135.11247621821298</v>
+        <v>134.8048781952359</v>
       </c>
       <c r="T38" s="6">
-        <v>46283.22310221065</v>
+        <v>46283.22611443287</v>
       </c>
       <c r="U38" s="6" t="inlineStr">
         <is>
@@ -11572,10 +11572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="515">
-        <v>995.5473889324242</v>
+        <v>995.5145102890048</v>
       </c>
       <c r="T39" s="6">
-        <v>46283.22310894676</v>
+        <v>46283.22612101852</v>
       </c>
       <c r="U39" s="6" t="inlineStr">
         <is>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="S40" s="515"/>
       <c r="T40" s="6">
-        <v>46283.2231196412</v>
+        <v>46283.22613256945</v>
       </c>
       <c r="U40" s="6"/>
       <c r="V40" s="6" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="S41" s="515"/>
       <c r="T41" s="6">
-        <v>46283.22312538194</v>
+        <v>46283.22613861111</v>
       </c>
       <c r="U41" s="6"/>
       <c r="V41" s="6" t="inlineStr">
@@ -11758,10 +11758,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="515">
-        <v>221.23642273884118</v>
+        <v>221.12203294162856</v>
       </c>
       <c r="T42" s="6">
-        <v>46283.22311445602</v>
+        <v>46283.226125960646</v>
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
       </c>
       <c r="S43" s="515"/>
       <c r="T43" s="6">
-        <v>46283.22313121528</v>
+        <v>46283.226143368054</v>
       </c>
       <c r="U43" s="6"/>
       <c r="V43" s="6" t="inlineStr">
@@ -11885,7 +11885,7 @@
       </c>
       <c r="S44" s="515"/>
       <c r="T44" s="6">
-        <v>46283.223137037035</v>
+        <v>46283.22615027778</v>
       </c>
       <c r="U44" s="6"/>
       <c r="V44" s="6" t="inlineStr">
@@ -11944,10 +11944,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="515">
-        <v>717.3017317044123</v>
+        <v>717.2780423169226</v>
       </c>
       <c r="T45" s="6">
-        <v>46283.22314377315</v>
+        <v>46283.22615565972</v>
       </c>
       <c r="U45" s="6" t="inlineStr">
         <is>
@@ -12010,10 +12010,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="515">
-        <v>47.88883784749432</v>
+        <v>47.88725628539003</v>
       </c>
       <c r="T46" s="6">
-        <v>46283.22314864583</v>
+        <v>46283.226160694445</v>
       </c>
       <c r="U46" s="6" t="inlineStr">
         <is>
@@ -12076,10 +12076,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="515">
-        <v>154.69545801645134</v>
+        <v>154.69034909159325</v>
       </c>
       <c r="T47" s="6">
-        <v>46283.223154444444</v>
+        <v>46283.226167175926</v>
       </c>
       <c r="U47" s="6" t="inlineStr">
         <is>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="S48" s="515"/>
       <c r="T48" s="6">
-        <v>46283.22316415509</v>
+        <v>46283.22617317129</v>
       </c>
       <c r="U48" s="6"/>
       <c r="V48" s="6" t="inlineStr">
@@ -12202,10 +12202,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="515">
-        <v>101.60239954603183</v>
+        <v>101.59904405627577</v>
       </c>
       <c r="T49" s="6">
-        <v>46283.223166655094</v>
+        <v>46283.22617835648</v>
       </c>
       <c r="U49" s="6" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="S50" s="515"/>
       <c r="T50" s="6">
-        <v>46283.22317268518</v>
+        <v>46283.22618491898</v>
       </c>
       <c r="U50" s="6"/>
       <c r="V50" s="6" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="S51" s="515"/>
       <c r="T51" s="6">
-        <v>46283.22317939815</v>
+        <v>46283.226190243055</v>
       </c>
       <c r="U51" s="6"/>
       <c r="V51" s="6" t="inlineStr">
@@ -12389,7 +12389,7 @@
       </c>
       <c r="S52" s="515"/>
       <c r="T52" s="6">
-        <v>46283.22318341435</v>
+        <v>46283.226196261574</v>
       </c>
       <c r="U52" s="6"/>
       <c r="V52" s="6" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="S53" s="515"/>
       <c r="T53" s="6">
-        <v>46283.22318922453</v>
+        <v>46283.22620135417</v>
       </c>
       <c r="U53" s="6"/>
       <c r="V53" s="6" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="S54" s="515"/>
       <c r="T54" s="6">
-        <v>46283.22319506944</v>
+        <v>46283.226208078704</v>
       </c>
       <c r="U54" s="6"/>
       <c r="V54" s="6" t="inlineStr">
@@ -12568,10 +12568,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="515">
-        <v>155.5161235762203</v>
+        <v>155.3808863295644</v>
       </c>
       <c r="T55" s="6">
-        <v>46283.22320076389</v>
+        <v>46283.22621375</v>
       </c>
       <c r="U55" s="6" t="inlineStr">
         <is>
@@ -12634,10 +12634,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="515">
-        <v>766.0312513448406</v>
+        <v>764.885080592701</v>
       </c>
       <c r="T56" s="6">
-        <v>46283.223206608796</v>
+        <v>46283.226219421296</v>
       </c>
       <c r="U56" s="6" t="inlineStr">
         <is>
@@ -12700,10 +12700,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="515">
-        <v>368.9892502819787</v>
+        <v>368.17644127130905</v>
       </c>
       <c r="T57" s="6">
-        <v>46283.22321239583</v>
+        <v>46283.226225300925</v>
       </c>
       <c r="U57" s="6" t="inlineStr">
         <is>
@@ -12767,7 +12767,7 @@
       </c>
       <c r="S58" s="515"/>
       <c r="T58" s="6">
-        <v>46283.22321815972</v>
+        <v>46283.22623158565</v>
       </c>
       <c r="U58" s="6"/>
       <c r="V58" s="6" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="S59" s="515"/>
       <c r="T59" s="6">
-        <v>46283.22322488426</v>
+        <v>46283.22623645833</v>
       </c>
       <c r="U59" s="6"/>
       <c r="V59" s="6" t="inlineStr">
@@ -12887,7 +12887,7 @@
       </c>
       <c r="S60" s="515"/>
       <c r="T60" s="6">
-        <v>46283.22323321759</v>
+        <v>46283.22624185185</v>
       </c>
       <c r="U60" s="6"/>
       <c r="V60" s="6" t="inlineStr">
@@ -12947,7 +12947,7 @@
       </c>
       <c r="S61" s="515"/>
       <c r="T61" s="6">
-        <v>46283.223237453705</v>
+        <v>46283.22624802083</v>
       </c>
       <c r="U61" s="6"/>
       <c r="V61" s="6" t="inlineStr">
@@ -13007,7 +13007,7 @@
       </c>
       <c r="S62" s="515"/>
       <c r="T62" s="6">
-        <v>46283.22324291667</v>
+        <v>46283.226254189816</v>
       </c>
       <c r="U62" s="6"/>
       <c r="V62" s="6" t="inlineStr">

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,11 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R96b765a9d9dc4e93"/>
-    <sheet name="单币测算" sheetId="2" r:id="R57dd9c4cd02349d1"/>
-    <sheet name="全Quote预算" sheetId="3" r:id="R188a5d39cb1d4558"/>
-    <sheet name="选中Quote曲线" sheetId="4" r:id="Rb8d713ca8d9340c9"/>
-    <sheet name="Quote参数" sheetId="5" r:id="R6b34ddec61354312"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R81efb20ad7014217"/>
+    <sheet name="单币测算" sheetId="2" r:id="Race44d43fd85422b"/>
+    <sheet name="全Quote预算" sheetId="3" r:id="R5d5f64c74dea4a1a"/>
+    <sheet name="选中Quote曲线" sheetId="4" r:id="Rf2ab475e3ee74623"/>
+    <sheet name="Quote参数" sheetId="5" r:id="R32cccb051ed843c5"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -18,7 +18,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="14">
+  <x:numFmts count="15">
     <x:numFmt numFmtId="200" formatCode="@"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00000000"/>
     <x:numFmt numFmtId="202" formatCode="0.0000x"/>
@@ -33,6 +33,7 @@
     <x:numFmt numFmtId="211" formatCode="0.0%"/>
     <x:numFmt numFmtId="212" formatCode="General"/>
     <x:numFmt numFmtId="213" formatCode="0.000000"/>
+    <x:numFmt numFmtId="214" formatCode="yyyy-mm-dd hh:mm:ss"/>
   </x:numFmts>
   <x:fonts count="31">
     <x:font>
@@ -647,7 +648,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="516">
+  <x:cellXfs count="520">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2018,6 +2019,16 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="213" fontId="30" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="214" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -9650,7 +9661,7 @@
         <v>说明</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="C9" s="25" t="n">
         <v>1</v>
       </c>
@@ -9696,27 +9707,27 @@
       <c r="Q9" s="39" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R9" s="33" t="str">
+      <c r="R9" s="518" t="str">
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="515">
         <v>2484.6630678668002</v>
       </c>
-      <c r="T9" s="6">
+      <c r="T9" s="516">
         <v>46283.226254189816</v>
       </c>
-      <c r="U9" s="6" t="inlineStr">
+      <c r="U9" s="517" t="inlineStr">
         <is>
           <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin&amp;vs_currencies=usd</t>
         </is>
       </c>
-      <c r="V9" s="6" t="inlineStr">
+      <c r="V9" s="517" t="inlineStr">
         <is>
           <t>每日原生币价格；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="36" customHeight="1">
       <c r="C10" s="26" t="n">
         <v>2</v>
       </c>
@@ -9762,27 +9773,27 @@
       <c r="Q10" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R10" s="35" t="str">
+      <c r="R10" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="515">
         <v>336.6318996179027</v>
       </c>
-      <c r="T10" s="6">
+      <c r="T10" s="516">
         <v>46283.225953946756</v>
       </c>
-      <c r="U10" s="6" t="inlineStr">
+      <c r="U10" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x8bb3514e2204e1cdf3ac149efee7ff04d91b719f</t>
         </is>
       </c>
-      <c r="V10" s="6" t="inlineStr">
+      <c r="V10" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="36" customHeight="1">
       <c r="C11" s="26" t="n">
         <v>3</v>
       </c>
@@ -9828,27 +9839,27 @@
       <c r="Q11" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R11" s="35" t="str">
+      <c r="R11" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="515">
         <v>2.712110021596802</v>
       </c>
-      <c r="T11" s="6">
+      <c r="T11" s="516">
         <v>46283.22595894676</v>
       </c>
-      <c r="U11" s="6" t="inlineStr">
+      <c r="U11" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xcf38764ae8c92222af4358a701871a6235cfc7b7</t>
         </is>
       </c>
-      <c r="V11" s="6" t="inlineStr">
+      <c r="V11" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="36" customHeight="1">
       <c r="C12" s="26" t="n">
         <v>4</v>
       </c>
@@ -9894,21 +9905,29 @@
       <c r="Q12" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R12" s="35" t="str">
+      <c r="R12" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x86923f96303D656E4aa86D9d42D1e57ad2023fdC</v>
       </c>
-      <c r="S12" s="515"/>
-      <c r="T12" s="6">
+      <c r="S12" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T12" s="516">
         <v>46283.22596384259</v>
       </c>
-      <c r="U12" s="6"/>
-      <c r="V12" s="6" t="inlineStr">
+      <c r="U12" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V12" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="36" customHeight="1">
       <c r="C13" s="26" t="n">
         <v>5</v>
       </c>
@@ -9954,21 +9973,29 @@
       <c r="Q13" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R13" s="35" t="str">
+      <c r="R13" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x12f190a9F9d7D37a250758b26824B97CE941bF54</v>
       </c>
-      <c r="S13" s="515"/>
-      <c r="T13" s="6">
+      <c r="S13" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T13" s="516">
         <v>46283.22596960649</v>
       </c>
-      <c r="U13" s="6"/>
-      <c r="V13" s="6" t="inlineStr">
+      <c r="U13" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V13" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="36" customHeight="1">
       <c r="C14" s="26" t="n">
         <v>6</v>
       </c>
@@ -10014,21 +10041,29 @@
       <c r="Q14" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R14" s="35" t="str">
+      <c r="R14" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xad25ac6c84d497db898fa1e8387bf6af3532a1c4</v>
       </c>
-      <c r="S14" s="515"/>
-      <c r="T14" s="6">
+      <c r="S14" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T14" s="516">
         <v>46283.22597613426</v>
       </c>
-      <c r="U14" s="6"/>
-      <c r="V14" s="6" t="inlineStr">
+      <c r="U14" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V14" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="36" customHeight="1">
       <c r="C15" s="26" t="n">
         <v>7</v>
       </c>
@@ -10074,21 +10109,29 @@
       <c r="Q15" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R15" s="35" t="str">
+      <c r="R15" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x48E39E56aCdbA37b09020C0b734A613C9a2f100A</v>
       </c>
-      <c r="S15" s="515"/>
-      <c r="T15" s="6">
+      <c r="S15" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T15" s="516">
         <v>46283.225981840274</v>
       </c>
-      <c r="U15" s="6"/>
-      <c r="V15" s="6" t="inlineStr">
+      <c r="U15" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V15" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="36" customHeight="1">
       <c r="C16" s="26" t="n">
         <v>8</v>
       </c>
@@ -10134,21 +10177,29 @@
       <c r="Q16" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R16" s="35" t="str">
+      <c r="R16" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x822cc93ffd030293e9842c30bbd678f530701867</v>
       </c>
-      <c r="S16" s="515"/>
-      <c r="T16" s="6">
+      <c r="S16" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T16" s="516">
         <v>46283.225988101854</v>
       </c>
-      <c r="U16" s="6"/>
-      <c r="V16" s="6" t="inlineStr">
+      <c r="U16" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V16" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="36" customHeight="1">
       <c r="C17" s="26" t="n">
         <v>9</v>
       </c>
@@ -10194,21 +10245,29 @@
       <c r="Q17" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R17" s="35" t="str">
+      <c r="R17" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xcef9027c7d6985b85f0ba431125073529a947a68</v>
       </c>
-      <c r="S17" s="515"/>
-      <c r="T17" s="6">
+      <c r="S17" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T17" s="516">
         <v>46283.225993611115</v>
       </c>
-      <c r="U17" s="6"/>
-      <c r="V17" s="6" t="inlineStr">
+      <c r="U17" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V17" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="36" customHeight="1">
       <c r="C18" s="26" t="n">
         <v>10</v>
       </c>
@@ -10254,27 +10313,27 @@
       <c r="Q18" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R18" s="35" t="str">
+      <c r="R18" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="515">
         <v>176.62741612974895</v>
       </c>
-      <c r="T18" s="6">
+      <c r="T18" s="516">
         <v>46283.225998622685</v>
       </c>
-      <c r="U18" s="6" t="inlineStr">
+      <c r="U18" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x6707aeac7d0e519b083219d27bb427364363183a</t>
         </is>
       </c>
-      <c r="V18" s="6" t="inlineStr">
+      <c r="V18" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19" ht="36" customHeight="1">
       <c r="C19" s="26" t="n">
         <v>11</v>
       </c>
@@ -10320,21 +10379,29 @@
       <c r="Q19" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R19" s="35" t="str">
+      <c r="R19" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x4EA005168D7F09a7A0Ba9D1DEf21a479950E44C2</v>
       </c>
-      <c r="S19" s="515"/>
-      <c r="T19" s="6">
+      <c r="S19" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T19" s="516">
         <v>46283.226004375</v>
       </c>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6" t="inlineStr">
+      <c r="U19" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V19" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="36" customHeight="1">
       <c r="C20" s="26" t="n">
         <v>12</v>
       </c>
@@ -10380,27 +10447,27 @@
       <c r="Q20" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R20" s="35" t="str">
+      <c r="R20" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="515">
         <v>86.24710024398982</v>
       </c>
-      <c r="T20" s="6">
+      <c r="T20" s="516">
         <v>46283.226011342595</v>
       </c>
-      <c r="U20" s="6" t="inlineStr">
+      <c r="U20" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x754ddd4bf8e8635b4301a7f4af2ea7a82ab6cea7</t>
         </is>
       </c>
-      <c r="V20" s="6" t="inlineStr">
+      <c r="V20" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="36" customHeight="1">
       <c r="C21" s="26" t="n">
         <v>13</v>
       </c>
@@ -10446,21 +10513,29 @@
       <c r="Q21" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R21" s="35" t="str">
+      <c r="R21" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x941AE714EC6D8130c7B75d67160Ca08f1e7d11Dd</v>
       </c>
-      <c r="S21" s="515"/>
-      <c r="T21" s="6">
+      <c r="S21" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T21" s="516">
         <v>46283.22601709491</v>
       </c>
-      <c r="U21" s="6"/>
-      <c r="V21" s="6" t="inlineStr">
+      <c r="U21" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V21" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22" ht="36" customHeight="1">
       <c r="C22" s="26" t="n">
         <v>14</v>
       </c>
@@ -10506,27 +10581,27 @@
       <c r="Q22" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R22" s="35" t="str">
+      <c r="R22" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="515">
         <v>8.76682058641623</v>
       </c>
-      <c r="T22" s="6">
+      <c r="T22" s="516">
         <v>46283.22602296296</v>
       </c>
-      <c r="U22" s="6" t="inlineStr">
+      <c r="U22" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x81b4caac5d313ea0c831c4d16f8c23937602dcf1</t>
         </is>
       </c>
-      <c r="V22" s="6" t="inlineStr">
+      <c r="V22" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="20" customHeight="1">
+    <row r="23" ht="36" customHeight="1">
       <c r="C23" s="26" t="n">
         <v>15</v>
       </c>
@@ -10572,21 +10647,29 @@
       <c r="Q23" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R23" s="35" t="str">
+      <c r="R23" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x25c288e6d899b9bc30160965ad9644c67e73be0c</v>
       </c>
-      <c r="S23" s="515"/>
-      <c r="T23" s="6">
+      <c r="S23" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T23" s="516">
         <v>46283.22602857639</v>
       </c>
-      <c r="U23" s="6"/>
-      <c r="V23" s="6" t="inlineStr">
+      <c r="U23" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V23" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" ht="36" customHeight="1">
       <c r="C24" s="26" t="n">
         <v>16</v>
       </c>
@@ -10632,21 +10715,29 @@
       <c r="Q24" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R24" s="35" t="str">
+      <c r="R24" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x41F4267525a8AFf329540eF24fD83d9044758B33</v>
       </c>
-      <c r="S24" s="515"/>
-      <c r="T24" s="6">
+      <c r="S24" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T24" s="516">
         <v>46283.226034155094</v>
       </c>
-      <c r="U24" s="6"/>
-      <c r="V24" s="6" t="inlineStr">
+      <c r="U24" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V24" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
+    <row r="25" ht="36" customHeight="1">
       <c r="C25" s="26" t="n">
         <v>17</v>
       </c>
@@ -10692,27 +10783,27 @@
       <c r="Q25" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R25" s="35" t="str">
+      <c r="R25" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="515">
         <v>402.5131552347726</v>
       </c>
-      <c r="T25" s="6">
+      <c r="T25" s="516">
         <v>46283.226039803245</v>
       </c>
-      <c r="U25" s="6" t="inlineStr">
+      <c r="U25" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x98996e833ea35ec17c3645ca7b6dd40d188564c4</t>
         </is>
       </c>
-      <c r="V25" s="6" t="inlineStr">
+      <c r="V25" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
+    <row r="26" ht="36" customHeight="1">
       <c r="C26" s="26" t="n">
         <v>18</v>
       </c>
@@ -10758,21 +10849,29 @@
       <c r="Q26" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R26" s="35" t="str">
+      <c r="R26" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x1b0E319c6A659F002271B69dB8A7df2F911c153E</v>
       </c>
-      <c r="S26" s="515"/>
-      <c r="T26" s="6">
+      <c r="S26" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T26" s="516">
         <v>46283.22604488426</v>
       </c>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6" t="inlineStr">
+      <c r="U26" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V26" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27" ht="36" customHeight="1">
       <c r="C27" s="26" t="n">
         <v>19</v>
       </c>
@@ -10818,27 +10917,27 @@
       <c r="Q27" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R27" s="35" t="str">
+      <c r="R27" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="515">
         <v>349.1416321898437</v>
       </c>
-      <c r="T27" s="6">
+      <c r="T27" s="516">
         <v>46283.22605157407</v>
       </c>
-      <c r="U27" s="6" t="inlineStr">
+      <c r="U27" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x8c2b4303fa0b99d07a5d3e9411497a277e65b673</t>
         </is>
       </c>
-      <c r="V27" s="6" t="inlineStr">
+      <c r="V27" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28" ht="36" customHeight="1">
       <c r="C28" s="26" t="n">
         <v>20</v>
       </c>
@@ -10884,27 +10983,27 @@
       <c r="Q28" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R28" s="35" t="str">
+      <c r="R28" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="515">
         <v>28.211948896241275</v>
       </c>
-      <c r="T28" s="6">
+      <c r="T28" s="516">
         <v>46283.226056481486</v>
       </c>
-      <c r="U28" s="6" t="inlineStr">
+      <c r="U28" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xd10e6245961d697d975963682ece9979e9917fbc</t>
         </is>
       </c>
-      <c r="V28" s="6" t="inlineStr">
+      <c r="V28" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="20" customHeight="1">
+    <row r="29" ht="36" customHeight="1">
       <c r="C29" s="26" t="n">
         <v>21</v>
       </c>
@@ -10950,21 +11049,29 @@
       <c r="Q29" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R29" s="35" t="str">
+      <c r="R29" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x980dcf6766fa79f5cf0c4aadb3ab477ff15a9619</v>
       </c>
-      <c r="S29" s="515"/>
-      <c r="T29" s="6">
+      <c r="S29" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T29" s="516">
         <v>46283.226063194445</v>
       </c>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6" t="inlineStr">
+      <c r="U29" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V29" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="20" customHeight="1">
+    <row r="30" ht="36" customHeight="1">
       <c r="C30" s="26" t="n">
         <v>22</v>
       </c>
@@ -11010,21 +11117,29 @@
       <c r="Q30" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R30" s="35" t="str">
+      <c r="R30" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xacef2e09adb47ad6abebad9ff06689e60615c2b6</v>
       </c>
-      <c r="S30" s="515"/>
-      <c r="T30" s="6">
+      <c r="S30" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T30" s="516">
         <v>46283.22606887731</v>
       </c>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6" t="inlineStr">
+      <c r="U30" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V30" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" ht="36" customHeight="1">
       <c r="C31" s="26" t="n">
         <v>23</v>
       </c>
@@ -11070,21 +11185,29 @@
       <c r="Q31" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R31" s="35" t="str">
+      <c r="R31" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x03DfbBE0AC4E7bCDaFd08eD41A400326B77D8c80</v>
       </c>
-      <c r="S31" s="515"/>
-      <c r="T31" s="6">
+      <c r="S31" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T31" s="516">
         <v>46283.22607498843</v>
       </c>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6" t="inlineStr">
+      <c r="U31" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V31" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" ht="36" customHeight="1">
       <c r="C32" s="26" t="n">
         <v>24</v>
       </c>
@@ -11130,27 +11253,27 @@
       <c r="Q32" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R32" s="35" t="str">
+      <c r="R32" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="515">
         <v>1157.4905276304964</v>
       </c>
-      <c r="T32" s="6">
+      <c r="T32" s="516">
         <v>46283.22607966435</v>
       </c>
-      <c r="U32" s="6" t="inlineStr">
+      <c r="U32" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x666ba98ab094793e276215448f2485fd8e3c3ce5</t>
         </is>
       </c>
-      <c r="V32" s="6" t="inlineStr">
+      <c r="V32" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33" ht="36" customHeight="1">
       <c r="C33" s="26" t="n">
         <v>25</v>
       </c>
@@ -11196,21 +11319,29 @@
       <c r="Q33" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R33" s="35" t="str">
+      <c r="R33" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x4e62068525Ab11FE768e29dfD00ef909B9803016</v>
       </c>
-      <c r="S33" s="515"/>
-      <c r="T33" s="6">
+      <c r="S33" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T33" s="516">
         <v>46283.22608563657</v>
       </c>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6" t="inlineStr">
+      <c r="U33" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V33" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" ht="36" customHeight="1">
       <c r="C34" s="26" t="n">
         <v>26</v>
       </c>
@@ -11256,27 +11387,27 @@
       <c r="Q34" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R34" s="35" t="str">
+      <c r="R34" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="515">
         <v>684.6196340753105</v>
       </c>
-      <c r="T34" s="6">
+      <c r="T34" s="516">
         <v>46283.22609211806</v>
       </c>
-      <c r="U34" s="6" t="inlineStr">
+      <c r="U34" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xa4bdb396a69617eb7f70e2cc1ef526f7340b1b0d</t>
         </is>
       </c>
-      <c r="V34" s="6" t="inlineStr">
+      <c r="V34" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" ht="36" customHeight="1">
       <c r="C35" s="26" t="n">
         <v>27</v>
       </c>
@@ -11322,21 +11453,29 @@
       <c r="Q35" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R35" s="35" t="str">
+      <c r="R35" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x43B07D15cE533bEc5476d70C22a78a1B2B662155</v>
       </c>
-      <c r="S35" s="515"/>
-      <c r="T35" s="6">
+      <c r="S35" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T35" s="516">
         <v>46283.22609819444</v>
       </c>
-      <c r="U35" s="6"/>
-      <c r="V35" s="6" t="inlineStr">
+      <c r="U35" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V35" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
+    <row r="36" ht="36" customHeight="1">
       <c r="C36" s="26" t="n">
         <v>28</v>
       </c>
@@ -11382,21 +11521,29 @@
       <c r="Q36" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R36" s="35" t="str">
+      <c r="R36" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x62fd0668e10D8B72339BE2DCF7643001688ff13B</v>
       </c>
-      <c r="S36" s="515"/>
-      <c r="T36" s="6">
+      <c r="S36" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T36" s="516">
         <v>46283.226103472225</v>
       </c>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6" t="inlineStr">
+      <c r="U36" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V36" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
+    <row r="37" ht="36" customHeight="1">
       <c r="C37" s="26" t="n">
         <v>29</v>
       </c>
@@ -11442,21 +11589,29 @@
       <c r="Q37" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R37" s="35" t="str">
+      <c r="R37" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xe93237C50D904957Cf27E7B1133b510C669c2e74</v>
       </c>
-      <c r="S37" s="515"/>
-      <c r="T37" s="6">
+      <c r="S37" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T37" s="516">
         <v>46283.226108842595</v>
       </c>
-      <c r="U37" s="6"/>
-      <c r="V37" s="6" t="inlineStr">
+      <c r="U37" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V37" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
+    <row r="38" ht="36" customHeight="1">
       <c r="C38" s="26" t="n">
         <v>30</v>
       </c>
@@ -11502,27 +11657,27 @@
       <c r="Q38" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R38" s="35" t="str">
+      <c r="R38" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="515">
         <v>134.8048781952359</v>
       </c>
-      <c r="T38" s="6">
+      <c r="T38" s="516">
         <v>46283.22611443287</v>
       </c>
-      <c r="U38" s="6" t="inlineStr">
+      <c r="U38" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x70504a6fafdbfb75fe971faa4dd716e79ac5624c</t>
         </is>
       </c>
-      <c r="V38" s="6" t="inlineStr">
+      <c r="V38" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="20" customHeight="1">
+    <row r="39" ht="36" customHeight="1">
       <c r="C39" s="26" t="n">
         <v>31</v>
       </c>
@@ -11568,27 +11723,27 @@
       <c r="Q39" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R39" s="35" t="str">
+      <c r="R39" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="515">
         <v>995.5145102890048</v>
       </c>
-      <c r="T39" s="6">
+      <c r="T39" s="516">
         <v>46283.22612101852</v>
       </c>
-      <c r="U39" s="6" t="inlineStr">
+      <c r="U39" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x301f48ec369bb3bfa0bc04d44a79037aa0ee2340</t>
         </is>
       </c>
-      <c r="V39" s="6" t="inlineStr">
+      <c r="V39" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="20" customHeight="1">
+    <row r="40" ht="36" customHeight="1">
       <c r="C40" s="26" t="n">
         <v>32</v>
       </c>
@@ -11634,21 +11789,29 @@
       <c r="Q40" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R40" s="35" t="str">
+      <c r="R40" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xe0444ef8bf4ed74f74fd73686e2ddf4c1c5591e8</v>
       </c>
-      <c r="S40" s="515"/>
-      <c r="T40" s="6">
+      <c r="S40" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T40" s="516">
         <v>46283.22613256945</v>
       </c>
-      <c r="U40" s="6"/>
-      <c r="V40" s="6" t="inlineStr">
+      <c r="U40" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V40" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="20" customHeight="1">
+    <row r="41" ht="36" customHeight="1">
       <c r="C41" s="26" t="n">
         <v>33</v>
       </c>
@@ -11694,21 +11857,29 @@
       <c r="Q41" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R41" s="35" t="str">
+      <c r="R41" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x408c14038a04f7bd235329e26d2bf569ee20e250</v>
       </c>
-      <c r="S41" s="515"/>
-      <c r="T41" s="6">
+      <c r="S41" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T41" s="516">
         <v>46283.22613861111</v>
       </c>
-      <c r="U41" s="6"/>
-      <c r="V41" s="6" t="inlineStr">
+      <c r="U41" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V41" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="20" customHeight="1">
+    <row r="42" ht="36" customHeight="1">
       <c r="C42" s="26" t="n">
         <v>34</v>
       </c>
@@ -11754,27 +11925,27 @@
       <c r="Q42" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R42" s="35" t="str">
+      <c r="R42" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="515">
         <v>221.12203294162856</v>
       </c>
-      <c r="T42" s="6">
+      <c r="T42" s="516">
         <v>46283.226125960646</v>
       </c>
-      <c r="U42" s="6" t="inlineStr">
+      <c r="U42" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x62ab521f71431f78ac374cdbadc6cda3c8916b6c</t>
         </is>
       </c>
-      <c r="V42" s="6" t="inlineStr">
+      <c r="V42" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
+    <row r="43" ht="36" customHeight="1">
       <c r="C43" s="26" t="n">
         <v>35</v>
       </c>
@@ -11820,21 +11991,29 @@
       <c r="Q43" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R43" s="35" t="str">
+      <c r="R43" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x7066A64c24e4206CD62E83bf198c1E7EB361F51e</v>
       </c>
-      <c r="S43" s="515"/>
-      <c r="T43" s="6">
+      <c r="S43" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T43" s="516">
         <v>46283.226143368054</v>
       </c>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6" t="inlineStr">
+      <c r="U43" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V43" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="20" customHeight="1">
+    <row r="44" ht="36" customHeight="1">
       <c r="C44" s="26" t="n">
         <v>36</v>
       </c>
@@ -11880,21 +12059,29 @@
       <c r="Q44" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R44" s="35" t="str">
+      <c r="R44" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x894E1EC2D74FFE5AEF8Dc8A9e84686acCB964F2A</v>
       </c>
-      <c r="S44" s="515"/>
-      <c r="T44" s="6">
+      <c r="S44" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T44" s="516">
         <v>46283.22615027778</v>
       </c>
-      <c r="U44" s="6"/>
-      <c r="V44" s="6" t="inlineStr">
+      <c r="U44" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V44" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
+    <row r="45" ht="36" customHeight="1">
       <c r="C45" s="26" t="n">
         <v>37</v>
       </c>
@@ -11940,27 +12127,27 @@
       <c r="Q45" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R45" s="35" t="str">
+      <c r="R45" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="515">
         <v>717.2780423169226</v>
       </c>
-      <c r="T45" s="6">
+      <c r="T45" s="516">
         <v>46283.22615565972</v>
       </c>
-      <c r="U45" s="6" t="inlineStr">
+      <c r="U45" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xa40d00a55d43ba2d188039dcf88bd68f4f133e78</t>
         </is>
       </c>
-      <c r="V45" s="6" t="inlineStr">
+      <c r="V45" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="20" customHeight="1">
+    <row r="46" ht="36" customHeight="1">
       <c r="C46" s="26" t="n">
         <v>38</v>
       </c>
@@ -12006,27 +12193,27 @@
       <c r="Q46" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R46" s="35" t="str">
+      <c r="R46" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="515">
         <v>47.88725628539003</v>
       </c>
-      <c r="T46" s="6">
+      <c r="T46" s="516">
         <v>46283.226160694445</v>
       </c>
-      <c r="U46" s="6" t="inlineStr">
+      <c r="U46" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x6d25417718a8d6c529130a8ccc4bfbf0a18219d3</t>
         </is>
       </c>
-      <c r="V46" s="6" t="inlineStr">
+      <c r="V46" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="20" customHeight="1">
+    <row r="47" ht="36" customHeight="1">
       <c r="C47" s="26" t="n">
         <v>39</v>
       </c>
@@ -12072,27 +12259,27 @@
       <c r="Q47" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R47" s="35" t="str">
+      <c r="R47" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="515">
         <v>154.69034909159325</v>
       </c>
-      <c r="T47" s="6">
+      <c r="T47" s="516">
         <v>46283.226167175926</v>
       </c>
-      <c r="U47" s="6" t="inlineStr">
+      <c r="U47" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xa541143f20d7b0643123064abf25f423e375b531</t>
         </is>
       </c>
-      <c r="V47" s="6" t="inlineStr">
+      <c r="V47" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="48" ht="20" customHeight="1">
+    <row r="48" ht="36" customHeight="1">
       <c r="C48" s="26" t="n">
         <v>40</v>
       </c>
@@ -12138,21 +12325,29 @@
       <c r="Q48" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R48" s="35" t="str">
+      <c r="R48" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xB1BF26c1D20ff267A4f93550d1E0d06ac40a114B</v>
       </c>
-      <c r="S48" s="515"/>
-      <c r="T48" s="6">
+      <c r="S48" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T48" s="516">
         <v>46283.22617317129</v>
       </c>
-      <c r="U48" s="6"/>
-      <c r="V48" s="6" t="inlineStr">
+      <c r="U48" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V48" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
+    <row r="49" ht="36" customHeight="1">
       <c r="C49" s="26" t="n">
         <v>41</v>
       </c>
@@ -12198,27 +12393,27 @@
       <c r="Q49" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R49" s="35" t="str">
+      <c r="R49" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="515">
         <v>101.59904405627577</v>
       </c>
-      <c r="T49" s="6">
+      <c r="T49" s="516">
         <v>46283.22617835648</v>
       </c>
-      <c r="U49" s="6" t="inlineStr">
+      <c r="U49" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0x7f310e3d05e575bd449e4484ef5da15863ea43b1</t>
         </is>
       </c>
-      <c r="V49" s="6" t="inlineStr">
+      <c r="V49" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="20" customHeight="1">
+    <row r="50" ht="36" customHeight="1">
       <c r="C50" s="26" t="n">
         <v>42</v>
       </c>
@@ -12264,21 +12459,29 @@
       <c r="Q50" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R50" s="35" t="str">
+      <c r="R50" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xf53f66751b1eff985311b693531e3290f600c410</v>
       </c>
-      <c r="S50" s="515"/>
-      <c r="T50" s="6">
+      <c r="S50" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T50" s="516">
         <v>46283.22618491898</v>
       </c>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6" t="inlineStr">
+      <c r="U50" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V50" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="20" customHeight="1">
+    <row r="51" ht="36" customHeight="1">
       <c r="C51" s="26" t="n">
         <v>43</v>
       </c>
@@ -12324,21 +12527,29 @@
       <c r="Q51" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R51" s="35" t="str">
+      <c r="R51" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x84CAb63bc87912E71ad199ff14A0bA45de68FeF8</v>
       </c>
-      <c r="S51" s="515"/>
-      <c r="T51" s="6">
+      <c r="S51" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T51" s="516">
         <v>46283.226190243055</v>
       </c>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6" t="inlineStr">
+      <c r="U51" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V51" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="20" customHeight="1">
+    <row r="52" ht="36" customHeight="1">
       <c r="C52" s="26" t="n">
         <v>44</v>
       </c>
@@ -12384,21 +12595,29 @@
       <c r="Q52" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R52" s="35" t="str">
+      <c r="R52" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x411efb0e7f985935daec3d4c3ebaea0d0ad7d89f</v>
       </c>
-      <c r="S52" s="515"/>
-      <c r="T52" s="6">
+      <c r="S52" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T52" s="516">
         <v>46283.226196261574</v>
       </c>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6" t="inlineStr">
+      <c r="U52" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V52" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="20" customHeight="1">
+    <row r="53" ht="36" customHeight="1">
       <c r="C53" s="26" t="n">
         <v>45</v>
       </c>
@@ -12444,21 +12663,29 @@
       <c r="Q53" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R53" s="35" t="str">
+      <c r="R53" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xF6589F11Bc40b669e584073F428B05562F568733</v>
       </c>
-      <c r="S53" s="515"/>
-      <c r="T53" s="6">
+      <c r="S53" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T53" s="516">
         <v>46283.22620135417</v>
       </c>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6" t="inlineStr">
+      <c r="U53" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V53" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="54" ht="20" customHeight="1">
+    <row r="54" ht="36" customHeight="1">
       <c r="C54" s="26" t="n">
         <v>46</v>
       </c>
@@ -12504,21 +12731,29 @@
       <c r="Q54" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R54" s="35" t="str">
+      <c r="R54" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xB90A19fF0Af67f7779afF50A882A9CfF42446400</v>
       </c>
-      <c r="S54" s="515"/>
-      <c r="T54" s="6">
+      <c r="S54" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T54" s="516">
         <v>46283.226208078704</v>
       </c>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6" t="inlineStr">
+      <c r="U54" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V54" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="20" customHeight="1">
+    <row r="55" ht="36" customHeight="1">
       <c r="C55" s="26" t="n">
         <v>47</v>
       </c>
@@ -12564,27 +12799,27 @@
       <c r="Q55" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R55" s="35" t="str">
+      <c r="R55" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="515">
         <v>155.3808863295644</v>
       </c>
-      <c r="T55" s="6">
+      <c r="T55" s="516">
         <v>46283.22621375</v>
       </c>
-      <c r="U55" s="6" t="inlineStr">
+      <c r="U55" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xc3c9f0171490ef0f4536fe493f3b0ebb5ee0cb5e</t>
         </is>
       </c>
-      <c r="V55" s="6" t="inlineStr">
+      <c r="V55" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="20" customHeight="1">
+    <row r="56" ht="36" customHeight="1">
       <c r="C56" s="26" t="n">
         <v>48</v>
       </c>
@@ -12630,27 +12865,27 @@
       <c r="Q56" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R56" s="35" t="str">
+      <c r="R56" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="515">
         <v>764.885080592701</v>
       </c>
-      <c r="T56" s="6">
+      <c r="T56" s="516">
         <v>46283.226219421296</v>
       </c>
-      <c r="U56" s="6" t="inlineStr">
+      <c r="U56" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xddcbba3666f578e3f09516f21ff85bfee859ab5e</t>
         </is>
       </c>
-      <c r="V56" s="6" t="inlineStr">
+      <c r="V56" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="57" ht="20" customHeight="1">
+    <row r="57" ht="36" customHeight="1">
       <c r="C57" s="26" t="n">
         <v>49</v>
       </c>
@@ -12696,27 +12931,27 @@
       <c r="Q57" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R57" s="35" t="str">
+      <c r="R57" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="515">
         <v>368.17644127130905</v>
       </c>
-      <c r="T57" s="6">
+      <c r="T57" s="516">
         <v>46283.226225300925</v>
       </c>
-      <c r="U57" s="6" t="inlineStr">
+      <c r="U57" s="517" t="inlineStr">
         <is>
           <t>https://dexscreener.com/robinhood/0xa953ca88ff430e9487c60ca34d757414f4efda07</t>
         </is>
       </c>
-      <c r="V57" s="6" t="inlineStr">
+      <c r="V57" s="517" t="inlineStr">
         <is>
           <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
+    <row r="58" ht="36" customHeight="1">
       <c r="C58" s="26" t="n">
         <v>50</v>
       </c>
@@ -12762,21 +12997,29 @@
       <c r="Q58" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R58" s="35" t="str">
+      <c r="R58" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x58FfE4a942d3885bAa22D7520691F611EF09e7AA</v>
       </c>
-      <c r="S58" s="515"/>
-      <c r="T58" s="6">
+      <c r="S58" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T58" s="516">
         <v>46283.22623158565</v>
       </c>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6" t="inlineStr">
+      <c r="U58" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V58" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="20" customHeight="1">
+    <row r="59" ht="36" customHeight="1">
       <c r="C59" s="26" t="n">
         <v>51</v>
       </c>
@@ -12822,21 +13065,29 @@
       <c r="Q59" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R59" s="35" t="str">
+      <c r="R59" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x5e81213613b6B86EaB4c6c50d718d34359459786</v>
       </c>
-      <c r="S59" s="515"/>
-      <c r="T59" s="6">
+      <c r="S59" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T59" s="516">
         <v>46283.22623645833</v>
       </c>
-      <c r="U59" s="6"/>
-      <c r="V59" s="6" t="inlineStr">
+      <c r="U59" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V59" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="20" customHeight="1">
+    <row r="60" ht="36" customHeight="1">
       <c r="C60" s="26" t="n">
         <v>52</v>
       </c>
@@ -12882,21 +13133,29 @@
       <c r="Q60" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R60" s="35" t="str">
+      <c r="R60" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xf23250dac154d05bb671cb0d0ebef3c635c79ce2</v>
       </c>
-      <c r="S60" s="515"/>
-      <c r="T60" s="6">
+      <c r="S60" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T60" s="516">
         <v>46283.22624185185</v>
       </c>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6" t="inlineStr">
+      <c r="U60" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V60" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="20" customHeight="1">
+    <row r="61" ht="36" customHeight="1">
       <c r="C61" s="26" t="n">
         <v>53</v>
       </c>
@@ -12942,21 +13201,29 @@
       <c r="Q61" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R61" s="35" t="str">
+      <c r="R61" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xa30FA36Db767ad9eD3f7a60fC79526fB4d56D344</v>
       </c>
-      <c r="S61" s="515"/>
-      <c r="T61" s="6">
+      <c r="S61" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T61" s="516">
         <v>46283.22624802083</v>
       </c>
-      <c r="U61" s="6"/>
-      <c r="V61" s="6" t="inlineStr">
+      <c r="U61" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V61" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
+    <row r="62" ht="36" customHeight="1">
       <c r="C62" s="26" t="n">
         <v>54</v>
       </c>
@@ -13002,15 +13269,23 @@
       <c r="Q62" s="40" t="str">
         <v>Approved / Native</v>
       </c>
-      <c r="R62" s="35" t="str">
+      <c r="R62" s="519" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x9e7ABD3C9139D14E4c86DcE0e455AAB7A0C2FB3E</v>
       </c>
-      <c r="S62" s="515"/>
-      <c r="T62" s="6">
+      <c r="S62" s="515" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="T62" s="516">
         <v>46283.226254189816</v>
       </c>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6" t="inlineStr">
+      <c r="U62" s="517" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="V62" s="517" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
         </is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -9711,10 +9711,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="515">
-        <v>2484.6630678668002</v>
+        <v>2481.7308596853964</v>
       </c>
       <c r="T9" s="516">
-        <v>46283.226254189816</v>
+        <v>46283.229076828706</v>
       </c>
       <c r="U9" s="517" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="515">
-        <v>336.6318996179027</v>
+        <v>336.2102267154778</v>
       </c>
       <c r="T10" s="516">
-        <v>46283.225953946756</v>
+        <v>46283.22877545139</v>
       </c>
       <c r="U10" s="517" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="515">
-        <v>2.712110021596802</v>
+        <v>2.7120991647535195</v>
       </c>
       <c r="T11" s="516">
-        <v>46283.22595894676</v>
+        <v>46283.228781875005</v>
       </c>
       <c r="U11" s="517" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="T12" s="516">
-        <v>46283.22596384259</v>
+        <v>46283.228786747684</v>
       </c>
       <c r="U12" s="517" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="T13" s="516">
-        <v>46283.22596960649</v>
+        <v>46283.22879292824</v>
       </c>
       <c r="U13" s="517" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="T14" s="516">
-        <v>46283.22597613426</v>
+        <v>46283.22879886574</v>
       </c>
       <c r="U14" s="517" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="T15" s="516">
-        <v>46283.225981840274</v>
+        <v>46283.22880457176</v>
       </c>
       <c r="U15" s="517" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="T16" s="516">
-        <v>46283.225988101854</v>
+        <v>46283.228810706016</v>
       </c>
       <c r="U16" s="517" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="T17" s="516">
-        <v>46283.225993611115</v>
+        <v>46283.228815891205</v>
       </c>
       <c r="U17" s="517" t="inlineStr">
         <is>
@@ -10317,10 +10317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="515">
-        <v>176.62741612974895</v>
+        <v>176.24641472499718</v>
       </c>
       <c r="T18" s="516">
-        <v>46283.225998622685</v>
+        <v>46283.22882157408</v>
       </c>
       <c r="U18" s="517" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="T19" s="516">
-        <v>46283.226004375</v>
+        <v>46283.2288278588</v>
       </c>
       <c r="U19" s="517" t="inlineStr">
         <is>
@@ -10451,10 +10451,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="515">
-        <v>86.24710024398982</v>
+        <v>86.246754988361</v>
       </c>
       <c r="T20" s="516">
-        <v>46283.226011342595</v>
+        <v>46283.228835625</v>
       </c>
       <c r="U20" s="517" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         </is>
       </c>
       <c r="T21" s="516">
-        <v>46283.22601709491</v>
+        <v>46283.22883954861</v>
       </c>
       <c r="U21" s="517" t="inlineStr">
         <is>
@@ -10585,10 +10585,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="515">
-        <v>8.76682058641623</v>
+        <v>8.766785491970786</v>
       </c>
       <c r="T22" s="516">
-        <v>46283.22602296296</v>
+        <v>46283.228845150465</v>
       </c>
       <c r="U22" s="517" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="T23" s="516">
-        <v>46283.22602857639</v>
+        <v>46283.22885092592</v>
       </c>
       <c r="U23" s="517" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="T24" s="516">
-        <v>46283.226034155094</v>
+        <v>46283.228857256945</v>
       </c>
       <c r="U24" s="517" t="inlineStr">
         <is>
@@ -10787,10 +10787,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="515">
-        <v>402.5131552347726</v>
+        <v>402.5115439350057</v>
       </c>
       <c r="T25" s="516">
-        <v>46283.226039803245</v>
+        <v>46283.228863055556</v>
       </c>
       <c r="U25" s="517" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         </is>
       </c>
       <c r="T26" s="516">
-        <v>46283.22604488426</v>
+        <v>46283.22886776621</v>
       </c>
       <c r="U26" s="517" t="inlineStr">
         <is>
@@ -10921,10 +10921,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="515">
-        <v>349.1416321898437</v>
+        <v>349.14023454153516</v>
       </c>
       <c r="T27" s="516">
-        <v>46283.22605157407</v>
+        <v>46283.22887355324</v>
       </c>
       <c r="U27" s="517" t="inlineStr">
         <is>
@@ -10987,10 +10987,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="515">
-        <v>28.211948896241275</v>
+        <v>28.281890183001646</v>
       </c>
       <c r="T28" s="516">
-        <v>46283.226056481486</v>
+        <v>46283.228878981485</v>
       </c>
       <c r="U28" s="517" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="T29" s="516">
-        <v>46283.226063194445</v>
+        <v>46283.22888631944</v>
       </c>
       <c r="U29" s="517" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="T30" s="516">
-        <v>46283.22606887731</v>
+        <v>46283.22889162037</v>
       </c>
       <c r="U30" s="517" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="T31" s="516">
-        <v>46283.22607498843</v>
+        <v>46283.228897395835</v>
       </c>
       <c r="U31" s="517" t="inlineStr">
         <is>
@@ -11257,10 +11257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="515">
-        <v>1157.4905276304964</v>
+        <v>1157.4858940820195</v>
       </c>
       <c r="T32" s="516">
-        <v>46283.22607966435</v>
+        <v>46283.22890365741</v>
       </c>
       <c r="U32" s="517" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="T33" s="516">
-        <v>46283.22608563657</v>
+        <v>46283.22890925926</v>
       </c>
       <c r="U33" s="517" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="515">
-        <v>684.6196340753105</v>
+        <v>683.7392141517536</v>
       </c>
       <c r="T34" s="516">
-        <v>46283.22609211806</v>
+        <v>46283.228914872685</v>
       </c>
       <c r="U34" s="517" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="T35" s="516">
-        <v>46283.22609819444</v>
+        <v>46283.22892003472</v>
       </c>
       <c r="U35" s="517" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="T36" s="516">
-        <v>46283.226103472225</v>
+        <v>46283.22892554398</v>
       </c>
       <c r="U36" s="517" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         </is>
       </c>
       <c r="T37" s="516">
-        <v>46283.226108842595</v>
+        <v>46283.22893216435</v>
       </c>
       <c r="U37" s="517" t="inlineStr">
         <is>
@@ -11661,10 +11661,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="515">
-        <v>134.8048781952359</v>
+        <v>134.80433855804392</v>
       </c>
       <c r="T38" s="516">
-        <v>46283.22611443287</v>
+        <v>46283.22893792824</v>
       </c>
       <c r="U38" s="517" t="inlineStr">
         <is>
@@ -11727,10 +11727,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="515">
-        <v>995.5145102890048</v>
+        <v>995.5105251464635</v>
       </c>
       <c r="T39" s="516">
-        <v>46283.22612101852</v>
+        <v>46283.22894375</v>
       </c>
       <c r="U39" s="517" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         </is>
       </c>
       <c r="T40" s="516">
-        <v>46283.22613256945</v>
+        <v>46283.22895483796</v>
       </c>
       <c r="U40" s="517" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="T41" s="516">
-        <v>46283.22613861111</v>
+        <v>46283.2289609838</v>
       </c>
       <c r="U41" s="517" t="inlineStr">
         <is>
@@ -11929,10 +11929,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="515">
-        <v>221.12203294162856</v>
+        <v>220.8209153885107</v>
       </c>
       <c r="T42" s="516">
-        <v>46283.226125960646</v>
+        <v>46283.228949687495</v>
       </c>
       <c r="U42" s="517" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="T43" s="516">
-        <v>46283.226143368054</v>
+        <v>46283.22896710648</v>
       </c>
       <c r="U43" s="517" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="T44" s="516">
-        <v>46283.22615027778</v>
+        <v>46283.22897207176</v>
       </c>
       <c r="U44" s="517" t="inlineStr">
         <is>
@@ -12131,10 +12131,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="515">
-        <v>717.2780423169226</v>
+        <v>717.2751709823403</v>
       </c>
       <c r="T45" s="516">
-        <v>46283.22615565972</v>
+        <v>46283.22897837963</v>
       </c>
       <c r="U45" s="517" t="inlineStr">
         <is>
@@ -12197,10 +12197,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="515">
-        <v>47.88725628539003</v>
+        <v>47.88706458799111</v>
       </c>
       <c r="T46" s="516">
-        <v>46283.226160694445</v>
+        <v>46283.22898378472</v>
       </c>
       <c r="U46" s="517" t="inlineStr">
         <is>
@@ -12263,10 +12263,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="515">
-        <v>154.69034909159325</v>
+        <v>154.6897298509046</v>
       </c>
       <c r="T47" s="516">
-        <v>46283.226167175926</v>
+        <v>46283.228990069445</v>
       </c>
       <c r="U47" s="517" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="T48" s="516">
-        <v>46283.22617317129</v>
+        <v>46283.228996226855</v>
       </c>
       <c r="U48" s="517" t="inlineStr">
         <is>
@@ -12397,10 +12397,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="515">
-        <v>101.59904405627577</v>
+        <v>101.59863734530526</v>
       </c>
       <c r="T49" s="516">
-        <v>46283.22617835648</v>
+        <v>46283.22900111111</v>
       </c>
       <c r="U49" s="517" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="T50" s="516">
-        <v>46283.22618491898</v>
+        <v>46283.22900706019</v>
       </c>
       <c r="U50" s="517" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="T51" s="516">
-        <v>46283.226190243055</v>
+        <v>46283.22901306713</v>
       </c>
       <c r="U51" s="517" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="T52" s="516">
-        <v>46283.226196261574</v>
+        <v>46283.229019363425</v>
       </c>
       <c r="U52" s="517" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="T53" s="516">
-        <v>46283.22620135417</v>
+        <v>46283.22902486111</v>
       </c>
       <c r="U53" s="517" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="T54" s="516">
-        <v>46283.226208078704</v>
+        <v>46283.22903109954</v>
       </c>
       <c r="U54" s="517" t="inlineStr">
         <is>
@@ -12803,10 +12803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="515">
-        <v>155.3808863295644</v>
+        <v>155.17810785548014</v>
       </c>
       <c r="T55" s="516">
-        <v>46283.22621375</v>
+        <v>46283.22903584491</v>
       </c>
       <c r="U55" s="517" t="inlineStr">
         <is>
@@ -12869,10 +12869,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="515">
-        <v>764.885080592701</v>
+        <v>763.9713137968788</v>
       </c>
       <c r="T56" s="516">
-        <v>46283.226219421296</v>
+        <v>46283.229042175924</v>
       </c>
       <c r="U56" s="517" t="inlineStr">
         <is>
@@ -12935,10 +12935,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="515">
-        <v>368.17644127130905</v>
+        <v>368.1749674247868</v>
       </c>
       <c r="T57" s="516">
-        <v>46283.226225300925</v>
+        <v>46283.22904818287</v>
       </c>
       <c r="U57" s="517" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="T58" s="516">
-        <v>46283.22623158565</v>
+        <v>46283.22905378472</v>
       </c>
       <c r="U58" s="517" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="T59" s="516">
-        <v>46283.22623645833</v>
+        <v>46283.22905945602</v>
       </c>
       <c r="U59" s="517" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="T60" s="516">
-        <v>46283.22624185185</v>
+        <v>46283.22906563657</v>
       </c>
       <c r="U60" s="517" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="T61" s="516">
-        <v>46283.22624802083</v>
+        <v>46283.229071168986</v>
       </c>
       <c r="U61" s="517" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="T62" s="516">
-        <v>46283.226254189816</v>
+        <v>46283.229076828706</v>
       </c>
       <c r="U62" s="517" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -9711,10 +9711,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="515">
-        <v>2481.7308596853964</v>
+        <v>2485.31866601016</v>
       </c>
       <c r="T9" s="516">
-        <v>46283.229076828706</v>
+        <v>46283.257387997684</v>
       </c>
       <c r="U9" s="517" t="inlineStr">
         <is>
@@ -9777,10 +9777,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="515">
-        <v>336.2102267154778</v>
+        <v>336.7099400737369</v>
       </c>
       <c r="T10" s="516">
-        <v>46283.22877545139</v>
+        <v>46283.25708674768</v>
       </c>
       <c r="U10" s="517" t="inlineStr">
         <is>
@@ -9843,10 +9843,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="515">
-        <v>2.7120991647535195</v>
+        <v>2.7120937363644733</v>
       </c>
       <c r="T11" s="516">
-        <v>46283.228781875005</v>
+        <v>46283.257092824075</v>
       </c>
       <c r="U11" s="517" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
         </is>
       </c>
       <c r="T12" s="516">
-        <v>46283.228786747684</v>
+        <v>46283.25709865741</v>
       </c>
       <c r="U12" s="517" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         </is>
       </c>
       <c r="T13" s="516">
-        <v>46283.22879292824</v>
+        <v>46283.25710438657</v>
       </c>
       <c r="U13" s="517" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         </is>
       </c>
       <c r="T14" s="516">
-        <v>46283.22879886574</v>
+        <v>46283.257110624996</v>
       </c>
       <c r="U14" s="517" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         </is>
       </c>
       <c r="T15" s="516">
-        <v>46283.22880457176</v>
+        <v>46283.25711600694</v>
       </c>
       <c r="U15" s="517" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         </is>
       </c>
       <c r="T16" s="516">
-        <v>46283.228810706016</v>
+        <v>46283.25712197917</v>
       </c>
       <c r="U16" s="517" t="inlineStr">
         <is>
@@ -10254,7 +10254,7 @@
         </is>
       </c>
       <c r="T17" s="516">
-        <v>46283.228815891205</v>
+        <v>46283.25712760416</v>
       </c>
       <c r="U17" s="517" t="inlineStr">
         <is>
@@ -10317,10 +10317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="515">
-        <v>176.24641472499718</v>
+        <v>176.14218176432206</v>
       </c>
       <c r="T18" s="516">
-        <v>46283.22882157408</v>
+        <v>46283.25713391203</v>
       </c>
       <c r="U18" s="517" t="inlineStr">
         <is>
@@ -10388,7 +10388,7 @@
         </is>
       </c>
       <c r="T19" s="516">
-        <v>46283.2288278588</v>
+        <v>46283.25713881945</v>
       </c>
       <c r="U19" s="517" t="inlineStr">
         <is>
@@ -10451,10 +10451,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="515">
-        <v>86.246754988361</v>
+        <v>86.24658236158315</v>
       </c>
       <c r="T20" s="516">
-        <v>46283.228835625</v>
+        <v>46283.257144930554</v>
       </c>
       <c r="U20" s="517" t="inlineStr">
         <is>
@@ -10522,7 +10522,7 @@
         </is>
       </c>
       <c r="T21" s="516">
-        <v>46283.22883954861</v>
+        <v>46283.257150729165</v>
       </c>
       <c r="U21" s="517" t="inlineStr">
         <is>
@@ -10585,10 +10585,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="515">
-        <v>8.766785491970786</v>
+        <v>8.766767944853427</v>
       </c>
       <c r="T22" s="516">
-        <v>46283.228845150465</v>
+        <v>46283.25715621527</v>
       </c>
       <c r="U22" s="517" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         </is>
       </c>
       <c r="T23" s="516">
-        <v>46283.22885092592</v>
+        <v>46283.25716231481</v>
       </c>
       <c r="U23" s="517" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         </is>
       </c>
       <c r="T24" s="516">
-        <v>46283.228857256945</v>
+        <v>46283.25716813657</v>
       </c>
       <c r="U24" s="517" t="inlineStr">
         <is>
@@ -10787,10 +10787,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="515">
-        <v>402.5115439350057</v>
+        <v>402.65084645346207</v>
       </c>
       <c r="T25" s="516">
-        <v>46283.228863055556</v>
+        <v>46283.257173923615</v>
       </c>
       <c r="U25" s="517" t="inlineStr">
         <is>
@@ -10858,7 +10858,7 @@
         </is>
       </c>
       <c r="T26" s="516">
-        <v>46283.22886776621</v>
+        <v>46283.25717967592</v>
       </c>
       <c r="U26" s="517" t="inlineStr">
         <is>
@@ -10921,10 +10921,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="515">
-        <v>349.14023454153516</v>
+        <v>349.13953572157703</v>
       </c>
       <c r="T27" s="516">
-        <v>46283.22887355324</v>
+        <v>46283.257185486116</v>
       </c>
       <c r="U27" s="517" t="inlineStr">
         <is>
@@ -10987,10 +10987,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="515">
-        <v>28.281890183001646</v>
+        <v>28.25181039762697</v>
       </c>
       <c r="T28" s="516">
-        <v>46283.228878981485</v>
+        <v>46283.25719162037</v>
       </c>
       <c r="U28" s="517" t="inlineStr">
         <is>
@@ -11058,7 +11058,7 @@
         </is>
       </c>
       <c r="T29" s="516">
-        <v>46283.22888631944</v>
+        <v>46283.25719707176</v>
       </c>
       <c r="U29" s="517" t="inlineStr">
         <is>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="T30" s="516">
-        <v>46283.22889162037</v>
+        <v>46283.25720289352</v>
       </c>
       <c r="U30" s="517" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         </is>
       </c>
       <c r="T31" s="516">
-        <v>46283.228897395835</v>
+        <v>46283.257208703704</v>
       </c>
       <c r="U31" s="517" t="inlineStr">
         <is>
@@ -11257,10 +11257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="515">
-        <v>1157.4858940820195</v>
+        <v>1155.2018158017988</v>
       </c>
       <c r="T32" s="516">
-        <v>46283.22890365741</v>
+        <v>46283.257215949074</v>
       </c>
       <c r="U32" s="517" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         </is>
       </c>
       <c r="T33" s="516">
-        <v>46283.22890925926</v>
+        <v>46283.25722060185</v>
       </c>
       <c r="U33" s="517" t="inlineStr">
         <is>
@@ -11391,10 +11391,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="515">
-        <v>683.7392141517536</v>
+        <v>684.858710924834</v>
       </c>
       <c r="T34" s="516">
-        <v>46283.228914872685</v>
+        <v>46283.257226180554</v>
       </c>
       <c r="U34" s="517" t="inlineStr">
         <is>
@@ -11462,7 +11462,7 @@
         </is>
       </c>
       <c r="T35" s="516">
-        <v>46283.22892003472</v>
+        <v>46283.25723180555</v>
       </c>
       <c r="U35" s="517" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         </is>
       </c>
       <c r="T36" s="516">
-        <v>46283.22892554398</v>
+        <v>46283.257237604164</v>
       </c>
       <c r="U36" s="517" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         </is>
       </c>
       <c r="T37" s="516">
-        <v>46283.22893216435</v>
+        <v>46283.25724339121</v>
       </c>
       <c r="U37" s="517" t="inlineStr">
         <is>
@@ -11661,10 +11661,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="515">
-        <v>134.80433855804392</v>
+        <v>134.95418463053477</v>
       </c>
       <c r="T38" s="516">
-        <v>46283.22893792824</v>
+        <v>46283.25724918982</v>
       </c>
       <c r="U38" s="517" t="inlineStr">
         <is>
@@ -11727,10 +11727,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="515">
-        <v>995.5105251464635</v>
+        <v>995.5085325871573</v>
       </c>
       <c r="T39" s="516">
-        <v>46283.22894375</v>
+        <v>46283.25725491898</v>
       </c>
       <c r="U39" s="517" t="inlineStr">
         <is>
@@ -11798,7 +11798,7 @@
         </is>
       </c>
       <c r="T40" s="516">
-        <v>46283.22895483796</v>
+        <v>46283.25726651621</v>
       </c>
       <c r="U40" s="517" t="inlineStr">
         <is>
@@ -11866,7 +11866,7 @@
         </is>
       </c>
       <c r="T41" s="516">
-        <v>46283.2289609838</v>
+        <v>46283.25727201389</v>
       </c>
       <c r="U41" s="517" t="inlineStr">
         <is>
@@ -11929,10 +11929,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="515">
-        <v>220.8209153885107</v>
+        <v>221.37089833351345</v>
       </c>
       <c r="T42" s="516">
-        <v>46283.228949687495</v>
+        <v>46283.2572607176</v>
       </c>
       <c r="U42" s="517" t="inlineStr">
         <is>
@@ -12000,7 +12000,7 @@
         </is>
       </c>
       <c r="T43" s="516">
-        <v>46283.22896710648</v>
+        <v>46283.25727810185</v>
       </c>
       <c r="U43" s="517" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         </is>
       </c>
       <c r="T44" s="516">
-        <v>46283.22897207176</v>
+        <v>46283.25728392361</v>
       </c>
       <c r="U44" s="517" t="inlineStr">
         <is>
@@ -12131,10 +12131,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="515">
-        <v>717.2751709823403</v>
+        <v>717.7140752661054</v>
       </c>
       <c r="T45" s="516">
-        <v>46283.22897837963</v>
+        <v>46283.25728935185</v>
       </c>
       <c r="U45" s="517" t="inlineStr">
         <is>
@@ -12197,10 +12197,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="515">
-        <v>47.88706458799111</v>
+        <v>47.686814220578285</v>
       </c>
       <c r="T46" s="516">
-        <v>46283.22898378472</v>
+        <v>46283.25729663194</v>
       </c>
       <c r="U46" s="517" t="inlineStr">
         <is>
@@ -12263,10 +12263,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="515">
-        <v>154.6897298509046</v>
+        <v>154.19503856977585</v>
       </c>
       <c r="T47" s="516">
-        <v>46283.228990069445</v>
+        <v>46283.257300937505</v>
       </c>
       <c r="U47" s="517" t="inlineStr">
         <is>
@@ -12334,7 +12334,7 @@
         </is>
       </c>
       <c r="T48" s="516">
-        <v>46283.228996226855</v>
+        <v>46283.25730696759</v>
       </c>
       <c r="U48" s="517" t="inlineStr">
         <is>
@@ -12397,10 +12397,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="515">
-        <v>101.59863734530526</v>
+        <v>101.86864259208109</v>
       </c>
       <c r="T49" s="516">
-        <v>46283.22900111111</v>
+        <v>46283.25731277778</v>
       </c>
       <c r="U49" s="517" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         </is>
       </c>
       <c r="T50" s="516">
-        <v>46283.22900706019</v>
+        <v>46283.25731861111</v>
       </c>
       <c r="U50" s="517" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         </is>
       </c>
       <c r="T51" s="516">
-        <v>46283.22901306713</v>
+        <v>46283.2573240162</v>
       </c>
       <c r="U51" s="517" t="inlineStr">
         <is>
@@ -12604,7 +12604,7 @@
         </is>
       </c>
       <c r="T52" s="516">
-        <v>46283.229019363425</v>
+        <v>46283.25733010417</v>
       </c>
       <c r="U52" s="517" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         </is>
       </c>
       <c r="T53" s="516">
-        <v>46283.22902486111</v>
+        <v>46283.25733571759</v>
       </c>
       <c r="U53" s="517" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         </is>
       </c>
       <c r="T54" s="516">
-        <v>46283.22903109954</v>
+        <v>46283.25734185185</v>
       </c>
       <c r="U54" s="517" t="inlineStr">
         <is>
@@ -12803,10 +12803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="515">
-        <v>155.17810785548014</v>
+        <v>155.4700228576461</v>
       </c>
       <c r="T55" s="516">
-        <v>46283.22903584491</v>
+        <v>46283.25734780092</v>
       </c>
       <c r="U55" s="517" t="inlineStr">
         <is>
@@ -12869,10 +12869,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="515">
-        <v>763.9713137968788</v>
+        <v>764.8504645586393</v>
       </c>
       <c r="T56" s="516">
-        <v>46283.229042175924</v>
+        <v>46283.257352939814</v>
       </c>
       <c r="U56" s="517" t="inlineStr">
         <is>
@@ -12935,10 +12935,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="515">
-        <v>368.1749674247868</v>
+        <v>368.38339197860745</v>
       </c>
       <c r="T57" s="516">
-        <v>46283.22904818287</v>
+        <v>46283.257358703704</v>
       </c>
       <c r="U57" s="517" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         </is>
       </c>
       <c r="T58" s="516">
-        <v>46283.22905378472</v>
+        <v>46283.257364502315</v>
       </c>
       <c r="U58" s="517" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="T59" s="516">
-        <v>46283.22905945602</v>
+        <v>46283.25737034722</v>
       </c>
       <c r="U59" s="517" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         </is>
       </c>
       <c r="T60" s="516">
-        <v>46283.22906563657</v>
+        <v>46283.25737608797</v>
       </c>
       <c r="U60" s="517" t="inlineStr">
         <is>
@@ -13210,7 +13210,7 @@
         </is>
       </c>
       <c r="T61" s="516">
-        <v>46283.229071168986</v>
+        <v>46283.257382233794</v>
       </c>
       <c r="U61" s="517" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="T62" s="516">
-        <v>46283.229076828706</v>
+        <v>46283.257387997684</v>
       </c>
       <c r="U62" s="517" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4065,10 +4065,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2485.31866601016</v>
+        <v>2485.135266324185</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.257387997684</v>
+        <v>46283.28159923611</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4133,10 +4133,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.7099400737369</v>
+        <v>337.4377112363475</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.25708674768</v>
+        <v>46283.28129850695</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4201,10 +4201,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.7120937363644733</v>
+        <v>2.7122321670735015</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.257092824075</v>
+        <v>46283.28130398148</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4274,7 +4274,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.25709865741</v>
+        <v>46283.28131009259</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4344,7 +4344,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.25710438657</v>
+        <v>46283.28131586806</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -4414,7 +4414,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.257110624996</v>
+        <v>46283.281321689814</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.25711600694</v>
+        <v>46283.281327199074</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.25712197917</v>
+        <v>46283.28133326388</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -4624,7 +4624,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.25712760416</v>
+        <v>46283.28133873842</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>176.14218176432206</v>
+        <v>176.57532148958595</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.25713391203</v>
+        <v>46283.28134487269</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -4762,7 +4762,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.25713881945</v>
+        <v>46283.2813503125</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -4827,10 +4827,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>86.24658236158315</v>
+        <v>86.25098456029313</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.257144930554</v>
+        <v>46283.28135612269</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.257150729165</v>
+        <v>46283.28136226851</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -4965,10 +4965,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.766767944853427</v>
+        <v>8.767215418289252</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.25715621527</v>
+        <v>46283.28136770833</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.25716231481</v>
+        <v>46283.28137424769</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.25716813657</v>
+        <v>46283.28137965278</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5173,10 +5173,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>402.65084645346207</v>
+        <v>402.40017534430837</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.257173923615</v>
+        <v>46283.281385393515</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.25717967592</v>
+        <v>46283.28139115741</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5311,10 +5311,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.13953572157703</v>
+        <v>349.15735650440314</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.257185486116</v>
+        <v>46283.281396956016</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5379,10 +5379,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.25181039762697</v>
+        <v>28.233235953189475</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.25719162037</v>
+        <v>46283.281402789355</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -5452,7 +5452,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.25719707176</v>
+        <v>46283.281408587965</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.25720289352</v>
+        <v>46283.28141402778</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.257208703704</v>
+        <v>46283.28142013889</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -5657,10 +5657,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1155.2018158017988</v>
+        <v>1154.930507807926</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.257215949074</v>
+        <v>46283.281425925925</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -5730,7 +5730,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.25722060185</v>
+        <v>46283.28143171296</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -5795,10 +5795,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>684.858710924834</v>
+        <v>685.9345241133453</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.257226180554</v>
+        <v>46283.281437488426</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.25723180555</v>
+        <v>46283.281442997686</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.257237604164</v>
+        <v>46283.28144908565</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.25724339121</v>
+        <v>46283.2814550463</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6073,10 +6073,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>134.95418463053477</v>
+        <v>135.23129535607805</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.25724918982</v>
+        <v>46283.281460694445</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6141,10 +6141,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>995.5085325871573</v>
+        <v>993.3475250130857</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.25725491898</v>
+        <v>46283.28146615741</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6214,7 +6214,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.25726651621</v>
+        <v>46283.28147803241</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6284,7 +6284,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.25727201389</v>
+        <v>46283.281483796294</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6349,10 +6349,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.37089833351345</v>
+        <v>221.4822799163712</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.2572607176</v>
+        <v>46283.28147228009</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -6422,7 +6422,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.25727810185</v>
+        <v>46283.28148965278</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -6492,7 +6492,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.25728392361</v>
+        <v>46283.28149541667</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -6557,10 +6557,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>717.7140752661054</v>
+        <v>719.9425126879422</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.25728935185</v>
+        <v>46283.281501192134</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -6625,10 +6625,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.686814220578285</v>
+        <v>47.73928943520518</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.25729663194</v>
+        <v>46283.28150696759</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -6693,10 +6693,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>154.19503856977585</v>
+        <v>154.41708526116994</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.257300937505</v>
+        <v>46283.2815127662</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -6766,7 +6766,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.25730696759</v>
+        <v>46283.28151855324</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -6831,10 +6831,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.86864259208109</v>
+        <v>101.90386688244425</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.25731277778</v>
+        <v>46283.28152434028</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.25731861111</v>
+        <v>46283.28153008102</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.2573240162</v>
+        <v>46283.281535856484</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.25733010417</v>
+        <v>46283.28154171296</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7114,7 +7114,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.25733571759</v>
+        <v>46283.281547962964</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.25734185185</v>
+        <v>46283.28155325232</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7249,10 +7249,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>155.4700228576461</v>
+        <v>155.70814780564407</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.25734780092</v>
+        <v>46283.28155905093</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7317,10 +7317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>764.8504645586393</v>
+        <v>765.3198582433344</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.257352939814</v>
+        <v>46283.28156487268</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7385,10 +7385,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>368.38339197860745</v>
+        <v>368.15298991069653</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.257358703704</v>
+        <v>46283.28157099537</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.257364502315</v>
+        <v>46283.281576423615</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.25737034722</v>
+        <v>46283.28158219907</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -7598,7 +7598,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.25737608797</v>
+        <v>46283.28158795139</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -7668,7 +7668,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.257382233794</v>
+        <v>46283.281593761574</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.257387997684</v>
+        <v>46283.28159923611</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R88c0330aa756435a"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R0a1c5690fff84951"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Rda86b20109df4d7c"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Ra4b1910f27474888"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -28,7 +28,7 @@
     <x:numFmt numFmtId="209" formatCode="0.000000E+00"/>
     <x:numFmt numFmtId="210" formatCode="0.0000000000"/>
   </x:numFmts>
-  <x:fonts count="11">
+  <x:fonts count="12">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -80,8 +80,13 @@
       <x:name val="Arial"/>
     </x:font>
     <x:font>
+      <x:sz val="9"/>
+      <x:color rgb="FF667085"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
       <x:b/>
-      <x:sz val="13"/>
+      <x:sz val="12"/>
       <x:color rgb="FF365F20"/>
       <x:name val="Arial"/>
     </x:font>
@@ -111,12 +116,12 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFE8F3DD"/>
+        <x:fgColor rgb="FFEAF3FA"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFEAF3FA"/>
+        <x:fgColor rgb="FFE8F3DD"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -154,7 +159,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="102">
+  <x:cellXfs count="104">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -325,10 +330,19 @@
     <x:xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="208" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="206" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -364,19 +378,16 @@
     <x:xf numFmtId="205" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="9" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="208" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -406,22 +417,22 @@
     <x:xf numFmtId="210" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="1" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="10" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="10" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment vertical="center"/>
-    </x:xf>
-    <x:xf numFmtId="202" fontId="10" fillId="4" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="208" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -703,7 +714,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0" showOutlineSymbols="1"/>
+  </sheetPr>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1"/>
   <cols>
     <col min="1" max="1" width="2" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="2" hidden="0" customWidth="1"/>
@@ -719,7 +733,7 @@
     <col min="12" max="12" width="17" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" ht="6" customHeight="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -733,7 +747,7 @@
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="4" t="str">
@@ -749,7 +763,7 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" ht="20" customHeight="1">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="str">
@@ -765,7 +779,7 @@
       <c r="K3" s="5"/>
       <c r="L3" s="5"/>
     </row>
-    <row r="4" ht="26" customHeight="1">
+    <row r="4" ht="6" customHeight="1">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -779,7 +793,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" ht="27" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="8" t="str">
@@ -795,7 +809,7 @@
       <c r="K5" s="8"/>
       <c r="L5" s="8"/>
     </row>
-    <row r="6" ht="26" customHeight="1">
+    <row r="6" ht="20" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="48" t="str">
@@ -815,7 +829,7 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
     </row>
-    <row r="7" ht="26" customHeight="1">
+    <row r="7" ht="20" customHeight="1">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="35" t="str">
@@ -841,7 +855,7 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" ht="26" customHeight="1">
+    <row r="8" ht="20" customHeight="1">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
       <c r="C8" s="35" t="str">
@@ -871,7 +885,7 @@
       </c>
       <c r="L8" s="35"/>
     </row>
-    <row r="9" ht="26" customHeight="1">
+    <row r="9" ht="20" customHeight="1">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
       <c r="C9" s="35" t="str">
@@ -897,15 +911,11 @@
       <c r="K9" s="35"/>
       <c r="L9" s="35"/>
     </row>
-    <row r="10" ht="26" customHeight="1">
+    <row r="10" ht="20" customHeight="1">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="35" t="str">
-        <v>资金预留 / Quote</v>
-      </c>
-      <c r="D10" s="54" t="n">
-        <v>5</v>
-      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="35" t="str">
         <v>Holder 地址数</v>
@@ -925,7 +935,7 @@
       </c>
       <c r="L10" s="35"/>
     </row>
-    <row r="11" ht="38" customHeight="1">
+    <row r="11" ht="24" customHeight="1">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -947,21 +957,25 @@
       </c>
       <c r="L11" s="35"/>
     </row>
-    <row r="12" ht="38" customHeight="1">
+    <row r="12" ht="24" customHeight="1">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
+      <c r="F12" s="35" t="str">
+        <v>资金预留 / Quote</v>
+      </c>
+      <c r="G12" s="54" t="n">
+        <v>5</v>
+      </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
       <c r="J12" s="2"/>
       <c r="K12" s="35"/>
       <c r="L12" s="35"/>
     </row>
-    <row r="13" ht="26" customHeight="1">
+    <row r="13" ht="20" customHeight="1">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="55" t="str">
@@ -977,7 +991,7 @@
       <c r="K13" s="55"/>
       <c r="L13" s="55"/>
     </row>
-    <row r="14" ht="26" customHeight="1">
+    <row r="14" ht="6" customHeight="1">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
@@ -991,7 +1005,7 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
     </row>
-    <row r="15" ht="26" customHeight="1">
+    <row r="15" ht="6" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
@@ -1005,7 +1019,7 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
     </row>
-    <row r="16" ht="26" customHeight="1">
+    <row r="16" ht="6" customHeight="1">
       <c r="A16" s="2"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
@@ -1019,7 +1033,7 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
     </row>
-    <row r="17" ht="27" customHeight="1">
+    <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
       <c r="C17" s="8" t="str">
@@ -1035,53 +1049,55 @@
       <c r="K17" s="8"/>
       <c r="L17" s="8"/>
     </row>
-    <row r="18" ht="38" customHeight="1">
+    <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
       <c r="C18" s="35" t="str">
         <v>建议总资金 / Quote</v>
       </c>
-      <c r="D18" s="71">
+      <c r="D18" s="74">
         <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($D$21="","",SUM($D$21,$G$21,$J$21,$D$22)))</f>
       </c>
-      <c r="E18" s="57">
+      <c r="E18" s="62">
         <f>$D$7</f>
       </c>
       <c r="F18" s="35" t="str">
         <v>折合 USDT（不含 Gas）</v>
       </c>
-      <c r="G18" s="71">
+      <c r="G18" s="74">
         <f>IF(OR($D$18="",$D$24=""),"",$D$18*$D$24)</f>
       </c>
-      <c r="H18" s="57" t="str">
+      <c r="H18" s="62" t="str">
         <v>USDT</v>
       </c>
       <c r="I18" s="35" t="str">
         <v>Gas 储备 / ETH</v>
       </c>
-      <c r="J18" s="71">
+      <c r="J18" s="74">
         <f>$G$22*MAX(0,$G$11)</f>
       </c>
-      <c r="K18" s="57" t="str">
+      <c r="K18" s="62" t="str">
         <v>ETH</v>
       </c>
-      <c r="L18" s="57"/>
-    </row>
-    <row r="19" ht="26" customHeight="1">
+      <c r="L18" s="62"/>
+    </row>
+    <row r="19" ht="18" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-    </row>
-    <row r="20" ht="26" customHeight="1">
+      <c r="C19" s="57" t="str">
+        <v>Quote 资金构成：预算控筹率理论资金 + 额外内盘资金 + 资金预留 + 洗筹损耗</v>
+      </c>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+    </row>
+    <row r="20" ht="6" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -1095,46 +1111,46 @@
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
     </row>
-    <row r="21" ht="26" customHeight="1">
+    <row r="21" ht="20" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="35" t="str">
-        <v>理论累计投入 / Quote</v>
-      </c>
-      <c r="D21" s="58">
+      <c r="C21" s="35">
+        <f>"预算 "&amp;TEXT($J$22,"0%")&amp;" 理论资金 / Quote"</f>
+      </c>
+      <c r="D21" s="60">
         <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$35="","",$J$31+$J$35))</f>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" s="35" t="str">
         <v>额外内盘资金 / Quote</v>
       </c>
-      <c r="G21" s="58">
+      <c r="G21" s="60">
         <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$31="","",$J$31*MAX(0,$G$7-1)))</f>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="35" t="str">
-        <v>洗筹预算 / Quote</v>
-      </c>
-      <c r="J21" s="58">
+        <v>洗筹损耗 / Quote</v>
+      </c>
+      <c r="J21" s="60">
         <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$36="","",$J$36*($G$32+$J$7)*2))</f>
       </c>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
     </row>
-    <row r="22" ht="26" customHeight="1">
+    <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="35" t="str">
         <v>资金预留 / Quote</v>
       </c>
-      <c r="D22" s="58">
-        <f>$D$10</f>
+      <c r="D22" s="60">
+        <f>$G$12</f>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" s="35" t="str">
         <v>地址总数</v>
       </c>
-      <c r="G22" s="61">
+      <c r="G22" s="64">
         <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
       </c>
       <c r="H22" s="2"/>
@@ -1147,125 +1163,159 @@
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
     </row>
-    <row r="23" ht="40" customHeight="1">
+    <row r="23" ht="32" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="35" t="str">
         <v>目标是否可达</v>
       </c>
-      <c r="D23" s="63">
+      <c r="D23" s="66">
         <f>IF($J$41&lt;&gt;"参数有效",$J$41,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$43),"Creator Tax无效",IF($J$22&gt;=$G$23,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" s="35" t="str">
         <v>当前控筹上限</v>
       </c>
-      <c r="G23" s="60">
+      <c r="G23" s="63">
         <f>MIN(1-$G$41/$D$35,$G$33+(1-$G$32-$J$7)*$G$38/$D$35)</f>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="35" t="str">
         <v>资金口径</v>
       </c>
-      <c r="J23" s="58" t="str">
+      <c r="J23" s="60" t="str">
         <v>Quote 预算 + 单独 Gas</v>
       </c>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
     </row>
-    <row r="24" ht="40" customHeight="1">
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="35" t="str">
         <v>使用价格 / USDT</v>
       </c>
-      <c r="D24" s="58">
+      <c r="D24" s="60">
         <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" s="35" t="str">
         <v>行情时间 / UTC</v>
       </c>
-      <c r="G24" s="62">
+      <c r="G24" s="65">
         <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="35" t="str">
         <v>价格状态</v>
       </c>
-      <c r="J24" s="58">
+      <c r="J24" s="60">
         <f>IF($D$9&lt;&gt;"",IF($D$24="","手动价格无效","手动价格"),IF($D$24="","缺少价格","每日行情"))</f>
       </c>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
     </row>
-    <row r="25" ht="26" customHeight="1">
+    <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
       <c r="C25" s="35" t="str">
         <v>价格采用方式</v>
       </c>
-      <c r="D25" s="58">
+      <c r="D25" s="60">
         <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="58"/>
+      <c r="G25" s="60"/>
       <c r="H25" s="2"/>
       <c r="I25" s="2" t="str">
         <v>价格缺失时 USDT 结果留空</v>
       </c>
-      <c r="J25" s="58"/>
+      <c r="J25" s="60"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
     </row>
-    <row r="26" ht="26" customHeight="1">
+    <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="C26" s="35" t="str">
+        <v>内盘基础手续费</v>
+      </c>
+      <c r="D26" s="59">
+        <f>$G$31</f>
+      </c>
       <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
+      <c r="F26" s="35" t="str">
+        <v>外盘 Hook 手续费</v>
+      </c>
+      <c r="G26" s="59">
+        <f>$G$32</f>
+      </c>
       <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="I26" s="35" t="str">
+        <v>洗筹双边总费率</v>
+      </c>
+      <c r="J26" s="59">
+        <f>SUM(G27,J27)</f>
+      </c>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" ht="26" customHeight="1">
+    <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
+      <c r="C27" s="35" t="str">
+        <v>内盘买入含税费率</v>
+      </c>
+      <c r="D27" s="59">
+        <f>$G$31+$J$7</f>
+      </c>
       <c r="E27" s="2"/>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
+      <c r="F27" s="35" t="str">
+        <v>外盘买入含税费率</v>
+      </c>
+      <c r="G27" s="59">
+        <f>$G$32+$J$7</f>
+      </c>
       <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="I27" s="35" t="str">
+        <v>外盘卖出含税费率</v>
+      </c>
+      <c r="J27" s="59">
+        <f>$G$32+$J$7</f>
+      </c>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
     </row>
-    <row r="28" ht="26" customHeight="1">
+    <row r="28" ht="32" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="C28" s="35" t="str">
+        <v>沉没成本 / Quote</v>
+      </c>
+      <c r="D28" s="60">
+        <f>E88</f>
+      </c>
       <c r="E28" s="2"/>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
+      <c r="F28" s="35" t="str">
+        <v>一套内盘打满 / Quote</v>
+      </c>
+      <c r="G28" s="60">
+        <f>$J$31</f>
+      </c>
       <c r="H28" s="2"/>
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="2"/>
-    </row>
-    <row r="29" ht="27" customHeight="1">
+      <c r="I28" s="58" t="str">
+        <v>费率为预算加总口径；双边合计用于 FDV 洗筹预算。沉没成本与一套打满仅作参考，不重复计入总额。</v>
+      </c>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+    </row>
+    <row r="29" ht="24" customHeight="1" collapsed="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
       <c r="C29" s="8" t="str">
-        <v>三、模型信息与计算口径</v>
+        <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -1277,7 +1327,7 @@
       <c r="K29" s="8"/>
       <c r="L29" s="8"/>
     </row>
-    <row r="30" ht="26" customHeight="1">
+    <row r="30" ht="20" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
       <c r="C30" s="48" t="str">
@@ -1297,198 +1347,198 @@
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" ht="36" customHeight="1">
+    <row r="31" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31" s="35" t="str">
         <v>Quote 名称</v>
       </c>
-      <c r="D31" s="63">
+      <c r="D31" s="66">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
       </c>
       <c r="E31" s="35"/>
       <c r="F31" s="35" t="str">
         <v>内盘基础费</v>
       </c>
-      <c r="G31" s="60">
+      <c r="G31" s="63">
         <f>1%</f>
       </c>
       <c r="H31" s="2"/>
       <c r="I31" s="35" t="str">
         <v>一套内盘打满 / Quote</v>
       </c>
-      <c r="J31" s="58">
+      <c r="J31" s="60">
         <f>IF(1-$G$31-$J$7&gt;0,$G$34/(1-$G$31-$J$7),"")</f>
       </c>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
     </row>
-    <row r="32" ht="36" customHeight="1">
+    <row r="32" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32" s="35" t="str">
         <v>Quote 合约</v>
       </c>
-      <c r="D32" s="66">
+      <c r="D32" s="69">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
       </c>
       <c r="E32" s="35"/>
       <c r="F32" s="35" t="str">
         <v>外盘 Hook 费</v>
       </c>
-      <c r="G32" s="60">
+      <c r="G32" s="63">
         <f>1%</f>
       </c>
       <c r="H32" s="2"/>
       <c r="I32" s="35" t="str">
         <v>目标+1% Pool TOKEN</v>
       </c>
-      <c r="J32" s="68">
+      <c r="J32" s="71">
         <f>IF($J$22&lt;$G$23,$D$35*(1-$J$22)-$G$41,"")</f>
       </c>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
     </row>
-    <row r="33" ht="26" customHeight="1">
+    <row r="33" ht="20" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
-      <c r="D33" s="63"/>
+      <c r="D33" s="66"/>
       <c r="E33" s="35"/>
       <c r="F33" s="35" t="str">
         <v>毕业控筹率</v>
       </c>
-      <c r="G33" s="60">
+      <c r="G33" s="63">
         <f>$G$34/($G$36+$G$34)</f>
       </c>
       <c r="H33" s="2"/>
       <c r="I33" s="35" t="str">
         <v>目标+1% Pool Quote</v>
       </c>
-      <c r="J33" s="58">
+      <c r="J33" s="60">
         <f>IF($J$32="","",$G$40/$J$32)</f>
       </c>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
     </row>
-    <row r="34" ht="26" customHeight="1">
+    <row r="34" ht="20" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34" s="35" t="str">
         <v>Decimals</v>
       </c>
-      <c r="D34" s="64">
+      <c r="D34" s="67">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" s="35" t="str">
         <v>毕业真实 Quote</v>
       </c>
-      <c r="G34" s="58">
+      <c r="G34" s="60">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
       </c>
       <c r="H34" s="2"/>
       <c r="I34" s="35" t="str">
         <v>外盘净增加 / Quote</v>
       </c>
-      <c r="J34" s="58">
+      <c r="J34" s="60">
         <f>IF($J$33="","",MAX(0,$J$33-$G$34))</f>
       </c>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
     </row>
-    <row r="35" ht="26" customHeight="1">
+    <row r="35" ht="20" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35" s="35" t="str">
         <v>总供应量</v>
       </c>
-      <c r="D35" s="61">
+      <c r="D35" s="64">
         <f>1000000000</f>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" s="35" t="str">
         <v>内盘初始 TOKEN</v>
       </c>
-      <c r="G35" s="68">
+      <c r="G35" s="71">
         <f>$D$35</f>
       </c>
       <c r="H35" s="2"/>
       <c r="I35" s="35" t="str">
         <v>外盘含费投入 / Quote</v>
       </c>
-      <c r="J35" s="58">
+      <c r="J35" s="60">
         <f>IF($J$32="","",$G$40/($G$38-MAX(0,($J$22-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
       <c r="K35" s="2"/>
       <c r="L35" s="2"/>
     </row>
-    <row r="36" ht="36" customHeight="1">
+    <row r="36" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="35" t="str">
         <v>协议参数证据</v>
       </c>
-      <c r="D36" s="69">
+      <c r="D36" s="72">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
       </c>
       <c r="E36" s="35"/>
       <c r="F36" s="35" t="str">
         <v>phantom Quote</v>
       </c>
-      <c r="G36" s="58">
+      <c r="G36" s="60">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
       </c>
       <c r="H36" s="2"/>
       <c r="I36" s="35" t="str">
         <v>目标+1% FDV / Quote</v>
       </c>
-      <c r="J36" s="58">
+      <c r="J36" s="60">
         <f>IF($J$33="","",$J$33/$J$32*$D$35)</f>
       </c>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
     </row>
-    <row r="37" ht="26" customHeight="1">
+    <row r="37" ht="20" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
       <c r="C37" s="35" t="str">
         <v>外盘机制</v>
       </c>
-      <c r="D37" s="63" t="str">
+      <c r="D37" s="66" t="str">
         <v>Uniswap V4 / exact-input</v>
       </c>
       <c r="E37" s="35"/>
       <c r="F37" s="35" t="str">
         <v>内盘 k</v>
       </c>
-      <c r="G37" s="65">
+      <c r="G37" s="68">
         <f>$G$36*$D$35</f>
       </c>
       <c r="H37" s="2"/>
       <c r="I37" s="35" t="str">
         <v>洗筹单边费率</v>
       </c>
-      <c r="J37" s="60">
+      <c r="J37" s="63">
         <f>$G$32+$J$7</f>
       </c>
       <c r="K37" s="2"/>
       <c r="L37" s="2"/>
     </row>
-    <row r="38" ht="36" customHeight="1">
+    <row r="38" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
       <c r="C38" s="35" t="str">
         <v>费用方向</v>
       </c>
-      <c r="D38" s="63" t="str">
+      <c r="D38" s="66" t="str">
         <v>Hook + Creator Tax 从 Meme 输出扣除</v>
       </c>
       <c r="E38" s="35"/>
       <c r="F38" s="35" t="str">
         <v>外盘初始 TOKEN</v>
       </c>
-      <c r="G38" s="68">
+      <c r="G38" s="71">
         <f>$D$35*$G$36*$G$34/($G$36+$G$34)^2</f>
       </c>
       <c r="H38" s="2"/>
@@ -1501,109 +1551,109 @@
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
     </row>
-    <row r="39" ht="36" customHeight="1">
+    <row r="39" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A39" s="2"/>
       <c r="B39" s="2"/>
       <c r="C39" s="35" t="str">
         <v>洗筹口径</v>
       </c>
-      <c r="D39" s="63" t="str">
+      <c r="D39" s="66" t="str">
         <v>目标+1% FDV ×（Hook + Creator Tax）×2</v>
       </c>
       <c r="E39" s="35"/>
       <c r="F39" s="35" t="str">
         <v>外盘初始 Quote</v>
       </c>
-      <c r="G39" s="58">
+      <c r="G39" s="60">
         <f>$G$34</f>
       </c>
       <c r="H39" s="2"/>
       <c r="I39" s="35" t="str">
         <v>分红与回购口径</v>
       </c>
-      <c r="J39" s="70" t="str">
+      <c r="J39" s="73" t="str">
         <v>不抵扣分红 / 回购收益</v>
       </c>
       <c r="K39" s="35"/>
       <c r="L39" s="35"/>
     </row>
-    <row r="40" ht="26" customHeight="1">
+    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A40" s="2"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
-      <c r="D40" s="63"/>
+      <c r="D40" s="66"/>
       <c r="E40" s="35"/>
       <c r="F40" s="35" t="str">
         <v>外盘 k</v>
       </c>
-      <c r="G40" s="65">
+      <c r="G40" s="68">
         <f>$G$38*$G$34</f>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
-      <c r="J40" s="63"/>
+      <c r="J40" s="66"/>
       <c r="K40" s="35"/>
       <c r="L40" s="35"/>
     </row>
-    <row r="41" ht="36" customHeight="1">
+    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A41" s="2"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
-      <c r="D41" s="58"/>
+      <c r="D41" s="60"/>
       <c r="E41" s="2"/>
       <c r="F41" s="35" t="str">
         <v>Locker TOKEN</v>
       </c>
-      <c r="G41" s="68">
+      <c r="G41" s="71">
         <f>$D$35*$G$36^2/($G$36+$G$34)^2</f>
       </c>
       <c r="H41" s="2"/>
       <c r="I41" s="35" t="str">
         <v>输入检查</v>
       </c>
-      <c r="J41" s="63">
-        <f>IF(COUNT($D$8,$D$10,$G$7:$G$11,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$D$10&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</f>
+      <c r="J41" s="66">
+        <f>IF(COUNT($D$8,$G$7:$G$12,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$G$12&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</f>
       </c>
       <c r="K41" s="35"/>
       <c r="L41" s="35"/>
     </row>
-    <row r="42" ht="36" customHeight="1">
+    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A42" s="2"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
-      <c r="D42" s="58"/>
+      <c r="D42" s="60"/>
       <c r="E42" s="2"/>
       <c r="F42" s="35" t="str">
         <v>Snipe 窗口</v>
       </c>
-      <c r="G42" s="70" t="str">
+      <c r="G42" s="73" t="str">
         <v>3 秒；默认豁免或避开</v>
       </c>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
-      <c r="J42" s="58"/>
+      <c r="J42" s="60"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
     </row>
-    <row r="43" ht="36" customHeight="1">
+    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
       <c r="C43" s="2"/>
-      <c r="D43" s="58"/>
+      <c r="D43" s="60"/>
       <c r="E43" s="2"/>
       <c r="F43" s="35" t="str">
         <v>Creator Tax 上限</v>
       </c>
-      <c r="G43" s="60">
+      <c r="G43" s="63">
         <f>10%</f>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="58"/>
+      <c r="J43" s="60"/>
       <c r="K43" s="2"/>
       <c r="L43" s="2"/>
     </row>
-    <row r="44" ht="26" customHeight="1">
+    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A44" s="2"/>
       <c r="B44" s="2"/>
       <c r="C44" s="2"/>
@@ -1617,7 +1667,7 @@
       <c r="K44" s="2"/>
       <c r="L44" s="2"/>
     </row>
-    <row r="45" ht="26" customHeight="1">
+    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A45" s="2"/>
       <c r="B45" s="2"/>
       <c r="C45" s="2"/>
@@ -1631,7 +1681,7 @@
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
     </row>
-    <row r="46" ht="26" customHeight="1">
+    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A46" s="2"/>
       <c r="B46" s="2"/>
       <c r="C46" s="2"/>
@@ -1645,7 +1695,7 @@
       <c r="K46" s="2"/>
       <c r="L46" s="2"/>
     </row>
-    <row r="47" ht="27" customHeight="1">
+    <row r="47" ht="24" customHeight="1">
       <c r="A47" s="2"/>
       <c r="B47" s="2"/>
       <c r="C47" s="8" t="str">
@@ -1661,59 +1711,59 @@
       <c r="K47" s="8"/>
       <c r="L47" s="8"/>
     </row>
-    <row r="48" ht="38" customHeight="1">
+    <row r="48" ht="30" customHeight="1">
       <c r="A48" s="2"/>
       <c r="B48" s="2"/>
-      <c r="C48" s="75" t="str">
+      <c r="C48" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D48" s="75" t="str">
+      <c r="D48" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E48" s="75" t="str">
+      <c r="E48" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F48" s="75" t="str">
+      <c r="F48" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G48" s="75" t="str">
+      <c r="G48" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H48" s="75" t="str">
+      <c r="H48" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I48" s="75" t="str">
+      <c r="I48" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J48" s="75" t="str">
+      <c r="J48" s="77" t="str">
         <v>区间净投入
 / Quote</v>
       </c>
-      <c r="K48" s="75" t="str">
+      <c r="K48" s="77" t="str">
         <v>区间含费
 / Quote</v>
       </c>
-      <c r="L48" s="75" t="str">
+      <c r="L48" s="77" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
     </row>
-    <row r="49" ht="26" customHeight="1">
+    <row r="49" ht="20" customHeight="1">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="76" t="n">
+      <c r="C49" s="78" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="79">
+      <c r="D49" s="81">
         <f>$D$35*(1-C49)</f>
       </c>
       <c r="E49" s="26">
         <f>$G$37/D49</f>
       </c>
-      <c r="F49" s="82">
+      <c r="F49" s="84">
         <f>IF(OR(D49="",E49=""),"",E49/D49)</f>
       </c>
-      <c r="G49" s="82">
+      <c r="G49" s="84">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F49))),"",F49*$D$24)</f>
       </c>
       <c r="H49" s="26">
@@ -1728,26 +1778,26 @@
       <c r="K49" s="26">
         <f>J49/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L49" s="88">
+      <c r="L49" s="90">
         <f>SUM($K$49:K49)</f>
       </c>
     </row>
-    <row r="50" ht="26" customHeight="1">
+    <row r="50" ht="20" customHeight="1">
       <c r="A50" s="2"/>
       <c r="B50" s="2"/>
-      <c r="C50" s="77" t="n">
+      <c r="C50" s="79" t="n">
         <v>0.1</v>
       </c>
-      <c r="D50" s="80">
+      <c r="D50" s="82">
         <f>$D$35*(1-C50)</f>
       </c>
       <c r="E50" s="27">
         <f>$G$37/D50</f>
       </c>
-      <c r="F50" s="83">
+      <c r="F50" s="85">
         <f>IF(OR(D50="",E50=""),"",E50/D50)</f>
       </c>
-      <c r="G50" s="83">
+      <c r="G50" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F50))),"",F50*$D$24)</f>
       </c>
       <c r="H50" s="27">
@@ -1762,26 +1812,26 @@
       <c r="K50" s="27">
         <f>J50/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L50" s="89">
+      <c r="L50" s="91">
         <f>SUM($K$49:K50)</f>
       </c>
     </row>
-    <row r="51" ht="26" customHeight="1">
+    <row r="51" ht="20" customHeight="1">
       <c r="A51" s="2"/>
       <c r="B51" s="2"/>
-      <c r="C51" s="77" t="n">
+      <c r="C51" s="79" t="n">
         <v>0.2</v>
       </c>
-      <c r="D51" s="80">
+      <c r="D51" s="82">
         <f>$D$35*(1-C51)</f>
       </c>
       <c r="E51" s="27">
         <f>$G$37/D51</f>
       </c>
-      <c r="F51" s="83">
+      <c r="F51" s="85">
         <f>IF(OR(D51="",E51=""),"",E51/D51)</f>
       </c>
-      <c r="G51" s="83">
+      <c r="G51" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F51))),"",F51*$D$24)</f>
       </c>
       <c r="H51" s="27">
@@ -1796,26 +1846,26 @@
       <c r="K51" s="27">
         <f>J51/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L51" s="89">
+      <c r="L51" s="91">
         <f>SUM($K$49:K51)</f>
       </c>
     </row>
-    <row r="52" ht="26" customHeight="1">
+    <row r="52" ht="20" customHeight="1">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
-      <c r="C52" s="77" t="n">
+      <c r="C52" s="79" t="n">
         <v>0.3</v>
       </c>
-      <c r="D52" s="80">
+      <c r="D52" s="82">
         <f>$D$35*(1-C52)</f>
       </c>
       <c r="E52" s="27">
         <f>$G$37/D52</f>
       </c>
-      <c r="F52" s="83">
+      <c r="F52" s="85">
         <f>IF(OR(D52="",E52=""),"",E52/D52)</f>
       </c>
-      <c r="G52" s="83">
+      <c r="G52" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F52))),"",F52*$D$24)</f>
       </c>
       <c r="H52" s="27">
@@ -1830,26 +1880,26 @@
       <c r="K52" s="27">
         <f>J52/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L52" s="89">
+      <c r="L52" s="91">
         <f>SUM($K$49:K52)</f>
       </c>
     </row>
-    <row r="53" ht="26" customHeight="1">
+    <row r="53" ht="20" customHeight="1">
       <c r="A53" s="2"/>
       <c r="B53" s="2"/>
-      <c r="C53" s="77" t="n">
+      <c r="C53" s="79" t="n">
         <v>0.4</v>
       </c>
-      <c r="D53" s="80">
+      <c r="D53" s="82">
         <f>$D$35*(1-C53)</f>
       </c>
       <c r="E53" s="27">
         <f>$G$37/D53</f>
       </c>
-      <c r="F53" s="83">
+      <c r="F53" s="85">
         <f>IF(OR(D53="",E53=""),"",E53/D53)</f>
       </c>
-      <c r="G53" s="83">
+      <c r="G53" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F53))),"",F53*$D$24)</f>
       </c>
       <c r="H53" s="27">
@@ -1864,26 +1914,26 @@
       <c r="K53" s="27">
         <f>J53/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L53" s="89">
+      <c r="L53" s="91">
         <f>SUM($K$49:K53)</f>
       </c>
     </row>
-    <row r="54" ht="26" customHeight="1">
+    <row r="54" ht="20" customHeight="1">
       <c r="A54" s="2"/>
       <c r="B54" s="2"/>
-      <c r="C54" s="77" t="n">
+      <c r="C54" s="79" t="n">
         <v>0.5</v>
       </c>
-      <c r="D54" s="80">
+      <c r="D54" s="82">
         <f>$D$35*(1-C54)</f>
       </c>
       <c r="E54" s="27">
         <f>$G$37/D54</f>
       </c>
-      <c r="F54" s="83">
+      <c r="F54" s="85">
         <f>IF(OR(D54="",E54=""),"",E54/D54)</f>
       </c>
-      <c r="G54" s="83">
+      <c r="G54" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F54))),"",F54*$D$24)</f>
       </c>
       <c r="H54" s="27">
@@ -1898,26 +1948,26 @@
       <c r="K54" s="27">
         <f>J54/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L54" s="89">
+      <c r="L54" s="91">
         <f>SUM($K$49:K54)</f>
       </c>
     </row>
-    <row r="55" ht="26" customHeight="1">
+    <row r="55" ht="20" customHeight="1">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
-      <c r="C55" s="77" t="n">
+      <c r="C55" s="79" t="n">
         <v>0.6</v>
       </c>
-      <c r="D55" s="80">
+      <c r="D55" s="82">
         <f>$D$35*(1-C55)</f>
       </c>
       <c r="E55" s="27">
         <f>$G$37/D55</f>
       </c>
-      <c r="F55" s="83">
+      <c r="F55" s="85">
         <f>IF(OR(D55="",E55=""),"",E55/D55)</f>
       </c>
-      <c r="G55" s="83">
+      <c r="G55" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F55))),"",F55*$D$24)</f>
       </c>
       <c r="H55" s="27">
@@ -1932,26 +1982,26 @@
       <c r="K55" s="27">
         <f>J55/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L55" s="89">
+      <c r="L55" s="91">
         <f>SUM($K$49:K55)</f>
       </c>
     </row>
-    <row r="56" ht="26" customHeight="1">
+    <row r="56" ht="20" customHeight="1">
       <c r="A56" s="2"/>
       <c r="B56" s="2"/>
-      <c r="C56" s="77" t="n">
+      <c r="C56" s="79" t="n">
         <v>0.7</v>
       </c>
-      <c r="D56" s="80">
+      <c r="D56" s="82">
         <f>$D$35*(1-C56)</f>
       </c>
       <c r="E56" s="27">
         <f>$G$37/D56</f>
       </c>
-      <c r="F56" s="83">
+      <c r="F56" s="85">
         <f>IF(OR(D56="",E56=""),"",E56/D56)</f>
       </c>
-      <c r="G56" s="83">
+      <c r="G56" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F56))),"",F56*$D$24)</f>
       </c>
       <c r="H56" s="27">
@@ -1966,45 +2016,45 @@
       <c r="K56" s="27">
         <f>J56/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L56" s="89">
+      <c r="L56" s="91">
         <f>SUM($K$49:K56)</f>
       </c>
     </row>
-    <row r="57" ht="26" customHeight="1">
+    <row r="57" ht="20" customHeight="1">
       <c r="A57" s="2"/>
       <c r="B57" s="2"/>
-      <c r="C57" s="91">
+      <c r="C57" s="93">
         <f>$G$33</f>
       </c>
-      <c r="D57" s="92">
+      <c r="D57" s="94">
         <f>$D$35*(1-C57)</f>
       </c>
-      <c r="E57" s="93">
+      <c r="E57" s="95">
         <f>$G$37/D57</f>
       </c>
-      <c r="F57" s="94">
+      <c r="F57" s="96">
         <f>IF(OR(D57="",E57=""),"",E57/D57)</f>
       </c>
-      <c r="G57" s="94">
+      <c r="G57" s="96">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F57))),"",F57*$D$24)</f>
       </c>
-      <c r="H57" s="93">
+      <c r="H57" s="95">
         <f>IF(NOT(ISNUMBER(F57)),"",F57*$D$35)</f>
       </c>
-      <c r="I57" s="93">
+      <c r="I57" s="95">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H57))),"",H57*$D$24)</f>
       </c>
-      <c r="J57" s="93">
+      <c r="J57" s="95">
         <f>E57-E56</f>
       </c>
-      <c r="K57" s="93">
+      <c r="K57" s="95">
         <f>J57/(1-$G$31-$J$7)</f>
       </c>
-      <c r="L57" s="90">
+      <c r="L57" s="92">
         <f>SUM($K$49:K57)</f>
       </c>
     </row>
-    <row r="58" ht="26" customHeight="1">
+    <row r="58" ht="20" customHeight="1">
       <c r="A58" s="2"/>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -2018,7 +2068,7 @@
       <c r="K58" s="2"/>
       <c r="L58" s="2"/>
     </row>
-    <row r="59" ht="26" customHeight="1">
+    <row r="59" ht="20" customHeight="1">
       <c r="A59" s="2"/>
       <c r="B59" s="2"/>
       <c r="C59" s="2"/>
@@ -2032,7 +2082,7 @@
       <c r="K59" s="2"/>
       <c r="L59" s="2"/>
     </row>
-    <row r="60" ht="27" customHeight="1">
+    <row r="60" ht="24" customHeight="1">
       <c r="A60" s="2"/>
       <c r="B60" s="2"/>
       <c r="C60" s="8" t="str">
@@ -2048,93 +2098,93 @@
       <c r="K60" s="8"/>
       <c r="L60" s="8"/>
     </row>
-    <row r="61" ht="38" customHeight="1">
+    <row r="61" ht="30" customHeight="1">
       <c r="A61" s="2"/>
       <c r="B61" s="2"/>
-      <c r="C61" s="75" t="str">
+      <c r="C61" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D61" s="75" t="str">
+      <c r="D61" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E61" s="75" t="str">
+      <c r="E61" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F61" s="75" t="str">
+      <c r="F61" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G61" s="75" t="str">
+      <c r="G61" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H61" s="75" t="str">
+      <c r="H61" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I61" s="75" t="str">
+      <c r="I61" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J61" s="75" t="str">
+      <c r="J61" s="77" t="str">
         <v>外盘净投入
 / Quote</v>
       </c>
-      <c r="K61" s="75" t="str">
+      <c r="K61" s="77" t="str">
         <v>外盘含费
 / Quote</v>
       </c>
-      <c r="L61" s="75" t="str">
+      <c r="L61" s="77" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
     </row>
-    <row r="62" ht="26" customHeight="1">
+    <row r="62" ht="20" customHeight="1">
       <c r="A62" s="2"/>
       <c r="B62" s="2"/>
-      <c r="C62" s="95">
+      <c r="C62" s="97">
         <f>$G$33</f>
       </c>
-      <c r="D62" s="96">
+      <c r="D62" s="98">
         <f>$G$38</f>
       </c>
-      <c r="E62" s="97">
+      <c r="E62" s="99">
         <f>$G$34</f>
       </c>
-      <c r="F62" s="98">
+      <c r="F62" s="100">
         <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
       </c>
-      <c r="G62" s="98">
+      <c r="G62" s="100">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F62))),"",F62*$D$24)</f>
       </c>
-      <c r="H62" s="97">
+      <c r="H62" s="99">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$35)</f>
       </c>
-      <c r="I62" s="97">
+      <c r="I62" s="99">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H62))),"",H62*$D$24)</f>
       </c>
-      <c r="J62" s="97">
+      <c r="J62" s="99">
         <f>0</f>
       </c>
-      <c r="K62" s="97">
+      <c r="K62" s="99">
         <f>0</f>
       </c>
-      <c r="L62" s="88">
+      <c r="L62" s="90">
         <f>$J$31</f>
       </c>
     </row>
-    <row r="63" ht="26" customHeight="1">
+    <row r="63" ht="20" customHeight="1">
       <c r="A63" s="2"/>
       <c r="B63" s="2"/>
-      <c r="C63" s="77" t="n">
+      <c r="C63" s="79" t="n">
         <v>0.75</v>
       </c>
-      <c r="D63" s="80">
+      <c r="D63" s="82">
         <f>IF(C63&lt;$G$23,$D$35*(1-C63)-$G$41,"")</f>
       </c>
       <c r="E63" s="27">
         <f>IF(D63="","",$G$40/D63)</f>
       </c>
-      <c r="F63" s="83">
+      <c r="F63" s="85">
         <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
       </c>
-      <c r="G63" s="83">
+      <c r="G63" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F63))),"",F63*$D$24)</f>
       </c>
       <c r="H63" s="27">
@@ -2149,26 +2199,26 @@
       <c r="K63" s="27">
         <f>IF(D63="","",$G$40/($G$38-MAX(0,(C63-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L63" s="89">
+      <c r="L63" s="91">
         <f>IF(K63="","",$J$31+K63)</f>
       </c>
     </row>
-    <row r="64" ht="26" customHeight="1">
+    <row r="64" ht="20" customHeight="1">
       <c r="A64" s="2"/>
       <c r="B64" s="2"/>
-      <c r="C64" s="77" t="n">
+      <c r="C64" s="79" t="n">
         <v>0.8</v>
       </c>
-      <c r="D64" s="80">
+      <c r="D64" s="82">
         <f>IF(C64&lt;$G$23,$D$35*(1-C64)-$G$41,"")</f>
       </c>
       <c r="E64" s="27">
         <f>IF(D64="","",$G$40/D64)</f>
       </c>
-      <c r="F64" s="83">
+      <c r="F64" s="85">
         <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
       </c>
-      <c r="G64" s="83">
+      <c r="G64" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F64))),"",F64*$D$24)</f>
       </c>
       <c r="H64" s="27">
@@ -2183,26 +2233,26 @@
       <c r="K64" s="27">
         <f>IF(D64="","",$G$40/($G$38-MAX(0,(C64-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L64" s="89">
+      <c r="L64" s="91">
         <f>IF(K64="","",$J$31+K64)</f>
       </c>
     </row>
-    <row r="65" ht="26" customHeight="1">
+    <row r="65" ht="20" customHeight="1">
       <c r="A65" s="2"/>
       <c r="B65" s="2"/>
-      <c r="C65" s="77" t="n">
+      <c r="C65" s="79" t="n">
         <v>0.82</v>
       </c>
-      <c r="D65" s="80">
+      <c r="D65" s="82">
         <f>IF(C65&lt;$G$23,$D$35*(1-C65)-$G$41,"")</f>
       </c>
       <c r="E65" s="27">
         <f>IF(D65="","",$G$40/D65)</f>
       </c>
-      <c r="F65" s="83">
+      <c r="F65" s="85">
         <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
       </c>
-      <c r="G65" s="83">
+      <c r="G65" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F65))),"",F65*$D$24)</f>
       </c>
       <c r="H65" s="27">
@@ -2217,26 +2267,26 @@
       <c r="K65" s="27">
         <f>IF(D65="","",$G$40/($G$38-MAX(0,(C65-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L65" s="89">
+      <c r="L65" s="91">
         <f>IF(K65="","",$J$31+K65)</f>
       </c>
     </row>
-    <row r="66" ht="26" customHeight="1">
+    <row r="66" ht="20" customHeight="1">
       <c r="A66" s="2"/>
       <c r="B66" s="2"/>
-      <c r="C66" s="77" t="n">
+      <c r="C66" s="79" t="n">
         <v>0.84</v>
       </c>
-      <c r="D66" s="80">
+      <c r="D66" s="82">
         <f>IF(C66&lt;$G$23,$D$35*(1-C66)-$G$41,"")</f>
       </c>
       <c r="E66" s="27">
         <f>IF(D66="","",$G$40/D66)</f>
       </c>
-      <c r="F66" s="83">
+      <c r="F66" s="85">
         <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
       </c>
-      <c r="G66" s="83">
+      <c r="G66" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F66))),"",F66*$D$24)</f>
       </c>
       <c r="H66" s="27">
@@ -2251,26 +2301,26 @@
       <c r="K66" s="27">
         <f>IF(D66="","",$G$40/($G$38-MAX(0,(C66-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L66" s="89">
+      <c r="L66" s="91">
         <f>IF(K66="","",$J$31+K66)</f>
       </c>
     </row>
-    <row r="67" ht="26" customHeight="1">
+    <row r="67" ht="20" customHeight="1">
       <c r="A67" s="2"/>
       <c r="B67" s="2"/>
-      <c r="C67" s="77" t="n">
+      <c r="C67" s="79" t="n">
         <v>0.86</v>
       </c>
-      <c r="D67" s="80">
+      <c r="D67" s="82">
         <f>IF(C67&lt;$G$23,$D$35*(1-C67)-$G$41,"")</f>
       </c>
       <c r="E67" s="27">
         <f>IF(D67="","",$G$40/D67)</f>
       </c>
-      <c r="F67" s="83">
+      <c r="F67" s="85">
         <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
       </c>
-      <c r="G67" s="83">
+      <c r="G67" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F67))),"",F67*$D$24)</f>
       </c>
       <c r="H67" s="27">
@@ -2285,26 +2335,26 @@
       <c r="K67" s="27">
         <f>IF(D67="","",$G$40/($G$38-MAX(0,(C67-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L67" s="89">
+      <c r="L67" s="91">
         <f>IF(K67="","",$J$31+K67)</f>
       </c>
     </row>
-    <row r="68" ht="26" customHeight="1">
+    <row r="68" ht="20" customHeight="1">
       <c r="A68" s="2"/>
       <c r="B68" s="2"/>
-      <c r="C68" s="77" t="n">
+      <c r="C68" s="79" t="n">
         <v>0.88</v>
       </c>
-      <c r="D68" s="80">
+      <c r="D68" s="82">
         <f>IF(C68&lt;$G$23,$D$35*(1-C68)-$G$41,"")</f>
       </c>
       <c r="E68" s="27">
         <f>IF(D68="","",$G$40/D68)</f>
       </c>
-      <c r="F68" s="83">
+      <c r="F68" s="85">
         <f>IF(OR(D68="",E68=""),"",E68/D68)</f>
       </c>
-      <c r="G68" s="83">
+      <c r="G68" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F68))),"",F68*$D$24)</f>
       </c>
       <c r="H68" s="27">
@@ -2319,26 +2369,26 @@
       <c r="K68" s="27">
         <f>IF(D68="","",$G$40/($G$38-MAX(0,(C68-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L68" s="89">
+      <c r="L68" s="91">
         <f>IF(K68="","",$J$31+K68)</f>
       </c>
     </row>
-    <row r="69" ht="26" customHeight="1">
+    <row r="69" ht="20" customHeight="1">
       <c r="A69" s="2"/>
       <c r="B69" s="2"/>
-      <c r="C69" s="77" t="n">
+      <c r="C69" s="79" t="n">
         <v>0.89</v>
       </c>
-      <c r="D69" s="80">
+      <c r="D69" s="82">
         <f>IF(C69&lt;$G$23,$D$35*(1-C69)-$G$41,"")</f>
       </c>
       <c r="E69" s="27">
         <f>IF(D69="","",$G$40/D69)</f>
       </c>
-      <c r="F69" s="83">
+      <c r="F69" s="85">
         <f>IF(OR(D69="",E69=""),"",E69/D69)</f>
       </c>
-      <c r="G69" s="83">
+      <c r="G69" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F69))),"",F69*$D$24)</f>
       </c>
       <c r="H69" s="27">
@@ -2353,26 +2403,26 @@
       <c r="K69" s="27">
         <f>IF(D69="","",$G$40/($G$38-MAX(0,(C69-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L69" s="89">
+      <c r="L69" s="91">
         <f>IF(K69="","",$J$31+K69)</f>
       </c>
     </row>
-    <row r="70" ht="26" customHeight="1">
+    <row r="70" ht="20" customHeight="1">
       <c r="A70" s="2"/>
       <c r="B70" s="2"/>
-      <c r="C70" s="77" t="n">
+      <c r="C70" s="79" t="n">
         <v>0.9</v>
       </c>
-      <c r="D70" s="80">
+      <c r="D70" s="82">
         <f>IF(C70&lt;$G$23,$D$35*(1-C70)-$G$41,"")</f>
       </c>
       <c r="E70" s="27">
         <f>IF(D70="","",$G$40/D70)</f>
       </c>
-      <c r="F70" s="83">
+      <c r="F70" s="85">
         <f>IF(OR(D70="",E70=""),"",E70/D70)</f>
       </c>
-      <c r="G70" s="83">
+      <c r="G70" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F70))),"",F70*$D$24)</f>
       </c>
       <c r="H70" s="27">
@@ -2387,26 +2437,26 @@
       <c r="K70" s="27">
         <f>IF(D70="","",$G$40/($G$38-MAX(0,(C70-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L70" s="89">
+      <c r="L70" s="91">
         <f>IF(K70="","",$J$31+K70)</f>
       </c>
     </row>
-    <row r="71" ht="26" customHeight="1">
+    <row r="71" ht="20" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="2"/>
-      <c r="C71" s="77" t="n">
+      <c r="C71" s="79" t="n">
         <v>0.905</v>
       </c>
-      <c r="D71" s="80">
+      <c r="D71" s="82">
         <f>IF(C71&lt;$G$23,$D$35*(1-C71)-$G$41,"")</f>
       </c>
       <c r="E71" s="27">
         <f>IF(D71="","",$G$40/D71)</f>
       </c>
-      <c r="F71" s="83">
+      <c r="F71" s="85">
         <f>IF(OR(D71="",E71=""),"",E71/D71)</f>
       </c>
-      <c r="G71" s="83">
+      <c r="G71" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F71))),"",F71*$D$24)</f>
       </c>
       <c r="H71" s="27">
@@ -2421,26 +2471,26 @@
       <c r="K71" s="27">
         <f>IF(D71="","",$G$40/($G$38-MAX(0,(C71-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L71" s="89">
+      <c r="L71" s="91">
         <f>IF(K71="","",$J$31+K71)</f>
       </c>
     </row>
-    <row r="72" ht="26" customHeight="1">
+    <row r="72" ht="20" customHeight="1">
       <c r="A72" s="2"/>
       <c r="B72" s="2"/>
-      <c r="C72" s="77" t="n">
+      <c r="C72" s="79" t="n">
         <v>0.91</v>
       </c>
-      <c r="D72" s="80">
+      <c r="D72" s="82">
         <f>IF(C72&lt;$G$23,$D$35*(1-C72)-$G$41,"")</f>
       </c>
       <c r="E72" s="27">
         <f>IF(D72="","",$G$40/D72)</f>
       </c>
-      <c r="F72" s="83">
+      <c r="F72" s="85">
         <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
       </c>
-      <c r="G72" s="83">
+      <c r="G72" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F72))),"",F72*$D$24)</f>
       </c>
       <c r="H72" s="27">
@@ -2455,26 +2505,26 @@
       <c r="K72" s="27">
         <f>IF(D72="","",$G$40/($G$38-MAX(0,(C72-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L72" s="89">
+      <c r="L72" s="91">
         <f>IF(K72="","",$J$31+K72)</f>
       </c>
     </row>
-    <row r="73" ht="26" customHeight="1">
+    <row r="73" ht="20" customHeight="1">
       <c r="A73" s="2"/>
       <c r="B73" s="2"/>
-      <c r="C73" s="77" t="n">
+      <c r="C73" s="79" t="n">
         <v>0.915</v>
       </c>
-      <c r="D73" s="80">
+      <c r="D73" s="82">
         <f>IF(C73&lt;$G$23,$D$35*(1-C73)-$G$41,"")</f>
       </c>
       <c r="E73" s="27">
         <f>IF(D73="","",$G$40/D73)</f>
       </c>
-      <c r="F73" s="83">
+      <c r="F73" s="85">
         <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
       </c>
-      <c r="G73" s="83">
+      <c r="G73" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F73))),"",F73*$D$24)</f>
       </c>
       <c r="H73" s="27">
@@ -2489,26 +2539,26 @@
       <c r="K73" s="27">
         <f>IF(D73="","",$G$40/($G$38-MAX(0,(C73-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L73" s="89">
+      <c r="L73" s="91">
         <f>IF(K73="","",$J$31+K73)</f>
       </c>
     </row>
-    <row r="74" ht="26" customHeight="1">
+    <row r="74" ht="20" customHeight="1">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
-      <c r="C74" s="77" t="n">
+      <c r="C74" s="79" t="n">
         <v>0.918</v>
       </c>
-      <c r="D74" s="80">
+      <c r="D74" s="82">
         <f>IF(C74&lt;$G$23,$D$35*(1-C74)-$G$41,"")</f>
       </c>
       <c r="E74" s="27">
         <f>IF(D74="","",$G$40/D74)</f>
       </c>
-      <c r="F74" s="83">
+      <c r="F74" s="85">
         <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
       </c>
-      <c r="G74" s="83">
+      <c r="G74" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F74))),"",F74*$D$24)</f>
       </c>
       <c r="H74" s="27">
@@ -2523,26 +2573,26 @@
       <c r="K74" s="27">
         <f>IF(D74="","",$G$40/($G$38-MAX(0,(C74-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L74" s="89">
+      <c r="L74" s="91">
         <f>IF(K74="","",$J$31+K74)</f>
       </c>
     </row>
-    <row r="75" ht="26" customHeight="1">
+    <row r="75" ht="20" customHeight="1">
       <c r="A75" s="2"/>
       <c r="B75" s="2"/>
-      <c r="C75" s="78" t="n">
+      <c r="C75" s="80" t="n">
         <v>0.9183673469387755</v>
       </c>
-      <c r="D75" s="81">
+      <c r="D75" s="83">
         <f>IF(C75&lt;$G$23,$D$35*(1-C75)-$G$41,"")</f>
       </c>
       <c r="E75" s="28">
         <f>IF(D75="","",$G$40/D75)</f>
       </c>
-      <c r="F75" s="84">
+      <c r="F75" s="86">
         <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
       </c>
-      <c r="G75" s="84">
+      <c r="G75" s="86">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F75))),"",F75*$D$24)</f>
       </c>
       <c r="H75" s="28">
@@ -2557,11 +2607,11 @@
       <c r="K75" s="28">
         <f>IF(D75="","",$G$40/($G$38-MAX(0,(C75-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
       </c>
-      <c r="L75" s="90">
+      <c r="L75" s="92">
         <f>IF(K75="","",$J$31+K75)</f>
       </c>
     </row>
-    <row r="76" ht="26" customHeight="1">
+    <row r="76" ht="20" customHeight="1">
       <c r="A76" s="2"/>
       <c r="B76" s="2"/>
       <c r="C76" s="2"/>
@@ -2575,7 +2625,7 @@
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
     </row>
-    <row r="77" ht="26" customHeight="1">
+    <row r="77" ht="20" customHeight="1">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="C77" s="2"/>
@@ -2589,98 +2639,98 @@
       <c r="K77" s="2"/>
       <c r="L77" s="2"/>
     </row>
-    <row r="78" ht="27" customHeight="1">
+    <row r="78" ht="24" customHeight="1">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
-      <c r="C78" s="100" t="str">
+      <c r="C78" s="102" t="str">
         <v>外盘回落参考</v>
       </c>
-      <c r="D78" s="100"/>
-      <c r="E78" s="100"/>
-      <c r="F78" s="100"/>
-      <c r="G78" s="100"/>
-      <c r="H78" s="100"/>
-      <c r="I78" s="100"/>
-      <c r="J78" s="100"/>
-      <c r="K78" s="100"/>
-      <c r="L78" s="100"/>
-    </row>
-    <row r="79" ht="38" customHeight="1">
+      <c r="D78" s="102"/>
+      <c r="E78" s="102"/>
+      <c r="F78" s="102"/>
+      <c r="G78" s="102"/>
+      <c r="H78" s="102"/>
+      <c r="I78" s="102"/>
+      <c r="J78" s="102"/>
+      <c r="K78" s="102"/>
+      <c r="L78" s="102"/>
+    </row>
+    <row r="79" ht="30" customHeight="1">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
-      <c r="C79" s="75" t="str">
+      <c r="C79" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D79" s="75" t="str">
+      <c r="D79" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E79" s="75" t="str">
+      <c r="E79" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F79" s="75" t="str">
+      <c r="F79" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G79" s="75" t="str">
+      <c r="G79" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H79" s="75" t="str">
+      <c r="H79" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I79" s="75" t="str">
+      <c r="I79" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J79" s="75" t="str">
+      <c r="J79" s="77" t="str">
         <v>较毕业点回撤</v>
       </c>
-      <c r="K79" s="75" t="str"/>
-      <c r="L79" s="75" t="str"/>
-    </row>
-    <row r="80" ht="26" customHeight="1">
+      <c r="K79" s="77" t="str"/>
+      <c r="L79" s="77" t="str"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
-      <c r="C80" s="95" t="n">
+      <c r="C80" s="97" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="D80" s="96">
+      <c r="D80" s="98">
         <f>$D$35*(1-C80)-$G$41</f>
       </c>
-      <c r="E80" s="97">
+      <c r="E80" s="99">
         <f>$G$40/D80</f>
       </c>
-      <c r="F80" s="98">
+      <c r="F80" s="100">
         <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
       </c>
-      <c r="G80" s="98">
+      <c r="G80" s="100">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F80))),"",F80*$D$24)</f>
       </c>
-      <c r="H80" s="97">
+      <c r="H80" s="99">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$35)</f>
       </c>
-      <c r="I80" s="97">
+      <c r="I80" s="99">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H80))),"",H80*$D$24)</f>
       </c>
-      <c r="J80" s="95">
+      <c r="J80" s="97">
         <f>IF($H$80&gt;0,1-H80/$H$80,0)</f>
       </c>
-      <c r="K80" s="97"/>
-      <c r="L80" s="97"/>
-    </row>
-    <row r="81" ht="26" customHeight="1">
+      <c r="K80" s="99"/>
+      <c r="L80" s="99"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
-      <c r="C81" s="77" t="n">
+      <c r="C81" s="79" t="n">
         <v>0.7</v>
       </c>
-      <c r="D81" s="80">
+      <c r="D81" s="82">
         <f>$D$35*(1-C81)-$G$41</f>
       </c>
       <c r="E81" s="27">
         <f>$G$40/D81</f>
       </c>
-      <c r="F81" s="83">
+      <c r="F81" s="85">
         <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
       </c>
-      <c r="G81" s="83">
+      <c r="G81" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F81))),"",F81*$D$24)</f>
       </c>
       <c r="H81" s="27">
@@ -2689,28 +2739,28 @@
       <c r="I81" s="27">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H81))),"",H81*$D$24)</f>
       </c>
-      <c r="J81" s="77">
+      <c r="J81" s="79">
         <f>IF($H$80&gt;0,1-H81/$H$80,0)</f>
       </c>
       <c r="K81" s="27"/>
       <c r="L81" s="27"/>
     </row>
-    <row r="82" ht="26" customHeight="1">
+    <row r="82" ht="20" customHeight="1">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
-      <c r="C82" s="77" t="n">
+      <c r="C82" s="79" t="n">
         <v>0.6</v>
       </c>
-      <c r="D82" s="80">
+      <c r="D82" s="82">
         <f>$D$35*(1-C82)-$G$41</f>
       </c>
       <c r="E82" s="27">
         <f>$G$40/D82</f>
       </c>
-      <c r="F82" s="83">
+      <c r="F82" s="85">
         <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
       </c>
-      <c r="G82" s="83">
+      <c r="G82" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F82))),"",F82*$D$24)</f>
       </c>
       <c r="H82" s="27">
@@ -2719,28 +2769,28 @@
       <c r="I82" s="27">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H82))),"",H82*$D$24)</f>
       </c>
-      <c r="J82" s="77">
+      <c r="J82" s="79">
         <f>IF($H$80&gt;0,1-H82/$H$80,0)</f>
       </c>
       <c r="K82" s="27"/>
       <c r="L82" s="27"/>
     </row>
-    <row r="83" ht="26" customHeight="1">
+    <row r="83" ht="20" customHeight="1">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
-      <c r="C83" s="77" t="n">
+      <c r="C83" s="79" t="n">
         <v>0.5</v>
       </c>
-      <c r="D83" s="80">
+      <c r="D83" s="82">
         <f>$D$35*(1-C83)-$G$41</f>
       </c>
       <c r="E83" s="27">
         <f>$G$40/D83</f>
       </c>
-      <c r="F83" s="83">
+      <c r="F83" s="85">
         <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
       </c>
-      <c r="G83" s="83">
+      <c r="G83" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F83))),"",F83*$D$24)</f>
       </c>
       <c r="H83" s="27">
@@ -2749,28 +2799,28 @@
       <c r="I83" s="27">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H83))),"",H83*$D$24)</f>
       </c>
-      <c r="J83" s="77">
+      <c r="J83" s="79">
         <f>IF($H$80&gt;0,1-H83/$H$80,0)</f>
       </c>
       <c r="K83" s="27"/>
       <c r="L83" s="27"/>
     </row>
-    <row r="84" ht="26" customHeight="1">
+    <row r="84" ht="20" customHeight="1">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
-      <c r="C84" s="77" t="n">
+      <c r="C84" s="79" t="n">
         <v>0.4</v>
       </c>
-      <c r="D84" s="80">
+      <c r="D84" s="82">
         <f>$D$35*(1-C84)-$G$41</f>
       </c>
       <c r="E84" s="27">
         <f>$G$40/D84</f>
       </c>
-      <c r="F84" s="83">
+      <c r="F84" s="85">
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
       </c>
-      <c r="G84" s="83">
+      <c r="G84" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F84))),"",F84*$D$24)</f>
       </c>
       <c r="H84" s="27">
@@ -2779,28 +2829,28 @@
       <c r="I84" s="27">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H84))),"",H84*$D$24)</f>
       </c>
-      <c r="J84" s="77">
+      <c r="J84" s="79">
         <f>IF($H$80&gt;0,1-H84/$H$80,0)</f>
       </c>
       <c r="K84" s="27"/>
       <c r="L84" s="27"/>
     </row>
-    <row r="85" ht="26" customHeight="1">
+    <row r="85" ht="20" customHeight="1">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
-      <c r="C85" s="77" t="n">
+      <c r="C85" s="79" t="n">
         <v>0.3</v>
       </c>
-      <c r="D85" s="80">
+      <c r="D85" s="82">
         <f>$D$35*(1-C85)-$G$41</f>
       </c>
       <c r="E85" s="27">
         <f>$G$40/D85</f>
       </c>
-      <c r="F85" s="83">
+      <c r="F85" s="85">
         <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
       </c>
-      <c r="G85" s="83">
+      <c r="G85" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F85))),"",F85*$D$24)</f>
       </c>
       <c r="H85" s="27">
@@ -2809,28 +2859,28 @@
       <c r="I85" s="27">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H85))),"",H85*$D$24)</f>
       </c>
-      <c r="J85" s="77">
+      <c r="J85" s="79">
         <f>IF($H$80&gt;0,1-H85/$H$80,0)</f>
       </c>
       <c r="K85" s="27"/>
       <c r="L85" s="27"/>
     </row>
-    <row r="86" ht="26" customHeight="1">
+    <row r="86" ht="20" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
-      <c r="C86" s="77" t="n">
+      <c r="C86" s="79" t="n">
         <v>0.2</v>
       </c>
-      <c r="D86" s="80">
+      <c r="D86" s="82">
         <f>$D$35*(1-C86)-$G$41</f>
       </c>
       <c r="E86" s="27">
         <f>$G$40/D86</f>
       </c>
-      <c r="F86" s="83">
+      <c r="F86" s="85">
         <f>IF(OR(D86="",E86=""),"",E86/D86)</f>
       </c>
-      <c r="G86" s="83">
+      <c r="G86" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F86))),"",F86*$D$24)</f>
       </c>
       <c r="H86" s="27">
@@ -2839,28 +2889,28 @@
       <c r="I86" s="27">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H86))),"",H86*$D$24)</f>
       </c>
-      <c r="J86" s="77">
+      <c r="J86" s="79">
         <f>IF($H$80&gt;0,1-H86/$H$80,0)</f>
       </c>
       <c r="K86" s="27"/>
       <c r="L86" s="27"/>
     </row>
-    <row r="87" ht="26" customHeight="1">
+    <row r="87" ht="20" customHeight="1">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
-      <c r="C87" s="77" t="n">
+      <c r="C87" s="79" t="n">
         <v>0.1</v>
       </c>
-      <c r="D87" s="80">
+      <c r="D87" s="82">
         <f>$D$35*(1-C87)-$G$41</f>
       </c>
       <c r="E87" s="27">
         <f>$G$40/D87</f>
       </c>
-      <c r="F87" s="83">
+      <c r="F87" s="85">
         <f>IF(OR(D87="",E87=""),"",E87/D87)</f>
       </c>
-      <c r="G87" s="83">
+      <c r="G87" s="85">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F87))),"",F87*$D$24)</f>
       </c>
       <c r="H87" s="27">
@@ -2869,28 +2919,28 @@
       <c r="I87" s="27">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H87))),"",H87*$D$24)</f>
       </c>
-      <c r="J87" s="77">
+      <c r="J87" s="79">
         <f>IF($H$80&gt;0,1-H87/$H$80,0)</f>
       </c>
       <c r="K87" s="27"/>
       <c r="L87" s="27"/>
     </row>
-    <row r="88" ht="26" customHeight="1">
+    <row r="88" ht="20" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
-      <c r="C88" s="78" t="n">
+      <c r="C88" s="80" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="81">
+      <c r="D88" s="83">
         <f>$D$35*(1-C88)-$G$41</f>
       </c>
       <c r="E88" s="28">
         <f>$G$40/D88</f>
       </c>
-      <c r="F88" s="84">
+      <c r="F88" s="86">
         <f>IF(OR(D88="",E88=""),"",E88/D88)</f>
       </c>
-      <c r="G88" s="84">
+      <c r="G88" s="86">
         <f>IF(OR($D$24="",NOT(ISNUMBER(F88))),"",F88*$D$24)</f>
       </c>
       <c r="H88" s="28">
@@ -2899,17 +2949,17 @@
       <c r="I88" s="28">
         <f>IF(OR($D$24="",NOT(ISNUMBER(H88))),"",H88*$D$24)</f>
       </c>
-      <c r="J88" s="78">
+      <c r="J88" s="80">
         <f>IF($H$80&gt;0,1-H88/$H$80,0)</f>
       </c>
-      <c r="K88" s="101" t="str">
+      <c r="K88" s="103" t="str">
         <v>沉没成本 / Quote</v>
       </c>
       <c r="L88" s="28">
         <f>E88</f>
       </c>
     </row>
-    <row r="89" ht="26" customHeight="1">
+    <row r="89" ht="20" customHeight="1">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -2923,7 +2973,7 @@
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
     </row>
-    <row r="90" ht="26" customHeight="1">
+    <row r="90" ht="20" customHeight="1">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -2937,7 +2987,7 @@
       <c r="K90" s="2"/>
       <c r="L90" s="2"/>
     </row>
-    <row r="91" ht="26" customHeight="1">
+    <row r="91" ht="20" customHeight="1">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -2951,7 +3001,7 @@
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
     </row>
-    <row r="92" ht="26" customHeight="1">
+    <row r="92" ht="20" customHeight="1">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -2965,7 +3015,7 @@
       <c r="K92" s="2"/>
       <c r="L92" s="2"/>
     </row>
-    <row r="93" ht="26" customHeight="1">
+    <row r="93" ht="20" customHeight="1">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -2979,7 +3029,7 @@
       <c r="K93" s="2"/>
       <c r="L93" s="2"/>
     </row>
-    <row r="94" ht="26" customHeight="1">
+    <row r="94" ht="20" customHeight="1">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -2993,7 +3043,7 @@
       <c r="K94" s="2"/>
       <c r="L94" s="2"/>
     </row>
-    <row r="95" ht="26" customHeight="1">
+    <row r="95" ht="20" customHeight="1">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -3007,7 +3057,7 @@
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
     </row>
-    <row r="96" ht="26" customHeight="1">
+    <row r="96" ht="20" customHeight="1">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -3021,7 +3071,7 @@
       <c r="K96" s="2"/>
       <c r="L96" s="2"/>
     </row>
-    <row r="97" ht="26" customHeight="1">
+    <row r="97" ht="20" customHeight="1">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -3035,7 +3085,7 @@
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
     </row>
-    <row r="98" ht="26" customHeight="1">
+    <row r="98" ht="20" customHeight="1">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -3049,7 +3099,7 @@
       <c r="K98" s="2"/>
       <c r="L98" s="2"/>
     </row>
-    <row r="99" ht="26" customHeight="1">
+    <row r="99" ht="20" customHeight="1">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -3063,7 +3113,7 @@
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
     </row>
-    <row r="100" ht="26" customHeight="1">
+    <row r="100" ht="20" customHeight="1">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -3077,7 +3127,7 @@
       <c r="K100" s="2"/>
       <c r="L100" s="2"/>
     </row>
-    <row r="101" ht="26" customHeight="1">
+    <row r="101" ht="20" customHeight="1">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -3091,7 +3141,7 @@
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
     </row>
-    <row r="102" ht="26" customHeight="1">
+    <row r="102" ht="20" customHeight="1">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -3105,7 +3155,7 @@
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
     </row>
-    <row r="103" ht="26" customHeight="1">
+    <row r="103" ht="20" customHeight="1">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -3119,7 +3169,7 @@
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
     </row>
-    <row r="104" ht="26" customHeight="1">
+    <row r="104" ht="20" customHeight="1">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -3133,7 +3183,7 @@
       <c r="K104" s="2"/>
       <c r="L104" s="2"/>
     </row>
-    <row r="105" ht="26" customHeight="1">
+    <row r="105" ht="20" customHeight="1">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -3147,7 +3197,7 @@
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
     </row>
-    <row r="106" ht="26" customHeight="1">
+    <row r="106" ht="20" customHeight="1">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -3161,7 +3211,7 @@
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
     </row>
-    <row r="107" ht="26" customHeight="1">
+    <row r="107" ht="20" customHeight="1">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -3175,7 +3225,7 @@
       <c r="K107" s="2"/>
       <c r="L107" s="2"/>
     </row>
-    <row r="108" ht="26" customHeight="1">
+    <row r="108" ht="20" customHeight="1">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -3189,7 +3239,7 @@
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
     </row>
-    <row r="109" ht="26" customHeight="1">
+    <row r="109" ht="20" customHeight="1">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -3203,7 +3253,7 @@
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
     </row>
-    <row r="110" ht="26" customHeight="1">
+    <row r="110" ht="20" customHeight="1">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -3217,7 +3267,7 @@
       <c r="K110" s="2"/>
       <c r="L110" s="2"/>
     </row>
-    <row r="111" ht="26" customHeight="1">
+    <row r="111" ht="20" customHeight="1">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -3231,7 +3281,7 @@
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
     </row>
-    <row r="112" ht="26" customHeight="1">
+    <row r="112" ht="20" customHeight="1">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -3245,7 +3295,7 @@
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
     </row>
-    <row r="113" ht="26" customHeight="1">
+    <row r="113" ht="20" customHeight="1">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -3259,7 +3309,7 @@
       <c r="K113" s="2"/>
       <c r="L113" s="2"/>
     </row>
-    <row r="114" ht="26" customHeight="1">
+    <row r="114" ht="20" customHeight="1">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -3273,7 +3323,7 @@
       <c r="K114" s="2"/>
       <c r="L114" s="2"/>
     </row>
-    <row r="115" ht="26" customHeight="1">
+    <row r="115" ht="20" customHeight="1">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -3287,7 +3337,7 @@
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
     </row>
-    <row r="116" ht="26" customHeight="1">
+    <row r="116" ht="20" customHeight="1">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -3301,7 +3351,7 @@
       <c r="K116" s="2"/>
       <c r="L116" s="2"/>
     </row>
-    <row r="117" ht="26" customHeight="1">
+    <row r="117" ht="20" customHeight="1">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -3315,7 +3365,7 @@
       <c r="K117" s="2"/>
       <c r="L117" s="2"/>
     </row>
-    <row r="118" ht="26" customHeight="1">
+    <row r="118" ht="20" customHeight="1">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -3329,7 +3379,7 @@
       <c r="K118" s="2"/>
       <c r="L118" s="2"/>
     </row>
-    <row r="119" ht="26" customHeight="1">
+    <row r="119" ht="20" customHeight="1">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -3343,7 +3393,7 @@
       <c r="K119" s="2"/>
       <c r="L119" s="2"/>
     </row>
-    <row r="120" ht="26" customHeight="1">
+    <row r="120" ht="20" customHeight="1">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -3357,7 +3407,7 @@
       <c r="K120" s="2"/>
       <c r="L120" s="2"/>
     </row>
-    <row r="121" ht="26" customHeight="1">
+    <row r="121" ht="20" customHeight="1">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -3371,7 +3421,7 @@
       <c r="K121" s="2"/>
       <c r="L121" s="2"/>
     </row>
-    <row r="122" ht="26" customHeight="1">
+    <row r="122" ht="20" customHeight="1">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -3385,7 +3435,7 @@
       <c r="K122" s="2"/>
       <c r="L122" s="2"/>
     </row>
-    <row r="123" ht="26" customHeight="1">
+    <row r="123" ht="20" customHeight="1">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -3399,7 +3449,7 @@
       <c r="K123" s="2"/>
       <c r="L123" s="2"/>
     </row>
-    <row r="124" ht="26" customHeight="1">
+    <row r="124" ht="20" customHeight="1">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -3413,7 +3463,7 @@
       <c r="K124" s="2"/>
       <c r="L124" s="2"/>
     </row>
-    <row r="125" ht="26" customHeight="1">
+    <row r="125" ht="20" customHeight="1">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -3427,7 +3477,7 @@
       <c r="K125" s="2"/>
       <c r="L125" s="2"/>
     </row>
-    <row r="126" ht="26" customHeight="1">
+    <row r="126" ht="20" customHeight="1">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -3441,7 +3491,7 @@
       <c r="K126" s="2"/>
       <c r="L126" s="2"/>
     </row>
-    <row r="127" ht="26" customHeight="1">
+    <row r="127" ht="20" customHeight="1">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -3455,7 +3505,7 @@
       <c r="K127" s="2"/>
       <c r="L127" s="2"/>
     </row>
-    <row r="128" ht="26" customHeight="1">
+    <row r="128" ht="20" customHeight="1">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -3469,7 +3519,7 @@
       <c r="K128" s="2"/>
       <c r="L128" s="2"/>
     </row>
-    <row r="129" ht="26" customHeight="1">
+    <row r="129" ht="20" customHeight="1">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -3483,7 +3533,7 @@
       <c r="K129" s="2"/>
       <c r="L129" s="2"/>
     </row>
-    <row r="130" ht="26" customHeight="1">
+    <row r="130" ht="20" customHeight="1">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -3497,7 +3547,7 @@
       <c r="K130" s="2"/>
       <c r="L130" s="2"/>
     </row>
-    <row r="131" ht="26" customHeight="1">
+    <row r="131" ht="20" customHeight="1">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -3511,7 +3561,7 @@
       <c r="K131" s="2"/>
       <c r="L131" s="2"/>
     </row>
-    <row r="132" ht="26" customHeight="1">
+    <row r="132" ht="20" customHeight="1">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -3525,7 +3575,7 @@
       <c r="K132" s="2"/>
       <c r="L132" s="2"/>
     </row>
-    <row r="133" ht="26" customHeight="1">
+    <row r="133" ht="20" customHeight="1">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -3539,7 +3589,7 @@
       <c r="K133" s="2"/>
       <c r="L133" s="2"/>
     </row>
-    <row r="134" ht="26" customHeight="1">
+    <row r="134" ht="20" customHeight="1">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -3553,7 +3603,7 @@
       <c r="K134" s="2"/>
       <c r="L134" s="2"/>
     </row>
-    <row r="135" ht="26" customHeight="1">
+    <row r="135" ht="20" customHeight="1">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -3567,7 +3617,7 @@
       <c r="K135" s="2"/>
       <c r="L135" s="2"/>
     </row>
-    <row r="136" ht="26" customHeight="1">
+    <row r="136" ht="20" customHeight="1">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -3581,7 +3631,7 @@
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
     </row>
-    <row r="137" ht="26" customHeight="1">
+    <row r="137" ht="20" customHeight="1">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -3595,7 +3645,7 @@
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
     </row>
-    <row r="138" ht="26" customHeight="1">
+    <row r="138" ht="20" customHeight="1">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -3609,7 +3659,7 @@
       <c r="K138" s="2"/>
       <c r="L138" s="2"/>
     </row>
-    <row r="139" ht="26" customHeight="1">
+    <row r="139" ht="20" customHeight="1">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -3623,7 +3673,7 @@
       <c r="K139" s="2"/>
       <c r="L139" s="2"/>
     </row>
-    <row r="140" ht="26" customHeight="1">
+    <row r="140" ht="20" customHeight="1">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -3644,6 +3694,8 @@
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="K11:L12"/>
     <mergeCell ref="C13:L13"/>
+    <mergeCell ref="C19:L19"/>
+    <mergeCell ref="I28:L28"/>
     <mergeCell ref="I25:L25"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="G24:H24"/>
@@ -3693,7 +3745,7 @@
     <dataValidation type="whole" errorStyle="stop" operator="greaterThan" showErrorMessage="1" errorTitle="地址参数无效" error="输入非负整数；内盘套数至少为 1。" sqref="G10">
       <formula1>-1</formula1>
     </dataValidation>
-    <dataValidation type="decimal" errorStyle="stop" operator="between" showErrorMessage="1" errorTitle="参数无效" error="Gas 与资金预留不能为负数。" sqref="D10">
+    <dataValidation type="decimal" errorStyle="stop" operator="between" showErrorMessage="1" errorTitle="参数无效" error="Gas 与资金预留不能为负数。" sqref="G12">
       <formula1>0</formula1>
       <formula2>1e+307</formula2>
     </dataValidation>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4117,10 +4117,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2485.135266324185</v>
+        <v>2492.22340544782</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.28159923611</v>
+        <v>46283.319202858795</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4185,10 +4185,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>337.4377112363475</v>
+        <v>337.67634954441365</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.28129850695</v>
+        <v>46283.31890171296</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4253,10 +4253,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.7122321670735015</v>
+        <v>2.7223085176229445</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.28130398148</v>
+        <v>46283.31890751157</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.28131009259</v>
+        <v>46283.31891328703</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.28131586806</v>
+        <v>46283.31891908565</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.281321689814</v>
+        <v>46283.31892493055</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.281327199074</v>
+        <v>46283.31893068287</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -4606,7 +4606,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.28133326388</v>
+        <v>46283.31893646991</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -4676,7 +4676,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.28133873842</v>
+        <v>46283.31894229166</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -4741,10 +4741,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>176.57532148958595</v>
+        <v>177.19325988438194</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.28134487269</v>
+        <v>46283.318948101856</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -4814,7 +4814,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.2813503125</v>
+        <v>46283.31895386574</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -4879,10 +4879,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>86.25098456029313</v>
+        <v>86.2531426649799</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.28135612269</v>
+        <v>46283.31895965277</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -4952,7 +4952,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.28136226851</v>
+        <v>46283.318965451384</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5017,10 +5017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.767215418289252</v>
+        <v>8.777443271894565</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.28136770833</v>
+        <v>46283.31897125</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.28137424769</v>
+        <v>46283.31897706018</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5160,7 +5160,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.28137965278</v>
+        <v>46283.318982847224</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5225,10 +5225,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>402.40017534430837</v>
+        <v>403.86247537912146</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.281385393515</v>
+        <v>46283.31898863426</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.28139115741</v>
+        <v>46283.31899443287</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5363,10 +5363,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.15735650440314</v>
+        <v>349.16609284673405</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.281396956016</v>
+        <v>46283.319000208336</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5431,10 +5431,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.233235953189475</v>
+        <v>28.334027255112332</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.281402789355</v>
+        <v>46283.31900599537</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.281408587965</v>
+        <v>46283.319011782405</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.28141402778</v>
+        <v>46283.31901756945</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.28142013889</v>
+        <v>46283.31902337963</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -5709,10 +5709,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1154.930507807926</v>
+        <v>1156.5007126042883</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.281425925925</v>
+        <v>46283.31902918982</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.28143171296</v>
+        <v>46283.31903496527</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -5847,10 +5847,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>685.9345241133453</v>
+        <v>687.4429516229762</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.281437488426</v>
+        <v>46283.31904077547</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.281442997686</v>
+        <v>46283.319046550925</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.28144908565</v>
+        <v>46283.31905237269</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6060,7 +6060,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.2814550463</v>
+        <v>46283.3190581713</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6125,10 +6125,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>135.23129535607805</v>
+        <v>135.63501849568433</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.281460694445</v>
+        <v>46283.31906393519</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6193,10 +6193,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>993.3475250130857</v>
+        <v>995.1538904991431</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.28146615741</v>
+        <v>46283.3190697338</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.28147803241</v>
+        <v>46283.319081331014</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6336,7 +6336,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.281483796294</v>
+        <v>46283.319087129625</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6401,10 +6401,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.4822799163712</v>
+        <v>222.3885855205214</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.28147228009</v>
+        <v>46283.3190755324</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -6474,7 +6474,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.28148965278</v>
+        <v>46283.319092881946</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.28149541667</v>
+        <v>46283.31909866898</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -6609,10 +6609,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>719.9425126879422</v>
+        <v>724.1640911492946</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.281501192134</v>
+        <v>46283.319104490736</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.73928943520518</v>
+        <v>47.830560315147245</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.28150696759</v>
+        <v>46283.31911027778</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -6745,10 +6745,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>154.41708526116994</v>
+        <v>154.42094896472207</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.2815127662</v>
+        <v>46283.31911606481</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -6818,7 +6818,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.28151855324</v>
+        <v>46283.31912184028</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -6883,10 +6883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.90386688244425</v>
+        <v>101.96646756449468</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.28152434028</v>
+        <v>46283.31912763889</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.28153008102</v>
+        <v>46283.31913341435</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7026,7 +7026,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.281535856484</v>
+        <v>46283.319139189814</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.28154171296</v>
+        <v>46283.31914501158</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.281547962964</v>
+        <v>46283.319150787036</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7236,7 +7236,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.28155325232</v>
+        <v>46283.319156655096</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>155.70814780564407</v>
+        <v>155.87217960830785</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.28155905093</v>
+        <v>46283.31916237269</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7369,10 +7369,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>765.3198582433344</v>
+        <v>765.3089820167502</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.28156487268</v>
+        <v>46283.31916814815</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7437,10 +7437,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>368.15298991069653</v>
+        <v>369.4432879081461</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.28157099537</v>
+        <v>46283.31917391204</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -7510,7 +7510,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.281576423615</v>
+        <v>46283.31917971065</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.28158219907</v>
+        <v>46283.31918549768</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.28158795139</v>
+        <v>46283.31919128472</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.281593761574</v>
+        <v>46283.319197060184</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -7790,7 +7790,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.28159923611</v>
+        <v>46283.319202858795</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Rda86b20109df4d7c"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Ra4b1910f27474888"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R8302c7757af445bf"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R6ca9761c17d04849"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -97,7 +97,7 @@
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -127,6 +127,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF7D2638"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -159,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="104">
+  <x:cellXfs count="126">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -468,11 +473,67 @@
     <x:xf numFmtId="202" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="4">
+  <x:dxfs count="23">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -516,6 +577,95 @@
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
@@ -767,7 +917,7 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5" t="str">
-        <v>蓝色格可编辑。Quote / USDT 资金不含 Gas，Gas 单独以 ETH 计价。</v>
+        <v>蓝色格可编辑。Quote 资金与原生币 Gas 分开准备；总折算价值包含 Gas。</v>
       </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
@@ -1036,7 +1186,7 @@
     <row r="17" ht="24" customHeight="1">
       <c r="A17" s="2"/>
       <c r="B17" s="2"/>
-      <c r="C17" s="8" t="str">
+      <c r="C17" s="9" t="str">
         <v>二、测算结果</v>
       </c>
       <c r="D17" s="8"/>
@@ -1052,2640 +1202,2826 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="2"/>
       <c r="B18" s="2"/>
-      <c r="C18" s="35" t="str">
-        <v>建议总资金 / Quote</v>
-      </c>
-      <c r="D18" s="74">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($D$21="","",SUM($D$21,$G$21,$J$21,$D$22)))</f>
+      <c r="C18" s="107" t="str">
+        <v>建议 Quote 资金</v>
+      </c>
+      <c r="D18" s="117">
+        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
       </c>
       <c r="E18" s="62">
         <f>$D$7</f>
       </c>
-      <c r="F18" s="35" t="str">
-        <v>折合 USDT（不含 Gas）</v>
+      <c r="F18" s="107" t="str">
+        <v>原生币 Gas 储备</v>
       </c>
       <c r="G18" s="74">
-        <f>IF(OR($D$18="",$D$24=""),"",$D$18*$D$24)</f>
+        <f>$D$32*MAX(0,$G$11)</f>
       </c>
       <c r="H18" s="62" t="str">
+        <v>ETH</v>
+      </c>
+      <c r="I18" s="107" t="str">
+        <v>总折算 / USDT</v>
+      </c>
+      <c r="J18" s="117">
+        <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
+      </c>
+      <c r="K18" s="62" t="str">
         <v>USDT</v>
       </c>
-      <c r="I18" s="35" t="str">
-        <v>Gas 储备 / ETH</v>
-      </c>
-      <c r="J18" s="74">
-        <f>$G$22*MAX(0,$G$11)</f>
-      </c>
-      <c r="K18" s="62" t="str">
-        <v>ETH</v>
-      </c>
       <c r="L18" s="62"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
+    <row r="19" ht="20" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="2"/>
-      <c r="C19" s="57" t="str">
-        <v>Quote 资金构成：预算控筹率理论资金 + 额外内盘资金 + 资金预留 + 洗筹损耗</v>
-      </c>
-      <c r="D19" s="57"/>
-      <c r="E19" s="57"/>
-      <c r="F19" s="57"/>
-      <c r="G19" s="57"/>
-      <c r="H19" s="57"/>
-      <c r="I19" s="57"/>
-      <c r="J19" s="57"/>
-      <c r="K19" s="57"/>
-      <c r="L19" s="57"/>
+      <c r="C19" s="107" t="str">
+        <v>Quote 折算 / USDT</v>
+      </c>
+      <c r="D19" s="118">
+        <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$33&gt;0,$D$18*$D$33,"")),"")</f>
+      </c>
+      <c r="E19" s="106" t="str">
+        <v>USDT</v>
+      </c>
+      <c r="F19" s="107" t="str">
+        <v>Gas 折算 / USDT</v>
+      </c>
+      <c r="G19" s="118">
+        <f>IF($G$18=0,0,IF($J$19="","",$G$18*$J$19))</f>
+      </c>
+      <c r="H19" s="106" t="str">
+        <v>USDT</v>
+      </c>
+      <c r="I19" s="107" t="str">
+        <v>原生币价格 / USDT</v>
+      </c>
+      <c r="J19" s="119">
+        <f>IF($D$7="ETH",$D$33,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+      </c>
+      <c r="K19" s="106"/>
+      <c r="L19" s="106"/>
     </row>
     <row r="20" ht="6" customHeight="1">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-    </row>
-    <row r="21" ht="20" customHeight="1">
+      <c r="C20" s="106"/>
+      <c r="D20" s="106"/>
+      <c r="E20" s="106"/>
+      <c r="F20" s="106"/>
+      <c r="G20" s="106"/>
+      <c r="H20" s="106"/>
+      <c r="I20" s="106"/>
+      <c r="J20" s="106"/>
+      <c r="K20" s="106"/>
+      <c r="L20" s="106"/>
+    </row>
+    <row r="21" ht="24" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="35">
-        <f>"预算 "&amp;TEXT($J$22,"0%")&amp;" 理论资金 / Quote"</f>
-      </c>
-      <c r="D21" s="60">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$35="","",$J$31+$J$35))</f>
-      </c>
-      <c r="E21" s="2"/>
-      <c r="F21" s="35" t="str">
-        <v>额外内盘资金 / Quote</v>
-      </c>
-      <c r="G21" s="60">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$31="","",$J$31*MAX(0,$G$7-1)))</f>
-      </c>
-      <c r="H21" s="2"/>
-      <c r="I21" s="35" t="str">
-        <v>洗筹损耗 / Quote</v>
-      </c>
-      <c r="J21" s="60">
-        <f>IF(LEFT($D$23,2)&lt;&gt;"可达","",IF($J$36="","",$J$36*($G$32+$J$7)*2))</f>
-      </c>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="C21" s="76" t="str">
+        <v>Quote 资金构成</v>
+      </c>
+      <c r="D21" s="75"/>
+      <c r="E21" s="75"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="106"/>
+      <c r="H21" s="106"/>
+      <c r="I21" s="76" t="str">
+        <v>手续费</v>
+      </c>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
+      <c r="L21" s="75"/>
     </row>
     <row r="22" ht="20" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
-      <c r="C22" s="35" t="str">
-        <v>资金预留 / Quote</v>
-      </c>
-      <c r="D22" s="60">
-        <f>$G$12</f>
-      </c>
-      <c r="E22" s="2"/>
-      <c r="F22" s="35" t="str">
-        <v>地址总数</v>
-      </c>
-      <c r="G22" s="64">
-        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
-      </c>
-      <c r="H22" s="2"/>
-      <c r="I22" s="35" t="str">
-        <v>预算使用控筹率</v>
-      </c>
-      <c r="J22" s="59">
-        <f>$D$8+1%</f>
-      </c>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-    </row>
-    <row r="23" ht="32" customHeight="1">
+      <c r="C22" s="106">
+        <f>"预算 "&amp;TEXT($D$31,"0%")&amp;" 理论资金"</f>
+      </c>
+      <c r="D22" s="118">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
+      </c>
+      <c r="E22" s="106">
+        <f>$D$7</f>
+      </c>
+      <c r="F22" s="106"/>
+      <c r="G22" s="106"/>
+      <c r="H22" s="106"/>
+      <c r="I22" s="115" t="str">
+        <v>内盘</v>
+      </c>
+      <c r="J22" s="116"/>
+      <c r="K22" s="116"/>
+      <c r="L22" s="116"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
-      <c r="C23" s="35" t="str">
-        <v>目标是否可达</v>
-      </c>
-      <c r="D23" s="66">
-        <f>IF($J$41&lt;&gt;"参数有效",$J$41,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$43),"Creator Tax无效",IF($J$22&gt;=$G$23,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
-      </c>
-      <c r="E23" s="2"/>
-      <c r="F23" s="35" t="str">
-        <v>当前控筹上限</v>
-      </c>
-      <c r="G23" s="63">
-        <f>MIN(1-$G$41/$D$35,$G$33+(1-$G$32-$J$7)*$G$38/$D$35)</f>
-      </c>
-      <c r="H23" s="2"/>
-      <c r="I23" s="35" t="str">
-        <v>资金口径</v>
-      </c>
-      <c r="J23" s="60" t="str">
-        <v>Quote 预算 + 单独 Gas</v>
-      </c>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
+      <c r="C23" s="107" t="str">
+        <v>额外内盘资金</v>
+      </c>
+      <c r="D23" s="118">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
+      </c>
+      <c r="E23" s="106">
+        <f>$D$7</f>
+      </c>
+      <c r="F23" s="106"/>
+      <c r="G23" s="106"/>
+      <c r="H23" s="106"/>
+      <c r="I23" s="107" t="str">
+        <v>基础手续费</v>
+      </c>
+      <c r="J23" s="120">
+        <f>$G$41</f>
+      </c>
+      <c r="K23" s="106"/>
+      <c r="L23" s="106"/>
     </row>
     <row r="24" ht="20" customHeight="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="35" t="str">
-        <v>使用价格 / USDT</v>
-      </c>
-      <c r="D24" s="60">
-        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
-      </c>
-      <c r="E24" s="2"/>
-      <c r="F24" s="35" t="str">
-        <v>行情时间 / UTC</v>
-      </c>
-      <c r="G24" s="65">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="35" t="str">
-        <v>价格状态</v>
-      </c>
-      <c r="J24" s="60">
-        <f>IF($D$9&lt;&gt;"",IF($D$24="","手动价格无效","手动价格"),IF($D$24="","缺少价格","每日行情"))</f>
-      </c>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
+      <c r="C24" s="107" t="str">
+        <v>洗筹损耗</v>
+      </c>
+      <c r="D24" s="118">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
+      </c>
+      <c r="E24" s="106">
+        <f>$D$7</f>
+      </c>
+      <c r="F24" s="106"/>
+      <c r="G24" s="106"/>
+      <c r="H24" s="106"/>
+      <c r="I24" s="107" t="str">
+        <v>买入含税费率</v>
+      </c>
+      <c r="J24" s="120">
+        <f>$G$41+$J$7</f>
+      </c>
+      <c r="K24" s="106"/>
+      <c r="L24" s="106"/>
     </row>
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="2"/>
       <c r="B25" s="2"/>
-      <c r="C25" s="35" t="str">
-        <v>价格采用方式</v>
-      </c>
-      <c r="D25" s="60">
-        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
-      </c>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="60"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2" t="str">
-        <v>价格缺失时 USDT 结果留空</v>
-      </c>
-      <c r="J25" s="60"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="C25" s="107" t="str">
+        <v>资金预留</v>
+      </c>
+      <c r="D25" s="118">
+        <f>$G$12</f>
+      </c>
+      <c r="E25" s="106">
+        <f>$D$7</f>
+      </c>
+      <c r="F25" s="106"/>
+      <c r="G25" s="106"/>
+      <c r="H25" s="106"/>
+      <c r="I25" s="107" t="str">
+        <v>卖出含税费率</v>
+      </c>
+      <c r="J25" s="120">
+        <f>$G$41+$J$7</f>
+      </c>
+      <c r="K25" s="106"/>
+      <c r="L25" s="106"/>
     </row>
     <row r="26" ht="20" customHeight="1">
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
-      <c r="C26" s="35" t="str">
-        <v>内盘基础手续费</v>
-      </c>
-      <c r="D26" s="59">
-        <f>$G$31</f>
-      </c>
-      <c r="E26" s="2"/>
-      <c r="F26" s="35" t="str">
-        <v>外盘 Hook 手续费</v>
-      </c>
-      <c r="G26" s="59">
-        <f>$G$32</f>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="35" t="str">
-        <v>洗筹双边总费率</v>
-      </c>
-      <c r="J26" s="59">
-        <f>SUM(G27,J27)</f>
-      </c>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
+      <c r="C26" s="107" t="str">
+        <v>恢复目标控筹资金</v>
+      </c>
+      <c r="D26" s="118">
+        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",0)</f>
+      </c>
+      <c r="E26" s="106">
+        <f>$D$7</f>
+      </c>
+      <c r="F26" s="106"/>
+      <c r="G26" s="106"/>
+      <c r="H26" s="106"/>
+      <c r="I26" s="106"/>
+      <c r="J26" s="106"/>
+      <c r="K26" s="106"/>
+      <c r="L26" s="106"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="2"/>
       <c r="B27" s="2"/>
-      <c r="C27" s="35" t="str">
-        <v>内盘买入含税费率</v>
-      </c>
-      <c r="D27" s="59">
-        <f>$G$31+$J$7</f>
-      </c>
-      <c r="E27" s="2"/>
-      <c r="F27" s="35" t="str">
-        <v>外盘买入含税费率</v>
-      </c>
-      <c r="G27" s="59">
-        <f>$G$32+$J$7</f>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="35" t="str">
-        <v>外盘卖出含税费率</v>
-      </c>
-      <c r="J27" s="59">
-        <f>$G$32+$J$7</f>
-      </c>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-    </row>
-    <row r="28" ht="32" customHeight="1">
+      <c r="C27" s="107" t="str">
+        <v>洗后控筹率（估算）</v>
+      </c>
+      <c r="D27" s="121">
+        <f>$D$8*$J$54</f>
+      </c>
+      <c r="E27" s="106"/>
+      <c r="F27" s="106"/>
+      <c r="G27" s="106"/>
+      <c r="H27" s="106"/>
+      <c r="I27" s="115" t="str">
+        <v>外盘 · Hook</v>
+      </c>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
+      <c r="L27" s="116"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
-      <c r="C28" s="35" t="str">
-        <v>沉没成本 / Quote</v>
-      </c>
-      <c r="D28" s="60">
-        <f>E88</f>
-      </c>
-      <c r="E28" s="2"/>
-      <c r="F28" s="35" t="str">
-        <v>一套内盘打满 / Quote</v>
-      </c>
-      <c r="G28" s="60">
-        <f>$J$31</f>
-      </c>
-      <c r="H28" s="2"/>
-      <c r="I28" s="58" t="str">
-        <v>费率为预算加总口径；双边合计用于 FDV 洗筹预算。沉没成本与一套打满仅作参考，不重复计入总额。</v>
-      </c>
-      <c r="J28" s="58"/>
-      <c r="K28" s="58"/>
-      <c r="L28" s="58"/>
-    </row>
-    <row r="29" ht="24" customHeight="1" collapsed="1">
+      <c r="C28" s="107" t="str">
+        <v>补回目标控筹率</v>
+      </c>
+      <c r="D28" s="120">
+        <f>$D$8</f>
+      </c>
+      <c r="E28" s="106"/>
+      <c r="F28" s="106"/>
+      <c r="G28" s="106"/>
+      <c r="H28" s="106"/>
+      <c r="I28" s="107" t="str">
+        <v>基础手续费</v>
+      </c>
+      <c r="J28" s="120">
+        <f>$G$42</f>
+      </c>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
       <c r="A29" s="2"/>
       <c r="B29" s="2"/>
-      <c r="C29" s="8" t="str">
-        <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
-      </c>
-      <c r="D29" s="8"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="8"/>
-      <c r="L29" s="8"/>
-    </row>
-    <row r="30" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C29" s="107" t="str">
+        <v>洗筹双边总费率</v>
+      </c>
+      <c r="D29" s="120">
+        <f>$J$47*2</f>
+      </c>
+      <c r="E29" s="106"/>
+      <c r="F29" s="106"/>
+      <c r="G29" s="106"/>
+      <c r="H29" s="106"/>
+      <c r="I29" s="107" t="str">
+        <v>买入含税费率</v>
+      </c>
+      <c r="J29" s="120">
+        <f>$G$42+$J$7</f>
+      </c>
+      <c r="K29" s="106"/>
+      <c r="L29" s="106"/>
+    </row>
+    <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="48" t="str">
-        <v>Quote 信息</v>
-      </c>
-      <c r="D30" s="2"/>
-      <c r="E30" s="2"/>
-      <c r="F30" s="48" t="str">
-        <v>协议与曲线参数</v>
-      </c>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-      <c r="I30" s="48" t="str">
-        <v>预算中间计算</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="2"/>
-    </row>
-    <row r="31" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C30" s="107" t="str">
+        <v>目标是否可达</v>
+      </c>
+      <c r="D30" s="107">
+        <f>IF($J$51&lt;&gt;"参数有效",$J$51,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$53),"Creator Tax无效",IF($D$31&gt;=$G$32,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
+      </c>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="107" t="str">
+        <v>卖出含税费率</v>
+      </c>
+      <c r="J30" s="120">
+        <f>$G$42+$J$7</f>
+      </c>
+      <c r="K30" s="106"/>
+      <c r="L30" s="106"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="35" t="str">
-        <v>Quote 名称</v>
-      </c>
-      <c r="D31" s="66">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
-      </c>
-      <c r="E31" s="35"/>
-      <c r="F31" s="35" t="str">
-        <v>内盘基础费</v>
-      </c>
-      <c r="G31" s="63">
-        <f>1%</f>
-      </c>
-      <c r="H31" s="2"/>
-      <c r="I31" s="35" t="str">
-        <v>一套内盘打满 / Quote</v>
-      </c>
-      <c r="J31" s="60">
-        <f>IF(1-$G$31-$J$7&gt;0,$G$34/(1-$G$31-$J$7),"")</f>
-      </c>
-      <c r="K31" s="2"/>
-      <c r="L31" s="2"/>
-    </row>
-    <row r="32" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C31" s="107" t="str">
+        <v>预算使用控筹率</v>
+      </c>
+      <c r="D31" s="120">
+        <f>$D$8+1%</f>
+      </c>
+      <c r="E31" s="106"/>
+      <c r="F31" s="106"/>
+      <c r="G31" s="106"/>
+      <c r="H31" s="106"/>
+      <c r="I31" s="106"/>
+      <c r="J31" s="106"/>
+      <c r="K31" s="106"/>
+      <c r="L31" s="106"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="35" t="str">
-        <v>Quote 合约</v>
-      </c>
-      <c r="D32" s="69">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
-      </c>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35" t="str">
-        <v>外盘 Hook 费</v>
-      </c>
-      <c r="G32" s="63">
-        <f>1%</f>
-      </c>
-      <c r="H32" s="2"/>
-      <c r="I32" s="35" t="str">
-        <v>目标+1% Pool TOKEN</v>
-      </c>
-      <c r="J32" s="71">
-        <f>IF($J$22&lt;$G$23,$D$35*(1-$J$22)-$G$41,"")</f>
-      </c>
-      <c r="K32" s="2"/>
-      <c r="L32" s="2"/>
-    </row>
-    <row r="33" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C32" s="107" t="str">
+        <v>地址总数</v>
+      </c>
+      <c r="D32" s="118">
+        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
+      </c>
+      <c r="E32" s="106"/>
+      <c r="F32" s="107" t="str">
+        <v>当前控筹上限</v>
+      </c>
+      <c r="G32" s="120">
+        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
+      </c>
+      <c r="H32" s="106"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="106"/>
+      <c r="K32" s="106"/>
+      <c r="L32" s="106"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="2"/>
-      <c r="D33" s="66"/>
-      <c r="E33" s="35"/>
-      <c r="F33" s="35" t="str">
-        <v>毕业控筹率</v>
-      </c>
-      <c r="G33" s="63">
-        <f>$G$34/($G$36+$G$34)</f>
-      </c>
-      <c r="H33" s="2"/>
-      <c r="I33" s="35" t="str">
-        <v>目标+1% Pool Quote</v>
-      </c>
-      <c r="J33" s="60">
-        <f>IF($J$32="","",$G$40/$J$32)</f>
-      </c>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
-    </row>
-    <row r="34" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C33" s="107" t="str">
+        <v>Quote 价格 / USDT</v>
+      </c>
+      <c r="D33" s="119">
+        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+      </c>
+      <c r="E33" s="106"/>
+      <c r="F33" s="106"/>
+      <c r="G33" s="106"/>
+      <c r="H33" s="106"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="106"/>
+      <c r="K33" s="106"/>
+      <c r="L33" s="106"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="35" t="str">
-        <v>Decimals</v>
-      </c>
-      <c r="D34" s="67">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
-      </c>
-      <c r="E34" s="2"/>
-      <c r="F34" s="35" t="str">
-        <v>毕业真实 Quote</v>
-      </c>
-      <c r="G34" s="60">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
-      </c>
-      <c r="H34" s="2"/>
-      <c r="I34" s="35" t="str">
-        <v>外盘净增加 / Quote</v>
-      </c>
-      <c r="J34" s="60">
-        <f>IF($J$33="","",MAX(0,$J$33-$G$34))</f>
-      </c>
-      <c r="K34" s="2"/>
-      <c r="L34" s="2"/>
-    </row>
-    <row r="35" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C34" s="107" t="str">
+        <v>行情时间 / UTC</v>
+      </c>
+      <c r="D34" s="122">
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
+      </c>
+      <c r="E34" s="106"/>
+      <c r="F34" s="106"/>
+      <c r="G34" s="106"/>
+      <c r="H34" s="106"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="106"/>
+      <c r="K34" s="106"/>
+      <c r="L34" s="106"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="35" t="str">
-        <v>总供应量</v>
-      </c>
-      <c r="D35" s="64">
-        <f>1000000000</f>
-      </c>
-      <c r="E35" s="2"/>
-      <c r="F35" s="35" t="str">
-        <v>内盘初始 TOKEN</v>
-      </c>
-      <c r="G35" s="71">
-        <f>$D$35</f>
-      </c>
-      <c r="H35" s="2"/>
-      <c r="I35" s="35" t="str">
-        <v>外盘含费投入 / Quote</v>
-      </c>
-      <c r="J35" s="60">
-        <f>IF($J$32="","",$G$40/($G$38-MAX(0,($J$22-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="K35" s="2"/>
-      <c r="L35" s="2"/>
-    </row>
-    <row r="36" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C35" s="107" t="str">
+        <v>价格采用方式</v>
+      </c>
+      <c r="D35" s="106">
+        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
+      </c>
+      <c r="E35" s="106"/>
+      <c r="F35" s="107">
+        <f>IF($D$9&lt;&gt;"",IF($D$33="","手动价格无效","手动价格"),IF($D$33="","缺少价格","每日行情"))</f>
+      </c>
+      <c r="G35" s="107"/>
+      <c r="H35" s="107"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="106"/>
+      <c r="K35" s="106"/>
+      <c r="L35" s="106"/>
+    </row>
+    <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="35" t="str">
-        <v>协议参数证据</v>
-      </c>
-      <c r="D36" s="72">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
-      </c>
-      <c r="E36" s="35"/>
-      <c r="F36" s="35" t="str">
-        <v>phantom Quote</v>
-      </c>
-      <c r="G36" s="60">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
-      </c>
-      <c r="H36" s="2"/>
-      <c r="I36" s="35" t="str">
-        <v>目标+1% FDV / Quote</v>
-      </c>
-      <c r="J36" s="60">
-        <f>IF($J$33="","",$J$33/$J$32*$D$35)</f>
-      </c>
-      <c r="K36" s="2"/>
-      <c r="L36" s="2"/>
-    </row>
-    <row r="37" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C36" s="111" t="str">
+        <v>Pons 按现有 Quote 洗筹损耗预算承担费用、持仓保持目标的口径，补回资金为 0；不代表免手续费。动态 Snipe Tax 未计入。</v>
+      </c>
+      <c r="D36" s="111"/>
+      <c r="E36" s="111"/>
+      <c r="F36" s="111"/>
+      <c r="G36" s="111"/>
+      <c r="H36" s="111"/>
+      <c r="I36" s="111"/>
+      <c r="J36" s="111"/>
+      <c r="K36" s="111"/>
+      <c r="L36" s="111"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="35" t="str">
-        <v>外盘机制</v>
-      </c>
-      <c r="D37" s="66" t="str">
-        <v>Uniswap V4 / exact-input</v>
-      </c>
-      <c r="E37" s="35"/>
-      <c r="F37" s="35" t="str">
-        <v>内盘 k</v>
-      </c>
-      <c r="G37" s="68">
-        <f>$G$36*$D$35</f>
-      </c>
-      <c r="H37" s="2"/>
-      <c r="I37" s="35" t="str">
-        <v>洗筹单边费率</v>
-      </c>
-      <c r="J37" s="63">
-        <f>$G$32+$J$7</f>
-      </c>
-      <c r="K37" s="2"/>
-      <c r="L37" s="2"/>
-    </row>
-    <row r="38" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="C37" s="123" t="str">
+        <v>沉没成本（模型参考，不重复计入预算）</v>
+      </c>
+      <c r="D37" s="123"/>
+      <c r="E37" s="123"/>
+      <c r="F37" s="123"/>
+      <c r="G37" s="124">
+        <f>E98</f>
+      </c>
+      <c r="H37" s="123">
+        <f>$D$7</f>
+      </c>
+      <c r="I37" s="106"/>
+      <c r="J37" s="106"/>
+      <c r="K37" s="106"/>
+      <c r="L37" s="106"/>
+    </row>
+    <row r="38" ht="6" customHeight="1">
       <c r="A38" s="2"/>
       <c r="B38" s="2"/>
-      <c r="C38" s="35" t="str">
+      <c r="C38" s="106"/>
+      <c r="D38" s="106"/>
+      <c r="E38" s="106"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="106"/>
+      <c r="H38" s="106"/>
+      <c r="I38" s="106"/>
+      <c r="J38" s="106"/>
+      <c r="K38" s="106"/>
+      <c r="L38" s="106"/>
+    </row>
+    <row r="39" ht="24" customHeight="1" collapsed="1">
+      <c r="A39"/>
+      <c r="B39"/>
+      <c r="C39" s="110" t="str">
+        <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
+      </c>
+      <c r="D39" s="110"/>
+      <c r="E39" s="110"/>
+      <c r="F39" s="110"/>
+      <c r="G39" s="110"/>
+      <c r="H39" s="110"/>
+      <c r="I39" s="110"/>
+      <c r="J39" s="110"/>
+      <c r="K39" s="110"/>
+      <c r="L39" s="110"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A40"/>
+      <c r="B40"/>
+      <c r="C40" t="str">
+        <v>Quote 信息</v>
+      </c>
+      <c r="D40"/>
+      <c r="E40"/>
+      <c r="F40" t="str">
+        <v>协议与曲线参数</v>
+      </c>
+      <c r="G40"/>
+      <c r="H40"/>
+      <c r="I40" t="str">
+        <v>预算中间计算</v>
+      </c>
+      <c r="J40"/>
+      <c r="K40"/>
+      <c r="L40"/>
+    </row>
+    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A41"/>
+      <c r="B41"/>
+      <c r="C41" t="str">
+        <v>Quote 名称</v>
+      </c>
+      <c r="D41">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
+      </c>
+      <c r="E41"/>
+      <c r="F41" t="str">
+        <v>内盘基础费</v>
+      </c>
+      <c r="G41">
+        <f>1%</f>
+      </c>
+      <c r="H41"/>
+      <c r="I41" t="str">
+        <v>一套内盘打满 / Quote</v>
+      </c>
+      <c r="J41">
+        <f>IF(1-$G$41-$J$7&gt;0,$G$44/(1-$G$41-$J$7),"")</f>
+      </c>
+      <c r="K41"/>
+      <c r="L41"/>
+    </row>
+    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A42"/>
+      <c r="B42"/>
+      <c r="C42" t="str">
+        <v>Quote 合约</v>
+      </c>
+      <c r="D42">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
+      </c>
+      <c r="E42"/>
+      <c r="F42" t="str">
+        <v>外盘 Hook 费</v>
+      </c>
+      <c r="G42">
+        <f>1%</f>
+      </c>
+      <c r="H42"/>
+      <c r="I42" t="str">
+        <v>目标+1% Pool TOKEN</v>
+      </c>
+      <c r="J42">
+        <f>IF($D$31&lt;$G$32,$D$45*(1-$D$31)-$G$51,"")</f>
+      </c>
+      <c r="K42"/>
+      <c r="L42"/>
+    </row>
+    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A43"/>
+      <c r="B43"/>
+      <c r="C43"/>
+      <c r="D43"/>
+      <c r="E43"/>
+      <c r="F43" t="str">
+        <v>毕业控筹率</v>
+      </c>
+      <c r="G43">
+        <f>$G$44/($G$46+$G$44)</f>
+      </c>
+      <c r="H43"/>
+      <c r="I43" t="str">
+        <v>目标+1% Pool Quote</v>
+      </c>
+      <c r="J43">
+        <f>IF($J$42="","",$G$50/$J$42)</f>
+      </c>
+      <c r="K43"/>
+      <c r="L43"/>
+    </row>
+    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A44"/>
+      <c r="B44"/>
+      <c r="C44" t="str">
+        <v>Decimals</v>
+      </c>
+      <c r="D44">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
+      </c>
+      <c r="E44"/>
+      <c r="F44" t="str">
+        <v>毕业真实 Quote</v>
+      </c>
+      <c r="G44">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
+      </c>
+      <c r="H44"/>
+      <c r="I44" t="str">
+        <v>外盘净增加 / Quote</v>
+      </c>
+      <c r="J44">
+        <f>IF($J$43="","",MAX(0,$J$43-$G$44))</f>
+      </c>
+      <c r="K44"/>
+      <c r="L44"/>
+    </row>
+    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A45"/>
+      <c r="B45"/>
+      <c r="C45" t="str">
+        <v>总供应量</v>
+      </c>
+      <c r="D45">
+        <f>1000000000</f>
+      </c>
+      <c r="E45"/>
+      <c r="F45" t="str">
+        <v>内盘初始 TOKEN</v>
+      </c>
+      <c r="G45">
+        <f>$D$45</f>
+      </c>
+      <c r="H45"/>
+      <c r="I45" t="str">
+        <v>外盘含费投入 / Quote</v>
+      </c>
+      <c r="J45">
+        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$31-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="K45"/>
+      <c r="L45"/>
+    </row>
+    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A46"/>
+      <c r="B46"/>
+      <c r="C46" t="str">
+        <v>协议参数证据</v>
+      </c>
+      <c r="D46">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
+      </c>
+      <c r="E46"/>
+      <c r="F46" t="str">
+        <v>phantom Quote</v>
+      </c>
+      <c r="G46">
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
+      </c>
+      <c r="H46"/>
+      <c r="I46" t="str">
+        <v>目标+1% FDV / Quote</v>
+      </c>
+      <c r="J46">
+        <f>IF($J$43="","",$J$43/$J$42*$D$45)</f>
+      </c>
+      <c r="K46"/>
+      <c r="L46"/>
+    </row>
+    <row r="47" ht="24" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A47"/>
+      <c r="B47"/>
+      <c r="C47" t="str">
+        <v>外盘机制</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Uniswap V4 / exact-input</v>
+      </c>
+      <c r="E47"/>
+      <c r="F47" t="str">
+        <v>内盘 k</v>
+      </c>
+      <c r="G47">
+        <f>$G$46*$D$45</f>
+      </c>
+      <c r="H47"/>
+      <c r="I47" t="str">
+        <v>洗筹单边费率</v>
+      </c>
+      <c r="J47">
+        <f>$G$42+$J$7</f>
+      </c>
+      <c r="K47"/>
+      <c r="L47"/>
+    </row>
+    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A48"/>
+      <c r="B48"/>
+      <c r="C48" t="str">
         <v>费用方向</v>
       </c>
-      <c r="D38" s="66" t="str">
+      <c r="D48" t="str">
         <v>Hook + Creator Tax 从 Meme 输出扣除</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35" t="str">
+      <c r="E48"/>
+      <c r="F48" t="str">
         <v>外盘初始 TOKEN</v>
       </c>
-      <c r="G38" s="71">
-        <f>$D$35*$G$36*$G$34/($G$36+$G$34)^2</f>
-      </c>
-      <c r="H38" s="2"/>
-      <c r="I38" s="35" t="str">
+      <c r="G48">
+        <f>$D$45*$G$46*$G$44/($G$46+$G$44)^2</f>
+      </c>
+      <c r="H48"/>
+      <c r="I48" t="str">
         <v>预算缓冲</v>
       </c>
-      <c r="J38" s="59" t="n">
+      <c r="J48" t="n">
         <v>0.01</v>
       </c>
-      <c r="K38" s="2"/>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A39" s="2"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="35" t="str">
+      <c r="K48"/>
+      <c r="L48"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A49"/>
+      <c r="B49"/>
+      <c r="C49" t="str">
         <v>洗筹口径</v>
       </c>
-      <c r="D39" s="66" t="str">
+      <c r="D49" t="str">
         <v>目标+1% FDV ×（Hook + Creator Tax）×2</v>
       </c>
-      <c r="E39" s="35"/>
-      <c r="F39" s="35" t="str">
+      <c r="E49"/>
+      <c r="F49" t="str">
         <v>外盘初始 Quote</v>
       </c>
-      <c r="G39" s="60">
-        <f>$G$34</f>
-      </c>
-      <c r="H39" s="2"/>
-      <c r="I39" s="35" t="str">
+      <c r="G49">
+        <f>$G$44</f>
+      </c>
+      <c r="H49"/>
+      <c r="I49" t="str">
         <v>分红与回购口径</v>
       </c>
-      <c r="J39" s="73" t="str">
+      <c r="J49" t="str">
         <v>不抵扣分红 / 回购收益</v>
       </c>
-      <c r="K39" s="35"/>
-      <c r="L39" s="35"/>
-    </row>
-    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A40" s="2"/>
-      <c r="B40" s="2"/>
-      <c r="C40" s="2"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35" t="str">
+      <c r="K49"/>
+      <c r="L49"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A50"/>
+      <c r="B50"/>
+      <c r="C50"/>
+      <c r="D50"/>
+      <c r="E50"/>
+      <c r="F50" t="str">
         <v>外盘 k</v>
       </c>
-      <c r="G40" s="68">
-        <f>$G$38*$G$34</f>
-      </c>
-      <c r="H40" s="2"/>
-      <c r="I40" s="2"/>
-      <c r="J40" s="66"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-    </row>
-    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A41" s="2"/>
-      <c r="B41" s="2"/>
-      <c r="C41" s="2"/>
-      <c r="D41" s="60"/>
-      <c r="E41" s="2"/>
-      <c r="F41" s="35" t="str">
+      <c r="G50">
+        <f>$G$48*$G$44</f>
+      </c>
+      <c r="H50"/>
+      <c r="I50"/>
+      <c r="J50"/>
+      <c r="K50"/>
+      <c r="L50"/>
+    </row>
+    <row r="51" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A51"/>
+      <c r="B51"/>
+      <c r="C51"/>
+      <c r="D51"/>
+      <c r="E51"/>
+      <c r="F51" t="str">
         <v>Locker TOKEN</v>
       </c>
-      <c r="G41" s="71">
-        <f>$D$35*$G$36^2/($G$36+$G$34)^2</f>
-      </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="35" t="str">
+      <c r="G51">
+        <f>$D$45*$G$46^2/($G$46+$G$44)^2</f>
+      </c>
+      <c r="H51"/>
+      <c r="I51" t="str">
         <v>输入检查</v>
       </c>
-      <c r="J41" s="66">
+      <c r="J51">
         <f>IF(COUNT($D$8,$G$7:$G$12,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$G$12&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</f>
       </c>
-      <c r="K41" s="35"/>
-      <c r="L41" s="35"/>
-    </row>
-    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A42" s="2"/>
-      <c r="B42" s="2"/>
-      <c r="C42" s="2"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="2"/>
-      <c r="F42" s="35" t="str">
+      <c r="K51"/>
+      <c r="L51"/>
+    </row>
+    <row r="52" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A52"/>
+      <c r="B52"/>
+      <c r="C52"/>
+      <c r="D52"/>
+      <c r="E52"/>
+      <c r="F52" t="str">
         <v>Snipe 窗口</v>
       </c>
-      <c r="G42" s="73" t="str">
+      <c r="G52" t="str">
         <v>3 秒；默认豁免或避开</v>
       </c>
-      <c r="H42" s="2"/>
-      <c r="I42" s="2"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="2"/>
-      <c r="L42" s="2"/>
-    </row>
-    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A43" s="2"/>
-      <c r="B43" s="2"/>
-      <c r="C43" s="2"/>
-      <c r="D43" s="60"/>
-      <c r="E43" s="2"/>
-      <c r="F43" s="35" t="str">
+      <c r="H52"/>
+      <c r="I52"/>
+      <c r="J52"/>
+      <c r="K52"/>
+      <c r="L52"/>
+    </row>
+    <row r="53" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A53"/>
+      <c r="B53"/>
+      <c r="C53"/>
+      <c r="D53"/>
+      <c r="E53"/>
+      <c r="F53" t="str">
         <v>Creator Tax 上限</v>
       </c>
-      <c r="G43" s="63">
+      <c r="G53">
         <f>10%</f>
       </c>
-      <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="60"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A44" s="2"/>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-      <c r="E44" s="2"/>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
-      <c r="H44" s="2"/>
-      <c r="I44" s="2"/>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-      <c r="L44" s="2"/>
-    </row>
-    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2"/>
-      <c r="H45" s="2"/>
-      <c r="I45" s="2"/>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-      <c r="L45" s="2"/>
-    </row>
-    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" ht="24" customHeight="1">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="8" t="str">
+      <c r="H53"/>
+      <c r="I53"/>
+      <c r="J53"/>
+      <c r="K53"/>
+      <c r="L53"/>
+    </row>
+    <row r="54" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A54"/>
+      <c r="B54"/>
+      <c r="C54"/>
+      <c r="D54"/>
+      <c r="E54"/>
+      <c r="F54"/>
+      <c r="G54"/>
+      <c r="H54"/>
+      <c r="I54" s="108" t="str">
+        <v>洗后持仓保留比例</v>
+      </c>
+      <c r="J54">
+        <f>1</f>
+      </c>
+      <c r="K54"/>
+      <c r="L54"/>
+    </row>
+    <row r="55" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A55"/>
+      <c r="B55"/>
+      <c r="C55"/>
+      <c r="D55"/>
+      <c r="E55"/>
+      <c r="F55"/>
+      <c r="G55"/>
+      <c r="H55"/>
+      <c r="I55" s="108" t="str">
+        <v>目标外盘 Pool TOKEN</v>
+      </c>
+      <c r="J55"/>
+      <c r="K55"/>
+      <c r="L55"/>
+    </row>
+    <row r="56" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="A56"/>
+      <c r="B56"/>
+      <c r="C56"/>
+      <c r="D56"/>
+      <c r="E56"/>
+      <c r="F56"/>
+      <c r="G56"/>
+      <c r="H56"/>
+      <c r="I56" s="108" t="str">
+        <v>洗后外盘 Pool TOKEN</v>
+      </c>
+      <c r="J56"/>
+      <c r="K56"/>
+      <c r="L56"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57"/>
+      <c r="B57"/>
+      <c r="C57" t="str">
         <v>内盘曲线</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="8"/>
-      <c r="H47" s="8"/>
-      <c r="I47" s="8"/>
-      <c r="J47" s="8"/>
-      <c r="K47" s="8"/>
-      <c r="L47" s="8"/>
-    </row>
-    <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="2"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="77" t="str">
+      <c r="D57"/>
+      <c r="E57"/>
+      <c r="F57"/>
+      <c r="G57"/>
+      <c r="H57"/>
+      <c r="I57"/>
+      <c r="J57"/>
+      <c r="K57"/>
+      <c r="L57"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58"/>
+      <c r="B58"/>
+      <c r="C58" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D48" s="77" t="str">
+      <c r="D58" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E48" s="77" t="str">
+      <c r="E58" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F48" s="77" t="str">
+      <c r="F58" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G48" s="77" t="str">
+      <c r="G58" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H48" s="77" t="str">
+      <c r="H58" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I48" s="77" t="str">
+      <c r="I58" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J48" s="77" t="str">
+      <c r="J58" t="str">
         <v>区间净投入
 / Quote</v>
       </c>
-      <c r="K48" s="77" t="str">
+      <c r="K58" t="str">
         <v>区间含费
 / Quote</v>
       </c>
-      <c r="L48" s="77" t="str">
+      <c r="L58" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="2"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="78" t="n">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59"/>
+      <c r="B59"/>
+      <c r="C59" t="n">
         <v>0</v>
       </c>
-      <c r="D49" s="81">
-        <f>$D$35*(1-C49)</f>
-      </c>
-      <c r="E49" s="26">
-        <f>$G$37/D49</f>
-      </c>
-      <c r="F49" s="84">
-        <f>IF(OR(D49="",E49=""),"",E49/D49)</f>
-      </c>
-      <c r="G49" s="84">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F49))),"",F49*$D$24)</f>
-      </c>
-      <c r="H49" s="26">
-        <f>IF(NOT(ISNUMBER(F49)),"",F49*$D$35)</f>
-      </c>
-      <c r="I49" s="26">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H49))),"",H49*$D$24)</f>
-      </c>
-      <c r="J49" s="26">
+      <c r="D59" s="125">
+        <f>$D$45*(1-C59)</f>
+      </c>
+      <c r="E59" s="125">
+        <f>$G$47/D59</f>
+      </c>
+      <c r="F59">
+        <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
+      </c>
+      <c r="G59">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F59))),"",F59*$D$33)</f>
+      </c>
+      <c r="H59" s="125">
+        <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
+      </c>
+      <c r="I59" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H59))),"",H59*$D$33)</f>
+      </c>
+      <c r="J59" s="125">
         <f>0</f>
       </c>
-      <c r="K49" s="26">
-        <f>J49/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L49" s="90">
-        <f>SUM($K$49:K49)</f>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1">
-      <c r="A50" s="2"/>
-      <c r="B50" s="2"/>
-      <c r="C50" s="79" t="n">
+      <c r="K59" s="125">
+        <f>J59/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L59" s="125">
+        <f>SUM($K$59:K59)</f>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60"/>
+      <c r="B60"/>
+      <c r="C60" t="n">
         <v>0.1</v>
       </c>
-      <c r="D50" s="82">
-        <f>$D$35*(1-C50)</f>
-      </c>
-      <c r="E50" s="27">
-        <f>$G$37/D50</f>
-      </c>
-      <c r="F50" s="85">
-        <f>IF(OR(D50="",E50=""),"",E50/D50)</f>
-      </c>
-      <c r="G50" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F50))),"",F50*$D$24)</f>
-      </c>
-      <c r="H50" s="27">
-        <f>IF(NOT(ISNUMBER(F50)),"",F50*$D$35)</f>
-      </c>
-      <c r="I50" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H50))),"",H50*$D$24)</f>
-      </c>
-      <c r="J50" s="27">
-        <f>E50-E49</f>
-      </c>
-      <c r="K50" s="27">
-        <f>J50/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L50" s="91">
-        <f>SUM($K$49:K50)</f>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1">
-      <c r="A51" s="2"/>
-      <c r="B51" s="2"/>
-      <c r="C51" s="79" t="n">
+      <c r="D60" s="125">
+        <f>$D$45*(1-C60)</f>
+      </c>
+      <c r="E60" s="125">
+        <f>$G$47/D60</f>
+      </c>
+      <c r="F60">
+        <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
+      </c>
+      <c r="G60">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F60))),"",F60*$D$33)</f>
+      </c>
+      <c r="H60" s="125">
+        <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
+      </c>
+      <c r="I60" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H60))),"",H60*$D$33)</f>
+      </c>
+      <c r="J60" s="125">
+        <f>E60-E59</f>
+      </c>
+      <c r="K60" s="125">
+        <f>J60/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L60" s="125">
+        <f>SUM($K$59:K60)</f>
+      </c>
+    </row>
+    <row r="61" ht="30" customHeight="1">
+      <c r="A61"/>
+      <c r="B61"/>
+      <c r="C61" t="n">
         <v>0.2</v>
       </c>
-      <c r="D51" s="82">
-        <f>$D$35*(1-C51)</f>
-      </c>
-      <c r="E51" s="27">
-        <f>$G$37/D51</f>
-      </c>
-      <c r="F51" s="85">
-        <f>IF(OR(D51="",E51=""),"",E51/D51)</f>
-      </c>
-      <c r="G51" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F51))),"",F51*$D$24)</f>
-      </c>
-      <c r="H51" s="27">
-        <f>IF(NOT(ISNUMBER(F51)),"",F51*$D$35)</f>
-      </c>
-      <c r="I51" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H51))),"",H51*$D$24)</f>
-      </c>
-      <c r="J51" s="27">
-        <f>E51-E50</f>
-      </c>
-      <c r="K51" s="27">
-        <f>J51/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L51" s="91">
-        <f>SUM($K$49:K51)</f>
-      </c>
-    </row>
-    <row r="52" ht="20" customHeight="1">
-      <c r="A52" s="2"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="79" t="n">
+      <c r="D61" s="125">
+        <f>$D$45*(1-C61)</f>
+      </c>
+      <c r="E61" s="125">
+        <f>$G$47/D61</f>
+      </c>
+      <c r="F61">
+        <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
+      </c>
+      <c r="G61">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F61))),"",F61*$D$33)</f>
+      </c>
+      <c r="H61" s="125">
+        <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
+      </c>
+      <c r="I61" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H61))),"",H61*$D$33)</f>
+      </c>
+      <c r="J61" s="125">
+        <f>E61-E60</f>
+      </c>
+      <c r="K61" s="125">
+        <f>J61/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L61" s="125">
+        <f>SUM($K$59:K61)</f>
+      </c>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62"/>
+      <c r="B62"/>
+      <c r="C62" t="n">
         <v>0.3</v>
       </c>
-      <c r="D52" s="82">
-        <f>$D$35*(1-C52)</f>
-      </c>
-      <c r="E52" s="27">
-        <f>$G$37/D52</f>
-      </c>
-      <c r="F52" s="85">
-        <f>IF(OR(D52="",E52=""),"",E52/D52)</f>
-      </c>
-      <c r="G52" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F52))),"",F52*$D$24)</f>
-      </c>
-      <c r="H52" s="27">
-        <f>IF(NOT(ISNUMBER(F52)),"",F52*$D$35)</f>
-      </c>
-      <c r="I52" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H52))),"",H52*$D$24)</f>
-      </c>
-      <c r="J52" s="27">
-        <f>E52-E51</f>
-      </c>
-      <c r="K52" s="27">
-        <f>J52/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L52" s="91">
-        <f>SUM($K$49:K52)</f>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1">
-      <c r="A53" s="2"/>
-      <c r="B53" s="2"/>
-      <c r="C53" s="79" t="n">
+      <c r="D62" s="125">
+        <f>$D$45*(1-C62)</f>
+      </c>
+      <c r="E62" s="125">
+        <f>$G$47/D62</f>
+      </c>
+      <c r="F62">
+        <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
+      </c>
+      <c r="G62">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F62))),"",F62*$D$33)</f>
+      </c>
+      <c r="H62" s="125">
+        <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
+      </c>
+      <c r="I62" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H62))),"",H62*$D$33)</f>
+      </c>
+      <c r="J62" s="125">
+        <f>E62-E61</f>
+      </c>
+      <c r="K62" s="125">
+        <f>J62/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L62" s="125">
+        <f>SUM($K$59:K62)</f>
+      </c>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63"/>
+      <c r="B63"/>
+      <c r="C63" t="n">
         <v>0.4</v>
       </c>
-      <c r="D53" s="82">
-        <f>$D$35*(1-C53)</f>
-      </c>
-      <c r="E53" s="27">
-        <f>$G$37/D53</f>
-      </c>
-      <c r="F53" s="85">
-        <f>IF(OR(D53="",E53=""),"",E53/D53)</f>
-      </c>
-      <c r="G53" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F53))),"",F53*$D$24)</f>
-      </c>
-      <c r="H53" s="27">
-        <f>IF(NOT(ISNUMBER(F53)),"",F53*$D$35)</f>
-      </c>
-      <c r="I53" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H53))),"",H53*$D$24)</f>
-      </c>
-      <c r="J53" s="27">
-        <f>E53-E52</f>
-      </c>
-      <c r="K53" s="27">
-        <f>J53/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L53" s="91">
-        <f>SUM($K$49:K53)</f>
-      </c>
-    </row>
-    <row r="54" ht="20" customHeight="1">
-      <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
-      <c r="C54" s="79" t="n">
+      <c r="D63" s="125">
+        <f>$D$45*(1-C63)</f>
+      </c>
+      <c r="E63" s="125">
+        <f>$G$47/D63</f>
+      </c>
+      <c r="F63">
+        <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
+      </c>
+      <c r="G63">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F63))),"",F63*$D$33)</f>
+      </c>
+      <c r="H63" s="125">
+        <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
+      </c>
+      <c r="I63" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H63))),"",H63*$D$33)</f>
+      </c>
+      <c r="J63" s="125">
+        <f>E63-E62</f>
+      </c>
+      <c r="K63" s="125">
+        <f>J63/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L63" s="125">
+        <f>SUM($K$59:K63)</f>
+      </c>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64"/>
+      <c r="B64"/>
+      <c r="C64" t="n">
         <v>0.5</v>
       </c>
-      <c r="D54" s="82">
-        <f>$D$35*(1-C54)</f>
-      </c>
-      <c r="E54" s="27">
-        <f>$G$37/D54</f>
-      </c>
-      <c r="F54" s="85">
-        <f>IF(OR(D54="",E54=""),"",E54/D54)</f>
-      </c>
-      <c r="G54" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F54))),"",F54*$D$24)</f>
-      </c>
-      <c r="H54" s="27">
-        <f>IF(NOT(ISNUMBER(F54)),"",F54*$D$35)</f>
-      </c>
-      <c r="I54" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H54))),"",H54*$D$24)</f>
-      </c>
-      <c r="J54" s="27">
-        <f>E54-E53</f>
-      </c>
-      <c r="K54" s="27">
-        <f>J54/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L54" s="91">
-        <f>SUM($K$49:K54)</f>
-      </c>
-    </row>
-    <row r="55" ht="20" customHeight="1">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="79" t="n">
+      <c r="D64" s="125">
+        <f>$D$45*(1-C64)</f>
+      </c>
+      <c r="E64" s="125">
+        <f>$G$47/D64</f>
+      </c>
+      <c r="F64">
+        <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
+      </c>
+      <c r="G64">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F64))),"",F64*$D$33)</f>
+      </c>
+      <c r="H64" s="125">
+        <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
+      </c>
+      <c r="I64" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H64))),"",H64*$D$33)</f>
+      </c>
+      <c r="J64" s="125">
+        <f>E64-E63</f>
+      </c>
+      <c r="K64" s="125">
+        <f>J64/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L64" s="125">
+        <f>SUM($K$59:K64)</f>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65"/>
+      <c r="B65"/>
+      <c r="C65" t="n">
         <v>0.6</v>
       </c>
-      <c r="D55" s="82">
-        <f>$D$35*(1-C55)</f>
-      </c>
-      <c r="E55" s="27">
-        <f>$G$37/D55</f>
-      </c>
-      <c r="F55" s="85">
-        <f>IF(OR(D55="",E55=""),"",E55/D55)</f>
-      </c>
-      <c r="G55" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F55))),"",F55*$D$24)</f>
-      </c>
-      <c r="H55" s="27">
-        <f>IF(NOT(ISNUMBER(F55)),"",F55*$D$35)</f>
-      </c>
-      <c r="I55" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H55))),"",H55*$D$24)</f>
-      </c>
-      <c r="J55" s="27">
-        <f>E55-E54</f>
-      </c>
-      <c r="K55" s="27">
-        <f>J55/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L55" s="91">
-        <f>SUM($K$49:K55)</f>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1">
-      <c r="A56" s="2"/>
-      <c r="B56" s="2"/>
-      <c r="C56" s="79" t="n">
+      <c r="D65" s="125">
+        <f>$D$45*(1-C65)</f>
+      </c>
+      <c r="E65" s="125">
+        <f>$G$47/D65</f>
+      </c>
+      <c r="F65">
+        <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
+      </c>
+      <c r="G65">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F65))),"",F65*$D$33)</f>
+      </c>
+      <c r="H65" s="125">
+        <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
+      </c>
+      <c r="I65" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H65))),"",H65*$D$33)</f>
+      </c>
+      <c r="J65" s="125">
+        <f>E65-E64</f>
+      </c>
+      <c r="K65" s="125">
+        <f>J65/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L65" s="125">
+        <f>SUM($K$59:K65)</f>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66"/>
+      <c r="B66"/>
+      <c r="C66" t="n">
         <v>0.7</v>
       </c>
-      <c r="D56" s="82">
-        <f>$D$35*(1-C56)</f>
-      </c>
-      <c r="E56" s="27">
-        <f>$G$37/D56</f>
-      </c>
-      <c r="F56" s="85">
-        <f>IF(OR(D56="",E56=""),"",E56/D56)</f>
-      </c>
-      <c r="G56" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F56))),"",F56*$D$24)</f>
-      </c>
-      <c r="H56" s="27">
-        <f>IF(NOT(ISNUMBER(F56)),"",F56*$D$35)</f>
-      </c>
-      <c r="I56" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H56))),"",H56*$D$24)</f>
-      </c>
-      <c r="J56" s="27">
-        <f>E56-E55</f>
-      </c>
-      <c r="K56" s="27">
-        <f>J56/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L56" s="91">
-        <f>SUM($K$49:K56)</f>
-      </c>
-    </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="A57" s="2"/>
-      <c r="B57" s="2"/>
-      <c r="C57" s="93">
-        <f>$G$33</f>
-      </c>
-      <c r="D57" s="94">
-        <f>$D$35*(1-C57)</f>
-      </c>
-      <c r="E57" s="95">
-        <f>$G$37/D57</f>
-      </c>
-      <c r="F57" s="96">
-        <f>IF(OR(D57="",E57=""),"",E57/D57)</f>
-      </c>
-      <c r="G57" s="96">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F57))),"",F57*$D$24)</f>
-      </c>
-      <c r="H57" s="95">
-        <f>IF(NOT(ISNUMBER(F57)),"",F57*$D$35)</f>
-      </c>
-      <c r="I57" s="95">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H57))),"",H57*$D$24)</f>
-      </c>
-      <c r="J57" s="95">
-        <f>E57-E56</f>
-      </c>
-      <c r="K57" s="95">
-        <f>J57/(1-$G$31-$J$7)</f>
-      </c>
-      <c r="L57" s="92">
-        <f>SUM($K$49:K57)</f>
-      </c>
-    </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="2"/>
-      <c r="B58" s="2"/>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
-      <c r="E58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="H58" s="2"/>
-      <c r="I58" s="2"/>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2"/>
-      <c r="L58" s="2"/>
-    </row>
-    <row r="59" ht="20" customHeight="1">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="2"/>
-    </row>
-    <row r="60" ht="24" customHeight="1">
-      <c r="A60" s="2"/>
-      <c r="B60" s="2"/>
-      <c r="C60" s="8" t="str">
+      <c r="D66" s="125">
+        <f>$D$45*(1-C66)</f>
+      </c>
+      <c r="E66" s="125">
+        <f>$G$47/D66</f>
+      </c>
+      <c r="F66">
+        <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
+      </c>
+      <c r="G66">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F66))),"",F66*$D$33)</f>
+      </c>
+      <c r="H66" s="125">
+        <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
+      </c>
+      <c r="I66" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H66))),"",H66*$D$33)</f>
+      </c>
+      <c r="J66" s="125">
+        <f>E66-E65</f>
+      </c>
+      <c r="K66" s="125">
+        <f>J66/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L66" s="125">
+        <f>SUM($K$59:K66)</f>
+      </c>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67"/>
+      <c r="B67"/>
+      <c r="C67">
+        <f>$G$43</f>
+      </c>
+      <c r="D67" s="125">
+        <f>$D$45*(1-C67)</f>
+      </c>
+      <c r="E67" s="125">
+        <f>$G$47/D67</f>
+      </c>
+      <c r="F67">
+        <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
+      </c>
+      <c r="G67">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F67))),"",F67*$D$33)</f>
+      </c>
+      <c r="H67" s="125">
+        <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
+      </c>
+      <c r="I67" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H67))),"",H67*$D$33)</f>
+      </c>
+      <c r="J67" s="125">
+        <f>E67-E66</f>
+      </c>
+      <c r="K67" s="125">
+        <f>J67/(1-$G$41-$J$7)</f>
+      </c>
+      <c r="L67" s="125">
+        <f>SUM($K$59:K67)</f>
+      </c>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68"/>
+      <c r="B68"/>
+      <c r="C68"/>
+      <c r="D68"/>
+      <c r="E68"/>
+      <c r="F68"/>
+      <c r="G68"/>
+      <c r="H68"/>
+      <c r="I68"/>
+      <c r="J68"/>
+      <c r="K68"/>
+      <c r="L68"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69"/>
+      <c r="B69"/>
+      <c r="C69"/>
+      <c r="D69"/>
+      <c r="E69"/>
+      <c r="F69"/>
+      <c r="G69"/>
+      <c r="H69"/>
+      <c r="I69"/>
+      <c r="J69"/>
+      <c r="K69"/>
+      <c r="L69"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70"/>
+      <c r="B70"/>
+      <c r="C70" t="str">
         <v>外盘曲线</v>
       </c>
-      <c r="D60" s="8"/>
-      <c r="E60" s="8"/>
-      <c r="F60" s="8"/>
-      <c r="G60" s="8"/>
-      <c r="H60" s="8"/>
-      <c r="I60" s="8"/>
-      <c r="J60" s="8"/>
-      <c r="K60" s="8"/>
-      <c r="L60" s="8"/>
-    </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="2"/>
-      <c r="B61" s="2"/>
-      <c r="C61" s="77" t="str">
+      <c r="D70"/>
+      <c r="E70"/>
+      <c r="F70"/>
+      <c r="G70"/>
+      <c r="H70"/>
+      <c r="I70"/>
+      <c r="J70"/>
+      <c r="K70"/>
+      <c r="L70"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71"/>
+      <c r="B71"/>
+      <c r="C71" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D61" s="77" t="str">
+      <c r="D71" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E61" s="77" t="str">
+      <c r="E71" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F61" s="77" t="str">
+      <c r="F71" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G61" s="77" t="str">
+      <c r="G71" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H61" s="77" t="str">
+      <c r="H71" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I61" s="77" t="str">
+      <c r="I71" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J61" s="77" t="str">
+      <c r="J71" t="str">
         <v>外盘净投入
 / Quote</v>
       </c>
-      <c r="K61" s="77" t="str">
+      <c r="K71" t="str">
         <v>外盘含费
 / Quote</v>
       </c>
-      <c r="L61" s="77" t="str">
+      <c r="L71" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
     </row>
-    <row r="62" ht="20" customHeight="1">
-      <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="97">
-        <f>$G$33</f>
-      </c>
-      <c r="D62" s="98">
-        <f>$G$38</f>
-      </c>
-      <c r="E62" s="99">
-        <f>$G$34</f>
-      </c>
-      <c r="F62" s="100">
-        <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
-      </c>
-      <c r="G62" s="100">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F62))),"",F62*$D$24)</f>
-      </c>
-      <c r="H62" s="99">
-        <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$35)</f>
-      </c>
-      <c r="I62" s="99">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H62))),"",H62*$D$24)</f>
-      </c>
-      <c r="J62" s="99">
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72"/>
+      <c r="B72"/>
+      <c r="C72">
+        <f>$G$43</f>
+      </c>
+      <c r="D72" s="125">
+        <f>$G$48</f>
+      </c>
+      <c r="E72" s="125">
+        <f>$G$44</f>
+      </c>
+      <c r="F72">
+        <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
+      </c>
+      <c r="G72">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F72))),"",F72*$D$33)</f>
+      </c>
+      <c r="H72" s="125">
+        <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
+      </c>
+      <c r="I72" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H72))),"",H72*$D$33)</f>
+      </c>
+      <c r="J72" s="125">
         <f>0</f>
       </c>
-      <c r="K62" s="99">
+      <c r="K72" s="125">
         <f>0</f>
       </c>
-      <c r="L62" s="90">
-        <f>$J$31</f>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="79" t="n">
+      <c r="L72" s="125">
+        <f>$J$41</f>
+      </c>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73"/>
+      <c r="B73"/>
+      <c r="C73" t="n">
         <v>0.75</v>
       </c>
-      <c r="D63" s="82">
-        <f>IF(C63&lt;$G$23,$D$35*(1-C63)-$G$41,"")</f>
-      </c>
-      <c r="E63" s="27">
-        <f>IF(D63="","",$G$40/D63)</f>
-      </c>
-      <c r="F63" s="85">
-        <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
-      </c>
-      <c r="G63" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F63))),"",F63*$D$24)</f>
-      </c>
-      <c r="H63" s="27">
-        <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$35)</f>
-      </c>
-      <c r="I63" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H63))),"",H63*$D$24)</f>
-      </c>
-      <c r="J63" s="27">
-        <f>IF(E63="","",MAX(0,E63-$G$34))</f>
-      </c>
-      <c r="K63" s="27">
-        <f>IF(D63="","",$G$40/($G$38-MAX(0,(C63-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L63" s="91">
-        <f>IF(K63="","",$J$31+K63)</f>
-      </c>
-    </row>
-    <row r="64" ht="20" customHeight="1">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="79" t="n">
+      <c r="D73" s="125">
+        <f>IF(C73&lt;$G$32,$D$45*(1-C73)-$G$51,"")</f>
+      </c>
+      <c r="E73" s="125">
+        <f>IF(D73="","",$G$50/D73)</f>
+      </c>
+      <c r="F73">
+        <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
+      </c>
+      <c r="G73">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F73))),"",F73*$D$33)</f>
+      </c>
+      <c r="H73" s="125">
+        <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
+      </c>
+      <c r="I73" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H73))),"",H73*$D$33)</f>
+      </c>
+      <c r="J73" s="125">
+        <f>IF(E73="","",MAX(0,E73-$G$44))</f>
+      </c>
+      <c r="K73" s="125">
+        <f>IF(D73="","",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L73" s="125">
+        <f>IF(K73="","",$J$41+K73)</f>
+      </c>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74"/>
+      <c r="B74"/>
+      <c r="C74" t="n">
         <v>0.8</v>
       </c>
-      <c r="D64" s="82">
-        <f>IF(C64&lt;$G$23,$D$35*(1-C64)-$G$41,"")</f>
-      </c>
-      <c r="E64" s="27">
-        <f>IF(D64="","",$G$40/D64)</f>
-      </c>
-      <c r="F64" s="85">
-        <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
-      </c>
-      <c r="G64" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F64))),"",F64*$D$24)</f>
-      </c>
-      <c r="H64" s="27">
-        <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$35)</f>
-      </c>
-      <c r="I64" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H64))),"",H64*$D$24)</f>
-      </c>
-      <c r="J64" s="27">
-        <f>IF(E64="","",MAX(0,E64-$G$34))</f>
-      </c>
-      <c r="K64" s="27">
-        <f>IF(D64="","",$G$40/($G$38-MAX(0,(C64-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L64" s="91">
-        <f>IF(K64="","",$J$31+K64)</f>
-      </c>
-    </row>
-    <row r="65" ht="20" customHeight="1">
-      <c r="A65" s="2"/>
-      <c r="B65" s="2"/>
-      <c r="C65" s="79" t="n">
+      <c r="D74" s="125">
+        <f>IF(C74&lt;$G$32,$D$45*(1-C74)-$G$51,"")</f>
+      </c>
+      <c r="E74" s="125">
+        <f>IF(D74="","",$G$50/D74)</f>
+      </c>
+      <c r="F74">
+        <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
+      </c>
+      <c r="G74">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F74))),"",F74*$D$33)</f>
+      </c>
+      <c r="H74" s="125">
+        <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
+      </c>
+      <c r="I74" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H74))),"",H74*$D$33)</f>
+      </c>
+      <c r="J74" s="125">
+        <f>IF(E74="","",MAX(0,E74-$G$44))</f>
+      </c>
+      <c r="K74" s="125">
+        <f>IF(D74="","",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L74" s="125">
+        <f>IF(K74="","",$J$41+K74)</f>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75"/>
+      <c r="B75"/>
+      <c r="C75" t="n">
         <v>0.82</v>
       </c>
-      <c r="D65" s="82">
-        <f>IF(C65&lt;$G$23,$D$35*(1-C65)-$G$41,"")</f>
-      </c>
-      <c r="E65" s="27">
-        <f>IF(D65="","",$G$40/D65)</f>
-      </c>
-      <c r="F65" s="85">
-        <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
-      </c>
-      <c r="G65" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F65))),"",F65*$D$24)</f>
-      </c>
-      <c r="H65" s="27">
-        <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$35)</f>
-      </c>
-      <c r="I65" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H65))),"",H65*$D$24)</f>
-      </c>
-      <c r="J65" s="27">
-        <f>IF(E65="","",MAX(0,E65-$G$34))</f>
-      </c>
-      <c r="K65" s="27">
-        <f>IF(D65="","",$G$40/($G$38-MAX(0,(C65-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L65" s="91">
-        <f>IF(K65="","",$J$31+K65)</f>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
-      <c r="C66" s="79" t="n">
+      <c r="D75" s="125">
+        <f>IF(C75&lt;$G$32,$D$45*(1-C75)-$G$51,"")</f>
+      </c>
+      <c r="E75" s="125">
+        <f>IF(D75="","",$G$50/D75)</f>
+      </c>
+      <c r="F75">
+        <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
+      </c>
+      <c r="G75">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F75))),"",F75*$D$33)</f>
+      </c>
+      <c r="H75" s="125">
+        <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
+      </c>
+      <c r="I75" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H75))),"",H75*$D$33)</f>
+      </c>
+      <c r="J75" s="125">
+        <f>IF(E75="","",MAX(0,E75-$G$44))</f>
+      </c>
+      <c r="K75" s="125">
+        <f>IF(D75="","",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L75" s="125">
+        <f>IF(K75="","",$J$41+K75)</f>
+      </c>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76"/>
+      <c r="B76"/>
+      <c r="C76" t="n">
         <v>0.84</v>
       </c>
-      <c r="D66" s="82">
-        <f>IF(C66&lt;$G$23,$D$35*(1-C66)-$G$41,"")</f>
-      </c>
-      <c r="E66" s="27">
-        <f>IF(D66="","",$G$40/D66)</f>
-      </c>
-      <c r="F66" s="85">
-        <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
-      </c>
-      <c r="G66" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F66))),"",F66*$D$24)</f>
-      </c>
-      <c r="H66" s="27">
-        <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$35)</f>
-      </c>
-      <c r="I66" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H66))),"",H66*$D$24)</f>
-      </c>
-      <c r="J66" s="27">
-        <f>IF(E66="","",MAX(0,E66-$G$34))</f>
-      </c>
-      <c r="K66" s="27">
-        <f>IF(D66="","",$G$40/($G$38-MAX(0,(C66-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L66" s="91">
-        <f>IF(K66="","",$J$31+K66)</f>
-      </c>
-    </row>
-    <row r="67" ht="20" customHeight="1">
-      <c r="A67" s="2"/>
-      <c r="B67" s="2"/>
-      <c r="C67" s="79" t="n">
+      <c r="D76" s="125">
+        <f>IF(C76&lt;$G$32,$D$45*(1-C76)-$G$51,"")</f>
+      </c>
+      <c r="E76" s="125">
+        <f>IF(D76="","",$G$50/D76)</f>
+      </c>
+      <c r="F76">
+        <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
+      </c>
+      <c r="G76">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F76))),"",F76*$D$33)</f>
+      </c>
+      <c r="H76" s="125">
+        <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
+      </c>
+      <c r="I76" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H76))),"",H76*$D$33)</f>
+      </c>
+      <c r="J76" s="125">
+        <f>IF(E76="","",MAX(0,E76-$G$44))</f>
+      </c>
+      <c r="K76" s="125">
+        <f>IF(D76="","",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L76" s="125">
+        <f>IF(K76="","",$J$41+K76)</f>
+      </c>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77"/>
+      <c r="B77"/>
+      <c r="C77" t="n">
         <v>0.86</v>
       </c>
-      <c r="D67" s="82">
-        <f>IF(C67&lt;$G$23,$D$35*(1-C67)-$G$41,"")</f>
-      </c>
-      <c r="E67" s="27">
-        <f>IF(D67="","",$G$40/D67)</f>
-      </c>
-      <c r="F67" s="85">
-        <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
-      </c>
-      <c r="G67" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F67))),"",F67*$D$24)</f>
-      </c>
-      <c r="H67" s="27">
-        <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$35)</f>
-      </c>
-      <c r="I67" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H67))),"",H67*$D$24)</f>
-      </c>
-      <c r="J67" s="27">
-        <f>IF(E67="","",MAX(0,E67-$G$34))</f>
-      </c>
-      <c r="K67" s="27">
-        <f>IF(D67="","",$G$40/($G$38-MAX(0,(C67-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L67" s="91">
-        <f>IF(K67="","",$J$31+K67)</f>
-      </c>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="2"/>
-      <c r="B68" s="2"/>
-      <c r="C68" s="79" t="n">
+      <c r="D77" s="125">
+        <f>IF(C77&lt;$G$32,$D$45*(1-C77)-$G$51,"")</f>
+      </c>
+      <c r="E77" s="125">
+        <f>IF(D77="","",$G$50/D77)</f>
+      </c>
+      <c r="F77">
+        <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
+      </c>
+      <c r="G77">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F77))),"",F77*$D$33)</f>
+      </c>
+      <c r="H77" s="125">
+        <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
+      </c>
+      <c r="I77" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H77))),"",H77*$D$33)</f>
+      </c>
+      <c r="J77" s="125">
+        <f>IF(E77="","",MAX(0,E77-$G$44))</f>
+      </c>
+      <c r="K77" s="125">
+        <f>IF(D77="","",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L77" s="125">
+        <f>IF(K77="","",$J$41+K77)</f>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78"/>
+      <c r="B78"/>
+      <c r="C78" t="n">
         <v>0.88</v>
       </c>
-      <c r="D68" s="82">
-        <f>IF(C68&lt;$G$23,$D$35*(1-C68)-$G$41,"")</f>
-      </c>
-      <c r="E68" s="27">
-        <f>IF(D68="","",$G$40/D68)</f>
-      </c>
-      <c r="F68" s="85">
-        <f>IF(OR(D68="",E68=""),"",E68/D68)</f>
-      </c>
-      <c r="G68" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F68))),"",F68*$D$24)</f>
-      </c>
-      <c r="H68" s="27">
-        <f>IF(NOT(ISNUMBER(F68)),"",F68*$D$35)</f>
-      </c>
-      <c r="I68" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H68))),"",H68*$D$24)</f>
-      </c>
-      <c r="J68" s="27">
-        <f>IF(E68="","",MAX(0,E68-$G$34))</f>
-      </c>
-      <c r="K68" s="27">
-        <f>IF(D68="","",$G$40/($G$38-MAX(0,(C68-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L68" s="91">
-        <f>IF(K68="","",$J$31+K68)</f>
-      </c>
-    </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="2"/>
-      <c r="B69" s="2"/>
-      <c r="C69" s="79" t="n">
+      <c r="D78" s="125">
+        <f>IF(C78&lt;$G$32,$D$45*(1-C78)-$G$51,"")</f>
+      </c>
+      <c r="E78" s="125">
+        <f>IF(D78="","",$G$50/D78)</f>
+      </c>
+      <c r="F78">
+        <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
+      </c>
+      <c r="G78">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F78))),"",F78*$D$33)</f>
+      </c>
+      <c r="H78" s="125">
+        <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
+      </c>
+      <c r="I78" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H78))),"",H78*$D$33)</f>
+      </c>
+      <c r="J78" s="125">
+        <f>IF(E78="","",MAX(0,E78-$G$44))</f>
+      </c>
+      <c r="K78" s="125">
+        <f>IF(D78="","",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L78" s="125">
+        <f>IF(K78="","",$J$41+K78)</f>
+      </c>
+    </row>
+    <row r="79" ht="30" customHeight="1">
+      <c r="A79"/>
+      <c r="B79"/>
+      <c r="C79" t="n">
         <v>0.89</v>
       </c>
-      <c r="D69" s="82">
-        <f>IF(C69&lt;$G$23,$D$35*(1-C69)-$G$41,"")</f>
-      </c>
-      <c r="E69" s="27">
-        <f>IF(D69="","",$G$40/D69)</f>
-      </c>
-      <c r="F69" s="85">
-        <f>IF(OR(D69="",E69=""),"",E69/D69)</f>
-      </c>
-      <c r="G69" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F69))),"",F69*$D$24)</f>
-      </c>
-      <c r="H69" s="27">
-        <f>IF(NOT(ISNUMBER(F69)),"",F69*$D$35)</f>
-      </c>
-      <c r="I69" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H69))),"",H69*$D$24)</f>
-      </c>
-      <c r="J69" s="27">
-        <f>IF(E69="","",MAX(0,E69-$G$34))</f>
-      </c>
-      <c r="K69" s="27">
-        <f>IF(D69="","",$G$40/($G$38-MAX(0,(C69-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L69" s="91">
-        <f>IF(K69="","",$J$31+K69)</f>
-      </c>
-    </row>
-    <row r="70" ht="20" customHeight="1">
-      <c r="A70" s="2"/>
-      <c r="B70" s="2"/>
-      <c r="C70" s="79" t="n">
+      <c r="D79" s="125">
+        <f>IF(C79&lt;$G$32,$D$45*(1-C79)-$G$51,"")</f>
+      </c>
+      <c r="E79" s="125">
+        <f>IF(D79="","",$G$50/D79)</f>
+      </c>
+      <c r="F79">
+        <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
+      </c>
+      <c r="G79">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F79))),"",F79*$D$33)</f>
+      </c>
+      <c r="H79" s="125">
+        <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
+      </c>
+      <c r="I79" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H79))),"",H79*$D$33)</f>
+      </c>
+      <c r="J79" s="125">
+        <f>IF(E79="","",MAX(0,E79-$G$44))</f>
+      </c>
+      <c r="K79" s="125">
+        <f>IF(D79="","",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L79" s="125">
+        <f>IF(K79="","",$J$41+K79)</f>
+      </c>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80"/>
+      <c r="B80"/>
+      <c r="C80" t="n">
         <v>0.9</v>
       </c>
-      <c r="D70" s="82">
-        <f>IF(C70&lt;$G$23,$D$35*(1-C70)-$G$41,"")</f>
-      </c>
-      <c r="E70" s="27">
-        <f>IF(D70="","",$G$40/D70)</f>
-      </c>
-      <c r="F70" s="85">
-        <f>IF(OR(D70="",E70=""),"",E70/D70)</f>
-      </c>
-      <c r="G70" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F70))),"",F70*$D$24)</f>
-      </c>
-      <c r="H70" s="27">
-        <f>IF(NOT(ISNUMBER(F70)),"",F70*$D$35)</f>
-      </c>
-      <c r="I70" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H70))),"",H70*$D$24)</f>
-      </c>
-      <c r="J70" s="27">
-        <f>IF(E70="","",MAX(0,E70-$G$34))</f>
-      </c>
-      <c r="K70" s="27">
-        <f>IF(D70="","",$G$40/($G$38-MAX(0,(C70-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L70" s="91">
-        <f>IF(K70="","",$J$31+K70)</f>
-      </c>
-    </row>
-    <row r="71" ht="20" customHeight="1">
-      <c r="A71" s="2"/>
-      <c r="B71" s="2"/>
-      <c r="C71" s="79" t="n">
+      <c r="D80" s="125">
+        <f>IF(C80&lt;$G$32,$D$45*(1-C80)-$G$51,"")</f>
+      </c>
+      <c r="E80" s="125">
+        <f>IF(D80="","",$G$50/D80)</f>
+      </c>
+      <c r="F80">
+        <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
+      </c>
+      <c r="G80">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F80))),"",F80*$D$33)</f>
+      </c>
+      <c r="H80" s="125">
+        <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
+      </c>
+      <c r="I80" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H80))),"",H80*$D$33)</f>
+      </c>
+      <c r="J80" s="125">
+        <f>IF(E80="","",MAX(0,E80-$G$44))</f>
+      </c>
+      <c r="K80" s="125">
+        <f>IF(D80="","",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L80" s="125">
+        <f>IF(K80="","",$J$41+K80)</f>
+      </c>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81"/>
+      <c r="B81"/>
+      <c r="C81" t="n">
         <v>0.905</v>
       </c>
-      <c r="D71" s="82">
-        <f>IF(C71&lt;$G$23,$D$35*(1-C71)-$G$41,"")</f>
-      </c>
-      <c r="E71" s="27">
-        <f>IF(D71="","",$G$40/D71)</f>
-      </c>
-      <c r="F71" s="85">
-        <f>IF(OR(D71="",E71=""),"",E71/D71)</f>
-      </c>
-      <c r="G71" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F71))),"",F71*$D$24)</f>
-      </c>
-      <c r="H71" s="27">
-        <f>IF(NOT(ISNUMBER(F71)),"",F71*$D$35)</f>
-      </c>
-      <c r="I71" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H71))),"",H71*$D$24)</f>
-      </c>
-      <c r="J71" s="27">
-        <f>IF(E71="","",MAX(0,E71-$G$34))</f>
-      </c>
-      <c r="K71" s="27">
-        <f>IF(D71="","",$G$40/($G$38-MAX(0,(C71-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L71" s="91">
-        <f>IF(K71="","",$J$31+K71)</f>
-      </c>
-    </row>
-    <row r="72" ht="20" customHeight="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="2"/>
-      <c r="C72" s="79" t="n">
+      <c r="D81" s="125">
+        <f>IF(C81&lt;$G$32,$D$45*(1-C81)-$G$51,"")</f>
+      </c>
+      <c r="E81" s="125">
+        <f>IF(D81="","",$G$50/D81)</f>
+      </c>
+      <c r="F81">
+        <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
+      </c>
+      <c r="G81">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F81))),"",F81*$D$33)</f>
+      </c>
+      <c r="H81" s="125">
+        <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
+      </c>
+      <c r="I81" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H81))),"",H81*$D$33)</f>
+      </c>
+      <c r="J81" s="125">
+        <f>IF(E81="","",MAX(0,E81-$G$44))</f>
+      </c>
+      <c r="K81" s="125">
+        <f>IF(D81="","",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L81" s="125">
+        <f>IF(K81="","",$J$41+K81)</f>
+      </c>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82"/>
+      <c r="B82"/>
+      <c r="C82" t="n">
         <v>0.91</v>
       </c>
-      <c r="D72" s="82">
-        <f>IF(C72&lt;$G$23,$D$35*(1-C72)-$G$41,"")</f>
-      </c>
-      <c r="E72" s="27">
-        <f>IF(D72="","",$G$40/D72)</f>
-      </c>
-      <c r="F72" s="85">
-        <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
-      </c>
-      <c r="G72" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F72))),"",F72*$D$24)</f>
-      </c>
-      <c r="H72" s="27">
-        <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$35)</f>
-      </c>
-      <c r="I72" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H72))),"",H72*$D$24)</f>
-      </c>
-      <c r="J72" s="27">
-        <f>IF(E72="","",MAX(0,E72-$G$34))</f>
-      </c>
-      <c r="K72" s="27">
-        <f>IF(D72="","",$G$40/($G$38-MAX(0,(C72-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L72" s="91">
-        <f>IF(K72="","",$J$31+K72)</f>
-      </c>
-    </row>
-    <row r="73" ht="20" customHeight="1">
-      <c r="A73" s="2"/>
-      <c r="B73" s="2"/>
-      <c r="C73" s="79" t="n">
+      <c r="D82" s="125">
+        <f>IF(C82&lt;$G$32,$D$45*(1-C82)-$G$51,"")</f>
+      </c>
+      <c r="E82" s="125">
+        <f>IF(D82="","",$G$50/D82)</f>
+      </c>
+      <c r="F82">
+        <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
+      </c>
+      <c r="G82">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F82))),"",F82*$D$33)</f>
+      </c>
+      <c r="H82" s="125">
+        <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
+      </c>
+      <c r="I82" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H82))),"",H82*$D$33)</f>
+      </c>
+      <c r="J82" s="125">
+        <f>IF(E82="","",MAX(0,E82-$G$44))</f>
+      </c>
+      <c r="K82" s="125">
+        <f>IF(D82="","",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L82" s="125">
+        <f>IF(K82="","",$J$41+K82)</f>
+      </c>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83"/>
+      <c r="B83"/>
+      <c r="C83" t="n">
         <v>0.915</v>
       </c>
-      <c r="D73" s="82">
-        <f>IF(C73&lt;$G$23,$D$35*(1-C73)-$G$41,"")</f>
-      </c>
-      <c r="E73" s="27">
-        <f>IF(D73="","",$G$40/D73)</f>
-      </c>
-      <c r="F73" s="85">
-        <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
-      </c>
-      <c r="G73" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F73))),"",F73*$D$24)</f>
-      </c>
-      <c r="H73" s="27">
-        <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$35)</f>
-      </c>
-      <c r="I73" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H73))),"",H73*$D$24)</f>
-      </c>
-      <c r="J73" s="27">
-        <f>IF(E73="","",MAX(0,E73-$G$34))</f>
-      </c>
-      <c r="K73" s="27">
-        <f>IF(D73="","",$G$40/($G$38-MAX(0,(C73-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L73" s="91">
-        <f>IF(K73="","",$J$31+K73)</f>
-      </c>
-    </row>
-    <row r="74" ht="20" customHeight="1">
-      <c r="A74" s="2"/>
-      <c r="B74" s="2"/>
-      <c r="C74" s="79" t="n">
+      <c r="D83" s="125">
+        <f>IF(C83&lt;$G$32,$D$45*(1-C83)-$G$51,"")</f>
+      </c>
+      <c r="E83" s="125">
+        <f>IF(D83="","",$G$50/D83)</f>
+      </c>
+      <c r="F83">
+        <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
+      </c>
+      <c r="G83">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F83))),"",F83*$D$33)</f>
+      </c>
+      <c r="H83" s="125">
+        <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
+      </c>
+      <c r="I83" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H83))),"",H83*$D$33)</f>
+      </c>
+      <c r="J83" s="125">
+        <f>IF(E83="","",MAX(0,E83-$G$44))</f>
+      </c>
+      <c r="K83" s="125">
+        <f>IF(D83="","",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L83" s="125">
+        <f>IF(K83="","",$J$41+K83)</f>
+      </c>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84"/>
+      <c r="B84"/>
+      <c r="C84" t="n">
         <v>0.918</v>
       </c>
-      <c r="D74" s="82">
-        <f>IF(C74&lt;$G$23,$D$35*(1-C74)-$G$41,"")</f>
-      </c>
-      <c r="E74" s="27">
-        <f>IF(D74="","",$G$40/D74)</f>
-      </c>
-      <c r="F74" s="85">
-        <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
-      </c>
-      <c r="G74" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F74))),"",F74*$D$24)</f>
-      </c>
-      <c r="H74" s="27">
-        <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$35)</f>
-      </c>
-      <c r="I74" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H74))),"",H74*$D$24)</f>
-      </c>
-      <c r="J74" s="27">
-        <f>IF(E74="","",MAX(0,E74-$G$34))</f>
-      </c>
-      <c r="K74" s="27">
-        <f>IF(D74="","",$G$40/($G$38-MAX(0,(C74-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L74" s="91">
-        <f>IF(K74="","",$J$31+K74)</f>
-      </c>
-    </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="A75" s="2"/>
-      <c r="B75" s="2"/>
-      <c r="C75" s="80" t="n">
+      <c r="D84" s="125">
+        <f>IF(C84&lt;$G$32,$D$45*(1-C84)-$G$51,"")</f>
+      </c>
+      <c r="E84" s="125">
+        <f>IF(D84="","",$G$50/D84)</f>
+      </c>
+      <c r="F84">
+        <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
+      </c>
+      <c r="G84">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F84))),"",F84*$D$33)</f>
+      </c>
+      <c r="H84" s="125">
+        <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
+      </c>
+      <c r="I84" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H84))),"",H84*$D$33)</f>
+      </c>
+      <c r="J84" s="125">
+        <f>IF(E84="","",MAX(0,E84-$G$44))</f>
+      </c>
+      <c r="K84" s="125">
+        <f>IF(D84="","",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L84" s="125">
+        <f>IF(K84="","",$J$41+K84)</f>
+      </c>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85"/>
+      <c r="B85"/>
+      <c r="C85" t="n">
         <v>0.9183673469387755</v>
       </c>
-      <c r="D75" s="83">
-        <f>IF(C75&lt;$G$23,$D$35*(1-C75)-$G$41,"")</f>
-      </c>
-      <c r="E75" s="28">
-        <f>IF(D75="","",$G$40/D75)</f>
-      </c>
-      <c r="F75" s="86">
-        <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
-      </c>
-      <c r="G75" s="86">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F75))),"",F75*$D$24)</f>
-      </c>
-      <c r="H75" s="28">
-        <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$35)</f>
-      </c>
-      <c r="I75" s="28">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H75))),"",H75*$D$24)</f>
-      </c>
-      <c r="J75" s="28">
-        <f>IF(E75="","",MAX(0,E75-$G$34))</f>
-      </c>
-      <c r="K75" s="28">
-        <f>IF(D75="","",$G$40/($G$38-MAX(0,(C75-$G$33)*$D$35)/(1-$G$32-$J$7))-$G$34)</f>
-      </c>
-      <c r="L75" s="92">
-        <f>IF(K75="","",$J$31+K75)</f>
-      </c>
-    </row>
-    <row r="76" ht="20" customHeight="1">
-      <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2"/>
-      <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
-      <c r="F76" s="2"/>
-      <c r="G76" s="2"/>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2"/>
-      <c r="J76" s="2"/>
-      <c r="K76" s="2"/>
-      <c r="L76" s="2"/>
-    </row>
-    <row r="77" ht="20" customHeight="1">
-      <c r="A77" s="2"/>
-      <c r="B77" s="2"/>
-      <c r="C77" s="2"/>
-      <c r="D77" s="2"/>
-      <c r="E77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
-      <c r="J77" s="2"/>
-      <c r="K77" s="2"/>
-      <c r="L77" s="2"/>
-    </row>
-    <row r="78" ht="24" customHeight="1">
-      <c r="A78" s="2"/>
-      <c r="B78" s="2"/>
-      <c r="C78" s="102" t="str">
+      <c r="D85" s="125">
+        <f>IF(C85&lt;$G$32,$D$45*(1-C85)-$G$51,"")</f>
+      </c>
+      <c r="E85" s="125">
+        <f>IF(D85="","",$G$50/D85)</f>
+      </c>
+      <c r="F85">
+        <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
+      </c>
+      <c r="G85">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F85))),"",F85*$D$33)</f>
+      </c>
+      <c r="H85" s="125">
+        <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$45)</f>
+      </c>
+      <c r="I85" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H85))),"",H85*$D$33)</f>
+      </c>
+      <c r="J85" s="125">
+        <f>IF(E85="","",MAX(0,E85-$G$44))</f>
+      </c>
+      <c r="K85" s="125">
+        <f>IF(D85="","",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+      </c>
+      <c r="L85" s="125">
+        <f>IF(K85="","",$J$41+K85)</f>
+      </c>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86"/>
+      <c r="B86"/>
+      <c r="C86"/>
+      <c r="D86"/>
+      <c r="E86"/>
+      <c r="F86"/>
+      <c r="G86"/>
+      <c r="H86"/>
+      <c r="I86"/>
+      <c r="J86"/>
+      <c r="K86"/>
+      <c r="L86"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87"/>
+      <c r="B87"/>
+      <c r="C87"/>
+      <c r="D87"/>
+      <c r="E87"/>
+      <c r="F87"/>
+      <c r="G87"/>
+      <c r="H87"/>
+      <c r="I87"/>
+      <c r="J87"/>
+      <c r="K87"/>
+      <c r="L87"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88"/>
+      <c r="B88"/>
+      <c r="C88" t="str">
         <v>外盘回落参考</v>
       </c>
-      <c r="D78" s="102"/>
-      <c r="E78" s="102"/>
-      <c r="F78" s="102"/>
-      <c r="G78" s="102"/>
-      <c r="H78" s="102"/>
-      <c r="I78" s="102"/>
-      <c r="J78" s="102"/>
-      <c r="K78" s="102"/>
-      <c r="L78" s="102"/>
-    </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="2"/>
-      <c r="B79" s="2"/>
-      <c r="C79" s="77" t="str">
+      <c r="D88"/>
+      <c r="E88"/>
+      <c r="F88"/>
+      <c r="G88"/>
+      <c r="H88"/>
+      <c r="I88"/>
+      <c r="J88"/>
+      <c r="K88"/>
+      <c r="L88"/>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89"/>
+      <c r="B89"/>
+      <c r="C89" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D79" s="77" t="str">
+      <c r="D89" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E79" s="77" t="str">
+      <c r="E89" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F79" s="77" t="str">
+      <c r="F89" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G79" s="77" t="str">
+      <c r="G89" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H79" s="77" t="str">
+      <c r="H89" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I79" s="77" t="str">
+      <c r="I89" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J79" s="77" t="str">
+      <c r="J89" t="str">
         <v>较毕业点回撤</v>
       </c>
-      <c r="K79" s="77" t="str"/>
-      <c r="L79" s="77" t="str"/>
-    </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="2"/>
-      <c r="B80" s="2"/>
-      <c r="C80" s="97" t="n">
+      <c r="K89" t="str"/>
+      <c r="L89" t="str"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90"/>
+      <c r="B90"/>
+      <c r="C90" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="D80" s="98">
-        <f>$D$35*(1-C80)-$G$41</f>
-      </c>
-      <c r="E80" s="99">
-        <f>$G$40/D80</f>
-      </c>
-      <c r="F80" s="100">
-        <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
-      </c>
-      <c r="G80" s="100">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F80))),"",F80*$D$24)</f>
-      </c>
-      <c r="H80" s="99">
-        <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$35)</f>
-      </c>
-      <c r="I80" s="99">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H80))),"",H80*$D$24)</f>
-      </c>
-      <c r="J80" s="97">
-        <f>IF($H$80&gt;0,1-H80/$H$80,0)</f>
-      </c>
-      <c r="K80" s="99"/>
-      <c r="L80" s="99"/>
-    </row>
-    <row r="81" ht="20" customHeight="1">
-      <c r="A81" s="2"/>
-      <c r="B81" s="2"/>
-      <c r="C81" s="79" t="n">
+      <c r="D90" s="125">
+        <f>$D$45*(1-C90)-$G$51</f>
+      </c>
+      <c r="E90" s="125">
+        <f>$G$50/D90</f>
+      </c>
+      <c r="F90">
+        <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
+      </c>
+      <c r="G90">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F90))),"",F90*$D$33)</f>
+      </c>
+      <c r="H90" s="125">
+        <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
+      </c>
+      <c r="I90" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H90))),"",H90*$D$33)</f>
+      </c>
+      <c r="J90">
+        <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
+      </c>
+      <c r="K90"/>
+      <c r="L90"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91"/>
+      <c r="B91"/>
+      <c r="C91" t="n">
         <v>0.7</v>
       </c>
-      <c r="D81" s="82">
-        <f>$D$35*(1-C81)-$G$41</f>
-      </c>
-      <c r="E81" s="27">
-        <f>$G$40/D81</f>
-      </c>
-      <c r="F81" s="85">
-        <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
-      </c>
-      <c r="G81" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F81))),"",F81*$D$24)</f>
-      </c>
-      <c r="H81" s="27">
-        <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$35)</f>
-      </c>
-      <c r="I81" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H81))),"",H81*$D$24)</f>
-      </c>
-      <c r="J81" s="79">
-        <f>IF($H$80&gt;0,1-H81/$H$80,0)</f>
-      </c>
-      <c r="K81" s="27"/>
-      <c r="L81" s="27"/>
-    </row>
-    <row r="82" ht="20" customHeight="1">
-      <c r="A82" s="2"/>
-      <c r="B82" s="2"/>
-      <c r="C82" s="79" t="n">
+      <c r="D91" s="125">
+        <f>$D$45*(1-C91)-$G$51</f>
+      </c>
+      <c r="E91" s="125">
+        <f>$G$50/D91</f>
+      </c>
+      <c r="F91">
+        <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
+      </c>
+      <c r="G91">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F91))),"",F91*$D$33)</f>
+      </c>
+      <c r="H91" s="125">
+        <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
+      </c>
+      <c r="I91" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H91))),"",H91*$D$33)</f>
+      </c>
+      <c r="J91">
+        <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
+      </c>
+      <c r="K91"/>
+      <c r="L91"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92"/>
+      <c r="B92"/>
+      <c r="C92" t="n">
         <v>0.6</v>
       </c>
-      <c r="D82" s="82">
-        <f>$D$35*(1-C82)-$G$41</f>
-      </c>
-      <c r="E82" s="27">
-        <f>$G$40/D82</f>
-      </c>
-      <c r="F82" s="85">
-        <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
-      </c>
-      <c r="G82" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F82))),"",F82*$D$24)</f>
-      </c>
-      <c r="H82" s="27">
-        <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$35)</f>
-      </c>
-      <c r="I82" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H82))),"",H82*$D$24)</f>
-      </c>
-      <c r="J82" s="79">
-        <f>IF($H$80&gt;0,1-H82/$H$80,0)</f>
-      </c>
-      <c r="K82" s="27"/>
-      <c r="L82" s="27"/>
-    </row>
-    <row r="83" ht="20" customHeight="1">
-      <c r="A83" s="2"/>
-      <c r="B83" s="2"/>
-      <c r="C83" s="79" t="n">
+      <c r="D92" s="125">
+        <f>$D$45*(1-C92)-$G$51</f>
+      </c>
+      <c r="E92" s="125">
+        <f>$G$50/D92</f>
+      </c>
+      <c r="F92">
+        <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
+      </c>
+      <c r="G92">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F92))),"",F92*$D$33)</f>
+      </c>
+      <c r="H92" s="125">
+        <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
+      </c>
+      <c r="I92" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H92))),"",H92*$D$33)</f>
+      </c>
+      <c r="J92">
+        <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
+      </c>
+      <c r="K92"/>
+      <c r="L92"/>
+    </row>
+    <row r="93" ht="20" customHeight="1">
+      <c r="A93"/>
+      <c r="B93"/>
+      <c r="C93" t="n">
         <v>0.5</v>
       </c>
-      <c r="D83" s="82">
-        <f>$D$35*(1-C83)-$G$41</f>
-      </c>
-      <c r="E83" s="27">
-        <f>$G$40/D83</f>
-      </c>
-      <c r="F83" s="85">
-        <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
-      </c>
-      <c r="G83" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F83))),"",F83*$D$24)</f>
-      </c>
-      <c r="H83" s="27">
-        <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$35)</f>
-      </c>
-      <c r="I83" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H83))),"",H83*$D$24)</f>
-      </c>
-      <c r="J83" s="79">
-        <f>IF($H$80&gt;0,1-H83/$H$80,0)</f>
-      </c>
-      <c r="K83" s="27"/>
-      <c r="L83" s="27"/>
-    </row>
-    <row r="84" ht="20" customHeight="1">
-      <c r="A84" s="2"/>
-      <c r="B84" s="2"/>
-      <c r="C84" s="79" t="n">
+      <c r="D93" s="125">
+        <f>$D$45*(1-C93)-$G$51</f>
+      </c>
+      <c r="E93" s="125">
+        <f>$G$50/D93</f>
+      </c>
+      <c r="F93">
+        <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
+      </c>
+      <c r="G93">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F93))),"",F93*$D$33)</f>
+      </c>
+      <c r="H93" s="125">
+        <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
+      </c>
+      <c r="I93" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H93))),"",H93*$D$33)</f>
+      </c>
+      <c r="J93">
+        <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
+      </c>
+      <c r="K93"/>
+      <c r="L93"/>
+    </row>
+    <row r="94" ht="20" customHeight="1">
+      <c r="A94"/>
+      <c r="B94"/>
+      <c r="C94" t="n">
         <v>0.4</v>
       </c>
-      <c r="D84" s="82">
-        <f>$D$35*(1-C84)-$G$41</f>
-      </c>
-      <c r="E84" s="27">
-        <f>$G$40/D84</f>
-      </c>
-      <c r="F84" s="85">
-        <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
-      </c>
-      <c r="G84" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F84))),"",F84*$D$24)</f>
-      </c>
-      <c r="H84" s="27">
-        <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$35)</f>
-      </c>
-      <c r="I84" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H84))),"",H84*$D$24)</f>
-      </c>
-      <c r="J84" s="79">
-        <f>IF($H$80&gt;0,1-H84/$H$80,0)</f>
-      </c>
-      <c r="K84" s="27"/>
-      <c r="L84" s="27"/>
-    </row>
-    <row r="85" ht="20" customHeight="1">
-      <c r="A85" s="2"/>
-      <c r="B85" s="2"/>
-      <c r="C85" s="79" t="n">
+      <c r="D94" s="125">
+        <f>$D$45*(1-C94)-$G$51</f>
+      </c>
+      <c r="E94" s="125">
+        <f>$G$50/D94</f>
+      </c>
+      <c r="F94">
+        <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
+      </c>
+      <c r="G94">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F94))),"",F94*$D$33)</f>
+      </c>
+      <c r="H94" s="125">
+        <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
+      </c>
+      <c r="I94" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H94))),"",H94*$D$33)</f>
+      </c>
+      <c r="J94">
+        <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
+      </c>
+      <c r="K94"/>
+      <c r="L94"/>
+    </row>
+    <row r="95" ht="20" customHeight="1">
+      <c r="A95"/>
+      <c r="B95"/>
+      <c r="C95" t="n">
         <v>0.3</v>
       </c>
-      <c r="D85" s="82">
-        <f>$D$35*(1-C85)-$G$41</f>
-      </c>
-      <c r="E85" s="27">
-        <f>$G$40/D85</f>
-      </c>
-      <c r="F85" s="85">
-        <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
-      </c>
-      <c r="G85" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F85))),"",F85*$D$24)</f>
-      </c>
-      <c r="H85" s="27">
-        <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$35)</f>
-      </c>
-      <c r="I85" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H85))),"",H85*$D$24)</f>
-      </c>
-      <c r="J85" s="79">
-        <f>IF($H$80&gt;0,1-H85/$H$80,0)</f>
-      </c>
-      <c r="K85" s="27"/>
-      <c r="L85" s="27"/>
-    </row>
-    <row r="86" ht="20" customHeight="1">
-      <c r="A86" s="2"/>
-      <c r="B86" s="2"/>
-      <c r="C86" s="79" t="n">
+      <c r="D95" s="125">
+        <f>$D$45*(1-C95)-$G$51</f>
+      </c>
+      <c r="E95" s="125">
+        <f>$G$50/D95</f>
+      </c>
+      <c r="F95">
+        <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
+      </c>
+      <c r="G95">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F95))),"",F95*$D$33)</f>
+      </c>
+      <c r="H95" s="125">
+        <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
+      </c>
+      <c r="I95" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H95))),"",H95*$D$33)</f>
+      </c>
+      <c r="J95">
+        <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
+      </c>
+      <c r="K95"/>
+      <c r="L95"/>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="A96"/>
+      <c r="B96"/>
+      <c r="C96" t="n">
         <v>0.2</v>
       </c>
-      <c r="D86" s="82">
-        <f>$D$35*(1-C86)-$G$41</f>
-      </c>
-      <c r="E86" s="27">
-        <f>$G$40/D86</f>
-      </c>
-      <c r="F86" s="85">
-        <f>IF(OR(D86="",E86=""),"",E86/D86)</f>
-      </c>
-      <c r="G86" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F86))),"",F86*$D$24)</f>
-      </c>
-      <c r="H86" s="27">
-        <f>IF(NOT(ISNUMBER(F86)),"",F86*$D$35)</f>
-      </c>
-      <c r="I86" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H86))),"",H86*$D$24)</f>
-      </c>
-      <c r="J86" s="79">
-        <f>IF($H$80&gt;0,1-H86/$H$80,0)</f>
-      </c>
-      <c r="K86" s="27"/>
-      <c r="L86" s="27"/>
-    </row>
-    <row r="87" ht="20" customHeight="1">
-      <c r="A87" s="2"/>
-      <c r="B87" s="2"/>
-      <c r="C87" s="79" t="n">
+      <c r="D96" s="125">
+        <f>$D$45*(1-C96)-$G$51</f>
+      </c>
+      <c r="E96" s="125">
+        <f>$G$50/D96</f>
+      </c>
+      <c r="F96">
+        <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
+      </c>
+      <c r="G96">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F96))),"",F96*$D$33)</f>
+      </c>
+      <c r="H96" s="125">
+        <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
+      </c>
+      <c r="I96" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H96))),"",H96*$D$33)</f>
+      </c>
+      <c r="J96">
+        <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
+      </c>
+      <c r="K96"/>
+      <c r="L96"/>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97"/>
+      <c r="B97"/>
+      <c r="C97" t="n">
         <v>0.1</v>
       </c>
-      <c r="D87" s="82">
-        <f>$D$35*(1-C87)-$G$41</f>
-      </c>
-      <c r="E87" s="27">
-        <f>$G$40/D87</f>
-      </c>
-      <c r="F87" s="85">
-        <f>IF(OR(D87="",E87=""),"",E87/D87)</f>
-      </c>
-      <c r="G87" s="85">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F87))),"",F87*$D$24)</f>
-      </c>
-      <c r="H87" s="27">
-        <f>IF(NOT(ISNUMBER(F87)),"",F87*$D$35)</f>
-      </c>
-      <c r="I87" s="27">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H87))),"",H87*$D$24)</f>
-      </c>
-      <c r="J87" s="79">
-        <f>IF($H$80&gt;0,1-H87/$H$80,0)</f>
-      </c>
-      <c r="K87" s="27"/>
-      <c r="L87" s="27"/>
-    </row>
-    <row r="88" ht="20" customHeight="1">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
-      <c r="C88" s="80" t="n">
+      <c r="D97" s="125">
+        <f>$D$45*(1-C97)-$G$51</f>
+      </c>
+      <c r="E97" s="125">
+        <f>$G$50/D97</f>
+      </c>
+      <c r="F97">
+        <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
+      </c>
+      <c r="G97">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F97))),"",F97*$D$33)</f>
+      </c>
+      <c r="H97" s="125">
+        <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
+      </c>
+      <c r="I97" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H97))),"",H97*$D$33)</f>
+      </c>
+      <c r="J97">
+        <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
+      </c>
+      <c r="K97"/>
+      <c r="L97"/>
+    </row>
+    <row r="98" ht="20" customHeight="1">
+      <c r="A98"/>
+      <c r="B98"/>
+      <c r="C98" t="n">
         <v>0</v>
       </c>
-      <c r="D88" s="83">
-        <f>$D$35*(1-C88)-$G$41</f>
-      </c>
-      <c r="E88" s="28">
-        <f>$G$40/D88</f>
-      </c>
-      <c r="F88" s="86">
-        <f>IF(OR(D88="",E88=""),"",E88/D88)</f>
-      </c>
-      <c r="G88" s="86">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(F88))),"",F88*$D$24)</f>
-      </c>
-      <c r="H88" s="28">
-        <f>IF(NOT(ISNUMBER(F88)),"",F88*$D$35)</f>
-      </c>
-      <c r="I88" s="28">
-        <f>IF(OR($D$24="",NOT(ISNUMBER(H88))),"",H88*$D$24)</f>
-      </c>
-      <c r="J88" s="80">
-        <f>IF($H$80&gt;0,1-H88/$H$80,0)</f>
-      </c>
-      <c r="K88" s="103" t="str">
+      <c r="D98" s="125">
+        <f>$D$45*(1-C98)-$G$51</f>
+      </c>
+      <c r="E98" s="125">
+        <f>$G$50/D98</f>
+      </c>
+      <c r="F98">
+        <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
+      </c>
+      <c r="G98">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(F98))),"",F98*$D$33)</f>
+      </c>
+      <c r="H98" s="125">
+        <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
+      </c>
+      <c r="I98" s="125">
+        <f>IF(OR($D$33="",NOT(ISNUMBER(H98))),"",H98*$D$33)</f>
+      </c>
+      <c r="J98">
+        <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
+      </c>
+      <c r="K98" t="str">
         <v>沉没成本 / Quote</v>
       </c>
-      <c r="L88" s="28">
-        <f>E88</f>
-      </c>
-    </row>
-    <row r="89" ht="20" customHeight="1">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
-      <c r="C89" s="2"/>
-      <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
-      <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
-      <c r="H89" s="2"/>
-      <c r="I89" s="2"/>
-      <c r="J89" s="2"/>
-      <c r="K89" s="2"/>
-      <c r="L89" s="2"/>
-    </row>
-    <row r="90" ht="20" customHeight="1">
-      <c r="A90" s="2"/>
-      <c r="B90" s="2"/>
-      <c r="C90" s="2"/>
-      <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
-    </row>
-    <row r="91" ht="20" customHeight="1">
-      <c r="A91" s="2"/>
-      <c r="B91" s="2"/>
-      <c r="C91" s="2"/>
-      <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
-      <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-    </row>
-    <row r="92" ht="20" customHeight="1">
-      <c r="A92" s="2"/>
-      <c r="B92" s="2"/>
-      <c r="C92" s="2"/>
-      <c r="D92" s="2"/>
-      <c r="E92" s="2"/>
-      <c r="F92" s="2"/>
-      <c r="G92" s="2"/>
-      <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
-    </row>
-    <row r="93" ht="20" customHeight="1">
-      <c r="A93" s="2"/>
-      <c r="B93" s="2"/>
-      <c r="C93" s="2"/>
-      <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
-      <c r="H93" s="2"/>
-      <c r="I93" s="2"/>
-      <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2"/>
-    </row>
-    <row r="94" ht="20" customHeight="1">
-      <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
-      <c r="C94" s="2"/>
-      <c r="D94" s="2"/>
-      <c r="E94" s="2"/>
-      <c r="F94" s="2"/>
-      <c r="G94" s="2"/>
-      <c r="H94" s="2"/>
-      <c r="I94" s="2"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="2"/>
-      <c r="L94" s="2"/>
-    </row>
-    <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="2"/>
-      <c r="F95" s="2"/>
-      <c r="G95" s="2"/>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
-    </row>
-    <row r="96" ht="20" customHeight="1">
-      <c r="A96" s="2"/>
-      <c r="B96" s="2"/>
-      <c r="C96" s="2"/>
-      <c r="D96" s="2"/>
-      <c r="E96" s="2"/>
-      <c r="F96" s="2"/>
-      <c r="G96" s="2"/>
-      <c r="H96" s="2"/>
-      <c r="I96" s="2"/>
-      <c r="J96" s="2"/>
-      <c r="K96" s="2"/>
-      <c r="L96" s="2"/>
-    </row>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="2"/>
-      <c r="B97" s="2"/>
-      <c r="C97" s="2"/>
-      <c r="D97" s="2"/>
-      <c r="E97" s="2"/>
-      <c r="F97" s="2"/>
-      <c r="G97" s="2"/>
-      <c r="H97" s="2"/>
-      <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
-      <c r="K97" s="2"/>
-      <c r="L97" s="2"/>
-    </row>
-    <row r="98" ht="20" customHeight="1">
-      <c r="A98" s="2"/>
-      <c r="B98" s="2"/>
-      <c r="C98" s="2"/>
-      <c r="D98" s="2"/>
-      <c r="E98" s="2"/>
-      <c r="F98" s="2"/>
-      <c r="G98" s="2"/>
-      <c r="H98" s="2"/>
-      <c r="I98" s="2"/>
-      <c r="J98" s="2"/>
-      <c r="K98" s="2"/>
-      <c r="L98" s="2"/>
+      <c r="L98">
+        <f>E98</f>
+      </c>
     </row>
     <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="2"/>
-      <c r="B99" s="2"/>
-      <c r="C99" s="2"/>
-      <c r="D99" s="2"/>
-      <c r="E99" s="2"/>
-      <c r="F99" s="2"/>
-      <c r="G99" s="2"/>
-      <c r="H99" s="2"/>
-      <c r="I99" s="2"/>
-      <c r="J99" s="2"/>
-      <c r="K99" s="2"/>
-      <c r="L99" s="2"/>
+      <c r="A99"/>
+      <c r="B99"/>
+      <c r="C99"/>
+      <c r="D99"/>
+      <c r="E99"/>
+      <c r="F99"/>
+      <c r="G99"/>
+      <c r="H99"/>
+      <c r="I99"/>
+      <c r="J99"/>
+      <c r="K99"/>
+      <c r="L99"/>
     </row>
     <row r="100" ht="20" customHeight="1">
-      <c r="A100" s="2"/>
-      <c r="B100" s="2"/>
-      <c r="C100" s="2"/>
-      <c r="D100" s="2"/>
-      <c r="E100" s="2"/>
-      <c r="F100" s="2"/>
-      <c r="G100" s="2"/>
-      <c r="H100" s="2"/>
-      <c r="I100" s="2"/>
-      <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
-      <c r="L100" s="2"/>
+      <c r="A100"/>
+      <c r="B100"/>
+      <c r="C100"/>
+      <c r="D100"/>
+      <c r="E100"/>
+      <c r="F100"/>
+      <c r="G100"/>
+      <c r="H100"/>
+      <c r="I100"/>
+      <c r="J100"/>
+      <c r="K100"/>
+      <c r="L100"/>
     </row>
     <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="2"/>
-      <c r="B101" s="2"/>
-      <c r="C101" s="2"/>
-      <c r="D101" s="2"/>
-      <c r="E101" s="2"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="2"/>
-      <c r="L101" s="2"/>
+      <c r="A101"/>
+      <c r="B101"/>
+      <c r="C101"/>
+      <c r="D101"/>
+      <c r="E101"/>
+      <c r="F101"/>
+      <c r="G101"/>
+      <c r="H101"/>
+      <c r="I101"/>
+      <c r="J101"/>
+      <c r="K101"/>
+      <c r="L101"/>
     </row>
     <row r="102" ht="20" customHeight="1">
-      <c r="A102" s="2"/>
-      <c r="B102" s="2"/>
-      <c r="C102" s="2"/>
-      <c r="D102" s="2"/>
-      <c r="E102" s="2"/>
-      <c r="F102" s="2"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
+      <c r="A102"/>
+      <c r="B102"/>
+      <c r="C102"/>
+      <c r="D102"/>
+      <c r="E102"/>
+      <c r="F102"/>
+      <c r="G102"/>
+      <c r="H102"/>
+      <c r="I102"/>
+      <c r="J102"/>
+      <c r="K102"/>
+      <c r="L102"/>
     </row>
     <row r="103" ht="20" customHeight="1">
-      <c r="A103" s="2"/>
-      <c r="B103" s="2"/>
-      <c r="C103" s="2"/>
-      <c r="D103" s="2"/>
-      <c r="E103" s="2"/>
-      <c r="F103" s="2"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
-      <c r="L103" s="2"/>
+      <c r="A103"/>
+      <c r="B103"/>
+      <c r="C103"/>
+      <c r="D103"/>
+      <c r="E103"/>
+      <c r="F103"/>
+      <c r="G103"/>
+      <c r="H103"/>
+      <c r="I103"/>
+      <c r="J103"/>
+      <c r="K103"/>
+      <c r="L103"/>
     </row>
     <row r="104" ht="20" customHeight="1">
-      <c r="A104" s="2"/>
-      <c r="B104" s="2"/>
-      <c r="C104" s="2"/>
-      <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="2"/>
-      <c r="L104" s="2"/>
+      <c r="A104"/>
+      <c r="B104"/>
+      <c r="C104"/>
+      <c r="D104"/>
+      <c r="E104"/>
+      <c r="F104"/>
+      <c r="G104"/>
+      <c r="H104"/>
+      <c r="I104"/>
+      <c r="J104"/>
+      <c r="K104"/>
+      <c r="L104"/>
     </row>
     <row r="105" ht="20" customHeight="1">
-      <c r="A105" s="2"/>
-      <c r="B105" s="2"/>
-      <c r="C105" s="2"/>
-      <c r="D105" s="2"/>
-      <c r="E105" s="2"/>
-      <c r="F105" s="2"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-      <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
+      <c r="A105"/>
+      <c r="B105"/>
+      <c r="C105"/>
+      <c r="D105"/>
+      <c r="E105"/>
+      <c r="F105"/>
+      <c r="G105"/>
+      <c r="H105"/>
+      <c r="I105"/>
+      <c r="J105"/>
+      <c r="K105"/>
+      <c r="L105"/>
     </row>
     <row r="106" ht="20" customHeight="1">
-      <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
-      <c r="C106" s="2"/>
-      <c r="D106" s="2"/>
-      <c r="E106" s="2"/>
-      <c r="F106" s="2"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
-      <c r="K106" s="2"/>
-      <c r="L106" s="2"/>
+      <c r="A106"/>
+      <c r="B106"/>
+      <c r="C106"/>
+      <c r="D106"/>
+      <c r="E106"/>
+      <c r="F106"/>
+      <c r="G106"/>
+      <c r="H106"/>
+      <c r="I106"/>
+      <c r="J106"/>
+      <c r="K106"/>
+      <c r="L106"/>
     </row>
     <row r="107" ht="20" customHeight="1">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="2"/>
-      <c r="L107" s="2"/>
+      <c r="A107"/>
+      <c r="B107"/>
+      <c r="C107"/>
+      <c r="D107"/>
+      <c r="E107"/>
+      <c r="F107"/>
+      <c r="G107"/>
+      <c r="H107"/>
+      <c r="I107"/>
+      <c r="J107"/>
+      <c r="K107"/>
+      <c r="L107"/>
     </row>
     <row r="108" ht="20" customHeight="1">
-      <c r="A108" s="2"/>
-      <c r="B108" s="2"/>
-      <c r="C108" s="2"/>
-      <c r="D108" s="2"/>
-      <c r="E108" s="2"/>
-      <c r="F108" s="2"/>
-      <c r="G108" s="2"/>
-      <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
+      <c r="A108"/>
+      <c r="B108"/>
+      <c r="C108"/>
+      <c r="D108"/>
+      <c r="E108"/>
+      <c r="F108"/>
+      <c r="G108"/>
+      <c r="H108"/>
+      <c r="I108"/>
+      <c r="J108"/>
+      <c r="K108"/>
+      <c r="L108"/>
     </row>
     <row r="109" ht="20" customHeight="1">
-      <c r="A109" s="2"/>
-      <c r="B109" s="2"/>
-      <c r="C109" s="2"/>
-      <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
-      <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="2"/>
-      <c r="K109" s="2"/>
-      <c r="L109" s="2"/>
+      <c r="A109"/>
+      <c r="B109"/>
+      <c r="C109"/>
+      <c r="D109"/>
+      <c r="E109"/>
+      <c r="F109"/>
+      <c r="G109"/>
+      <c r="H109"/>
+      <c r="I109"/>
+      <c r="J109"/>
+      <c r="K109"/>
+      <c r="L109"/>
     </row>
     <row r="110" ht="20" customHeight="1">
-      <c r="A110" s="2"/>
-      <c r="B110" s="2"/>
-      <c r="C110" s="2"/>
-      <c r="D110" s="2"/>
-      <c r="E110" s="2"/>
-      <c r="F110" s="2"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
-      <c r="K110" s="2"/>
-      <c r="L110" s="2"/>
+      <c r="A110"/>
+      <c r="B110"/>
+      <c r="C110"/>
+      <c r="D110"/>
+      <c r="E110"/>
+      <c r="F110"/>
+      <c r="G110"/>
+      <c r="H110"/>
+      <c r="I110"/>
+      <c r="J110"/>
+      <c r="K110"/>
+      <c r="L110"/>
     </row>
     <row r="111" ht="20" customHeight="1">
-      <c r="A111" s="2"/>
-      <c r="B111" s="2"/>
-      <c r="C111" s="2"/>
-      <c r="D111" s="2"/>
-      <c r="E111" s="2"/>
-      <c r="F111" s="2"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-      <c r="K111" s="2"/>
-      <c r="L111" s="2"/>
+      <c r="A111"/>
+      <c r="B111"/>
+      <c r="C111"/>
+      <c r="D111"/>
+      <c r="E111"/>
+      <c r="F111"/>
+      <c r="G111"/>
+      <c r="H111"/>
+      <c r="I111"/>
+      <c r="J111"/>
+      <c r="K111"/>
+      <c r="L111"/>
     </row>
     <row r="112" ht="20" customHeight="1">
-      <c r="A112" s="2"/>
-      <c r="B112" s="2"/>
-      <c r="C112" s="2"/>
-      <c r="D112" s="2"/>
-      <c r="E112" s="2"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-      <c r="J112" s="2"/>
-      <c r="K112" s="2"/>
-      <c r="L112" s="2"/>
+      <c r="A112"/>
+      <c r="B112"/>
+      <c r="C112"/>
+      <c r="D112"/>
+      <c r="E112"/>
+      <c r="F112"/>
+      <c r="G112"/>
+      <c r="H112"/>
+      <c r="I112"/>
+      <c r="J112"/>
+      <c r="K112"/>
+      <c r="L112"/>
     </row>
     <row r="113" ht="20" customHeight="1">
-      <c r="A113" s="2"/>
-      <c r="B113" s="2"/>
-      <c r="C113" s="2"/>
-      <c r="D113" s="2"/>
-      <c r="E113" s="2"/>
-      <c r="F113" s="2"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-      <c r="K113" s="2"/>
-      <c r="L113" s="2"/>
+      <c r="A113"/>
+      <c r="B113"/>
+      <c r="C113"/>
+      <c r="D113"/>
+      <c r="E113"/>
+      <c r="F113"/>
+      <c r="G113"/>
+      <c r="H113"/>
+      <c r="I113"/>
+      <c r="J113"/>
+      <c r="K113"/>
+      <c r="L113"/>
     </row>
     <row r="114" ht="20" customHeight="1">
-      <c r="A114" s="2"/>
-      <c r="B114" s="2"/>
-      <c r="C114" s="2"/>
-      <c r="D114" s="2"/>
-      <c r="E114" s="2"/>
-      <c r="F114" s="2"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
-      <c r="L114" s="2"/>
+      <c r="A114"/>
+      <c r="B114"/>
+      <c r="C114"/>
+      <c r="D114"/>
+      <c r="E114"/>
+      <c r="F114"/>
+      <c r="G114"/>
+      <c r="H114"/>
+      <c r="I114"/>
+      <c r="J114"/>
+      <c r="K114"/>
+      <c r="L114"/>
     </row>
     <row r="115" ht="20" customHeight="1">
-      <c r="A115" s="2"/>
-      <c r="B115" s="2"/>
-      <c r="C115" s="2"/>
-      <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
-      <c r="J115" s="2"/>
-      <c r="K115" s="2"/>
-      <c r="L115" s="2"/>
+      <c r="A115"/>
+      <c r="B115"/>
+      <c r="C115"/>
+      <c r="D115"/>
+      <c r="E115"/>
+      <c r="F115"/>
+      <c r="G115"/>
+      <c r="H115"/>
+      <c r="I115"/>
+      <c r="J115"/>
+      <c r="K115"/>
+      <c r="L115"/>
     </row>
     <row r="116" ht="20" customHeight="1">
-      <c r="A116" s="2"/>
-      <c r="B116" s="2"/>
-      <c r="C116" s="2"/>
-      <c r="D116" s="2"/>
-      <c r="E116" s="2"/>
-      <c r="F116" s="2"/>
-      <c r="G116" s="2"/>
-      <c r="H116" s="2"/>
-      <c r="I116" s="2"/>
-      <c r="J116" s="2"/>
-      <c r="K116" s="2"/>
-      <c r="L116" s="2"/>
+      <c r="A116"/>
+      <c r="B116"/>
+      <c r="C116"/>
+      <c r="D116"/>
+      <c r="E116"/>
+      <c r="F116"/>
+      <c r="G116"/>
+      <c r="H116"/>
+      <c r="I116"/>
+      <c r="J116"/>
+      <c r="K116"/>
+      <c r="L116"/>
     </row>
     <row r="117" ht="20" customHeight="1">
-      <c r="A117" s="2"/>
-      <c r="B117" s="2"/>
-      <c r="C117" s="2"/>
-      <c r="D117" s="2"/>
-      <c r="E117" s="2"/>
-      <c r="F117" s="2"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-      <c r="K117" s="2"/>
-      <c r="L117" s="2"/>
+      <c r="A117"/>
+      <c r="B117"/>
+      <c r="C117"/>
+      <c r="D117"/>
+      <c r="E117"/>
+      <c r="F117"/>
+      <c r="G117"/>
+      <c r="H117"/>
+      <c r="I117"/>
+      <c r="J117"/>
+      <c r="K117"/>
+      <c r="L117"/>
     </row>
     <row r="118" ht="20" customHeight="1">
-      <c r="A118" s="2"/>
-      <c r="B118" s="2"/>
-      <c r="C118" s="2"/>
-      <c r="D118" s="2"/>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-      <c r="K118" s="2"/>
-      <c r="L118" s="2"/>
+      <c r="A118"/>
+      <c r="B118"/>
+      <c r="C118"/>
+      <c r="D118"/>
+      <c r="E118"/>
+      <c r="F118"/>
+      <c r="G118"/>
+      <c r="H118"/>
+      <c r="I118"/>
+      <c r="J118"/>
+      <c r="K118"/>
+      <c r="L118"/>
     </row>
     <row r="119" ht="20" customHeight="1">
-      <c r="A119" s="2"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
-      <c r="J119" s="2"/>
-      <c r="K119" s="2"/>
-      <c r="L119" s="2"/>
+      <c r="A119"/>
+      <c r="B119"/>
+      <c r="C119"/>
+      <c r="D119"/>
+      <c r="E119"/>
+      <c r="F119"/>
+      <c r="G119"/>
+      <c r="H119"/>
+      <c r="I119"/>
+      <c r="J119"/>
+      <c r="K119"/>
+      <c r="L119"/>
     </row>
     <row r="120" ht="20" customHeight="1">
-      <c r="A120" s="2"/>
-      <c r="B120" s="2"/>
-      <c r="C120" s="2"/>
-      <c r="D120" s="2"/>
-      <c r="E120" s="2"/>
-      <c r="F120" s="2"/>
-      <c r="G120" s="2"/>
-      <c r="H120" s="2"/>
-      <c r="I120" s="2"/>
-      <c r="J120" s="2"/>
-      <c r="K120" s="2"/>
-      <c r="L120" s="2"/>
+      <c r="A120"/>
+      <c r="B120"/>
+      <c r="C120"/>
+      <c r="D120"/>
+      <c r="E120"/>
+      <c r="F120"/>
+      <c r="G120"/>
+      <c r="H120"/>
+      <c r="I120"/>
+      <c r="J120"/>
+      <c r="K120"/>
+      <c r="L120"/>
     </row>
     <row r="121" ht="20" customHeight="1">
-      <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
-      <c r="C121" s="2"/>
-      <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
-      <c r="F121" s="2"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
-      <c r="J121" s="2"/>
-      <c r="K121" s="2"/>
-      <c r="L121" s="2"/>
+      <c r="A121"/>
+      <c r="B121"/>
+      <c r="C121"/>
+      <c r="D121"/>
+      <c r="E121"/>
+      <c r="F121"/>
+      <c r="G121"/>
+      <c r="H121"/>
+      <c r="I121"/>
+      <c r="J121"/>
+      <c r="K121"/>
+      <c r="L121"/>
     </row>
     <row r="122" ht="20" customHeight="1">
-      <c r="A122" s="2"/>
-      <c r="B122" s="2"/>
-      <c r="C122" s="2"/>
-      <c r="D122" s="2"/>
-      <c r="E122" s="2"/>
-      <c r="F122" s="2"/>
-      <c r="G122" s="2"/>
-      <c r="H122" s="2"/>
-      <c r="I122" s="2"/>
-      <c r="J122" s="2"/>
-      <c r="K122" s="2"/>
-      <c r="L122" s="2"/>
+      <c r="A122"/>
+      <c r="B122"/>
+      <c r="C122"/>
+      <c r="D122"/>
+      <c r="E122"/>
+      <c r="F122"/>
+      <c r="G122"/>
+      <c r="H122"/>
+      <c r="I122"/>
+      <c r="J122"/>
+      <c r="K122"/>
+      <c r="L122"/>
     </row>
     <row r="123" ht="20" customHeight="1">
-      <c r="A123" s="2"/>
-      <c r="B123" s="2"/>
-      <c r="C123" s="2"/>
-      <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="2"/>
-      <c r="I123" s="2"/>
-      <c r="J123" s="2"/>
-      <c r="K123" s="2"/>
-      <c r="L123" s="2"/>
+      <c r="A123"/>
+      <c r="B123"/>
+      <c r="C123"/>
+      <c r="D123"/>
+      <c r="E123"/>
+      <c r="F123"/>
+      <c r="G123"/>
+      <c r="H123"/>
+      <c r="I123"/>
+      <c r="J123"/>
+      <c r="K123"/>
+      <c r="L123"/>
     </row>
     <row r="124" ht="20" customHeight="1">
-      <c r="A124" s="2"/>
-      <c r="B124" s="2"/>
-      <c r="C124" s="2"/>
-      <c r="D124" s="2"/>
-      <c r="E124" s="2"/>
-      <c r="F124" s="2"/>
-      <c r="G124" s="2"/>
-      <c r="H124" s="2"/>
-      <c r="I124" s="2"/>
-      <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
-      <c r="L124" s="2"/>
+      <c r="A124"/>
+      <c r="B124"/>
+      <c r="C124"/>
+      <c r="D124"/>
+      <c r="E124"/>
+      <c r="F124"/>
+      <c r="G124"/>
+      <c r="H124"/>
+      <c r="I124"/>
+      <c r="J124"/>
+      <c r="K124"/>
+      <c r="L124"/>
     </row>
     <row r="125" ht="20" customHeight="1">
-      <c r="A125" s="2"/>
-      <c r="B125" s="2"/>
-      <c r="C125" s="2"/>
-      <c r="D125" s="2"/>
-      <c r="E125" s="2"/>
-      <c r="F125" s="2"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
-      <c r="J125" s="2"/>
-      <c r="K125" s="2"/>
-      <c r="L125" s="2"/>
+      <c r="A125"/>
+      <c r="B125"/>
+      <c r="C125"/>
+      <c r="D125"/>
+      <c r="E125"/>
+      <c r="F125"/>
+      <c r="G125"/>
+      <c r="H125"/>
+      <c r="I125"/>
+      <c r="J125"/>
+      <c r="K125"/>
+      <c r="L125"/>
     </row>
     <row r="126" ht="20" customHeight="1">
-      <c r="A126" s="2"/>
-      <c r="B126" s="2"/>
-      <c r="C126" s="2"/>
-      <c r="D126" s="2"/>
-      <c r="E126" s="2"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="2"/>
-      <c r="J126" s="2"/>
-      <c r="K126" s="2"/>
-      <c r="L126" s="2"/>
+      <c r="A126"/>
+      <c r="B126"/>
+      <c r="C126"/>
+      <c r="D126"/>
+      <c r="E126"/>
+      <c r="F126"/>
+      <c r="G126"/>
+      <c r="H126"/>
+      <c r="I126"/>
+      <c r="J126"/>
+      <c r="K126"/>
+      <c r="L126"/>
     </row>
     <row r="127" ht="20" customHeight="1">
-      <c r="A127" s="2"/>
-      <c r="B127" s="2"/>
-      <c r="C127" s="2"/>
-      <c r="D127" s="2"/>
-      <c r="E127" s="2"/>
-      <c r="F127" s="2"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
-      <c r="L127" s="2"/>
+      <c r="A127"/>
+      <c r="B127"/>
+      <c r="C127"/>
+      <c r="D127"/>
+      <c r="E127"/>
+      <c r="F127"/>
+      <c r="G127"/>
+      <c r="H127"/>
+      <c r="I127"/>
+      <c r="J127"/>
+      <c r="K127"/>
+      <c r="L127"/>
     </row>
     <row r="128" ht="20" customHeight="1">
-      <c r="A128" s="2"/>
-      <c r="B128" s="2"/>
-      <c r="C128" s="2"/>
-      <c r="D128" s="2"/>
-      <c r="E128" s="2"/>
-      <c r="F128" s="2"/>
-      <c r="G128" s="2"/>
-      <c r="H128" s="2"/>
-      <c r="I128" s="2"/>
-      <c r="J128" s="2"/>
-      <c r="K128" s="2"/>
-      <c r="L128" s="2"/>
+      <c r="A128"/>
+      <c r="B128"/>
+      <c r="C128"/>
+      <c r="D128"/>
+      <c r="E128"/>
+      <c r="F128"/>
+      <c r="G128"/>
+      <c r="H128"/>
+      <c r="I128"/>
+      <c r="J128"/>
+      <c r="K128"/>
+      <c r="L128"/>
     </row>
     <row r="129" ht="20" customHeight="1">
-      <c r="A129" s="2"/>
-      <c r="B129" s="2"/>
-      <c r="C129" s="2"/>
-      <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
-      <c r="L129" s="2"/>
+      <c r="A129"/>
+      <c r="B129"/>
+      <c r="C129"/>
+      <c r="D129"/>
+      <c r="E129"/>
+      <c r="F129"/>
+      <c r="G129"/>
+      <c r="H129"/>
+      <c r="I129"/>
+      <c r="J129"/>
+      <c r="K129"/>
+      <c r="L129"/>
     </row>
     <row r="130" ht="20" customHeight="1">
-      <c r="A130" s="2"/>
-      <c r="B130" s="2"/>
-      <c r="C130" s="2"/>
-      <c r="D130" s="2"/>
-      <c r="E130" s="2"/>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="2"/>
-      <c r="I130" s="2"/>
-      <c r="J130" s="2"/>
-      <c r="K130" s="2"/>
-      <c r="L130" s="2"/>
+      <c r="A130"/>
+      <c r="B130"/>
+      <c r="C130"/>
+      <c r="D130"/>
+      <c r="E130"/>
+      <c r="F130"/>
+      <c r="G130"/>
+      <c r="H130"/>
+      <c r="I130"/>
+      <c r="J130"/>
+      <c r="K130"/>
+      <c r="L130"/>
     </row>
     <row r="131" ht="20" customHeight="1">
-      <c r="A131" s="2"/>
-      <c r="B131" s="2"/>
-      <c r="C131" s="2"/>
-      <c r="D131" s="2"/>
-      <c r="E131" s="2"/>
-      <c r="F131" s="2"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
-      <c r="K131" s="2"/>
-      <c r="L131" s="2"/>
+      <c r="A131"/>
+      <c r="B131"/>
+      <c r="C131"/>
+      <c r="D131"/>
+      <c r="E131"/>
+      <c r="F131"/>
+      <c r="G131"/>
+      <c r="H131"/>
+      <c r="I131"/>
+      <c r="J131"/>
+      <c r="K131"/>
+      <c r="L131"/>
     </row>
     <row r="132" ht="20" customHeight="1">
-      <c r="A132" s="2"/>
-      <c r="B132" s="2"/>
-      <c r="C132" s="2"/>
-      <c r="D132" s="2"/>
-      <c r="E132" s="2"/>
-      <c r="F132" s="2"/>
-      <c r="G132" s="2"/>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
-      <c r="L132" s="2"/>
+      <c r="A132"/>
+      <c r="B132"/>
+      <c r="C132"/>
+      <c r="D132"/>
+      <c r="E132"/>
+      <c r="F132"/>
+      <c r="G132"/>
+      <c r="H132"/>
+      <c r="I132"/>
+      <c r="J132"/>
+      <c r="K132"/>
+      <c r="L132"/>
     </row>
     <row r="133" ht="20" customHeight="1">
-      <c r="A133" s="2"/>
-      <c r="B133" s="2"/>
-      <c r="C133" s="2"/>
-      <c r="D133" s="2"/>
-      <c r="E133" s="2"/>
-      <c r="F133" s="2"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
-      <c r="J133" s="2"/>
-      <c r="K133" s="2"/>
-      <c r="L133" s="2"/>
+      <c r="A133"/>
+      <c r="B133"/>
+      <c r="C133"/>
+      <c r="D133"/>
+      <c r="E133"/>
+      <c r="F133"/>
+      <c r="G133"/>
+      <c r="H133"/>
+      <c r="I133"/>
+      <c r="J133"/>
+      <c r="K133"/>
+      <c r="L133"/>
     </row>
     <row r="134" ht="20" customHeight="1">
-      <c r="A134" s="2"/>
-      <c r="B134" s="2"/>
-      <c r="C134" s="2"/>
-      <c r="D134" s="2"/>
-      <c r="E134" s="2"/>
-      <c r="F134" s="2"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
-      <c r="J134" s="2"/>
-      <c r="K134" s="2"/>
-      <c r="L134" s="2"/>
+      <c r="A134"/>
+      <c r="B134"/>
+      <c r="C134"/>
+      <c r="D134"/>
+      <c r="E134"/>
+      <c r="F134"/>
+      <c r="G134"/>
+      <c r="H134"/>
+      <c r="I134"/>
+      <c r="J134"/>
+      <c r="K134"/>
+      <c r="L134"/>
     </row>
     <row r="135" ht="20" customHeight="1">
-      <c r="A135" s="2"/>
-      <c r="B135" s="2"/>
-      <c r="C135" s="2"/>
-      <c r="D135" s="2"/>
-      <c r="E135" s="2"/>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
-      <c r="I135" s="2"/>
-      <c r="J135" s="2"/>
-      <c r="K135" s="2"/>
-      <c r="L135" s="2"/>
+      <c r="A135"/>
+      <c r="B135"/>
+      <c r="C135"/>
+      <c r="D135"/>
+      <c r="E135"/>
+      <c r="F135"/>
+      <c r="G135"/>
+      <c r="H135"/>
+      <c r="I135"/>
+      <c r="J135"/>
+      <c r="K135"/>
+      <c r="L135"/>
     </row>
     <row r="136" ht="20" customHeight="1">
-      <c r="A136" s="2"/>
-      <c r="B136" s="2"/>
-      <c r="C136" s="2"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="2"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
-      <c r="J136" s="2"/>
-      <c r="K136" s="2"/>
-      <c r="L136" s="2"/>
+      <c r="A136"/>
+      <c r="B136"/>
+      <c r="C136"/>
+      <c r="D136"/>
+      <c r="E136"/>
+      <c r="F136"/>
+      <c r="G136"/>
+      <c r="H136"/>
+      <c r="I136"/>
+      <c r="J136"/>
+      <c r="K136"/>
+      <c r="L136"/>
     </row>
     <row r="137" ht="20" customHeight="1">
-      <c r="A137" s="2"/>
-      <c r="B137" s="2"/>
-      <c r="C137" s="2"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="2"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="2"/>
-      <c r="I137" s="2"/>
-      <c r="J137" s="2"/>
-      <c r="K137" s="2"/>
-      <c r="L137" s="2"/>
+      <c r="A137"/>
+      <c r="B137"/>
+      <c r="C137"/>
+      <c r="D137"/>
+      <c r="E137"/>
+      <c r="F137"/>
+      <c r="G137"/>
+      <c r="H137"/>
+      <c r="I137"/>
+      <c r="J137"/>
+      <c r="K137"/>
+      <c r="L137"/>
     </row>
     <row r="138" ht="20" customHeight="1">
-      <c r="A138" s="2"/>
-      <c r="B138" s="2"/>
-      <c r="C138" s="2"/>
-      <c r="D138" s="2"/>
-      <c r="E138" s="2"/>
-      <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
-      <c r="J138" s="2"/>
-      <c r="K138" s="2"/>
-      <c r="L138" s="2"/>
+      <c r="A138"/>
+      <c r="B138"/>
+      <c r="C138"/>
+      <c r="D138"/>
+      <c r="E138"/>
+      <c r="F138"/>
+      <c r="G138"/>
+      <c r="H138"/>
+      <c r="I138"/>
+      <c r="J138"/>
+      <c r="K138"/>
+      <c r="L138"/>
     </row>
     <row r="139" ht="20" customHeight="1">
-      <c r="A139" s="2"/>
-      <c r="B139" s="2"/>
-      <c r="C139" s="2"/>
-      <c r="D139" s="2"/>
-      <c r="E139" s="2"/>
-      <c r="F139" s="2"/>
-      <c r="G139" s="2"/>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2"/>
-      <c r="J139" s="2"/>
-      <c r="K139" s="2"/>
-      <c r="L139" s="2"/>
+      <c r="A139"/>
+      <c r="B139"/>
+      <c r="C139"/>
+      <c r="D139"/>
+      <c r="E139"/>
+      <c r="F139"/>
+      <c r="G139"/>
+      <c r="H139"/>
+      <c r="I139"/>
+      <c r="J139"/>
+      <c r="K139"/>
+      <c r="L139"/>
     </row>
     <row r="140" ht="20" customHeight="1">
-      <c r="A140" s="2"/>
-      <c r="B140" s="2"/>
-      <c r="C140" s="2"/>
-      <c r="D140" s="2"/>
-      <c r="E140" s="2"/>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-      <c r="J140" s="2"/>
-      <c r="K140" s="2"/>
-      <c r="L140" s="2"/>
+      <c r="A140"/>
+      <c r="B140"/>
+      <c r="C140"/>
+      <c r="D140"/>
+      <c r="E140"/>
+      <c r="F140"/>
+      <c r="G140"/>
+      <c r="H140"/>
+      <c r="I140"/>
+      <c r="J140"/>
+      <c r="K140"/>
+      <c r="L140"/>
+    </row>
+    <row r="141">
+      <c r="A141"/>
+      <c r="B141"/>
+      <c r="C141"/>
+      <c r="D141"/>
+      <c r="E141"/>
+      <c r="F141"/>
+      <c r="G141"/>
+      <c r="H141"/>
+      <c r="I141"/>
+      <c r="J141"/>
+      <c r="K141"/>
+      <c r="L141"/>
+    </row>
+    <row r="142">
+      <c r="A142"/>
+      <c r="B142"/>
+      <c r="C142"/>
+      <c r="D142"/>
+      <c r="E142"/>
+      <c r="F142"/>
+      <c r="G142"/>
+      <c r="H142"/>
+      <c r="I142"/>
+      <c r="J142"/>
+      <c r="K142"/>
+      <c r="L142"/>
+    </row>
+    <row r="143">
+      <c r="A143"/>
+      <c r="B143"/>
+      <c r="C143"/>
+      <c r="D143"/>
+      <c r="E143"/>
+      <c r="F143"/>
+      <c r="G143"/>
+      <c r="H143"/>
+      <c r="I143"/>
+      <c r="J143"/>
+      <c r="K143"/>
+      <c r="L143"/>
+    </row>
+    <row r="144">
+      <c r="A144"/>
+      <c r="B144"/>
+      <c r="C144"/>
+      <c r="D144"/>
+      <c r="E144"/>
+      <c r="F144"/>
+      <c r="G144"/>
+      <c r="H144"/>
+      <c r="I144"/>
+      <c r="J144"/>
+      <c r="K144"/>
+      <c r="L144"/>
+    </row>
+    <row r="145">
+      <c r="A145"/>
+      <c r="B145"/>
+      <c r="C145"/>
+      <c r="D145"/>
+      <c r="E145"/>
+      <c r="F145"/>
+      <c r="G145"/>
+      <c r="H145"/>
+      <c r="I145"/>
+      <c r="J145"/>
+      <c r="K145"/>
+      <c r="L145"/>
+    </row>
+    <row r="146">
+      <c r="A146"/>
+      <c r="B146"/>
+      <c r="C146"/>
+      <c r="D146"/>
+      <c r="E146"/>
+      <c r="F146"/>
+      <c r="G146"/>
+      <c r="H146"/>
+      <c r="I146"/>
+      <c r="J146"/>
+      <c r="K146"/>
+      <c r="L146"/>
+    </row>
+    <row r="147">
+      <c r="A147"/>
+      <c r="B147"/>
+      <c r="C147"/>
+      <c r="D147"/>
+      <c r="E147"/>
+      <c r="F147"/>
+      <c r="G147"/>
+      <c r="H147"/>
+      <c r="I147"/>
+      <c r="J147"/>
+      <c r="K147"/>
+      <c r="L147"/>
+    </row>
+    <row r="148">
+      <c r="A148"/>
+      <c r="B148"/>
+      <c r="C148"/>
+      <c r="D148"/>
+      <c r="E148"/>
+      <c r="F148"/>
+      <c r="G148"/>
+      <c r="H148"/>
+      <c r="I148"/>
+      <c r="J148"/>
+      <c r="K148"/>
+      <c r="L148"/>
+    </row>
+    <row r="149">
+      <c r="A149"/>
+      <c r="B149"/>
+      <c r="C149"/>
+      <c r="D149"/>
+      <c r="E149"/>
+      <c r="F149"/>
+      <c r="G149"/>
+      <c r="H149"/>
+      <c r="I149"/>
+      <c r="J149"/>
+      <c r="K149"/>
+      <c r="L149"/>
+    </row>
+    <row r="150">
+      <c r="A150"/>
+      <c r="B150"/>
+      <c r="C150"/>
+      <c r="D150"/>
+      <c r="E150"/>
+      <c r="F150"/>
+      <c r="G150"/>
+      <c r="H150"/>
+      <c r="I150"/>
+      <c r="J150"/>
+      <c r="K150"/>
+      <c r="L150"/>
     </row>
   </sheetData>
   <mergeCells>
@@ -3694,20 +4030,20 @@
     <mergeCell ref="K10:L10"/>
     <mergeCell ref="K11:L12"/>
     <mergeCell ref="C13:L13"/>
-    <mergeCell ref="C19:L19"/>
-    <mergeCell ref="I28:L28"/>
-    <mergeCell ref="I25:L25"/>
-    <mergeCell ref="J23:L23"/>
-    <mergeCell ref="G24:H24"/>
-    <mergeCell ref="D32:E33"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="D37:E37"/>
-    <mergeCell ref="D38:E38"/>
-    <mergeCell ref="D39:E40"/>
-    <mergeCell ref="J39:L40"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="J41:L41"/>
+    <mergeCell ref="D42:E43"/>
+    <mergeCell ref="D41:E41"/>
+    <mergeCell ref="D46:E46"/>
+    <mergeCell ref="D47:E47"/>
+    <mergeCell ref="D48:E48"/>
+    <mergeCell ref="D49:E50"/>
+    <mergeCell ref="J51:L51"/>
+    <mergeCell ref="J49:L50"/>
+    <mergeCell ref="C36:L36"/>
+    <mergeCell ref="C37:F37"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="I27:L27"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="F35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="D23:D23">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不可达"/>
@@ -3716,6 +4052,89 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="J24:J24">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D30:D30">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="不可达"/>
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="无效"/>
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F35:F35">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D18:D18">
+    <cfRule type="expression" dxfId="8" priority="9">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D22:D26">
+    <cfRule type="expression" dxfId="9" priority="10">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G37:G37">
+    <cfRule type="expression" dxfId="10" priority="11">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E59:E67">
+    <cfRule type="expression" dxfId="11" priority="12">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H59:H67">
+    <cfRule type="expression" dxfId="12" priority="13">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J59:J67">
+    <cfRule type="expression" dxfId="13" priority="14">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K59:K67">
+    <cfRule type="expression" dxfId="14" priority="15">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L59:L67">
+    <cfRule type="expression" dxfId="15" priority="16">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E72:E85">
+    <cfRule type="expression" dxfId="16" priority="17">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H72:H85">
+    <cfRule type="expression" dxfId="17" priority="18">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J72:J85">
+    <cfRule type="expression" dxfId="18" priority="19">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K72:K85">
+    <cfRule type="expression" dxfId="19" priority="20">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L72:L85">
+    <cfRule type="expression" dxfId="20" priority="21">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E90:E98">
+    <cfRule type="expression" dxfId="21" priority="22">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H90:H98">
+    <cfRule type="expression" dxfId="22" priority="23">
+      <formula>$D$7="ETH"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="list" sqref="D7">

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4536,10 +4536,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2492.22340544782</v>
+        <v>2501.338633822848</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.319202858795</v>
+        <v>46283.34975868055</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4604,10 +4604,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>337.67634954441365</v>
+        <v>335.40408726191083</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.31890171296</v>
+        <v>46283.349456550925</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4672,10 +4672,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.7223085176229445</v>
+        <v>2.7122973158265054</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.31890751157</v>
+        <v>46283.34946334491</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.31891328703</v>
+        <v>46283.34946857639</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.31891908565</v>
+        <v>46283.34947450231</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -4885,7 +4885,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.31892493055</v>
+        <v>46283.34948023148</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -4955,7 +4955,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.31893068287</v>
+        <v>46283.34948679398</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.31893646991</v>
+        <v>46283.349492430556</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.31894229166</v>
+        <v>46283.34949822917</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5160,10 +5160,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>177.19325988438194</v>
+        <v>178.02078360371235</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.318948101856</v>
+        <v>46283.349504351856</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5233,7 +5233,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.31895386574</v>
+        <v>46283.3495099537</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5298,10 +5298,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>86.2531426649799</v>
+        <v>86.2530563387189</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.31895965277</v>
+        <v>46283.349514768524</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.318965451384</v>
+        <v>46283.34952186343</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5436,10 +5436,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.777443271894565</v>
+        <v>8.71738362392947</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.31897125</v>
+        <v>46283.34952603009</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5509,7 +5509,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.31897706018</v>
+        <v>46283.34953179398</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.318982847224</v>
+        <v>46283.34953803241</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5644,10 +5644,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>403.86247537912146</v>
+        <v>403.5217829501588</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.31898863426</v>
+        <v>46283.34954460648</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.31899443287</v>
+        <v>46283.34954983796</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5782,10 +5782,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.16609284673405</v>
+        <v>349.1657433846468</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.319000208336</v>
+        <v>46283.34955539352</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5850,10 +5850,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.334027255112332</v>
+        <v>28.293964988345127</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.31900599537</v>
+        <v>46283.34956188657</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -5923,7 +5923,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.319011782405</v>
+        <v>46283.34956761574</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.31901756945</v>
+        <v>46283.349573368054</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6063,7 +6063,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.31902337963</v>
+        <v>46283.34957922454</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6128,10 +6128,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1156.5007126042883</v>
+        <v>1151.6354352136261</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.31902918982</v>
+        <v>46283.34958501157</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.31903496527</v>
+        <v>46283.34959200231</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6266,10 +6266,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>687.4429516229762</v>
+        <v>683.829203335225</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.31904077547</v>
+        <v>46283.349595995365</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.319046550925</v>
+        <v>46283.34960244213</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.31905237269</v>
+        <v>46283.34960841435</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6479,7 +6479,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.3190581713</v>
+        <v>46283.34961388889</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6544,10 +6544,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>135.63501849568433</v>
+        <v>135.54480645106406</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.31906393519</v>
+        <v>46283.34961914352</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6612,10 +6612,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>995.1538904991431</v>
+        <v>995.5031912029489</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.3190697338</v>
+        <v>46283.34962496528</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.319081331014</v>
+        <v>46283.34963667824</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.319087129625</v>
+        <v>46283.34964212963</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6820,10 +6820,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>222.3885855205214</v>
+        <v>220.89709984356753</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.3190755324</v>
+        <v>46283.34963069444</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.319092881946</v>
+        <v>46283.34964872685</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.31909866898</v>
+        <v>46283.34965340278</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7028,10 +7028,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>724.1640911492946</v>
+        <v>720.5402976320944</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.319104490736</v>
+        <v>46283.34966047454</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7096,10 +7096,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.830560315147245</v>
+        <v>47.68038528633753</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.31911027778</v>
+        <v>46283.34966608796</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>154.42094896472207</v>
+        <v>154.7410656826332</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.31911606481</v>
+        <v>46283.34967207176</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7237,7 +7237,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.31912184028</v>
+        <v>46283.34967752315</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7302,10 +7302,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.96646756449468</v>
+        <v>101.59605185592197</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.31912763889</v>
+        <v>46283.349683472225</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7375,7 +7375,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.31913341435</v>
+        <v>46283.349689131945</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.319139189814</v>
+        <v>46283.349695185185</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7515,7 +7515,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.31914501158</v>
+        <v>46283.349700798615</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.319150787036</v>
+        <v>46283.34970590278</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7655,7 +7655,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.319156655096</v>
+        <v>46283.349711539355</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7720,10 +7720,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>155.87217960830785</v>
+        <v>156.24233725965894</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.31916237269</v>
+        <v>46283.34971766204</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7788,10 +7788,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>765.3089820167502</v>
+        <v>764.7167150576538</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.31916814815</v>
+        <v>46283.34972400463</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7856,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>369.4432879081461</v>
+        <v>368.3780161797042</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.31917391204</v>
+        <v>46283.34972859954</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -7929,7 +7929,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.31917971065</v>
+        <v>46283.34973488426</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -7999,7 +7999,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.31918549768</v>
+        <v>46283.34974016204</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8069,7 +8069,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.31919128472</v>
+        <v>46283.34974641204</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.319197060184</v>
+        <v>46283.34975175926</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8209,7 +8209,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.319202858795</v>
+        <v>46283.34975868055</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R8302c7757af445bf"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R6ca9761c17d04849"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R595ba0064e4749df"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R1fa0ef5cf6d64459"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -164,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="126">
+  <x:cellXfs count="150">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -481,11 +481,27 @@
     <x:xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <x:alignment wrapText="1"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="202" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="206" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="209" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
@@ -528,7 +544,69 @@
     <x:xf numFmtId="207" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
-    <x:xf numFmtId="207" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="208" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="1" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="11" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="11" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -1205,7 +1283,7 @@
       <c r="C18" s="107" t="str">
         <v>建议 Quote 资金</v>
       </c>
-      <c r="D18" s="117">
+      <c r="D18" s="121">
         <f>IF(ISNUMBER($D$26),(IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
       </c>
       <c r="E18" s="62">
@@ -1223,7 +1301,7 @@
       <c r="I18" s="107" t="str">
         <v>总折算 / USDT</v>
       </c>
-      <c r="J18" s="117">
+      <c r="J18" s="121">
         <f>IF(AND(ISNUMBER($D$19),ISNUMBER($G$19)),SUM(D19,G19),"")</f>
       </c>
       <c r="K18" s="62" t="str">
@@ -1237,7 +1315,7 @@
       <c r="C19" s="107" t="str">
         <v>Quote 折算 / USDT</v>
       </c>
-      <c r="D19" s="118">
+      <c r="D19" s="122">
         <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$33&gt;0,$D$18*$D$33,"")),"")</f>
       </c>
       <c r="E19" s="106" t="str">
@@ -1246,7 +1324,7 @@
       <c r="F19" s="107" t="str">
         <v>Gas 折算 / USDT</v>
       </c>
-      <c r="G19" s="118">
+      <c r="G19" s="122">
         <f>IF($G$18=0,0,IF($J$19="","",$G$18*$J$19))</f>
       </c>
       <c r="H19" s="106" t="str">
@@ -1255,7 +1333,7 @@
       <c r="I19" s="107" t="str">
         <v>原生币价格 / USDT</v>
       </c>
-      <c r="J19" s="119">
+      <c r="J19" s="123">
         <f>IF($D$7="ETH",$D$33,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
       </c>
       <c r="K19" s="106"/>
@@ -1299,7 +1377,7 @@
       <c r="C22" s="106">
         <f>"预算 "&amp;TEXT($D$31,"0%")&amp;" 理论资金"</f>
       </c>
-      <c r="D22" s="118">
+      <c r="D22" s="122">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
       </c>
       <c r="E22" s="106">
@@ -1308,12 +1386,12 @@
       <c r="F22" s="106"/>
       <c r="G22" s="106"/>
       <c r="H22" s="106"/>
-      <c r="I22" s="115" t="str">
+      <c r="I22" s="119" t="str">
         <v>内盘</v>
       </c>
-      <c r="J22" s="116"/>
-      <c r="K22" s="116"/>
-      <c r="L22" s="116"/>
+      <c r="J22" s="120"/>
+      <c r="K22" s="120"/>
+      <c r="L22" s="120"/>
     </row>
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="2"/>
@@ -1321,7 +1399,7 @@
       <c r="C23" s="107" t="str">
         <v>额外内盘资金</v>
       </c>
-      <c r="D23" s="118">
+      <c r="D23" s="122">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
       </c>
       <c r="E23" s="106">
@@ -1333,7 +1411,7 @@
       <c r="I23" s="107" t="str">
         <v>基础手续费</v>
       </c>
-      <c r="J23" s="120">
+      <c r="J23" s="124">
         <f>$G$41</f>
       </c>
       <c r="K23" s="106"/>
@@ -1345,7 +1423,7 @@
       <c r="C24" s="107" t="str">
         <v>洗筹损耗</v>
       </c>
-      <c r="D24" s="118">
+      <c r="D24" s="122">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
       </c>
       <c r="E24" s="106">
@@ -1357,7 +1435,7 @@
       <c r="I24" s="107" t="str">
         <v>买入含税费率</v>
       </c>
-      <c r="J24" s="120">
+      <c r="J24" s="124">
         <f>$G$41+$J$7</f>
       </c>
       <c r="K24" s="106"/>
@@ -1369,7 +1447,7 @@
       <c r="C25" s="107" t="str">
         <v>资金预留</v>
       </c>
-      <c r="D25" s="118">
+      <c r="D25" s="122">
         <f>$G$12</f>
       </c>
       <c r="E25" s="106">
@@ -1381,7 +1459,7 @@
       <c r="I25" s="107" t="str">
         <v>卖出含税费率</v>
       </c>
-      <c r="J25" s="120">
+      <c r="J25" s="124">
         <f>$G$41+$J$7</f>
       </c>
       <c r="K25" s="106"/>
@@ -1393,7 +1471,7 @@
       <c r="C26" s="107" t="str">
         <v>恢复目标控筹资金</v>
       </c>
-      <c r="D26" s="118">
+      <c r="D26" s="122">
         <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",0)</f>
       </c>
       <c r="E26" s="106">
@@ -1413,19 +1491,19 @@
       <c r="C27" s="107" t="str">
         <v>洗后控筹率（估算）</v>
       </c>
-      <c r="D27" s="121">
+      <c r="D27" s="125">
         <f>$D$8*$J$54</f>
       </c>
       <c r="E27" s="106"/>
       <c r="F27" s="106"/>
       <c r="G27" s="106"/>
       <c r="H27" s="106"/>
-      <c r="I27" s="115" t="str">
+      <c r="I27" s="119" t="str">
         <v>外盘 · Hook</v>
       </c>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
-      <c r="L27" s="116"/>
+      <c r="J27" s="120"/>
+      <c r="K27" s="120"/>
+      <c r="L27" s="120"/>
     </row>
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="2"/>
@@ -1433,7 +1511,7 @@
       <c r="C28" s="107" t="str">
         <v>补回目标控筹率</v>
       </c>
-      <c r="D28" s="120">
+      <c r="D28" s="124">
         <f>$D$8</f>
       </c>
       <c r="E28" s="106"/>
@@ -1443,7 +1521,7 @@
       <c r="I28" s="107" t="str">
         <v>基础手续费</v>
       </c>
-      <c r="J28" s="120">
+      <c r="J28" s="124">
         <f>$G$42</f>
       </c>
       <c r="K28" s="106"/>
@@ -1455,7 +1533,7 @@
       <c r="C29" s="107" t="str">
         <v>洗筹双边总费率</v>
       </c>
-      <c r="D29" s="120">
+      <c r="D29" s="124">
         <f>$J$47*2</f>
       </c>
       <c r="E29" s="106"/>
@@ -1465,7 +1543,7 @@
       <c r="I29" s="107" t="str">
         <v>买入含税费率</v>
       </c>
-      <c r="J29" s="120">
+      <c r="J29" s="124">
         <f>$G$42+$J$7</f>
       </c>
       <c r="K29" s="106"/>
@@ -1487,7 +1565,7 @@
       <c r="I30" s="107" t="str">
         <v>卖出含税费率</v>
       </c>
-      <c r="J30" s="120">
+      <c r="J30" s="124">
         <f>$G$42+$J$7</f>
       </c>
       <c r="K30" s="106"/>
@@ -1499,7 +1577,7 @@
       <c r="C31" s="107" t="str">
         <v>预算使用控筹率</v>
       </c>
-      <c r="D31" s="120">
+      <c r="D31" s="124">
         <f>$D$8+1%</f>
       </c>
       <c r="E31" s="106"/>
@@ -1517,14 +1595,14 @@
       <c r="C32" s="107" t="str">
         <v>地址总数</v>
       </c>
-      <c r="D32" s="118">
+      <c r="D32" s="122">
         <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
       </c>
       <c r="E32" s="106"/>
       <c r="F32" s="107" t="str">
         <v>当前控筹上限</v>
       </c>
-      <c r="G32" s="120">
+      <c r="G32" s="124">
         <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
       </c>
       <c r="H32" s="106"/>
@@ -1539,7 +1617,7 @@
       <c r="C33" s="107" t="str">
         <v>Quote 价格 / USDT</v>
       </c>
-      <c r="D33" s="119">
+      <c r="D33" s="123">
         <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
       </c>
       <c r="E33" s="106"/>
@@ -1557,7 +1635,7 @@
       <c r="C34" s="107" t="str">
         <v>行情时间 / UTC</v>
       </c>
-      <c r="D34" s="122">
+      <c r="D34" s="126">
         <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
       </c>
       <c r="E34" s="106"/>
@@ -1592,32 +1670,32 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
-      <c r="C36" s="111" t="str">
+      <c r="C36" s="115" t="str">
         <v>Pons 按现有 Quote 洗筹损耗预算承担费用、持仓保持目标的口径，补回资金为 0；不代表免手续费。动态 Snipe Tax 未计入。</v>
       </c>
-      <c r="D36" s="111"/>
-      <c r="E36" s="111"/>
-      <c r="F36" s="111"/>
-      <c r="G36" s="111"/>
-      <c r="H36" s="111"/>
-      <c r="I36" s="111"/>
-      <c r="J36" s="111"/>
-      <c r="K36" s="111"/>
-      <c r="L36" s="111"/>
+      <c r="D36" s="115"/>
+      <c r="E36" s="115"/>
+      <c r="F36" s="115"/>
+      <c r="G36" s="115"/>
+      <c r="H36" s="115"/>
+      <c r="I36" s="115"/>
+      <c r="J36" s="115"/>
+      <c r="K36" s="115"/>
+      <c r="L36" s="115"/>
     </row>
     <row r="37" ht="22" customHeight="1">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="123" t="str">
+      <c r="C37" s="127" t="str">
         <v>沉没成本（模型参考，不重复计入预算）</v>
       </c>
-      <c r="D37" s="123"/>
-      <c r="E37" s="123"/>
-      <c r="F37" s="123"/>
-      <c r="G37" s="124">
+      <c r="D37" s="127"/>
+      <c r="E37" s="127"/>
+      <c r="F37" s="127"/>
+      <c r="G37" s="128">
         <f>E98</f>
       </c>
-      <c r="H37" s="123">
+      <c r="H37" s="127">
         <f>$D$7</f>
       </c>
       <c r="I37" s="106"/>
@@ -1642,444 +1720,444 @@
     <row r="39" ht="24" customHeight="1" collapsed="1">
       <c r="A39"/>
       <c r="B39"/>
-      <c r="C39" s="110" t="str">
+      <c r="C39" s="8" t="str">
         <v>三、模型信息与计算口径（默认折叠，点左侧 + 展开）</v>
       </c>
-      <c r="D39" s="110"/>
-      <c r="E39" s="110"/>
-      <c r="F39" s="110"/>
-      <c r="G39" s="110"/>
-      <c r="H39" s="110"/>
-      <c r="I39" s="110"/>
-      <c r="J39" s="110"/>
-      <c r="K39" s="110"/>
-      <c r="L39" s="110"/>
-    </row>
-    <row r="40" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="D39" s="8"/>
+      <c r="E39" s="8"/>
+      <c r="F39" s="8"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="8"/>
+      <c r="I39" s="8"/>
+      <c r="J39" s="8"/>
+      <c r="K39" s="8"/>
+      <c r="L39" s="8"/>
+    </row>
+    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A40"/>
       <c r="B40"/>
-      <c r="C40" t="str">
+      <c r="C40" s="107" t="str">
         <v>Quote 信息</v>
       </c>
-      <c r="D40"/>
-      <c r="E40"/>
-      <c r="F40" t="str">
+      <c r="D40" s="107"/>
+      <c r="E40" s="107"/>
+      <c r="F40" s="107" t="str">
         <v>协议与曲线参数</v>
       </c>
-      <c r="G40"/>
-      <c r="H40"/>
-      <c r="I40" t="str">
+      <c r="G40" s="107"/>
+      <c r="H40" s="107"/>
+      <c r="I40" s="107" t="str">
         <v>预算中间计算</v>
       </c>
-      <c r="J40"/>
-      <c r="K40"/>
-      <c r="L40"/>
-    </row>
-    <row r="41" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="J40" s="107"/>
+      <c r="K40" s="107"/>
+      <c r="L40" s="107"/>
+    </row>
+    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A41"/>
       <c r="B41"/>
-      <c r="C41" t="str">
+      <c r="C41" s="107" t="str">
         <v>Quote 名称</v>
       </c>
-      <c r="D41">
+      <c r="D41" s="108">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
       </c>
-      <c r="E41"/>
-      <c r="F41" t="str">
+      <c r="E41" s="107"/>
+      <c r="F41" s="107" t="str">
         <v>内盘基础费</v>
       </c>
-      <c r="G41">
+      <c r="G41" s="112">
         <f>1%</f>
       </c>
-      <c r="H41"/>
-      <c r="I41" t="str">
+      <c r="H41" s="107"/>
+      <c r="I41" s="107" t="str">
         <v>一套内盘打满 / Quote</v>
       </c>
-      <c r="J41">
+      <c r="J41" s="108">
         <f>IF(1-$G$41-$J$7&gt;0,$G$44/(1-$G$41-$J$7),"")</f>
       </c>
-      <c r="K41"/>
-      <c r="L41"/>
-    </row>
-    <row r="42" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K41" s="107"/>
+      <c r="L41" s="107"/>
+    </row>
+    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A42"/>
       <c r="B42"/>
-      <c r="C42" t="str">
+      <c r="C42" s="107" t="str">
         <v>Quote 合约</v>
       </c>
-      <c r="D42">
+      <c r="D42" s="109">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
       </c>
-      <c r="E42"/>
-      <c r="F42" t="str">
+      <c r="E42" s="107"/>
+      <c r="F42" s="107" t="str">
         <v>外盘 Hook 费</v>
       </c>
-      <c r="G42">
+      <c r="G42" s="112">
         <f>1%</f>
       </c>
-      <c r="H42"/>
-      <c r="I42" t="str">
+      <c r="H42" s="107"/>
+      <c r="I42" s="107" t="str">
         <v>目标+1% Pool TOKEN</v>
       </c>
-      <c r="J42">
+      <c r="J42" s="108">
         <f>IF($D$31&lt;$G$32,$D$45*(1-$D$31)-$G$51,"")</f>
       </c>
-      <c r="K42"/>
-      <c r="L42"/>
-    </row>
-    <row r="43" ht="36" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K42" s="107"/>
+      <c r="L42" s="107"/>
+    </row>
+    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A43"/>
       <c r="B43"/>
-      <c r="C43"/>
-      <c r="D43"/>
-      <c r="E43"/>
-      <c r="F43" t="str">
+      <c r="C43" s="107"/>
+      <c r="D43" s="108"/>
+      <c r="E43" s="107"/>
+      <c r="F43" s="107" t="str">
         <v>毕业控筹率</v>
       </c>
-      <c r="G43">
+      <c r="G43" s="112">
         <f>$G$44/($G$46+$G$44)</f>
       </c>
-      <c r="H43"/>
-      <c r="I43" t="str">
+      <c r="H43" s="107"/>
+      <c r="I43" s="107" t="str">
         <v>目标+1% Pool Quote</v>
       </c>
-      <c r="J43">
+      <c r="J43" s="108">
         <f>IF($J$42="","",$G$50/$J$42)</f>
       </c>
-      <c r="K43"/>
-      <c r="L43"/>
-    </row>
-    <row r="44" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K43" s="107"/>
+      <c r="L43" s="107"/>
+    </row>
+    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A44"/>
       <c r="B44"/>
-      <c r="C44" t="str">
+      <c r="C44" s="107" t="str">
         <v>Decimals</v>
       </c>
-      <c r="D44">
+      <c r="D44" s="110">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
       </c>
-      <c r="E44"/>
-      <c r="F44" t="str">
+      <c r="E44" s="107"/>
+      <c r="F44" s="107" t="str">
         <v>毕业真实 Quote</v>
       </c>
-      <c r="G44">
+      <c r="G44" s="108">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
       </c>
-      <c r="H44"/>
-      <c r="I44" t="str">
+      <c r="H44" s="107"/>
+      <c r="I44" s="107" t="str">
         <v>外盘净增加 / Quote</v>
       </c>
-      <c r="J44">
+      <c r="J44" s="108">
         <f>IF($J$43="","",MAX(0,$J$43-$G$44))</f>
       </c>
-      <c r="K44"/>
-      <c r="L44"/>
-    </row>
-    <row r="45" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K44" s="107"/>
+      <c r="L44" s="107"/>
+    </row>
+    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A45"/>
       <c r="B45"/>
-      <c r="C45" t="str">
+      <c r="C45" s="107" t="str">
         <v>总供应量</v>
       </c>
-      <c r="D45">
+      <c r="D45" s="111">
         <f>1000000000</f>
       </c>
-      <c r="E45"/>
-      <c r="F45" t="str">
+      <c r="E45" s="107"/>
+      <c r="F45" s="107" t="str">
         <v>内盘初始 TOKEN</v>
       </c>
-      <c r="G45">
+      <c r="G45" s="108">
         <f>$D$45</f>
       </c>
-      <c r="H45"/>
-      <c r="I45" t="str">
+      <c r="H45" s="107"/>
+      <c r="I45" s="107" t="str">
         <v>外盘含费投入 / Quote</v>
       </c>
-      <c r="J45">
+      <c r="J45" s="108">
         <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$31-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="K45"/>
-      <c r="L45"/>
-    </row>
-    <row r="46" ht="6" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K45" s="107"/>
+      <c r="L45" s="107"/>
+    </row>
+    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A46"/>
       <c r="B46"/>
-      <c r="C46" t="str">
+      <c r="C46" s="107" t="str">
         <v>协议参数证据</v>
       </c>
-      <c r="D46">
+      <c r="D46" s="108">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
       </c>
-      <c r="E46"/>
-      <c r="F46" t="str">
+      <c r="E46" s="107"/>
+      <c r="F46" s="107" t="str">
         <v>phantom Quote</v>
       </c>
-      <c r="G46">
+      <c r="G46" s="108">
         <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
       </c>
-      <c r="H46"/>
-      <c r="I46" t="str">
+      <c r="H46" s="107"/>
+      <c r="I46" s="107" t="str">
         <v>目标+1% FDV / Quote</v>
       </c>
-      <c r="J46">
+      <c r="J46" s="108">
         <f>IF($J$43="","",$J$43/$J$42*$D$45)</f>
       </c>
-      <c r="K46"/>
-      <c r="L46"/>
-    </row>
-    <row r="47" ht="24" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K46" s="107"/>
+      <c r="L46" s="107"/>
+    </row>
+    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A47"/>
       <c r="B47"/>
-      <c r="C47" t="str">
+      <c r="C47" s="107" t="str">
         <v>外盘机制</v>
       </c>
-      <c r="D47" t="str">
+      <c r="D47" s="108" t="str">
         <v>Uniswap V4 / exact-input</v>
       </c>
-      <c r="E47"/>
-      <c r="F47" t="str">
+      <c r="E47" s="107"/>
+      <c r="F47" s="107" t="str">
         <v>内盘 k</v>
       </c>
-      <c r="G47">
+      <c r="G47" s="114">
         <f>$G$46*$D$45</f>
       </c>
-      <c r="H47"/>
-      <c r="I47" t="str">
+      <c r="H47" s="107"/>
+      <c r="I47" s="107" t="str">
         <v>洗筹单边费率</v>
       </c>
-      <c r="J47">
+      <c r="J47" s="112">
         <f>$G$42+$J$7</f>
       </c>
-      <c r="K47"/>
-      <c r="L47"/>
+      <c r="K47" s="107"/>
+      <c r="L47" s="107"/>
     </row>
     <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A48"/>
       <c r="B48"/>
-      <c r="C48" t="str">
+      <c r="C48" s="107" t="str">
         <v>费用方向</v>
       </c>
-      <c r="D48" t="str">
+      <c r="D48" s="108" t="str">
         <v>Hook + Creator Tax 从 Meme 输出扣除</v>
       </c>
-      <c r="E48"/>
-      <c r="F48" t="str">
+      <c r="E48" s="107"/>
+      <c r="F48" s="107" t="str">
         <v>外盘初始 TOKEN</v>
       </c>
-      <c r="G48">
+      <c r="G48" s="108">
         <f>$D$45*$G$46*$G$44/($G$46+$G$44)^2</f>
       </c>
-      <c r="H48"/>
-      <c r="I48" t="str">
+      <c r="H48" s="107"/>
+      <c r="I48" s="107" t="str">
         <v>预算缓冲</v>
       </c>
-      <c r="J48" t="n">
+      <c r="J48" s="113" t="n">
         <v>0.01</v>
       </c>
-      <c r="K48"/>
-      <c r="L48"/>
-    </row>
-    <row r="49" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K48" s="107"/>
+      <c r="L48" s="107"/>
+    </row>
+    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A49"/>
       <c r="B49"/>
-      <c r="C49" t="str">
+      <c r="C49" s="107" t="str">
         <v>洗筹口径</v>
       </c>
-      <c r="D49" t="str">
+      <c r="D49" s="108" t="str">
         <v>目标+1% FDV ×（Hook + Creator Tax）×2</v>
       </c>
-      <c r="E49"/>
-      <c r="F49" t="str">
+      <c r="E49" s="107"/>
+      <c r="F49" s="107" t="str">
         <v>外盘初始 Quote</v>
       </c>
-      <c r="G49">
+      <c r="G49" s="108">
         <f>$G$44</f>
       </c>
-      <c r="H49"/>
-      <c r="I49" t="str">
+      <c r="H49" s="107"/>
+      <c r="I49" s="107" t="str">
         <v>分红与回购口径</v>
       </c>
-      <c r="J49" t="str">
+      <c r="J49" s="108" t="str">
         <v>不抵扣分红 / 回购收益</v>
       </c>
-      <c r="K49"/>
-      <c r="L49"/>
-    </row>
-    <row r="50" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K49" s="107"/>
+      <c r="L49" s="107"/>
+    </row>
+    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A50"/>
       <c r="B50"/>
-      <c r="C50"/>
-      <c r="D50"/>
-      <c r="E50"/>
-      <c r="F50" t="str">
+      <c r="C50" s="107"/>
+      <c r="D50" s="108"/>
+      <c r="E50" s="107"/>
+      <c r="F50" s="107" t="str">
         <v>外盘 k</v>
       </c>
-      <c r="G50">
+      <c r="G50" s="114">
         <f>$G$48*$G$44</f>
       </c>
-      <c r="H50"/>
-      <c r="I50"/>
-      <c r="J50"/>
-      <c r="K50"/>
-      <c r="L50"/>
-    </row>
-    <row r="51" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="H50" s="107"/>
+      <c r="I50" s="107"/>
+      <c r="J50" s="108"/>
+      <c r="K50" s="107"/>
+      <c r="L50" s="107"/>
+    </row>
+    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A51"/>
       <c r="B51"/>
-      <c r="C51"/>
-      <c r="D51"/>
-      <c r="E51"/>
-      <c r="F51" t="str">
+      <c r="C51" s="107"/>
+      <c r="D51" s="108"/>
+      <c r="E51" s="107"/>
+      <c r="F51" s="107" t="str">
         <v>Locker TOKEN</v>
       </c>
-      <c r="G51">
+      <c r="G51" s="108">
         <f>$D$45*$G$46^2/($G$46+$G$44)^2</f>
       </c>
-      <c r="H51"/>
-      <c r="I51" t="str">
+      <c r="H51" s="107"/>
+      <c r="I51" s="107" t="str">
         <v>输入检查</v>
       </c>
-      <c r="J51">
+      <c r="J51" s="108">
         <f>IF(COUNT($D$8,$G$7:$G$12,$J$7:$J$8)&lt;&gt;9,"缺少或非数值参数",IF(OR($G$7&lt;1,$G$8&lt;0,$G$9&lt;0,$G$10&lt;0,$G$11&lt;0,$G$12&lt;0,$G$7&lt;&gt;INT($G$7),$G$8&lt;&gt;INT($G$8),$G$9&lt;&gt;INT($G$9),$G$10&lt;&gt;INT($G$10)),"地址/Gas/预留参数无效",IF(OR($J$8&lt;0,$J$8&gt;1,AND($J$9&lt;&gt;"是",$J$9&lt;&gt;"否"),AND($J$10&lt;&gt;"是",$J$10&lt;&gt;"否")),"平台设置无效","参数有效")))</f>
       </c>
-      <c r="K51"/>
-      <c r="L51"/>
-    </row>
-    <row r="52" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K51" s="107"/>
+      <c r="L51" s="107"/>
+    </row>
+    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A52"/>
       <c r="B52"/>
-      <c r="C52"/>
-      <c r="D52"/>
-      <c r="E52"/>
-      <c r="F52" t="str">
+      <c r="C52" s="107"/>
+      <c r="D52" s="108"/>
+      <c r="E52" s="107"/>
+      <c r="F52" s="107" t="str">
         <v>Snipe 窗口</v>
       </c>
-      <c r="G52" t="str">
+      <c r="G52" s="108" t="str">
         <v>3 秒；默认豁免或避开</v>
       </c>
-      <c r="H52"/>
-      <c r="I52"/>
-      <c r="J52"/>
-      <c r="K52"/>
-      <c r="L52"/>
-    </row>
-    <row r="53" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="H52" s="107"/>
+      <c r="I52" s="107"/>
+      <c r="J52" s="108"/>
+      <c r="K52" s="107"/>
+      <c r="L52" s="107"/>
+    </row>
+    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A53"/>
       <c r="B53"/>
-      <c r="C53"/>
-      <c r="D53"/>
-      <c r="E53"/>
-      <c r="F53" t="str">
+      <c r="C53" s="107"/>
+      <c r="D53" s="108"/>
+      <c r="E53" s="107"/>
+      <c r="F53" s="107" t="str">
         <v>Creator Tax 上限</v>
       </c>
-      <c r="G53">
+      <c r="G53" s="112">
         <f>10%</f>
       </c>
-      <c r="H53"/>
-      <c r="I53"/>
-      <c r="J53"/>
-      <c r="K53"/>
-      <c r="L53"/>
-    </row>
-    <row r="54" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="H53" s="107"/>
+      <c r="I53" s="107"/>
+      <c r="J53" s="108"/>
+      <c r="K53" s="107"/>
+      <c r="L53" s="107"/>
+    </row>
+    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A54"/>
       <c r="B54"/>
-      <c r="C54"/>
-      <c r="D54"/>
-      <c r="E54"/>
-      <c r="F54"/>
-      <c r="G54"/>
-      <c r="H54"/>
-      <c r="I54" s="108" t="str">
+      <c r="C54" s="107"/>
+      <c r="D54" s="108"/>
+      <c r="E54" s="107"/>
+      <c r="F54" s="107"/>
+      <c r="G54" s="108"/>
+      <c r="H54" s="107"/>
+      <c r="I54" s="107" t="str">
         <v>洗后持仓保留比例</v>
       </c>
-      <c r="J54">
+      <c r="J54" s="112">
         <f>1</f>
       </c>
-      <c r="K54"/>
-      <c r="L54"/>
-    </row>
-    <row r="55" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="K54" s="107"/>
+      <c r="L54" s="107"/>
+    </row>
+    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A55"/>
       <c r="B55"/>
-      <c r="C55"/>
-      <c r="D55"/>
-      <c r="E55"/>
-      <c r="F55"/>
-      <c r="G55"/>
-      <c r="H55"/>
-      <c r="I55" s="108" t="str">
+      <c r="C55" s="107"/>
+      <c r="D55" s="108"/>
+      <c r="E55" s="107"/>
+      <c r="F55" s="107"/>
+      <c r="G55" s="108"/>
+      <c r="H55" s="107"/>
+      <c r="I55" s="107" t="str">
         <v>目标外盘 Pool TOKEN</v>
       </c>
-      <c r="J55"/>
-      <c r="K55"/>
-      <c r="L55"/>
-    </row>
-    <row r="56" ht="20" customHeight="1" outlineLevel="1" hidden="1">
+      <c r="J55" s="108"/>
+      <c r="K55" s="107"/>
+      <c r="L55" s="107"/>
+    </row>
+    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A56"/>
       <c r="B56"/>
-      <c r="C56"/>
-      <c r="D56"/>
-      <c r="E56"/>
-      <c r="F56"/>
-      <c r="G56"/>
-      <c r="H56"/>
-      <c r="I56" s="108" t="str">
+      <c r="C56" s="107"/>
+      <c r="D56" s="108"/>
+      <c r="E56" s="107"/>
+      <c r="F56" s="107"/>
+      <c r="G56" s="108"/>
+      <c r="H56" s="107"/>
+      <c r="I56" s="107" t="str">
         <v>洗后外盘 Pool TOKEN</v>
       </c>
-      <c r="J56"/>
-      <c r="K56"/>
-      <c r="L56"/>
-    </row>
-    <row r="57" ht="20" customHeight="1">
+      <c r="J56" s="108"/>
+      <c r="K56" s="107"/>
+      <c r="L56" s="107"/>
+    </row>
+    <row r="57" ht="24" customHeight="1">
       <c r="A57"/>
       <c r="B57"/>
-      <c r="C57" t="str">
+      <c r="C57" s="8" t="str">
         <v>内盘曲线</v>
       </c>
-      <c r="D57"/>
-      <c r="E57"/>
-      <c r="F57"/>
-      <c r="G57"/>
-      <c r="H57"/>
-      <c r="I57"/>
-      <c r="J57"/>
-      <c r="K57"/>
-      <c r="L57"/>
-    </row>
-    <row r="58" ht="20" customHeight="1">
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+    </row>
+    <row r="58" ht="32" customHeight="1">
       <c r="A58"/>
       <c r="B58"/>
-      <c r="C58" t="str">
+      <c r="C58" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D58" t="str">
+      <c r="D58" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E58" t="str">
+      <c r="E58" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F58" t="str">
+      <c r="F58" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G58" t="str">
+      <c r="G58" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H58" t="str">
+      <c r="H58" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I58" t="str">
+      <c r="I58" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J58" t="str">
+      <c r="J58" s="77" t="str">
         <v>区间净投入
 / Quote</v>
       </c>
-      <c r="K58" t="str">
+      <c r="K58" s="77" t="str">
         <v>区间含费
 / Quote</v>
       </c>
-      <c r="L58" t="str">
+      <c r="L58" s="77" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
@@ -2087,386 +2165,386 @@
     <row r="59" ht="20" customHeight="1">
       <c r="A59"/>
       <c r="B59"/>
-      <c r="C59" t="n">
+      <c r="C59" s="132" t="n">
         <v>0</v>
       </c>
-      <c r="D59" s="125">
+      <c r="D59" s="144">
         <f>$D$45*(1-C59)</f>
       </c>
-      <c r="E59" s="125">
+      <c r="E59" s="144">
         <f>$G$47/D59</f>
       </c>
-      <c r="F59">
+      <c r="F59" s="135">
         <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
       </c>
-      <c r="G59">
+      <c r="G59" s="135">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F59))),"",F59*$D$33)</f>
       </c>
-      <c r="H59" s="125">
+      <c r="H59" s="144">
         <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
       </c>
-      <c r="I59" s="125">
+      <c r="I59" s="144">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H59))),"",H59*$D$33)</f>
       </c>
-      <c r="J59" s="125">
+      <c r="J59" s="144">
         <f>0</f>
       </c>
-      <c r="K59" s="125">
+      <c r="K59" s="144">
         <f>J59/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L59" s="125">
+      <c r="L59" s="147">
         <f>SUM($K$59:K59)</f>
       </c>
     </row>
-    <row r="60" ht="24" customHeight="1">
+    <row r="60" ht="20" customHeight="1">
       <c r="A60"/>
       <c r="B60"/>
-      <c r="C60" t="n">
+      <c r="C60" s="133" t="n">
         <v>0.1</v>
       </c>
-      <c r="D60" s="125">
+      <c r="D60" s="145">
         <f>$D$45*(1-C60)</f>
       </c>
-      <c r="E60" s="125">
+      <c r="E60" s="145">
         <f>$G$47/D60</f>
       </c>
-      <c r="F60">
+      <c r="F60" s="136">
         <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
       </c>
-      <c r="G60">
+      <c r="G60" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F60))),"",F60*$D$33)</f>
       </c>
-      <c r="H60" s="125">
+      <c r="H60" s="145">
         <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
       </c>
-      <c r="I60" s="125">
+      <c r="I60" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H60))),"",H60*$D$33)</f>
       </c>
-      <c r="J60" s="125">
+      <c r="J60" s="145">
         <f>E60-E59</f>
       </c>
-      <c r="K60" s="125">
+      <c r="K60" s="145">
         <f>J60/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L60" s="125">
+      <c r="L60" s="148">
         <f>SUM($K$59:K60)</f>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
+    <row r="61" ht="20" customHeight="1">
       <c r="A61"/>
       <c r="B61"/>
-      <c r="C61" t="n">
+      <c r="C61" s="133" t="n">
         <v>0.2</v>
       </c>
-      <c r="D61" s="125">
+      <c r="D61" s="145">
         <f>$D$45*(1-C61)</f>
       </c>
-      <c r="E61" s="125">
+      <c r="E61" s="145">
         <f>$G$47/D61</f>
       </c>
-      <c r="F61">
+      <c r="F61" s="136">
         <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
       </c>
-      <c r="G61">
+      <c r="G61" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F61))),"",F61*$D$33)</f>
       </c>
-      <c r="H61" s="125">
+      <c r="H61" s="145">
         <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
       </c>
-      <c r="I61" s="125">
+      <c r="I61" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H61))),"",H61*$D$33)</f>
       </c>
-      <c r="J61" s="125">
+      <c r="J61" s="145">
         <f>E61-E60</f>
       </c>
-      <c r="K61" s="125">
+      <c r="K61" s="145">
         <f>J61/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L61" s="125">
+      <c r="L61" s="148">
         <f>SUM($K$59:K61)</f>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1">
       <c r="A62"/>
       <c r="B62"/>
-      <c r="C62" t="n">
+      <c r="C62" s="133" t="n">
         <v>0.3</v>
       </c>
-      <c r="D62" s="125">
+      <c r="D62" s="145">
         <f>$D$45*(1-C62)</f>
       </c>
-      <c r="E62" s="125">
+      <c r="E62" s="145">
         <f>$G$47/D62</f>
       </c>
-      <c r="F62">
+      <c r="F62" s="136">
         <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
       </c>
-      <c r="G62">
+      <c r="G62" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F62))),"",F62*$D$33)</f>
       </c>
-      <c r="H62" s="125">
+      <c r="H62" s="145">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
       </c>
-      <c r="I62" s="125">
+      <c r="I62" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H62))),"",H62*$D$33)</f>
       </c>
-      <c r="J62" s="125">
+      <c r="J62" s="145">
         <f>E62-E61</f>
       </c>
-      <c r="K62" s="125">
+      <c r="K62" s="145">
         <f>J62/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L62" s="125">
+      <c r="L62" s="148">
         <f>SUM($K$59:K62)</f>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1">
       <c r="A63"/>
       <c r="B63"/>
-      <c r="C63" t="n">
+      <c r="C63" s="133" t="n">
         <v>0.4</v>
       </c>
-      <c r="D63" s="125">
+      <c r="D63" s="145">
         <f>$D$45*(1-C63)</f>
       </c>
-      <c r="E63" s="125">
+      <c r="E63" s="145">
         <f>$G$47/D63</f>
       </c>
-      <c r="F63">
+      <c r="F63" s="136">
         <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
       </c>
-      <c r="G63">
+      <c r="G63" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F63))),"",F63*$D$33)</f>
       </c>
-      <c r="H63" s="125">
+      <c r="H63" s="145">
         <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
       </c>
-      <c r="I63" s="125">
+      <c r="I63" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H63))),"",H63*$D$33)</f>
       </c>
-      <c r="J63" s="125">
+      <c r="J63" s="145">
         <f>E63-E62</f>
       </c>
-      <c r="K63" s="125">
+      <c r="K63" s="145">
         <f>J63/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L63" s="125">
+      <c r="L63" s="148">
         <f>SUM($K$59:K63)</f>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1">
       <c r="A64"/>
       <c r="B64"/>
-      <c r="C64" t="n">
+      <c r="C64" s="133" t="n">
         <v>0.5</v>
       </c>
-      <c r="D64" s="125">
+      <c r="D64" s="145">
         <f>$D$45*(1-C64)</f>
       </c>
-      <c r="E64" s="125">
+      <c r="E64" s="145">
         <f>$G$47/D64</f>
       </c>
-      <c r="F64">
+      <c r="F64" s="136">
         <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
       </c>
-      <c r="G64">
+      <c r="G64" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F64))),"",F64*$D$33)</f>
       </c>
-      <c r="H64" s="125">
+      <c r="H64" s="145">
         <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
       </c>
-      <c r="I64" s="125">
+      <c r="I64" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H64))),"",H64*$D$33)</f>
       </c>
-      <c r="J64" s="125">
+      <c r="J64" s="145">
         <f>E64-E63</f>
       </c>
-      <c r="K64" s="125">
+      <c r="K64" s="145">
         <f>J64/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L64" s="125">
+      <c r="L64" s="148">
         <f>SUM($K$59:K64)</f>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1">
       <c r="A65"/>
       <c r="B65"/>
-      <c r="C65" t="n">
+      <c r="C65" s="133" t="n">
         <v>0.6</v>
       </c>
-      <c r="D65" s="125">
+      <c r="D65" s="145">
         <f>$D$45*(1-C65)</f>
       </c>
-      <c r="E65" s="125">
+      <c r="E65" s="145">
         <f>$G$47/D65</f>
       </c>
-      <c r="F65">
+      <c r="F65" s="136">
         <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
       </c>
-      <c r="G65">
+      <c r="G65" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F65))),"",F65*$D$33)</f>
       </c>
-      <c r="H65" s="125">
+      <c r="H65" s="145">
         <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
       </c>
-      <c r="I65" s="125">
+      <c r="I65" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H65))),"",H65*$D$33)</f>
       </c>
-      <c r="J65" s="125">
+      <c r="J65" s="145">
         <f>E65-E64</f>
       </c>
-      <c r="K65" s="125">
+      <c r="K65" s="145">
         <f>J65/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L65" s="125">
+      <c r="L65" s="148">
         <f>SUM($K$59:K65)</f>
       </c>
     </row>
     <row r="66" ht="20" customHeight="1">
       <c r="A66"/>
       <c r="B66"/>
-      <c r="C66" t="n">
+      <c r="C66" s="133" t="n">
         <v>0.7</v>
       </c>
-      <c r="D66" s="125">
+      <c r="D66" s="145">
         <f>$D$45*(1-C66)</f>
       </c>
-      <c r="E66" s="125">
+      <c r="E66" s="145">
         <f>$G$47/D66</f>
       </c>
-      <c r="F66">
+      <c r="F66" s="136">
         <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
       </c>
-      <c r="G66">
+      <c r="G66" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F66))),"",F66*$D$33)</f>
       </c>
-      <c r="H66" s="125">
+      <c r="H66" s="145">
         <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
       </c>
-      <c r="I66" s="125">
+      <c r="I66" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H66))),"",H66*$D$33)</f>
       </c>
-      <c r="J66" s="125">
+      <c r="J66" s="145">
         <f>E66-E65</f>
       </c>
-      <c r="K66" s="125">
+      <c r="K66" s="145">
         <f>J66/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L66" s="125">
+      <c r="L66" s="148">
         <f>SUM($K$59:K66)</f>
       </c>
     </row>
     <row r="67" ht="20" customHeight="1">
       <c r="A67"/>
       <c r="B67"/>
-      <c r="C67">
+      <c r="C67" s="134">
         <f>$G$43</f>
       </c>
-      <c r="D67" s="125">
+      <c r="D67" s="146">
         <f>$D$45*(1-C67)</f>
       </c>
-      <c r="E67" s="125">
+      <c r="E67" s="146">
         <f>$G$47/D67</f>
       </c>
-      <c r="F67">
+      <c r="F67" s="137">
         <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
       </c>
-      <c r="G67">
+      <c r="G67" s="137">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F67))),"",F67*$D$33)</f>
       </c>
-      <c r="H67" s="125">
+      <c r="H67" s="146">
         <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
       </c>
-      <c r="I67" s="125">
+      <c r="I67" s="146">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H67))),"",H67*$D$33)</f>
       </c>
-      <c r="J67" s="125">
+      <c r="J67" s="146">
         <f>E67-E66</f>
       </c>
-      <c r="K67" s="125">
+      <c r="K67" s="146">
         <f>J67/(1-$G$41-$J$7)</f>
       </c>
-      <c r="L67" s="125">
+      <c r="L67" s="149">
         <f>SUM($K$59:K67)</f>
       </c>
     </row>
     <row r="68" ht="20" customHeight="1">
       <c r="A68"/>
       <c r="B68"/>
-      <c r="C68"/>
-      <c r="D68"/>
-      <c r="E68"/>
-      <c r="F68"/>
-      <c r="G68"/>
-      <c r="H68"/>
-      <c r="I68"/>
-      <c r="J68"/>
-      <c r="K68"/>
-      <c r="L68"/>
+      <c r="C68" s="106"/>
+      <c r="D68" s="106"/>
+      <c r="E68" s="106"/>
+      <c r="F68" s="106"/>
+      <c r="G68" s="106"/>
+      <c r="H68" s="106"/>
+      <c r="I68" s="106"/>
+      <c r="J68" s="106"/>
+      <c r="K68" s="106"/>
+      <c r="L68" s="106"/>
     </row>
     <row r="69" ht="20" customHeight="1">
       <c r="A69"/>
       <c r="B69"/>
-      <c r="C69"/>
-      <c r="D69"/>
-      <c r="E69"/>
-      <c r="F69"/>
-      <c r="G69"/>
-      <c r="H69"/>
-      <c r="I69"/>
-      <c r="J69"/>
-      <c r="K69"/>
-      <c r="L69"/>
-    </row>
-    <row r="70" ht="20" customHeight="1">
+      <c r="C69" s="106"/>
+      <c r="D69" s="106"/>
+      <c r="E69" s="106"/>
+      <c r="F69" s="106"/>
+      <c r="G69" s="106"/>
+      <c r="H69" s="106"/>
+      <c r="I69" s="106"/>
+      <c r="J69" s="106"/>
+      <c r="K69" s="106"/>
+      <c r="L69" s="106"/>
+    </row>
+    <row r="70" ht="24" customHeight="1">
       <c r="A70"/>
       <c r="B70"/>
-      <c r="C70" t="str">
+      <c r="C70" s="8" t="str">
         <v>外盘曲线</v>
       </c>
-      <c r="D70"/>
-      <c r="E70"/>
-      <c r="F70"/>
-      <c r="G70"/>
-      <c r="H70"/>
-      <c r="I70"/>
-      <c r="J70"/>
-      <c r="K70"/>
-      <c r="L70"/>
-    </row>
-    <row r="71" ht="20" customHeight="1">
+      <c r="D70" s="8"/>
+      <c r="E70" s="8"/>
+      <c r="F70" s="8"/>
+      <c r="G70" s="8"/>
+      <c r="H70" s="8"/>
+      <c r="I70" s="8"/>
+      <c r="J70" s="8"/>
+      <c r="K70" s="8"/>
+      <c r="L70" s="8"/>
+    </row>
+    <row r="71" ht="32" customHeight="1">
       <c r="A71"/>
       <c r="B71"/>
-      <c r="C71" t="str">
+      <c r="C71" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D71" t="str">
+      <c r="D71" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E71" t="str">
+      <c r="E71" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F71" t="str">
+      <c r="F71" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G71" t="str">
+      <c r="G71" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H71" t="str">
+      <c r="H71" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I71" t="str">
+      <c r="I71" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J71" t="str">
+      <c r="J71" s="77" t="str">
         <v>外盘净投入
 / Quote</v>
       </c>
-      <c r="K71" t="str">
+      <c r="K71" s="77" t="str">
         <v>外盘含费
 / Quote</v>
       </c>
-      <c r="L71" t="str">
+      <c r="L71" s="77" t="str">
         <v>理论累计所需
 / Quote</v>
       </c>
@@ -2474,1554 +2552,1554 @@
     <row r="72" ht="20" customHeight="1">
       <c r="A72"/>
       <c r="B72"/>
-      <c r="C72">
+      <c r="C72" s="132">
         <f>$G$43</f>
       </c>
-      <c r="D72" s="125">
+      <c r="D72" s="144">
         <f>$G$48</f>
       </c>
-      <c r="E72" s="125">
+      <c r="E72" s="144">
         <f>$G$44</f>
       </c>
-      <c r="F72">
+      <c r="F72" s="135">
         <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
       </c>
-      <c r="G72">
+      <c r="G72" s="135">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F72))),"",F72*$D$33)</f>
       </c>
-      <c r="H72" s="125">
+      <c r="H72" s="144">
         <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
       </c>
-      <c r="I72" s="125">
+      <c r="I72" s="144">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H72))),"",H72*$D$33)</f>
       </c>
-      <c r="J72" s="125">
+      <c r="J72" s="144">
         <f>0</f>
       </c>
-      <c r="K72" s="125">
+      <c r="K72" s="144">
         <f>0</f>
       </c>
-      <c r="L72" s="125">
+      <c r="L72" s="147">
         <f>$J$41</f>
       </c>
     </row>
     <row r="73" ht="20" customHeight="1">
       <c r="A73"/>
       <c r="B73"/>
-      <c r="C73" t="n">
+      <c r="C73" s="133" t="n">
         <v>0.75</v>
       </c>
-      <c r="D73" s="125">
+      <c r="D73" s="145">
         <f>IF(C73&lt;$G$32,$D$45*(1-C73)-$G$51,"")</f>
       </c>
-      <c r="E73" s="125">
+      <c r="E73" s="145">
         <f>IF(D73="","",$G$50/D73)</f>
       </c>
-      <c r="F73">
+      <c r="F73" s="136">
         <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
       </c>
-      <c r="G73">
+      <c r="G73" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F73))),"",F73*$D$33)</f>
       </c>
-      <c r="H73" s="125">
+      <c r="H73" s="145">
         <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
       </c>
-      <c r="I73" s="125">
+      <c r="I73" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H73))),"",H73*$D$33)</f>
       </c>
-      <c r="J73" s="125">
+      <c r="J73" s="145">
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
       </c>
-      <c r="K73" s="125">
+      <c r="K73" s="145">
         <f>IF(D73="","",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L73" s="125">
+      <c r="L73" s="148">
         <f>IF(K73="","",$J$41+K73)</f>
       </c>
     </row>
     <row r="74" ht="20" customHeight="1">
       <c r="A74"/>
       <c r="B74"/>
-      <c r="C74" t="n">
+      <c r="C74" s="133" t="n">
         <v>0.8</v>
       </c>
-      <c r="D74" s="125">
+      <c r="D74" s="145">
         <f>IF(C74&lt;$G$32,$D$45*(1-C74)-$G$51,"")</f>
       </c>
-      <c r="E74" s="125">
+      <c r="E74" s="145">
         <f>IF(D74="","",$G$50/D74)</f>
       </c>
-      <c r="F74">
+      <c r="F74" s="136">
         <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
       </c>
-      <c r="G74">
+      <c r="G74" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F74))),"",F74*$D$33)</f>
       </c>
-      <c r="H74" s="125">
+      <c r="H74" s="145">
         <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
       </c>
-      <c r="I74" s="125">
+      <c r="I74" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H74))),"",H74*$D$33)</f>
       </c>
-      <c r="J74" s="125">
+      <c r="J74" s="145">
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
       </c>
-      <c r="K74" s="125">
+      <c r="K74" s="145">
         <f>IF(D74="","",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L74" s="125">
+      <c r="L74" s="148">
         <f>IF(K74="","",$J$41+K74)</f>
       </c>
     </row>
     <row r="75" ht="20" customHeight="1">
       <c r="A75"/>
       <c r="B75"/>
-      <c r="C75" t="n">
+      <c r="C75" s="133" t="n">
         <v>0.82</v>
       </c>
-      <c r="D75" s="125">
+      <c r="D75" s="145">
         <f>IF(C75&lt;$G$32,$D$45*(1-C75)-$G$51,"")</f>
       </c>
-      <c r="E75" s="125">
+      <c r="E75" s="145">
         <f>IF(D75="","",$G$50/D75)</f>
       </c>
-      <c r="F75">
+      <c r="F75" s="136">
         <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
       </c>
-      <c r="G75">
+      <c r="G75" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F75))),"",F75*$D$33)</f>
       </c>
-      <c r="H75" s="125">
+      <c r="H75" s="145">
         <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
       </c>
-      <c r="I75" s="125">
+      <c r="I75" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H75))),"",H75*$D$33)</f>
       </c>
-      <c r="J75" s="125">
+      <c r="J75" s="145">
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
       </c>
-      <c r="K75" s="125">
+      <c r="K75" s="145">
         <f>IF(D75="","",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L75" s="125">
+      <c r="L75" s="148">
         <f>IF(K75="","",$J$41+K75)</f>
       </c>
     </row>
     <row r="76" ht="20" customHeight="1">
       <c r="A76"/>
       <c r="B76"/>
-      <c r="C76" t="n">
+      <c r="C76" s="133" t="n">
         <v>0.84</v>
       </c>
-      <c r="D76" s="125">
+      <c r="D76" s="145">
         <f>IF(C76&lt;$G$32,$D$45*(1-C76)-$G$51,"")</f>
       </c>
-      <c r="E76" s="125">
+      <c r="E76" s="145">
         <f>IF(D76="","",$G$50/D76)</f>
       </c>
-      <c r="F76">
+      <c r="F76" s="136">
         <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
       </c>
-      <c r="G76">
+      <c r="G76" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F76))),"",F76*$D$33)</f>
       </c>
-      <c r="H76" s="125">
+      <c r="H76" s="145">
         <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
       </c>
-      <c r="I76" s="125">
+      <c r="I76" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H76))),"",H76*$D$33)</f>
       </c>
-      <c r="J76" s="125">
+      <c r="J76" s="145">
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
       </c>
-      <c r="K76" s="125">
+      <c r="K76" s="145">
         <f>IF(D76="","",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L76" s="125">
+      <c r="L76" s="148">
         <f>IF(K76="","",$J$41+K76)</f>
       </c>
     </row>
     <row r="77" ht="20" customHeight="1">
       <c r="A77"/>
       <c r="B77"/>
-      <c r="C77" t="n">
+      <c r="C77" s="133" t="n">
         <v>0.86</v>
       </c>
-      <c r="D77" s="125">
+      <c r="D77" s="145">
         <f>IF(C77&lt;$G$32,$D$45*(1-C77)-$G$51,"")</f>
       </c>
-      <c r="E77" s="125">
+      <c r="E77" s="145">
         <f>IF(D77="","",$G$50/D77)</f>
       </c>
-      <c r="F77">
+      <c r="F77" s="136">
         <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
       </c>
-      <c r="G77">
+      <c r="G77" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F77))),"",F77*$D$33)</f>
       </c>
-      <c r="H77" s="125">
+      <c r="H77" s="145">
         <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
       </c>
-      <c r="I77" s="125">
+      <c r="I77" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H77))),"",H77*$D$33)</f>
       </c>
-      <c r="J77" s="125">
+      <c r="J77" s="145">
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
       </c>
-      <c r="K77" s="125">
+      <c r="K77" s="145">
         <f>IF(D77="","",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L77" s="125">
+      <c r="L77" s="148">
         <f>IF(K77="","",$J$41+K77)</f>
       </c>
     </row>
-    <row r="78" ht="24" customHeight="1">
+    <row r="78" ht="20" customHeight="1">
       <c r="A78"/>
       <c r="B78"/>
-      <c r="C78" t="n">
+      <c r="C78" s="133" t="n">
         <v>0.88</v>
       </c>
-      <c r="D78" s="125">
+      <c r="D78" s="145">
         <f>IF(C78&lt;$G$32,$D$45*(1-C78)-$G$51,"")</f>
       </c>
-      <c r="E78" s="125">
+      <c r="E78" s="145">
         <f>IF(D78="","",$G$50/D78)</f>
       </c>
-      <c r="F78">
+      <c r="F78" s="136">
         <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
       </c>
-      <c r="G78">
+      <c r="G78" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F78))),"",F78*$D$33)</f>
       </c>
-      <c r="H78" s="125">
+      <c r="H78" s="145">
         <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
       </c>
-      <c r="I78" s="125">
+      <c r="I78" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H78))),"",H78*$D$33)</f>
       </c>
-      <c r="J78" s="125">
+      <c r="J78" s="145">
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
       </c>
-      <c r="K78" s="125">
+      <c r="K78" s="145">
         <f>IF(D78="","",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L78" s="125">
+      <c r="L78" s="148">
         <f>IF(K78="","",$J$41+K78)</f>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
+    <row r="79" ht="20" customHeight="1">
       <c r="A79"/>
       <c r="B79"/>
-      <c r="C79" t="n">
+      <c r="C79" s="133" t="n">
         <v>0.89</v>
       </c>
-      <c r="D79" s="125">
+      <c r="D79" s="145">
         <f>IF(C79&lt;$G$32,$D$45*(1-C79)-$G$51,"")</f>
       </c>
-      <c r="E79" s="125">
+      <c r="E79" s="145">
         <f>IF(D79="","",$G$50/D79)</f>
       </c>
-      <c r="F79">
+      <c r="F79" s="136">
         <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
       </c>
-      <c r="G79">
+      <c r="G79" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F79))),"",F79*$D$33)</f>
       </c>
-      <c r="H79" s="125">
+      <c r="H79" s="145">
         <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
       </c>
-      <c r="I79" s="125">
+      <c r="I79" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H79))),"",H79*$D$33)</f>
       </c>
-      <c r="J79" s="125">
+      <c r="J79" s="145">
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
       </c>
-      <c r="K79" s="125">
+      <c r="K79" s="145">
         <f>IF(D79="","",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L79" s="125">
+      <c r="L79" s="148">
         <f>IF(K79="","",$J$41+K79)</f>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1">
       <c r="A80"/>
       <c r="B80"/>
-      <c r="C80" t="n">
+      <c r="C80" s="133" t="n">
         <v>0.9</v>
       </c>
-      <c r="D80" s="125">
+      <c r="D80" s="145">
         <f>IF(C80&lt;$G$32,$D$45*(1-C80)-$G$51,"")</f>
       </c>
-      <c r="E80" s="125">
+      <c r="E80" s="145">
         <f>IF(D80="","",$G$50/D80)</f>
       </c>
-      <c r="F80">
+      <c r="F80" s="136">
         <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
       </c>
-      <c r="G80">
+      <c r="G80" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F80))),"",F80*$D$33)</f>
       </c>
-      <c r="H80" s="125">
+      <c r="H80" s="145">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
       </c>
-      <c r="I80" s="125">
+      <c r="I80" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H80))),"",H80*$D$33)</f>
       </c>
-      <c r="J80" s="125">
+      <c r="J80" s="145">
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
       </c>
-      <c r="K80" s="125">
+      <c r="K80" s="145">
         <f>IF(D80="","",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L80" s="125">
+      <c r="L80" s="148">
         <f>IF(K80="","",$J$41+K80)</f>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1">
       <c r="A81"/>
       <c r="B81"/>
-      <c r="C81" t="n">
+      <c r="C81" s="133" t="n">
         <v>0.905</v>
       </c>
-      <c r="D81" s="125">
+      <c r="D81" s="145">
         <f>IF(C81&lt;$G$32,$D$45*(1-C81)-$G$51,"")</f>
       </c>
-      <c r="E81" s="125">
+      <c r="E81" s="145">
         <f>IF(D81="","",$G$50/D81)</f>
       </c>
-      <c r="F81">
+      <c r="F81" s="136">
         <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
       </c>
-      <c r="G81">
+      <c r="G81" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F81))),"",F81*$D$33)</f>
       </c>
-      <c r="H81" s="125">
+      <c r="H81" s="145">
         <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
       </c>
-      <c r="I81" s="125">
+      <c r="I81" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H81))),"",H81*$D$33)</f>
       </c>
-      <c r="J81" s="125">
+      <c r="J81" s="145">
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
       </c>
-      <c r="K81" s="125">
+      <c r="K81" s="145">
         <f>IF(D81="","",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L81" s="125">
+      <c r="L81" s="148">
         <f>IF(K81="","",$J$41+K81)</f>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1">
       <c r="A82"/>
       <c r="B82"/>
-      <c r="C82" t="n">
+      <c r="C82" s="133" t="n">
         <v>0.91</v>
       </c>
-      <c r="D82" s="125">
+      <c r="D82" s="145">
         <f>IF(C82&lt;$G$32,$D$45*(1-C82)-$G$51,"")</f>
       </c>
-      <c r="E82" s="125">
+      <c r="E82" s="145">
         <f>IF(D82="","",$G$50/D82)</f>
       </c>
-      <c r="F82">
+      <c r="F82" s="136">
         <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
       </c>
-      <c r="G82">
+      <c r="G82" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F82))),"",F82*$D$33)</f>
       </c>
-      <c r="H82" s="125">
+      <c r="H82" s="145">
         <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
       </c>
-      <c r="I82" s="125">
+      <c r="I82" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H82))),"",H82*$D$33)</f>
       </c>
-      <c r="J82" s="125">
+      <c r="J82" s="145">
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
       </c>
-      <c r="K82" s="125">
+      <c r="K82" s="145">
         <f>IF(D82="","",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L82" s="125">
+      <c r="L82" s="148">
         <f>IF(K82="","",$J$41+K82)</f>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1">
       <c r="A83"/>
       <c r="B83"/>
-      <c r="C83" t="n">
+      <c r="C83" s="133" t="n">
         <v>0.915</v>
       </c>
-      <c r="D83" s="125">
+      <c r="D83" s="145">
         <f>IF(C83&lt;$G$32,$D$45*(1-C83)-$G$51,"")</f>
       </c>
-      <c r="E83" s="125">
+      <c r="E83" s="145">
         <f>IF(D83="","",$G$50/D83)</f>
       </c>
-      <c r="F83">
+      <c r="F83" s="136">
         <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
       </c>
-      <c r="G83">
+      <c r="G83" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F83))),"",F83*$D$33)</f>
       </c>
-      <c r="H83" s="125">
+      <c r="H83" s="145">
         <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
       </c>
-      <c r="I83" s="125">
+      <c r="I83" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H83))),"",H83*$D$33)</f>
       </c>
-      <c r="J83" s="125">
+      <c r="J83" s="145">
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
       </c>
-      <c r="K83" s="125">
+      <c r="K83" s="145">
         <f>IF(D83="","",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L83" s="125">
+      <c r="L83" s="148">
         <f>IF(K83="","",$J$41+K83)</f>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1">
       <c r="A84"/>
       <c r="B84"/>
-      <c r="C84" t="n">
+      <c r="C84" s="133" t="n">
         <v>0.918</v>
       </c>
-      <c r="D84" s="125">
+      <c r="D84" s="145">
         <f>IF(C84&lt;$G$32,$D$45*(1-C84)-$G$51,"")</f>
       </c>
-      <c r="E84" s="125">
+      <c r="E84" s="145">
         <f>IF(D84="","",$G$50/D84)</f>
       </c>
-      <c r="F84">
+      <c r="F84" s="136">
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
       </c>
-      <c r="G84">
+      <c r="G84" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F84))),"",F84*$D$33)</f>
       </c>
-      <c r="H84" s="125">
+      <c r="H84" s="145">
         <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
       </c>
-      <c r="I84" s="125">
+      <c r="I84" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H84))),"",H84*$D$33)</f>
       </c>
-      <c r="J84" s="125">
+      <c r="J84" s="145">
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
       </c>
-      <c r="K84" s="125">
+      <c r="K84" s="145">
         <f>IF(D84="","",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L84" s="125">
+      <c r="L84" s="148">
         <f>IF(K84="","",$J$41+K84)</f>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1">
       <c r="A85"/>
       <c r="B85"/>
-      <c r="C85" t="n">
+      <c r="C85" s="134" t="n">
         <v>0.9183673469387755</v>
       </c>
-      <c r="D85" s="125">
+      <c r="D85" s="146">
         <f>IF(C85&lt;$G$32,$D$45*(1-C85)-$G$51,"")</f>
       </c>
-      <c r="E85" s="125">
+      <c r="E85" s="146">
         <f>IF(D85="","",$G$50/D85)</f>
       </c>
-      <c r="F85">
+      <c r="F85" s="137">
         <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
       </c>
-      <c r="G85">
+      <c r="G85" s="137">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F85))),"",F85*$D$33)</f>
       </c>
-      <c r="H85" s="125">
+      <c r="H85" s="146">
         <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$45)</f>
       </c>
-      <c r="I85" s="125">
+      <c r="I85" s="146">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H85))),"",H85*$D$33)</f>
       </c>
-      <c r="J85" s="125">
+      <c r="J85" s="146">
         <f>IF(E85="","",MAX(0,E85-$G$44))</f>
       </c>
-      <c r="K85" s="125">
+      <c r="K85" s="146">
         <f>IF(D85="","",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
-      <c r="L85" s="125">
+      <c r="L85" s="149">
         <f>IF(K85="","",$J$41+K85)</f>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
       <c r="A86"/>
       <c r="B86"/>
-      <c r="C86"/>
-      <c r="D86"/>
-      <c r="E86"/>
-      <c r="F86"/>
-      <c r="G86"/>
-      <c r="H86"/>
-      <c r="I86"/>
-      <c r="J86"/>
-      <c r="K86"/>
-      <c r="L86"/>
+      <c r="C86" s="106"/>
+      <c r="D86" s="106"/>
+      <c r="E86" s="106"/>
+      <c r="F86" s="106"/>
+      <c r="G86" s="106"/>
+      <c r="H86" s="106"/>
+      <c r="I86" s="106"/>
+      <c r="J86" s="106"/>
+      <c r="K86" s="106"/>
+      <c r="L86" s="106"/>
     </row>
     <row r="87" ht="20" customHeight="1">
       <c r="A87"/>
       <c r="B87"/>
-      <c r="C87"/>
-      <c r="D87"/>
-      <c r="E87"/>
-      <c r="F87"/>
-      <c r="G87"/>
-      <c r="H87"/>
-      <c r="I87"/>
-      <c r="J87"/>
-      <c r="K87"/>
-      <c r="L87"/>
-    </row>
-    <row r="88" ht="20" customHeight="1">
+      <c r="C87" s="106"/>
+      <c r="D87" s="106"/>
+      <c r="E87" s="106"/>
+      <c r="F87" s="106"/>
+      <c r="G87" s="106"/>
+      <c r="H87" s="106"/>
+      <c r="I87" s="106"/>
+      <c r="J87" s="106"/>
+      <c r="K87" s="106"/>
+      <c r="L87" s="106"/>
+    </row>
+    <row r="88" ht="24" customHeight="1">
       <c r="A88"/>
       <c r="B88"/>
-      <c r="C88" t="str">
+      <c r="C88" s="102" t="str">
         <v>外盘回落参考</v>
       </c>
-      <c r="D88"/>
-      <c r="E88"/>
-      <c r="F88"/>
-      <c r="G88"/>
-      <c r="H88"/>
-      <c r="I88"/>
-      <c r="J88"/>
-      <c r="K88"/>
-      <c r="L88"/>
-    </row>
-    <row r="89" ht="20" customHeight="1">
+      <c r="D88" s="102"/>
+      <c r="E88" s="102"/>
+      <c r="F88" s="102"/>
+      <c r="G88" s="102"/>
+      <c r="H88" s="102"/>
+      <c r="I88" s="102"/>
+      <c r="J88" s="102"/>
+      <c r="K88" s="102"/>
+      <c r="L88" s="102"/>
+    </row>
+    <row r="89" ht="32" customHeight="1">
       <c r="A89"/>
       <c r="B89"/>
-      <c r="C89" t="str">
+      <c r="C89" s="77" t="str">
         <v>控筹率</v>
       </c>
-      <c r="D89" t="str">
+      <c r="D89" s="77" t="str">
         <v>pooled TOKEN</v>
       </c>
-      <c r="E89" t="str">
+      <c r="E89" s="77" t="str">
         <v>pooled Quote</v>
       </c>
-      <c r="F89" t="str">
+      <c r="F89" s="77" t="str">
         <v>价格 / Quote</v>
       </c>
-      <c r="G89" t="str">
+      <c r="G89" s="77" t="str">
         <v>价格 / USDT</v>
       </c>
-      <c r="H89" t="str">
+      <c r="H89" s="77" t="str">
         <v>市值 / Quote</v>
       </c>
-      <c r="I89" t="str">
+      <c r="I89" s="77" t="str">
         <v>市值 / USDT</v>
       </c>
-      <c r="J89" t="str">
+      <c r="J89" s="77" t="str">
         <v>较毕业点回撤</v>
       </c>
-      <c r="K89" t="str"/>
-      <c r="L89" t="str"/>
+      <c r="K89" s="77" t="str"/>
+      <c r="L89" s="77" t="str"/>
     </row>
     <row r="90" ht="20" customHeight="1">
       <c r="A90"/>
       <c r="B90"/>
-      <c r="C90" t="n">
+      <c r="C90" s="132" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="D90" s="125">
+      <c r="D90" s="144">
         <f>$D$45*(1-C90)-$G$51</f>
       </c>
-      <c r="E90" s="125">
+      <c r="E90" s="144">
         <f>$G$50/D90</f>
       </c>
-      <c r="F90">
+      <c r="F90" s="135">
         <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
       </c>
-      <c r="G90">
+      <c r="G90" s="135">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F90))),"",F90*$D$33)</f>
       </c>
-      <c r="H90" s="125">
+      <c r="H90" s="144">
         <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
       </c>
-      <c r="I90" s="125">
+      <c r="I90" s="144">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H90))),"",H90*$D$33)</f>
       </c>
-      <c r="J90">
+      <c r="J90" s="132">
         <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
       </c>
-      <c r="K90"/>
-      <c r="L90"/>
+      <c r="K90" s="129"/>
+      <c r="L90" s="129"/>
     </row>
     <row r="91" ht="20" customHeight="1">
       <c r="A91"/>
       <c r="B91"/>
-      <c r="C91" t="n">
+      <c r="C91" s="133" t="n">
         <v>0.7</v>
       </c>
-      <c r="D91" s="125">
+      <c r="D91" s="145">
         <f>$D$45*(1-C91)-$G$51</f>
       </c>
-      <c r="E91" s="125">
+      <c r="E91" s="145">
         <f>$G$50/D91</f>
       </c>
-      <c r="F91">
+      <c r="F91" s="136">
         <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
       </c>
-      <c r="G91">
+      <c r="G91" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F91))),"",F91*$D$33)</f>
       </c>
-      <c r="H91" s="125">
+      <c r="H91" s="145">
         <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
       </c>
-      <c r="I91" s="125">
+      <c r="I91" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H91))),"",H91*$D$33)</f>
       </c>
-      <c r="J91">
+      <c r="J91" s="133">
         <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
       </c>
-      <c r="K91"/>
-      <c r="L91"/>
+      <c r="K91" s="130"/>
+      <c r="L91" s="130"/>
     </row>
     <row r="92" ht="20" customHeight="1">
       <c r="A92"/>
       <c r="B92"/>
-      <c r="C92" t="n">
+      <c r="C92" s="133" t="n">
         <v>0.6</v>
       </c>
-      <c r="D92" s="125">
+      <c r="D92" s="145">
         <f>$D$45*(1-C92)-$G$51</f>
       </c>
-      <c r="E92" s="125">
+      <c r="E92" s="145">
         <f>$G$50/D92</f>
       </c>
-      <c r="F92">
+      <c r="F92" s="136">
         <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
       </c>
-      <c r="G92">
+      <c r="G92" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F92))),"",F92*$D$33)</f>
       </c>
-      <c r="H92" s="125">
+      <c r="H92" s="145">
         <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
       </c>
-      <c r="I92" s="125">
+      <c r="I92" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H92))),"",H92*$D$33)</f>
       </c>
-      <c r="J92">
+      <c r="J92" s="133">
         <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
       </c>
-      <c r="K92"/>
-      <c r="L92"/>
+      <c r="K92" s="130"/>
+      <c r="L92" s="130"/>
     </row>
     <row r="93" ht="20" customHeight="1">
       <c r="A93"/>
       <c r="B93"/>
-      <c r="C93" t="n">
+      <c r="C93" s="133" t="n">
         <v>0.5</v>
       </c>
-      <c r="D93" s="125">
+      <c r="D93" s="145">
         <f>$D$45*(1-C93)-$G$51</f>
       </c>
-      <c r="E93" s="125">
+      <c r="E93" s="145">
         <f>$G$50/D93</f>
       </c>
-      <c r="F93">
+      <c r="F93" s="136">
         <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
       </c>
-      <c r="G93">
+      <c r="G93" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F93))),"",F93*$D$33)</f>
       </c>
-      <c r="H93" s="125">
+      <c r="H93" s="145">
         <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
       </c>
-      <c r="I93" s="125">
+      <c r="I93" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H93))),"",H93*$D$33)</f>
       </c>
-      <c r="J93">
+      <c r="J93" s="133">
         <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
       </c>
-      <c r="K93"/>
-      <c r="L93"/>
+      <c r="K93" s="130"/>
+      <c r="L93" s="130"/>
     </row>
     <row r="94" ht="20" customHeight="1">
       <c r="A94"/>
       <c r="B94"/>
-      <c r="C94" t="n">
+      <c r="C94" s="133" t="n">
         <v>0.4</v>
       </c>
-      <c r="D94" s="125">
+      <c r="D94" s="145">
         <f>$D$45*(1-C94)-$G$51</f>
       </c>
-      <c r="E94" s="125">
+      <c r="E94" s="145">
         <f>$G$50/D94</f>
       </c>
-      <c r="F94">
+      <c r="F94" s="136">
         <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
       </c>
-      <c r="G94">
+      <c r="G94" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F94))),"",F94*$D$33)</f>
       </c>
-      <c r="H94" s="125">
+      <c r="H94" s="145">
         <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
       </c>
-      <c r="I94" s="125">
+      <c r="I94" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H94))),"",H94*$D$33)</f>
       </c>
-      <c r="J94">
+      <c r="J94" s="133">
         <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
       </c>
-      <c r="K94"/>
-      <c r="L94"/>
+      <c r="K94" s="130"/>
+      <c r="L94" s="130"/>
     </row>
     <row r="95" ht="20" customHeight="1">
       <c r="A95"/>
       <c r="B95"/>
-      <c r="C95" t="n">
+      <c r="C95" s="133" t="n">
         <v>0.3</v>
       </c>
-      <c r="D95" s="125">
+      <c r="D95" s="145">
         <f>$D$45*(1-C95)-$G$51</f>
       </c>
-      <c r="E95" s="125">
+      <c r="E95" s="145">
         <f>$G$50/D95</f>
       </c>
-      <c r="F95">
+      <c r="F95" s="136">
         <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
       </c>
-      <c r="G95">
+      <c r="G95" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F95))),"",F95*$D$33)</f>
       </c>
-      <c r="H95" s="125">
+      <c r="H95" s="145">
         <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
       </c>
-      <c r="I95" s="125">
+      <c r="I95" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H95))),"",H95*$D$33)</f>
       </c>
-      <c r="J95">
+      <c r="J95" s="133">
         <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
       </c>
-      <c r="K95"/>
-      <c r="L95"/>
+      <c r="K95" s="130"/>
+      <c r="L95" s="130"/>
     </row>
     <row r="96" ht="20" customHeight="1">
       <c r="A96"/>
       <c r="B96"/>
-      <c r="C96" t="n">
+      <c r="C96" s="133" t="n">
         <v>0.2</v>
       </c>
-      <c r="D96" s="125">
+      <c r="D96" s="145">
         <f>$D$45*(1-C96)-$G$51</f>
       </c>
-      <c r="E96" s="125">
+      <c r="E96" s="145">
         <f>$G$50/D96</f>
       </c>
-      <c r="F96">
+      <c r="F96" s="136">
         <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
       </c>
-      <c r="G96">
+      <c r="G96" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F96))),"",F96*$D$33)</f>
       </c>
-      <c r="H96" s="125">
+      <c r="H96" s="145">
         <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
       </c>
-      <c r="I96" s="125">
+      <c r="I96" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H96))),"",H96*$D$33)</f>
       </c>
-      <c r="J96">
+      <c r="J96" s="133">
         <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
       </c>
-      <c r="K96"/>
-      <c r="L96"/>
+      <c r="K96" s="130"/>
+      <c r="L96" s="130"/>
     </row>
     <row r="97" ht="20" customHeight="1">
       <c r="A97"/>
       <c r="B97"/>
-      <c r="C97" t="n">
+      <c r="C97" s="133" t="n">
         <v>0.1</v>
       </c>
-      <c r="D97" s="125">
+      <c r="D97" s="145">
         <f>$D$45*(1-C97)-$G$51</f>
       </c>
-      <c r="E97" s="125">
+      <c r="E97" s="145">
         <f>$G$50/D97</f>
       </c>
-      <c r="F97">
+      <c r="F97" s="136">
         <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
       </c>
-      <c r="G97">
+      <c r="G97" s="136">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F97))),"",F97*$D$33)</f>
       </c>
-      <c r="H97" s="125">
+      <c r="H97" s="145">
         <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
       </c>
-      <c r="I97" s="125">
+      <c r="I97" s="145">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H97))),"",H97*$D$33)</f>
       </c>
-      <c r="J97">
+      <c r="J97" s="133">
         <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
       </c>
-      <c r="K97"/>
-      <c r="L97"/>
+      <c r="K97" s="130"/>
+      <c r="L97" s="130"/>
     </row>
     <row r="98" ht="20" customHeight="1">
       <c r="A98"/>
       <c r="B98"/>
-      <c r="C98" t="n">
+      <c r="C98" s="134" t="n">
         <v>0</v>
       </c>
-      <c r="D98" s="125">
+      <c r="D98" s="146">
         <f>$D$45*(1-C98)-$G$51</f>
       </c>
-      <c r="E98" s="125">
+      <c r="E98" s="146">
         <f>$G$50/D98</f>
       </c>
-      <c r="F98">
+      <c r="F98" s="137">
         <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
       </c>
-      <c r="G98">
+      <c r="G98" s="137">
         <f>IF(OR($D$33="",NOT(ISNUMBER(F98))),"",F98*$D$33)</f>
       </c>
-      <c r="H98" s="125">
+      <c r="H98" s="146">
         <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
       </c>
-      <c r="I98" s="125">
+      <c r="I98" s="146">
         <f>IF(OR($D$33="",NOT(ISNUMBER(H98))),"",H98*$D$33)</f>
       </c>
-      <c r="J98">
+      <c r="J98" s="134">
         <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
       </c>
-      <c r="K98" t="str">
+      <c r="K98" s="131" t="str">
         <v>沉没成本 / Quote</v>
       </c>
-      <c r="L98">
+      <c r="L98" s="131">
         <f>E98</f>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1">
       <c r="A99"/>
       <c r="B99"/>
-      <c r="C99"/>
-      <c r="D99"/>
-      <c r="E99"/>
-      <c r="F99"/>
-      <c r="G99"/>
-      <c r="H99"/>
-      <c r="I99"/>
-      <c r="J99"/>
-      <c r="K99"/>
-      <c r="L99"/>
+      <c r="C99" s="106"/>
+      <c r="D99" s="106"/>
+      <c r="E99" s="106"/>
+      <c r="F99" s="106"/>
+      <c r="G99" s="106"/>
+      <c r="H99" s="106"/>
+      <c r="I99" s="106"/>
+      <c r="J99" s="106"/>
+      <c r="K99" s="106"/>
+      <c r="L99" s="106"/>
     </row>
     <row r="100" ht="20" customHeight="1">
       <c r="A100"/>
       <c r="B100"/>
-      <c r="C100"/>
-      <c r="D100"/>
-      <c r="E100"/>
-      <c r="F100"/>
-      <c r="G100"/>
-      <c r="H100"/>
-      <c r="I100"/>
-      <c r="J100"/>
-      <c r="K100"/>
-      <c r="L100"/>
+      <c r="C100" s="106"/>
+      <c r="D100" s="106"/>
+      <c r="E100" s="106"/>
+      <c r="F100" s="106"/>
+      <c r="G100" s="106"/>
+      <c r="H100" s="106"/>
+      <c r="I100" s="106"/>
+      <c r="J100" s="106"/>
+      <c r="K100" s="106"/>
+      <c r="L100" s="106"/>
     </row>
     <row r="101" ht="20" customHeight="1">
       <c r="A101"/>
       <c r="B101"/>
-      <c r="C101"/>
-      <c r="D101"/>
-      <c r="E101"/>
-      <c r="F101"/>
-      <c r="G101"/>
-      <c r="H101"/>
-      <c r="I101"/>
-      <c r="J101"/>
-      <c r="K101"/>
-      <c r="L101"/>
+      <c r="C101" s="106"/>
+      <c r="D101" s="106"/>
+      <c r="E101" s="106"/>
+      <c r="F101" s="106"/>
+      <c r="G101" s="106"/>
+      <c r="H101" s="106"/>
+      <c r="I101" s="106"/>
+      <c r="J101" s="106"/>
+      <c r="K101" s="106"/>
+      <c r="L101" s="106"/>
     </row>
     <row r="102" ht="20" customHeight="1">
       <c r="A102"/>
       <c r="B102"/>
-      <c r="C102"/>
-      <c r="D102"/>
-      <c r="E102"/>
-      <c r="F102"/>
-      <c r="G102"/>
-      <c r="H102"/>
-      <c r="I102"/>
-      <c r="J102"/>
-      <c r="K102"/>
-      <c r="L102"/>
+      <c r="C102" s="106"/>
+      <c r="D102" s="106"/>
+      <c r="E102" s="106"/>
+      <c r="F102" s="106"/>
+      <c r="G102" s="106"/>
+      <c r="H102" s="106"/>
+      <c r="I102" s="106"/>
+      <c r="J102" s="106"/>
+      <c r="K102" s="106"/>
+      <c r="L102" s="106"/>
     </row>
     <row r="103" ht="20" customHeight="1">
       <c r="A103"/>
       <c r="B103"/>
-      <c r="C103"/>
-      <c r="D103"/>
-      <c r="E103"/>
-      <c r="F103"/>
-      <c r="G103"/>
-      <c r="H103"/>
-      <c r="I103"/>
-      <c r="J103"/>
-      <c r="K103"/>
-      <c r="L103"/>
+      <c r="C103" s="106"/>
+      <c r="D103" s="106"/>
+      <c r="E103" s="106"/>
+      <c r="F103" s="106"/>
+      <c r="G103" s="106"/>
+      <c r="H103" s="106"/>
+      <c r="I103" s="106"/>
+      <c r="J103" s="106"/>
+      <c r="K103" s="106"/>
+      <c r="L103" s="106"/>
     </row>
     <row r="104" ht="20" customHeight="1">
       <c r="A104"/>
       <c r="B104"/>
-      <c r="C104"/>
-      <c r="D104"/>
-      <c r="E104"/>
-      <c r="F104"/>
-      <c r="G104"/>
-      <c r="H104"/>
-      <c r="I104"/>
-      <c r="J104"/>
-      <c r="K104"/>
-      <c r="L104"/>
+      <c r="C104" s="106"/>
+      <c r="D104" s="106"/>
+      <c r="E104" s="106"/>
+      <c r="F104" s="106"/>
+      <c r="G104" s="106"/>
+      <c r="H104" s="106"/>
+      <c r="I104" s="106"/>
+      <c r="J104" s="106"/>
+      <c r="K104" s="106"/>
+      <c r="L104" s="106"/>
     </row>
     <row r="105" ht="20" customHeight="1">
       <c r="A105"/>
       <c r="B105"/>
-      <c r="C105"/>
-      <c r="D105"/>
-      <c r="E105"/>
-      <c r="F105"/>
-      <c r="G105"/>
-      <c r="H105"/>
-      <c r="I105"/>
-      <c r="J105"/>
-      <c r="K105"/>
-      <c r="L105"/>
+      <c r="C105" s="106"/>
+      <c r="D105" s="106"/>
+      <c r="E105" s="106"/>
+      <c r="F105" s="106"/>
+      <c r="G105" s="106"/>
+      <c r="H105" s="106"/>
+      <c r="I105" s="106"/>
+      <c r="J105" s="106"/>
+      <c r="K105" s="106"/>
+      <c r="L105" s="106"/>
     </row>
     <row r="106" ht="20" customHeight="1">
       <c r="A106"/>
       <c r="B106"/>
-      <c r="C106"/>
-      <c r="D106"/>
-      <c r="E106"/>
-      <c r="F106"/>
-      <c r="G106"/>
-      <c r="H106"/>
-      <c r="I106"/>
-      <c r="J106"/>
-      <c r="K106"/>
-      <c r="L106"/>
+      <c r="C106" s="106"/>
+      <c r="D106" s="106"/>
+      <c r="E106" s="106"/>
+      <c r="F106" s="106"/>
+      <c r="G106" s="106"/>
+      <c r="H106" s="106"/>
+      <c r="I106" s="106"/>
+      <c r="J106" s="106"/>
+      <c r="K106" s="106"/>
+      <c r="L106" s="106"/>
     </row>
     <row r="107" ht="20" customHeight="1">
       <c r="A107"/>
       <c r="B107"/>
-      <c r="C107"/>
-      <c r="D107"/>
-      <c r="E107"/>
-      <c r="F107"/>
-      <c r="G107"/>
-      <c r="H107"/>
-      <c r="I107"/>
-      <c r="J107"/>
-      <c r="K107"/>
-      <c r="L107"/>
+      <c r="C107" s="106"/>
+      <c r="D107" s="106"/>
+      <c r="E107" s="106"/>
+      <c r="F107" s="106"/>
+      <c r="G107" s="106"/>
+      <c r="H107" s="106"/>
+      <c r="I107" s="106"/>
+      <c r="J107" s="106"/>
+      <c r="K107" s="106"/>
+      <c r="L107" s="106"/>
     </row>
     <row r="108" ht="20" customHeight="1">
       <c r="A108"/>
       <c r="B108"/>
-      <c r="C108"/>
-      <c r="D108"/>
-      <c r="E108"/>
-      <c r="F108"/>
-      <c r="G108"/>
-      <c r="H108"/>
-      <c r="I108"/>
-      <c r="J108"/>
-      <c r="K108"/>
-      <c r="L108"/>
+      <c r="C108" s="106"/>
+      <c r="D108" s="106"/>
+      <c r="E108" s="106"/>
+      <c r="F108" s="106"/>
+      <c r="G108" s="106"/>
+      <c r="H108" s="106"/>
+      <c r="I108" s="106"/>
+      <c r="J108" s="106"/>
+      <c r="K108" s="106"/>
+      <c r="L108" s="106"/>
     </row>
     <row r="109" ht="20" customHeight="1">
       <c r="A109"/>
       <c r="B109"/>
-      <c r="C109"/>
-      <c r="D109"/>
-      <c r="E109"/>
-      <c r="F109"/>
-      <c r="G109"/>
-      <c r="H109"/>
-      <c r="I109"/>
-      <c r="J109"/>
-      <c r="K109"/>
-      <c r="L109"/>
+      <c r="C109" s="106"/>
+      <c r="D109" s="106"/>
+      <c r="E109" s="106"/>
+      <c r="F109" s="106"/>
+      <c r="G109" s="106"/>
+      <c r="H109" s="106"/>
+      <c r="I109" s="106"/>
+      <c r="J109" s="106"/>
+      <c r="K109" s="106"/>
+      <c r="L109" s="106"/>
     </row>
     <row r="110" ht="20" customHeight="1">
       <c r="A110"/>
       <c r="B110"/>
-      <c r="C110"/>
-      <c r="D110"/>
-      <c r="E110"/>
-      <c r="F110"/>
-      <c r="G110"/>
-      <c r="H110"/>
-      <c r="I110"/>
-      <c r="J110"/>
-      <c r="K110"/>
-      <c r="L110"/>
+      <c r="C110" s="106"/>
+      <c r="D110" s="106"/>
+      <c r="E110" s="106"/>
+      <c r="F110" s="106"/>
+      <c r="G110" s="106"/>
+      <c r="H110" s="106"/>
+      <c r="I110" s="106"/>
+      <c r="J110" s="106"/>
+      <c r="K110" s="106"/>
+      <c r="L110" s="106"/>
     </row>
     <row r="111" ht="20" customHeight="1">
       <c r="A111"/>
       <c r="B111"/>
-      <c r="C111"/>
-      <c r="D111"/>
-      <c r="E111"/>
-      <c r="F111"/>
-      <c r="G111"/>
-      <c r="H111"/>
-      <c r="I111"/>
-      <c r="J111"/>
-      <c r="K111"/>
-      <c r="L111"/>
+      <c r="C111" s="106"/>
+      <c r="D111" s="106"/>
+      <c r="E111" s="106"/>
+      <c r="F111" s="106"/>
+      <c r="G111" s="106"/>
+      <c r="H111" s="106"/>
+      <c r="I111" s="106"/>
+      <c r="J111" s="106"/>
+      <c r="K111" s="106"/>
+      <c r="L111" s="106"/>
     </row>
     <row r="112" ht="20" customHeight="1">
       <c r="A112"/>
       <c r="B112"/>
-      <c r="C112"/>
-      <c r="D112"/>
-      <c r="E112"/>
-      <c r="F112"/>
-      <c r="G112"/>
-      <c r="H112"/>
-      <c r="I112"/>
-      <c r="J112"/>
-      <c r="K112"/>
-      <c r="L112"/>
+      <c r="C112" s="106"/>
+      <c r="D112" s="106"/>
+      <c r="E112" s="106"/>
+      <c r="F112" s="106"/>
+      <c r="G112" s="106"/>
+      <c r="H112" s="106"/>
+      <c r="I112" s="106"/>
+      <c r="J112" s="106"/>
+      <c r="K112" s="106"/>
+      <c r="L112" s="106"/>
     </row>
     <row r="113" ht="20" customHeight="1">
       <c r="A113"/>
       <c r="B113"/>
-      <c r="C113"/>
-      <c r="D113"/>
-      <c r="E113"/>
-      <c r="F113"/>
-      <c r="G113"/>
-      <c r="H113"/>
-      <c r="I113"/>
-      <c r="J113"/>
-      <c r="K113"/>
-      <c r="L113"/>
+      <c r="C113" s="106"/>
+      <c r="D113" s="106"/>
+      <c r="E113" s="106"/>
+      <c r="F113" s="106"/>
+      <c r="G113" s="106"/>
+      <c r="H113" s="106"/>
+      <c r="I113" s="106"/>
+      <c r="J113" s="106"/>
+      <c r="K113" s="106"/>
+      <c r="L113" s="106"/>
     </row>
     <row r="114" ht="20" customHeight="1">
       <c r="A114"/>
       <c r="B114"/>
-      <c r="C114"/>
-      <c r="D114"/>
-      <c r="E114"/>
-      <c r="F114"/>
-      <c r="G114"/>
-      <c r="H114"/>
-      <c r="I114"/>
-      <c r="J114"/>
-      <c r="K114"/>
-      <c r="L114"/>
+      <c r="C114" s="106"/>
+      <c r="D114" s="106"/>
+      <c r="E114" s="106"/>
+      <c r="F114" s="106"/>
+      <c r="G114" s="106"/>
+      <c r="H114" s="106"/>
+      <c r="I114" s="106"/>
+      <c r="J114" s="106"/>
+      <c r="K114" s="106"/>
+      <c r="L114" s="106"/>
     </row>
     <row r="115" ht="20" customHeight="1">
       <c r="A115"/>
       <c r="B115"/>
-      <c r="C115"/>
-      <c r="D115"/>
-      <c r="E115"/>
-      <c r="F115"/>
-      <c r="G115"/>
-      <c r="H115"/>
-      <c r="I115"/>
-      <c r="J115"/>
-      <c r="K115"/>
-      <c r="L115"/>
+      <c r="C115" s="106"/>
+      <c r="D115" s="106"/>
+      <c r="E115" s="106"/>
+      <c r="F115" s="106"/>
+      <c r="G115" s="106"/>
+      <c r="H115" s="106"/>
+      <c r="I115" s="106"/>
+      <c r="J115" s="106"/>
+      <c r="K115" s="106"/>
+      <c r="L115" s="106"/>
     </row>
     <row r="116" ht="20" customHeight="1">
       <c r="A116"/>
       <c r="B116"/>
-      <c r="C116"/>
-      <c r="D116"/>
-      <c r="E116"/>
-      <c r="F116"/>
-      <c r="G116"/>
-      <c r="H116"/>
-      <c r="I116"/>
-      <c r="J116"/>
-      <c r="K116"/>
-      <c r="L116"/>
+      <c r="C116" s="106"/>
+      <c r="D116" s="106"/>
+      <c r="E116" s="106"/>
+      <c r="F116" s="106"/>
+      <c r="G116" s="106"/>
+      <c r="H116" s="106"/>
+      <c r="I116" s="106"/>
+      <c r="J116" s="106"/>
+      <c r="K116" s="106"/>
+      <c r="L116" s="106"/>
     </row>
     <row r="117" ht="20" customHeight="1">
       <c r="A117"/>
       <c r="B117"/>
-      <c r="C117"/>
-      <c r="D117"/>
-      <c r="E117"/>
-      <c r="F117"/>
-      <c r="G117"/>
-      <c r="H117"/>
-      <c r="I117"/>
-      <c r="J117"/>
-      <c r="K117"/>
-      <c r="L117"/>
+      <c r="C117" s="106"/>
+      <c r="D117" s="106"/>
+      <c r="E117" s="106"/>
+      <c r="F117" s="106"/>
+      <c r="G117" s="106"/>
+      <c r="H117" s="106"/>
+      <c r="I117" s="106"/>
+      <c r="J117" s="106"/>
+      <c r="K117" s="106"/>
+      <c r="L117" s="106"/>
     </row>
     <row r="118" ht="20" customHeight="1">
       <c r="A118"/>
       <c r="B118"/>
-      <c r="C118"/>
-      <c r="D118"/>
-      <c r="E118"/>
-      <c r="F118"/>
-      <c r="G118"/>
-      <c r="H118"/>
-      <c r="I118"/>
-      <c r="J118"/>
-      <c r="K118"/>
-      <c r="L118"/>
+      <c r="C118" s="106"/>
+      <c r="D118" s="106"/>
+      <c r="E118" s="106"/>
+      <c r="F118" s="106"/>
+      <c r="G118" s="106"/>
+      <c r="H118" s="106"/>
+      <c r="I118" s="106"/>
+      <c r="J118" s="106"/>
+      <c r="K118" s="106"/>
+      <c r="L118" s="106"/>
     </row>
     <row r="119" ht="20" customHeight="1">
       <c r="A119"/>
       <c r="B119"/>
-      <c r="C119"/>
-      <c r="D119"/>
-      <c r="E119"/>
-      <c r="F119"/>
-      <c r="G119"/>
-      <c r="H119"/>
-      <c r="I119"/>
-      <c r="J119"/>
-      <c r="K119"/>
-      <c r="L119"/>
+      <c r="C119" s="106"/>
+      <c r="D119" s="106"/>
+      <c r="E119" s="106"/>
+      <c r="F119" s="106"/>
+      <c r="G119" s="106"/>
+      <c r="H119" s="106"/>
+      <c r="I119" s="106"/>
+      <c r="J119" s="106"/>
+      <c r="K119" s="106"/>
+      <c r="L119" s="106"/>
     </row>
     <row r="120" ht="20" customHeight="1">
       <c r="A120"/>
       <c r="B120"/>
-      <c r="C120"/>
-      <c r="D120"/>
-      <c r="E120"/>
-      <c r="F120"/>
-      <c r="G120"/>
-      <c r="H120"/>
-      <c r="I120"/>
-      <c r="J120"/>
-      <c r="K120"/>
-      <c r="L120"/>
+      <c r="C120" s="106"/>
+      <c r="D120" s="106"/>
+      <c r="E120" s="106"/>
+      <c r="F120" s="106"/>
+      <c r="G120" s="106"/>
+      <c r="H120" s="106"/>
+      <c r="I120" s="106"/>
+      <c r="J120" s="106"/>
+      <c r="K120" s="106"/>
+      <c r="L120" s="106"/>
     </row>
     <row r="121" ht="20" customHeight="1">
       <c r="A121"/>
       <c r="B121"/>
-      <c r="C121"/>
-      <c r="D121"/>
-      <c r="E121"/>
-      <c r="F121"/>
-      <c r="G121"/>
-      <c r="H121"/>
-      <c r="I121"/>
-      <c r="J121"/>
-      <c r="K121"/>
-      <c r="L121"/>
+      <c r="C121" s="106"/>
+      <c r="D121" s="106"/>
+      <c r="E121" s="106"/>
+      <c r="F121" s="106"/>
+      <c r="G121" s="106"/>
+      <c r="H121" s="106"/>
+      <c r="I121" s="106"/>
+      <c r="J121" s="106"/>
+      <c r="K121" s="106"/>
+      <c r="L121" s="106"/>
     </row>
     <row r="122" ht="20" customHeight="1">
       <c r="A122"/>
       <c r="B122"/>
-      <c r="C122"/>
-      <c r="D122"/>
-      <c r="E122"/>
-      <c r="F122"/>
-      <c r="G122"/>
-      <c r="H122"/>
-      <c r="I122"/>
-      <c r="J122"/>
-      <c r="K122"/>
-      <c r="L122"/>
+      <c r="C122" s="106"/>
+      <c r="D122" s="106"/>
+      <c r="E122" s="106"/>
+      <c r="F122" s="106"/>
+      <c r="G122" s="106"/>
+      <c r="H122" s="106"/>
+      <c r="I122" s="106"/>
+      <c r="J122" s="106"/>
+      <c r="K122" s="106"/>
+      <c r="L122" s="106"/>
     </row>
     <row r="123" ht="20" customHeight="1">
       <c r="A123"/>
       <c r="B123"/>
-      <c r="C123"/>
-      <c r="D123"/>
-      <c r="E123"/>
-      <c r="F123"/>
-      <c r="G123"/>
-      <c r="H123"/>
-      <c r="I123"/>
-      <c r="J123"/>
-      <c r="K123"/>
-      <c r="L123"/>
+      <c r="C123" s="106"/>
+      <c r="D123" s="106"/>
+      <c r="E123" s="106"/>
+      <c r="F123" s="106"/>
+      <c r="G123" s="106"/>
+      <c r="H123" s="106"/>
+      <c r="I123" s="106"/>
+      <c r="J123" s="106"/>
+      <c r="K123" s="106"/>
+      <c r="L123" s="106"/>
     </row>
     <row r="124" ht="20" customHeight="1">
       <c r="A124"/>
       <c r="B124"/>
-      <c r="C124"/>
-      <c r="D124"/>
-      <c r="E124"/>
-      <c r="F124"/>
-      <c r="G124"/>
-      <c r="H124"/>
-      <c r="I124"/>
-      <c r="J124"/>
-      <c r="K124"/>
-      <c r="L124"/>
+      <c r="C124" s="106"/>
+      <c r="D124" s="106"/>
+      <c r="E124" s="106"/>
+      <c r="F124" s="106"/>
+      <c r="G124" s="106"/>
+      <c r="H124" s="106"/>
+      <c r="I124" s="106"/>
+      <c r="J124" s="106"/>
+      <c r="K124" s="106"/>
+      <c r="L124" s="106"/>
     </row>
     <row r="125" ht="20" customHeight="1">
       <c r="A125"/>
       <c r="B125"/>
-      <c r="C125"/>
-      <c r="D125"/>
-      <c r="E125"/>
-      <c r="F125"/>
-      <c r="G125"/>
-      <c r="H125"/>
-      <c r="I125"/>
-      <c r="J125"/>
-      <c r="K125"/>
-      <c r="L125"/>
+      <c r="C125" s="106"/>
+      <c r="D125" s="106"/>
+      <c r="E125" s="106"/>
+      <c r="F125" s="106"/>
+      <c r="G125" s="106"/>
+      <c r="H125" s="106"/>
+      <c r="I125" s="106"/>
+      <c r="J125" s="106"/>
+      <c r="K125" s="106"/>
+      <c r="L125" s="106"/>
     </row>
     <row r="126" ht="20" customHeight="1">
       <c r="A126"/>
       <c r="B126"/>
-      <c r="C126"/>
-      <c r="D126"/>
-      <c r="E126"/>
-      <c r="F126"/>
-      <c r="G126"/>
-      <c r="H126"/>
-      <c r="I126"/>
-      <c r="J126"/>
-      <c r="K126"/>
-      <c r="L126"/>
+      <c r="C126" s="106"/>
+      <c r="D126" s="106"/>
+      <c r="E126" s="106"/>
+      <c r="F126" s="106"/>
+      <c r="G126" s="106"/>
+      <c r="H126" s="106"/>
+      <c r="I126" s="106"/>
+      <c r="J126" s="106"/>
+      <c r="K126" s="106"/>
+      <c r="L126" s="106"/>
     </row>
     <row r="127" ht="20" customHeight="1">
       <c r="A127"/>
       <c r="B127"/>
-      <c r="C127"/>
-      <c r="D127"/>
-      <c r="E127"/>
-      <c r="F127"/>
-      <c r="G127"/>
-      <c r="H127"/>
-      <c r="I127"/>
-      <c r="J127"/>
-      <c r="K127"/>
-      <c r="L127"/>
+      <c r="C127" s="106"/>
+      <c r="D127" s="106"/>
+      <c r="E127" s="106"/>
+      <c r="F127" s="106"/>
+      <c r="G127" s="106"/>
+      <c r="H127" s="106"/>
+      <c r="I127" s="106"/>
+      <c r="J127" s="106"/>
+      <c r="K127" s="106"/>
+      <c r="L127" s="106"/>
     </row>
     <row r="128" ht="20" customHeight="1">
       <c r="A128"/>
       <c r="B128"/>
-      <c r="C128"/>
-      <c r="D128"/>
-      <c r="E128"/>
-      <c r="F128"/>
-      <c r="G128"/>
-      <c r="H128"/>
-      <c r="I128"/>
-      <c r="J128"/>
-      <c r="K128"/>
-      <c r="L128"/>
+      <c r="C128" s="106"/>
+      <c r="D128" s="106"/>
+      <c r="E128" s="106"/>
+      <c r="F128" s="106"/>
+      <c r="G128" s="106"/>
+      <c r="H128" s="106"/>
+      <c r="I128" s="106"/>
+      <c r="J128" s="106"/>
+      <c r="K128" s="106"/>
+      <c r="L128" s="106"/>
     </row>
     <row r="129" ht="20" customHeight="1">
       <c r="A129"/>
       <c r="B129"/>
-      <c r="C129"/>
-      <c r="D129"/>
-      <c r="E129"/>
-      <c r="F129"/>
-      <c r="G129"/>
-      <c r="H129"/>
-      <c r="I129"/>
-      <c r="J129"/>
-      <c r="K129"/>
-      <c r="L129"/>
+      <c r="C129" s="106"/>
+      <c r="D129" s="106"/>
+      <c r="E129" s="106"/>
+      <c r="F129" s="106"/>
+      <c r="G129" s="106"/>
+      <c r="H129" s="106"/>
+      <c r="I129" s="106"/>
+      <c r="J129" s="106"/>
+      <c r="K129" s="106"/>
+      <c r="L129" s="106"/>
     </row>
     <row r="130" ht="20" customHeight="1">
       <c r="A130"/>
       <c r="B130"/>
-      <c r="C130"/>
-      <c r="D130"/>
-      <c r="E130"/>
-      <c r="F130"/>
-      <c r="G130"/>
-      <c r="H130"/>
-      <c r="I130"/>
-      <c r="J130"/>
-      <c r="K130"/>
-      <c r="L130"/>
+      <c r="C130" s="106"/>
+      <c r="D130" s="106"/>
+      <c r="E130" s="106"/>
+      <c r="F130" s="106"/>
+      <c r="G130" s="106"/>
+      <c r="H130" s="106"/>
+      <c r="I130" s="106"/>
+      <c r="J130" s="106"/>
+      <c r="K130" s="106"/>
+      <c r="L130" s="106"/>
     </row>
     <row r="131" ht="20" customHeight="1">
       <c r="A131"/>
       <c r="B131"/>
-      <c r="C131"/>
-      <c r="D131"/>
-      <c r="E131"/>
-      <c r="F131"/>
-      <c r="G131"/>
-      <c r="H131"/>
-      <c r="I131"/>
-      <c r="J131"/>
-      <c r="K131"/>
-      <c r="L131"/>
+      <c r="C131" s="106"/>
+      <c r="D131" s="106"/>
+      <c r="E131" s="106"/>
+      <c r="F131" s="106"/>
+      <c r="G131" s="106"/>
+      <c r="H131" s="106"/>
+      <c r="I131" s="106"/>
+      <c r="J131" s="106"/>
+      <c r="K131" s="106"/>
+      <c r="L131" s="106"/>
     </row>
     <row r="132" ht="20" customHeight="1">
       <c r="A132"/>
       <c r="B132"/>
-      <c r="C132"/>
-      <c r="D132"/>
-      <c r="E132"/>
-      <c r="F132"/>
-      <c r="G132"/>
-      <c r="H132"/>
-      <c r="I132"/>
-      <c r="J132"/>
-      <c r="K132"/>
-      <c r="L132"/>
+      <c r="C132" s="106"/>
+      <c r="D132" s="106"/>
+      <c r="E132" s="106"/>
+      <c r="F132" s="106"/>
+      <c r="G132" s="106"/>
+      <c r="H132" s="106"/>
+      <c r="I132" s="106"/>
+      <c r="J132" s="106"/>
+      <c r="K132" s="106"/>
+      <c r="L132" s="106"/>
     </row>
     <row r="133" ht="20" customHeight="1">
       <c r="A133"/>
       <c r="B133"/>
-      <c r="C133"/>
-      <c r="D133"/>
-      <c r="E133"/>
-      <c r="F133"/>
-      <c r="G133"/>
-      <c r="H133"/>
-      <c r="I133"/>
-      <c r="J133"/>
-      <c r="K133"/>
-      <c r="L133"/>
+      <c r="C133" s="106"/>
+      <c r="D133" s="106"/>
+      <c r="E133" s="106"/>
+      <c r="F133" s="106"/>
+      <c r="G133" s="106"/>
+      <c r="H133" s="106"/>
+      <c r="I133" s="106"/>
+      <c r="J133" s="106"/>
+      <c r="K133" s="106"/>
+      <c r="L133" s="106"/>
     </row>
     <row r="134" ht="20" customHeight="1">
       <c r="A134"/>
       <c r="B134"/>
-      <c r="C134"/>
-      <c r="D134"/>
-      <c r="E134"/>
-      <c r="F134"/>
-      <c r="G134"/>
-      <c r="H134"/>
-      <c r="I134"/>
-      <c r="J134"/>
-      <c r="K134"/>
-      <c r="L134"/>
+      <c r="C134" s="106"/>
+      <c r="D134" s="106"/>
+      <c r="E134" s="106"/>
+      <c r="F134" s="106"/>
+      <c r="G134" s="106"/>
+      <c r="H134" s="106"/>
+      <c r="I134" s="106"/>
+      <c r="J134" s="106"/>
+      <c r="K134" s="106"/>
+      <c r="L134" s="106"/>
     </row>
     <row r="135" ht="20" customHeight="1">
       <c r="A135"/>
       <c r="B135"/>
-      <c r="C135"/>
-      <c r="D135"/>
-      <c r="E135"/>
-      <c r="F135"/>
-      <c r="G135"/>
-      <c r="H135"/>
-      <c r="I135"/>
-      <c r="J135"/>
-      <c r="K135"/>
-      <c r="L135"/>
+      <c r="C135" s="106"/>
+      <c r="D135" s="106"/>
+      <c r="E135" s="106"/>
+      <c r="F135" s="106"/>
+      <c r="G135" s="106"/>
+      <c r="H135" s="106"/>
+      <c r="I135" s="106"/>
+      <c r="J135" s="106"/>
+      <c r="K135" s="106"/>
+      <c r="L135" s="106"/>
     </row>
     <row r="136" ht="20" customHeight="1">
       <c r="A136"/>
       <c r="B136"/>
-      <c r="C136"/>
-      <c r="D136"/>
-      <c r="E136"/>
-      <c r="F136"/>
-      <c r="G136"/>
-      <c r="H136"/>
-      <c r="I136"/>
-      <c r="J136"/>
-      <c r="K136"/>
-      <c r="L136"/>
+      <c r="C136" s="106"/>
+      <c r="D136" s="106"/>
+      <c r="E136" s="106"/>
+      <c r="F136" s="106"/>
+      <c r="G136" s="106"/>
+      <c r="H136" s="106"/>
+      <c r="I136" s="106"/>
+      <c r="J136" s="106"/>
+      <c r="K136" s="106"/>
+      <c r="L136" s="106"/>
     </row>
     <row r="137" ht="20" customHeight="1">
       <c r="A137"/>
       <c r="B137"/>
-      <c r="C137"/>
-      <c r="D137"/>
-      <c r="E137"/>
-      <c r="F137"/>
-      <c r="G137"/>
-      <c r="H137"/>
-      <c r="I137"/>
-      <c r="J137"/>
-      <c r="K137"/>
-      <c r="L137"/>
+      <c r="C137" s="106"/>
+      <c r="D137" s="106"/>
+      <c r="E137" s="106"/>
+      <c r="F137" s="106"/>
+      <c r="G137" s="106"/>
+      <c r="H137" s="106"/>
+      <c r="I137" s="106"/>
+      <c r="J137" s="106"/>
+      <c r="K137" s="106"/>
+      <c r="L137" s="106"/>
     </row>
     <row r="138" ht="20" customHeight="1">
       <c r="A138"/>
       <c r="B138"/>
-      <c r="C138"/>
-      <c r="D138"/>
-      <c r="E138"/>
-      <c r="F138"/>
-      <c r="G138"/>
-      <c r="H138"/>
-      <c r="I138"/>
-      <c r="J138"/>
-      <c r="K138"/>
-      <c r="L138"/>
+      <c r="C138" s="106"/>
+      <c r="D138" s="106"/>
+      <c r="E138" s="106"/>
+      <c r="F138" s="106"/>
+      <c r="G138" s="106"/>
+      <c r="H138" s="106"/>
+      <c r="I138" s="106"/>
+      <c r="J138" s="106"/>
+      <c r="K138" s="106"/>
+      <c r="L138" s="106"/>
     </row>
     <row r="139" ht="20" customHeight="1">
       <c r="A139"/>
       <c r="B139"/>
-      <c r="C139"/>
-      <c r="D139"/>
-      <c r="E139"/>
-      <c r="F139"/>
-      <c r="G139"/>
-      <c r="H139"/>
-      <c r="I139"/>
-      <c r="J139"/>
-      <c r="K139"/>
-      <c r="L139"/>
+      <c r="C139" s="106"/>
+      <c r="D139" s="106"/>
+      <c r="E139" s="106"/>
+      <c r="F139" s="106"/>
+      <c r="G139" s="106"/>
+      <c r="H139" s="106"/>
+      <c r="I139" s="106"/>
+      <c r="J139" s="106"/>
+      <c r="K139" s="106"/>
+      <c r="L139" s="106"/>
     </row>
     <row r="140" ht="20" customHeight="1">
       <c r="A140"/>
       <c r="B140"/>
-      <c r="C140"/>
-      <c r="D140"/>
-      <c r="E140"/>
-      <c r="F140"/>
-      <c r="G140"/>
-      <c r="H140"/>
-      <c r="I140"/>
-      <c r="J140"/>
-      <c r="K140"/>
-      <c r="L140"/>
-    </row>
-    <row r="141">
+      <c r="C140" s="106"/>
+      <c r="D140" s="106"/>
+      <c r="E140" s="106"/>
+      <c r="F140" s="106"/>
+      <c r="G140" s="106"/>
+      <c r="H140" s="106"/>
+      <c r="I140" s="106"/>
+      <c r="J140" s="106"/>
+      <c r="K140" s="106"/>
+      <c r="L140" s="106"/>
+    </row>
+    <row r="141" ht="20" customHeight="1">
       <c r="A141"/>
       <c r="B141"/>
-      <c r="C141"/>
-      <c r="D141"/>
-      <c r="E141"/>
-      <c r="F141"/>
-      <c r="G141"/>
-      <c r="H141"/>
-      <c r="I141"/>
-      <c r="J141"/>
-      <c r="K141"/>
-      <c r="L141"/>
-    </row>
-    <row r="142">
+      <c r="C141" s="106"/>
+      <c r="D141" s="106"/>
+      <c r="E141" s="106"/>
+      <c r="F141" s="106"/>
+      <c r="G141" s="106"/>
+      <c r="H141" s="106"/>
+      <c r="I141" s="106"/>
+      <c r="J141" s="106"/>
+      <c r="K141" s="106"/>
+      <c r="L141" s="106"/>
+    </row>
+    <row r="142" ht="20" customHeight="1">
       <c r="A142"/>
       <c r="B142"/>
-      <c r="C142"/>
-      <c r="D142"/>
-      <c r="E142"/>
-      <c r="F142"/>
-      <c r="G142"/>
-      <c r="H142"/>
-      <c r="I142"/>
-      <c r="J142"/>
-      <c r="K142"/>
-      <c r="L142"/>
-    </row>
-    <row r="143">
+      <c r="C142" s="106"/>
+      <c r="D142" s="106"/>
+      <c r="E142" s="106"/>
+      <c r="F142" s="106"/>
+      <c r="G142" s="106"/>
+      <c r="H142" s="106"/>
+      <c r="I142" s="106"/>
+      <c r="J142" s="106"/>
+      <c r="K142" s="106"/>
+      <c r="L142" s="106"/>
+    </row>
+    <row r="143" ht="20" customHeight="1">
       <c r="A143"/>
       <c r="B143"/>
-      <c r="C143"/>
-      <c r="D143"/>
-      <c r="E143"/>
-      <c r="F143"/>
-      <c r="G143"/>
-      <c r="H143"/>
-      <c r="I143"/>
-      <c r="J143"/>
-      <c r="K143"/>
-      <c r="L143"/>
-    </row>
-    <row r="144">
+      <c r="C143" s="106"/>
+      <c r="D143" s="106"/>
+      <c r="E143" s="106"/>
+      <c r="F143" s="106"/>
+      <c r="G143" s="106"/>
+      <c r="H143" s="106"/>
+      <c r="I143" s="106"/>
+      <c r="J143" s="106"/>
+      <c r="K143" s="106"/>
+      <c r="L143" s="106"/>
+    </row>
+    <row r="144" ht="20" customHeight="1">
       <c r="A144"/>
       <c r="B144"/>
-      <c r="C144"/>
-      <c r="D144"/>
-      <c r="E144"/>
-      <c r="F144"/>
-      <c r="G144"/>
-      <c r="H144"/>
-      <c r="I144"/>
-      <c r="J144"/>
-      <c r="K144"/>
-      <c r="L144"/>
-    </row>
-    <row r="145">
+      <c r="C144" s="106"/>
+      <c r="D144" s="106"/>
+      <c r="E144" s="106"/>
+      <c r="F144" s="106"/>
+      <c r="G144" s="106"/>
+      <c r="H144" s="106"/>
+      <c r="I144" s="106"/>
+      <c r="J144" s="106"/>
+      <c r="K144" s="106"/>
+      <c r="L144" s="106"/>
+    </row>
+    <row r="145" ht="20" customHeight="1">
       <c r="A145"/>
       <c r="B145"/>
-      <c r="C145"/>
-      <c r="D145"/>
-      <c r="E145"/>
-      <c r="F145"/>
-      <c r="G145"/>
-      <c r="H145"/>
-      <c r="I145"/>
-      <c r="J145"/>
-      <c r="K145"/>
-      <c r="L145"/>
-    </row>
-    <row r="146">
+      <c r="C145" s="106"/>
+      <c r="D145" s="106"/>
+      <c r="E145" s="106"/>
+      <c r="F145" s="106"/>
+      <c r="G145" s="106"/>
+      <c r="H145" s="106"/>
+      <c r="I145" s="106"/>
+      <c r="J145" s="106"/>
+      <c r="K145" s="106"/>
+      <c r="L145" s="106"/>
+    </row>
+    <row r="146" ht="20" customHeight="1">
       <c r="A146"/>
       <c r="B146"/>
-      <c r="C146"/>
-      <c r="D146"/>
-      <c r="E146"/>
-      <c r="F146"/>
-      <c r="G146"/>
-      <c r="H146"/>
-      <c r="I146"/>
-      <c r="J146"/>
-      <c r="K146"/>
-      <c r="L146"/>
-    </row>
-    <row r="147">
+      <c r="C146" s="106"/>
+      <c r="D146" s="106"/>
+      <c r="E146" s="106"/>
+      <c r="F146" s="106"/>
+      <c r="G146" s="106"/>
+      <c r="H146" s="106"/>
+      <c r="I146" s="106"/>
+      <c r="J146" s="106"/>
+      <c r="K146" s="106"/>
+      <c r="L146" s="106"/>
+    </row>
+    <row r="147" ht="20" customHeight="1">
       <c r="A147"/>
       <c r="B147"/>
-      <c r="C147"/>
-      <c r="D147"/>
-      <c r="E147"/>
-      <c r="F147"/>
-      <c r="G147"/>
-      <c r="H147"/>
-      <c r="I147"/>
-      <c r="J147"/>
-      <c r="K147"/>
-      <c r="L147"/>
-    </row>
-    <row r="148">
+      <c r="C147" s="106"/>
+      <c r="D147" s="106"/>
+      <c r="E147" s="106"/>
+      <c r="F147" s="106"/>
+      <c r="G147" s="106"/>
+      <c r="H147" s="106"/>
+      <c r="I147" s="106"/>
+      <c r="J147" s="106"/>
+      <c r="K147" s="106"/>
+      <c r="L147" s="106"/>
+    </row>
+    <row r="148" ht="20" customHeight="1">
       <c r="A148"/>
       <c r="B148"/>
-      <c r="C148"/>
-      <c r="D148"/>
-      <c r="E148"/>
-      <c r="F148"/>
-      <c r="G148"/>
-      <c r="H148"/>
-      <c r="I148"/>
-      <c r="J148"/>
-      <c r="K148"/>
-      <c r="L148"/>
-    </row>
-    <row r="149">
+      <c r="C148" s="106"/>
+      <c r="D148" s="106"/>
+      <c r="E148" s="106"/>
+      <c r="F148" s="106"/>
+      <c r="G148" s="106"/>
+      <c r="H148" s="106"/>
+      <c r="I148" s="106"/>
+      <c r="J148" s="106"/>
+      <c r="K148" s="106"/>
+      <c r="L148" s="106"/>
+    </row>
+    <row r="149" ht="20" customHeight="1">
       <c r="A149"/>
       <c r="B149"/>
-      <c r="C149"/>
-      <c r="D149"/>
-      <c r="E149"/>
-      <c r="F149"/>
-      <c r="G149"/>
-      <c r="H149"/>
-      <c r="I149"/>
-      <c r="J149"/>
-      <c r="K149"/>
-      <c r="L149"/>
-    </row>
-    <row r="150">
+      <c r="C149" s="106"/>
+      <c r="D149" s="106"/>
+      <c r="E149" s="106"/>
+      <c r="F149" s="106"/>
+      <c r="G149" s="106"/>
+      <c r="H149" s="106"/>
+      <c r="I149" s="106"/>
+      <c r="J149" s="106"/>
+      <c r="K149" s="106"/>
+      <c r="L149" s="106"/>
+    </row>
+    <row r="150" ht="20" customHeight="1">
       <c r="A150"/>
       <c r="B150"/>
-      <c r="C150"/>
-      <c r="D150"/>
-      <c r="E150"/>
-      <c r="F150"/>
-      <c r="G150"/>
-      <c r="H150"/>
-      <c r="I150"/>
-      <c r="J150"/>
-      <c r="K150"/>
-      <c r="L150"/>
+      <c r="C150" s="106"/>
+      <c r="D150" s="106"/>
+      <c r="E150" s="106"/>
+      <c r="F150" s="106"/>
+      <c r="G150" s="106"/>
+      <c r="H150" s="106"/>
+      <c r="I150" s="106"/>
+      <c r="J150" s="106"/>
+      <c r="K150" s="106"/>
+      <c r="L150" s="106"/>
     </row>
   </sheetData>
   <mergeCells>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R595ba0064e4749df"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R1fa0ef5cf6d64459"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R74814a66d1064eec"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rb96d4fcf946144c7"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -164,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="150">
+  <x:cellXfs count="151">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -606,12 +606,15 @@
     </x:xf>
     <x:xf numFmtId="207" fontId="11" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="23">
+  <x:dxfs count="27">
     <x:dxf>
       <x:font>
         <x:b/>
@@ -744,6 +747,50 @@
     </x:dxf>
     <x:dxf>
       <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
+    </x:dxf>
+    <x:dxf>
+      <x:font>
+        <x:b/>
+        <x:color rgb="FF7D2638"/>
+      </x:font>
+      <x:fill>
+        <x:patternFill patternType="solid">
+          <x:bgColor rgb="FFFDE8E7"/>
+        </x:patternFill>
+      </x:fill>
     </x:dxf>
   </x:dxfs>
 </x:styleSheet>
@@ -1284,7 +1331,7 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="121">
-        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
+        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
       </c>
       <c r="E18" s="62">
         <f>$D$7</f>
@@ -1293,7 +1340,7 @@
         <v>原生币 Gas 储备</v>
       </c>
       <c r="G18" s="74">
-        <f>$D$32*MAX(0,$G$11)</f>
+        <f>$D$53*MAX(0,$G$11)</f>
       </c>
       <c r="H18" s="62" t="str">
         <v>ETH</v>
@@ -1316,7 +1363,7 @@
         <v>Quote 折算 / USDT</v>
       </c>
       <c r="D19" s="122">
-        <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$33&gt;0,$D$18*$D$33,"")),"")</f>
+        <f>IF(ISNUMBER($D$18),IF($D$18=0,0,IF($D$55&gt;0,$D$18*$D$55,"")),"")</f>
       </c>
       <c r="E19" s="106" t="str">
         <v>USDT</v>
@@ -1334,7 +1381,7 @@
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J19" s="123">
-        <f>IF($D$7="ETH",$D$33,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+        <f>IF($D$7="ETH",$D$55,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="106"/>
@@ -1375,10 +1422,10 @@
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="106">
-        <f>"预算 "&amp;TEXT($D$31,"0%")&amp;" 理论资金"</f>
+        <f>"预算 "&amp;TEXT($D$52,"0%")&amp;" 理论资金"</f>
       </c>
       <c r="D22" s="122">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$45="","",$J$41+$J$45))</f>
       </c>
       <c r="E22" s="106">
         <f>$D$7</f>
@@ -1400,7 +1447,7 @@
         <v>额外内盘资金</v>
       </c>
       <c r="D23" s="122">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$41="","",$J$41*MAX(0,$G$7-1)))</f>
       </c>
       <c r="E23" s="106">
         <f>$D$7</f>
@@ -1424,7 +1471,7 @@
         <v>洗筹损耗</v>
       </c>
       <c r="D24" s="122">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
       </c>
       <c r="E24" s="106">
         <f>$D$7</f>
@@ -1472,7 +1519,7 @@
         <v>恢复目标控筹资金</v>
       </c>
       <c r="D26" s="122">
-        <f>IF(LEFT($D$30,2)&lt;&gt;"可达","",0)</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
       </c>
       <c r="E26" s="106">
         <f>$D$7</f>
@@ -1552,16 +1599,12 @@
     <row r="30" ht="32" customHeight="1">
       <c r="A30" s="2"/>
       <c r="B30" s="2"/>
-      <c r="C30" s="107" t="str">
-        <v>目标是否可达</v>
-      </c>
-      <c r="D30" s="107">
-        <f>IF($J$51&lt;&gt;"参数有效",$J$51,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$53),"Creator Tax无效",IF($D$31&gt;=$G$32,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
-      </c>
-      <c r="E30" s="106"/>
-      <c r="F30" s="106"/>
-      <c r="G30" s="106"/>
-      <c r="H30" s="106"/>
+      <c r="C30"/>
+      <c r="D30"/>
+      <c r="E30"/>
+      <c r="F30"/>
+      <c r="G30"/>
+      <c r="H30"/>
       <c r="I30" s="107" t="str">
         <v>卖出含税费率</v>
       </c>
@@ -1571,97 +1614,71 @@
       <c r="K30" s="106"/>
       <c r="L30" s="106"/>
     </row>
-    <row r="31" ht="20" customHeight="1">
+    <row r="31" customHeight="1" hidden="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
-      <c r="C31" s="107" t="str">
-        <v>预算使用控筹率</v>
-      </c>
-      <c r="D31" s="124">
-        <f>$D$8+1%</f>
-      </c>
-      <c r="E31" s="106"/>
-      <c r="F31" s="106"/>
-      <c r="G31" s="106"/>
-      <c r="H31" s="106"/>
+      <c r="C31"/>
+      <c r="D31"/>
+      <c r="E31"/>
+      <c r="F31"/>
+      <c r="G31"/>
+      <c r="H31"/>
       <c r="I31" s="106"/>
       <c r="J31" s="106"/>
       <c r="K31" s="106"/>
       <c r="L31" s="106"/>
     </row>
-    <row r="32" ht="20" customHeight="1">
+    <row r="32" customHeight="1" hidden="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
-      <c r="C32" s="107" t="str">
-        <v>地址总数</v>
-      </c>
-      <c r="D32" s="122">
-        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
-      </c>
-      <c r="E32" s="106"/>
-      <c r="F32" s="107" t="str">
-        <v>当前控筹上限</v>
-      </c>
-      <c r="G32" s="124">
-        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
-      </c>
-      <c r="H32" s="106"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32"/>
+      <c r="F32"/>
+      <c r="G32"/>
+      <c r="H32"/>
       <c r="I32" s="106"/>
       <c r="J32" s="106"/>
       <c r="K32" s="106"/>
       <c r="L32" s="106"/>
     </row>
-    <row r="33" ht="20" customHeight="1">
+    <row r="33" customHeight="1" hidden="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
-      <c r="C33" s="107" t="str">
-        <v>Quote 价格 / USDT</v>
-      </c>
-      <c r="D33" s="123">
-        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
-      </c>
-      <c r="E33" s="106"/>
-      <c r="F33" s="106"/>
-      <c r="G33" s="106"/>
-      <c r="H33" s="106"/>
+      <c r="C33"/>
+      <c r="D33"/>
+      <c r="E33"/>
+      <c r="F33"/>
+      <c r="G33"/>
+      <c r="H33"/>
       <c r="I33" s="106"/>
       <c r="J33" s="106"/>
       <c r="K33" s="106"/>
       <c r="L33" s="106"/>
     </row>
-    <row r="34" ht="20" customHeight="1">
+    <row r="34" customHeight="1" hidden="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
-      <c r="C34" s="107" t="str">
-        <v>行情时间 / UTC</v>
-      </c>
-      <c r="D34" s="126">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
-      </c>
-      <c r="E34" s="106"/>
-      <c r="F34" s="106"/>
-      <c r="G34" s="106"/>
-      <c r="H34" s="106"/>
+      <c r="C34"/>
+      <c r="D34"/>
+      <c r="E34"/>
+      <c r="F34"/>
+      <c r="G34"/>
+      <c r="H34"/>
       <c r="I34" s="106"/>
       <c r="J34" s="106"/>
       <c r="K34" s="106"/>
       <c r="L34" s="106"/>
     </row>
-    <row r="35" ht="20" customHeight="1">
+    <row r="35" customHeight="1" hidden="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="107" t="str">
-        <v>价格采用方式</v>
-      </c>
-      <c r="D35" s="106">
-        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
-      </c>
-      <c r="E35" s="106"/>
-      <c r="F35" s="107">
-        <f>IF($D$9&lt;&gt;"",IF($D$33="","手动价格无效","手动价格"),IF($D$33="","缺少价格","每日行情"))</f>
-      </c>
-      <c r="G35" s="107"/>
-      <c r="H35" s="107"/>
+      <c r="C35"/>
+      <c r="D35"/>
+      <c r="E35"/>
+      <c r="F35"/>
+      <c r="G35"/>
+      <c r="H35"/>
       <c r="I35" s="106"/>
       <c r="J35" s="106"/>
       <c r="K35" s="106"/>
@@ -1800,7 +1817,7 @@
         <v>目标+1% Pool TOKEN</v>
       </c>
       <c r="J42" s="108">
-        <f>IF($D$31&lt;$G$32,$D$45*(1-$D$31)-$G$51,"")</f>
+        <f>IF($D$52&lt;$D$54,$D$45*(1-$D$52)-$G$51,"")</f>
       </c>
       <c r="K42" s="107"/>
       <c r="L42" s="107"/>
@@ -1874,7 +1891,7 @@
         <v>外盘含费投入 / Quote</v>
       </c>
       <c r="J45" s="108">
-        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$31-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
       </c>
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
@@ -2004,8 +2021,12 @@
     <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A51"/>
       <c r="B51"/>
-      <c r="C51" s="107"/>
-      <c r="D51" s="108"/>
+      <c r="C51" s="107" t="str">
+        <v>目标是否可达</v>
+      </c>
+      <c r="D51" s="108">
+        <f>IF($J$51&lt;&gt;"参数有效",$J$51,IF(OR($D$8&lt;0,$D$8&gt;=1),"目标控筹率无效",IF(OR($J$7&lt;0,$J$7&gt;$G$53),"Creator Tax无效",IF($D$52&gt;=$D$54,"目标+1%不可达",IF($J$9="否","可达；Snipe税未计","可达")))))</f>
+      </c>
       <c r="E51" s="107"/>
       <c r="F51" s="107" t="str">
         <v>Locker TOKEN</v>
@@ -2026,8 +2047,12 @@
     <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A52"/>
       <c r="B52"/>
-      <c r="C52" s="107"/>
-      <c r="D52" s="108"/>
+      <c r="C52" s="107" t="str">
+        <v>预算使用控筹率</v>
+      </c>
+      <c r="D52" s="113">
+        <f>$D$8+1%</f>
+      </c>
       <c r="E52" s="107"/>
       <c r="F52" s="107" t="str">
         <v>Snipe 窗口</v>
@@ -2044,8 +2069,12 @@
     <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A53"/>
       <c r="B53"/>
-      <c r="C53" s="107"/>
-      <c r="D53" s="108"/>
+      <c r="C53" s="107" t="str">
+        <v>地址总数</v>
+      </c>
+      <c r="D53" s="111">
+        <f>MAX(0,$G$8)*MAX(0,$G$7)+MAX(0,$G$9)+MAX(0,$G$10)</f>
+      </c>
       <c r="E53" s="107"/>
       <c r="F53" s="107" t="str">
         <v>Creator Tax 上限</v>
@@ -2062,11 +2091,19 @@
     <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A54"/>
       <c r="B54"/>
-      <c r="C54" s="107"/>
-      <c r="D54" s="108"/>
+      <c r="C54" s="107" t="str">
+        <v>当前控筹上限</v>
+      </c>
+      <c r="D54" s="113">
+        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
+      </c>
       <c r="E54" s="107"/>
-      <c r="F54" s="107"/>
-      <c r="G54" s="108"/>
+      <c r="F54" s="107" t="str">
+        <v>价格采用方式</v>
+      </c>
+      <c r="G54" s="108">
+        <f>IF($D$9&lt;&gt;"","手动覆盖","每日行情")</f>
+      </c>
       <c r="H54" s="107"/>
       <c r="I54" s="107" t="str">
         <v>洗后持仓保留比例</v>
@@ -2080,11 +2117,19 @@
     <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A55"/>
       <c r="B55"/>
-      <c r="C55" s="107"/>
-      <c r="D55" s="108"/>
+      <c r="C55" s="107" t="str">
+        <v>Quote 价格 / USDT</v>
+      </c>
+      <c r="D55" s="108">
+        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+      </c>
       <c r="E55" s="107"/>
-      <c r="F55" s="107"/>
-      <c r="G55" s="108"/>
+      <c r="F55" s="107" t="str">
+        <v>价格状态</v>
+      </c>
+      <c r="G55" s="108">
+        <f>IF($D$9&lt;&gt;"",IF($D$55="","手动价格无效","手动价格"),IF($D$55="","缺少价格","每日行情"))</f>
+      </c>
       <c r="H55" s="107"/>
       <c r="I55" s="107" t="str">
         <v>目标外盘 Pool TOKEN</v>
@@ -2096,8 +2141,12 @@
     <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
       <c r="A56"/>
       <c r="B56"/>
-      <c r="C56" s="107"/>
-      <c r="D56" s="108"/>
+      <c r="C56" s="107" t="str">
+        <v>行情时间 / UTC</v>
+      </c>
+      <c r="D56" s="150">
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
+      </c>
       <c r="E56" s="107"/>
       <c r="F56" s="107"/>
       <c r="G56" s="108"/>
@@ -2178,13 +2227,13 @@
         <f>IF(OR(D59="",E59=""),"",E59/D59)</f>
       </c>
       <c r="G59" s="135">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F59))),"",F59*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F59))),"",F59*$D$55)</f>
       </c>
       <c r="H59" s="144">
         <f>IF(NOT(ISNUMBER(F59)),"",F59*$D$45)</f>
       </c>
       <c r="I59" s="144">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H59))),"",H59*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H59))),"",H59*$D$55)</f>
       </c>
       <c r="J59" s="144">
         <f>0</f>
@@ -2212,13 +2261,13 @@
         <f>IF(OR(D60="",E60=""),"",E60/D60)</f>
       </c>
       <c r="G60" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F60))),"",F60*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F60))),"",F60*$D$55)</f>
       </c>
       <c r="H60" s="145">
         <f>IF(NOT(ISNUMBER(F60)),"",F60*$D$45)</f>
       </c>
       <c r="I60" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H60))),"",H60*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H60))),"",H60*$D$55)</f>
       </c>
       <c r="J60" s="145">
         <f>E60-E59</f>
@@ -2246,13 +2295,13 @@
         <f>IF(OR(D61="",E61=""),"",E61/D61)</f>
       </c>
       <c r="G61" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F61))),"",F61*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F61))),"",F61*$D$55)</f>
       </c>
       <c r="H61" s="145">
         <f>IF(NOT(ISNUMBER(F61)),"",F61*$D$45)</f>
       </c>
       <c r="I61" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H61))),"",H61*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H61))),"",H61*$D$55)</f>
       </c>
       <c r="J61" s="145">
         <f>E61-E60</f>
@@ -2280,13 +2329,13 @@
         <f>IF(OR(D62="",E62=""),"",E62/D62)</f>
       </c>
       <c r="G62" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F62))),"",F62*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F62))),"",F62*$D$55)</f>
       </c>
       <c r="H62" s="145">
         <f>IF(NOT(ISNUMBER(F62)),"",F62*$D$45)</f>
       </c>
       <c r="I62" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H62))),"",H62*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H62))),"",H62*$D$55)</f>
       </c>
       <c r="J62" s="145">
         <f>E62-E61</f>
@@ -2314,13 +2363,13 @@
         <f>IF(OR(D63="",E63=""),"",E63/D63)</f>
       </c>
       <c r="G63" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F63))),"",F63*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F63))),"",F63*$D$55)</f>
       </c>
       <c r="H63" s="145">
         <f>IF(NOT(ISNUMBER(F63)),"",F63*$D$45)</f>
       </c>
       <c r="I63" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H63))),"",H63*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H63))),"",H63*$D$55)</f>
       </c>
       <c r="J63" s="145">
         <f>E63-E62</f>
@@ -2348,13 +2397,13 @@
         <f>IF(OR(D64="",E64=""),"",E64/D64)</f>
       </c>
       <c r="G64" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F64))),"",F64*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F64))),"",F64*$D$55)</f>
       </c>
       <c r="H64" s="145">
         <f>IF(NOT(ISNUMBER(F64)),"",F64*$D$45)</f>
       </c>
       <c r="I64" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H64))),"",H64*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H64))),"",H64*$D$55)</f>
       </c>
       <c r="J64" s="145">
         <f>E64-E63</f>
@@ -2382,13 +2431,13 @@
         <f>IF(OR(D65="",E65=""),"",E65/D65)</f>
       </c>
       <c r="G65" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F65))),"",F65*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F65))),"",F65*$D$55)</f>
       </c>
       <c r="H65" s="145">
         <f>IF(NOT(ISNUMBER(F65)),"",F65*$D$45)</f>
       </c>
       <c r="I65" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H65))),"",H65*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H65))),"",H65*$D$55)</f>
       </c>
       <c r="J65" s="145">
         <f>E65-E64</f>
@@ -2416,13 +2465,13 @@
         <f>IF(OR(D66="",E66=""),"",E66/D66)</f>
       </c>
       <c r="G66" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F66))),"",F66*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F66))),"",F66*$D$55)</f>
       </c>
       <c r="H66" s="145">
         <f>IF(NOT(ISNUMBER(F66)),"",F66*$D$45)</f>
       </c>
       <c r="I66" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H66))),"",H66*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H66))),"",H66*$D$55)</f>
       </c>
       <c r="J66" s="145">
         <f>E66-E65</f>
@@ -2450,13 +2499,13 @@
         <f>IF(OR(D67="",E67=""),"",E67/D67)</f>
       </c>
       <c r="G67" s="137">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F67))),"",F67*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F67))),"",F67*$D$55)</f>
       </c>
       <c r="H67" s="146">
         <f>IF(NOT(ISNUMBER(F67)),"",F67*$D$45)</f>
       </c>
       <c r="I67" s="146">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H67))),"",H67*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H67))),"",H67*$D$55)</f>
       </c>
       <c r="J67" s="146">
         <f>E67-E66</f>
@@ -2565,13 +2614,13 @@
         <f>IF(OR(D72="",E72=""),"",E72/D72)</f>
       </c>
       <c r="G72" s="135">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F72))),"",F72*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F72))),"",F72*$D$55)</f>
       </c>
       <c r="H72" s="144">
         <f>IF(NOT(ISNUMBER(F72)),"",F72*$D$45)</f>
       </c>
       <c r="I72" s="144">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H72))),"",H72*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H72))),"",H72*$D$55)</f>
       </c>
       <c r="J72" s="144">
         <f>0</f>
@@ -2590,7 +2639,7 @@
         <v>0.75</v>
       </c>
       <c r="D73" s="145">
-        <f>IF(C73&lt;$G$32,$D$45*(1-C73)-$G$51,"")</f>
+        <f>IF(C73&lt;$D$54,$D$45*(1-C73)-$G$51,"")</f>
       </c>
       <c r="E73" s="145">
         <f>IF(D73="","",$G$50/D73)</f>
@@ -2599,13 +2648,13 @@
         <f>IF(OR(D73="",E73=""),"",E73/D73)</f>
       </c>
       <c r="G73" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F73))),"",F73*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F73))),"",F73*$D$55)</f>
       </c>
       <c r="H73" s="145">
         <f>IF(NOT(ISNUMBER(F73)),"",F73*$D$45)</f>
       </c>
       <c r="I73" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H73))),"",H73*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H73))),"",H73*$D$55)</f>
       </c>
       <c r="J73" s="145">
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
@@ -2624,7 +2673,7 @@
         <v>0.8</v>
       </c>
       <c r="D74" s="145">
-        <f>IF(C74&lt;$G$32,$D$45*(1-C74)-$G$51,"")</f>
+        <f>IF(C74&lt;$D$54,$D$45*(1-C74)-$G$51,"")</f>
       </c>
       <c r="E74" s="145">
         <f>IF(D74="","",$G$50/D74)</f>
@@ -2633,13 +2682,13 @@
         <f>IF(OR(D74="",E74=""),"",E74/D74)</f>
       </c>
       <c r="G74" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F74))),"",F74*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F74))),"",F74*$D$55)</f>
       </c>
       <c r="H74" s="145">
         <f>IF(NOT(ISNUMBER(F74)),"",F74*$D$45)</f>
       </c>
       <c r="I74" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H74))),"",H74*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H74))),"",H74*$D$55)</f>
       </c>
       <c r="J74" s="145">
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
@@ -2658,7 +2707,7 @@
         <v>0.82</v>
       </c>
       <c r="D75" s="145">
-        <f>IF(C75&lt;$G$32,$D$45*(1-C75)-$G$51,"")</f>
+        <f>IF(C75&lt;$D$54,$D$45*(1-C75)-$G$51,"")</f>
       </c>
       <c r="E75" s="145">
         <f>IF(D75="","",$G$50/D75)</f>
@@ -2667,13 +2716,13 @@
         <f>IF(OR(D75="",E75=""),"",E75/D75)</f>
       </c>
       <c r="G75" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F75))),"",F75*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F75))),"",F75*$D$55)</f>
       </c>
       <c r="H75" s="145">
         <f>IF(NOT(ISNUMBER(F75)),"",F75*$D$45)</f>
       </c>
       <c r="I75" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H75))),"",H75*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H75))),"",H75*$D$55)</f>
       </c>
       <c r="J75" s="145">
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
@@ -2692,7 +2741,7 @@
         <v>0.84</v>
       </c>
       <c r="D76" s="145">
-        <f>IF(C76&lt;$G$32,$D$45*(1-C76)-$G$51,"")</f>
+        <f>IF(C76&lt;$D$54,$D$45*(1-C76)-$G$51,"")</f>
       </c>
       <c r="E76" s="145">
         <f>IF(D76="","",$G$50/D76)</f>
@@ -2701,13 +2750,13 @@
         <f>IF(OR(D76="",E76=""),"",E76/D76)</f>
       </c>
       <c r="G76" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F76))),"",F76*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F76))),"",F76*$D$55)</f>
       </c>
       <c r="H76" s="145">
         <f>IF(NOT(ISNUMBER(F76)),"",F76*$D$45)</f>
       </c>
       <c r="I76" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H76))),"",H76*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H76))),"",H76*$D$55)</f>
       </c>
       <c r="J76" s="145">
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
@@ -2726,7 +2775,7 @@
         <v>0.86</v>
       </c>
       <c r="D77" s="145">
-        <f>IF(C77&lt;$G$32,$D$45*(1-C77)-$G$51,"")</f>
+        <f>IF(C77&lt;$D$54,$D$45*(1-C77)-$G$51,"")</f>
       </c>
       <c r="E77" s="145">
         <f>IF(D77="","",$G$50/D77)</f>
@@ -2735,13 +2784,13 @@
         <f>IF(OR(D77="",E77=""),"",E77/D77)</f>
       </c>
       <c r="G77" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F77))),"",F77*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F77))),"",F77*$D$55)</f>
       </c>
       <c r="H77" s="145">
         <f>IF(NOT(ISNUMBER(F77)),"",F77*$D$45)</f>
       </c>
       <c r="I77" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H77))),"",H77*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H77))),"",H77*$D$55)</f>
       </c>
       <c r="J77" s="145">
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
@@ -2760,7 +2809,7 @@
         <v>0.88</v>
       </c>
       <c r="D78" s="145">
-        <f>IF(C78&lt;$G$32,$D$45*(1-C78)-$G$51,"")</f>
+        <f>IF(C78&lt;$D$54,$D$45*(1-C78)-$G$51,"")</f>
       </c>
       <c r="E78" s="145">
         <f>IF(D78="","",$G$50/D78)</f>
@@ -2769,13 +2818,13 @@
         <f>IF(OR(D78="",E78=""),"",E78/D78)</f>
       </c>
       <c r="G78" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F78))),"",F78*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F78))),"",F78*$D$55)</f>
       </c>
       <c r="H78" s="145">
         <f>IF(NOT(ISNUMBER(F78)),"",F78*$D$45)</f>
       </c>
       <c r="I78" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H78))),"",H78*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H78))),"",H78*$D$55)</f>
       </c>
       <c r="J78" s="145">
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
@@ -2794,7 +2843,7 @@
         <v>0.89</v>
       </c>
       <c r="D79" s="145">
-        <f>IF(C79&lt;$G$32,$D$45*(1-C79)-$G$51,"")</f>
+        <f>IF(C79&lt;$D$54,$D$45*(1-C79)-$G$51,"")</f>
       </c>
       <c r="E79" s="145">
         <f>IF(D79="","",$G$50/D79)</f>
@@ -2803,13 +2852,13 @@
         <f>IF(OR(D79="",E79=""),"",E79/D79)</f>
       </c>
       <c r="G79" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F79))),"",F79*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F79))),"",F79*$D$55)</f>
       </c>
       <c r="H79" s="145">
         <f>IF(NOT(ISNUMBER(F79)),"",F79*$D$45)</f>
       </c>
       <c r="I79" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H79))),"",H79*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H79))),"",H79*$D$55)</f>
       </c>
       <c r="J79" s="145">
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
@@ -2828,7 +2877,7 @@
         <v>0.9</v>
       </c>
       <c r="D80" s="145">
-        <f>IF(C80&lt;$G$32,$D$45*(1-C80)-$G$51,"")</f>
+        <f>IF(C80&lt;$D$54,$D$45*(1-C80)-$G$51,"")</f>
       </c>
       <c r="E80" s="145">
         <f>IF(D80="","",$G$50/D80)</f>
@@ -2837,13 +2886,13 @@
         <f>IF(OR(D80="",E80=""),"",E80/D80)</f>
       </c>
       <c r="G80" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F80))),"",F80*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F80))),"",F80*$D$55)</f>
       </c>
       <c r="H80" s="145">
         <f>IF(NOT(ISNUMBER(F80)),"",F80*$D$45)</f>
       </c>
       <c r="I80" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H80))),"",H80*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H80))),"",H80*$D$55)</f>
       </c>
       <c r="J80" s="145">
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
@@ -2862,7 +2911,7 @@
         <v>0.905</v>
       </c>
       <c r="D81" s="145">
-        <f>IF(C81&lt;$G$32,$D$45*(1-C81)-$G$51,"")</f>
+        <f>IF(C81&lt;$D$54,$D$45*(1-C81)-$G$51,"")</f>
       </c>
       <c r="E81" s="145">
         <f>IF(D81="","",$G$50/D81)</f>
@@ -2871,13 +2920,13 @@
         <f>IF(OR(D81="",E81=""),"",E81/D81)</f>
       </c>
       <c r="G81" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F81))),"",F81*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F81))),"",F81*$D$55)</f>
       </c>
       <c r="H81" s="145">
         <f>IF(NOT(ISNUMBER(F81)),"",F81*$D$45)</f>
       </c>
       <c r="I81" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H81))),"",H81*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H81))),"",H81*$D$55)</f>
       </c>
       <c r="J81" s="145">
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
@@ -2896,7 +2945,7 @@
         <v>0.91</v>
       </c>
       <c r="D82" s="145">
-        <f>IF(C82&lt;$G$32,$D$45*(1-C82)-$G$51,"")</f>
+        <f>IF(C82&lt;$D$54,$D$45*(1-C82)-$G$51,"")</f>
       </c>
       <c r="E82" s="145">
         <f>IF(D82="","",$G$50/D82)</f>
@@ -2905,13 +2954,13 @@
         <f>IF(OR(D82="",E82=""),"",E82/D82)</f>
       </c>
       <c r="G82" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F82))),"",F82*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F82))),"",F82*$D$55)</f>
       </c>
       <c r="H82" s="145">
         <f>IF(NOT(ISNUMBER(F82)),"",F82*$D$45)</f>
       </c>
       <c r="I82" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H82))),"",H82*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H82))),"",H82*$D$55)</f>
       </c>
       <c r="J82" s="145">
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
@@ -2930,7 +2979,7 @@
         <v>0.915</v>
       </c>
       <c r="D83" s="145">
-        <f>IF(C83&lt;$G$32,$D$45*(1-C83)-$G$51,"")</f>
+        <f>IF(C83&lt;$D$54,$D$45*(1-C83)-$G$51,"")</f>
       </c>
       <c r="E83" s="145">
         <f>IF(D83="","",$G$50/D83)</f>
@@ -2939,13 +2988,13 @@
         <f>IF(OR(D83="",E83=""),"",E83/D83)</f>
       </c>
       <c r="G83" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F83))),"",F83*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F83))),"",F83*$D$55)</f>
       </c>
       <c r="H83" s="145">
         <f>IF(NOT(ISNUMBER(F83)),"",F83*$D$45)</f>
       </c>
       <c r="I83" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H83))),"",H83*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H83))),"",H83*$D$55)</f>
       </c>
       <c r="J83" s="145">
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
@@ -2964,7 +3013,7 @@
         <v>0.918</v>
       </c>
       <c r="D84" s="145">
-        <f>IF(C84&lt;$G$32,$D$45*(1-C84)-$G$51,"")</f>
+        <f>IF(C84&lt;$D$54,$D$45*(1-C84)-$G$51,"")</f>
       </c>
       <c r="E84" s="145">
         <f>IF(D84="","",$G$50/D84)</f>
@@ -2973,13 +3022,13 @@
         <f>IF(OR(D84="",E84=""),"",E84/D84)</f>
       </c>
       <c r="G84" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F84))),"",F84*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F84))),"",F84*$D$55)</f>
       </c>
       <c r="H84" s="145">
         <f>IF(NOT(ISNUMBER(F84)),"",F84*$D$45)</f>
       </c>
       <c r="I84" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H84))),"",H84*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H84))),"",H84*$D$55)</f>
       </c>
       <c r="J84" s="145">
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
@@ -2998,7 +3047,7 @@
         <v>0.9183673469387755</v>
       </c>
       <c r="D85" s="146">
-        <f>IF(C85&lt;$G$32,$D$45*(1-C85)-$G$51,"")</f>
+        <f>IF(C85&lt;$D$54,$D$45*(1-C85)-$G$51,"")</f>
       </c>
       <c r="E85" s="146">
         <f>IF(D85="","",$G$50/D85)</f>
@@ -3007,13 +3056,13 @@
         <f>IF(OR(D85="",E85=""),"",E85/D85)</f>
       </c>
       <c r="G85" s="137">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F85))),"",F85*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F85))),"",F85*$D$55)</f>
       </c>
       <c r="H85" s="146">
         <f>IF(NOT(ISNUMBER(F85)),"",F85*$D$45)</f>
       </c>
       <c r="I85" s="146">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H85))),"",H85*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H85))),"",H85*$D$55)</f>
       </c>
       <c r="J85" s="146">
         <f>IF(E85="","",MAX(0,E85-$G$44))</f>
@@ -3115,13 +3164,13 @@
         <f>IF(OR(D90="",E90=""),"",E90/D90)</f>
       </c>
       <c r="G90" s="135">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F90))),"",F90*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F90))),"",F90*$D$55)</f>
       </c>
       <c r="H90" s="144">
         <f>IF(NOT(ISNUMBER(F90)),"",F90*$D$45)</f>
       </c>
       <c r="I90" s="144">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H90))),"",H90*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H90))),"",H90*$D$55)</f>
       </c>
       <c r="J90" s="132">
         <f>IF($H$90&gt;0,1-H90/$H$90,0)</f>
@@ -3145,13 +3194,13 @@
         <f>IF(OR(D91="",E91=""),"",E91/D91)</f>
       </c>
       <c r="G91" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F91))),"",F91*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F91))),"",F91*$D$55)</f>
       </c>
       <c r="H91" s="145">
         <f>IF(NOT(ISNUMBER(F91)),"",F91*$D$45)</f>
       </c>
       <c r="I91" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H91))),"",H91*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H91))),"",H91*$D$55)</f>
       </c>
       <c r="J91" s="133">
         <f>IF($H$90&gt;0,1-H91/$H$90,0)</f>
@@ -3175,13 +3224,13 @@
         <f>IF(OR(D92="",E92=""),"",E92/D92)</f>
       </c>
       <c r="G92" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F92))),"",F92*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F92))),"",F92*$D$55)</f>
       </c>
       <c r="H92" s="145">
         <f>IF(NOT(ISNUMBER(F92)),"",F92*$D$45)</f>
       </c>
       <c r="I92" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H92))),"",H92*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H92))),"",H92*$D$55)</f>
       </c>
       <c r="J92" s="133">
         <f>IF($H$90&gt;0,1-H92/$H$90,0)</f>
@@ -3205,13 +3254,13 @@
         <f>IF(OR(D93="",E93=""),"",E93/D93)</f>
       </c>
       <c r="G93" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F93))),"",F93*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F93))),"",F93*$D$55)</f>
       </c>
       <c r="H93" s="145">
         <f>IF(NOT(ISNUMBER(F93)),"",F93*$D$45)</f>
       </c>
       <c r="I93" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H93))),"",H93*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H93))),"",H93*$D$55)</f>
       </c>
       <c r="J93" s="133">
         <f>IF($H$90&gt;0,1-H93/$H$90,0)</f>
@@ -3235,13 +3284,13 @@
         <f>IF(OR(D94="",E94=""),"",E94/D94)</f>
       </c>
       <c r="G94" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F94))),"",F94*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F94))),"",F94*$D$55)</f>
       </c>
       <c r="H94" s="145">
         <f>IF(NOT(ISNUMBER(F94)),"",F94*$D$45)</f>
       </c>
       <c r="I94" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H94))),"",H94*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H94))),"",H94*$D$55)</f>
       </c>
       <c r="J94" s="133">
         <f>IF($H$90&gt;0,1-H94/$H$90,0)</f>
@@ -3265,13 +3314,13 @@
         <f>IF(OR(D95="",E95=""),"",E95/D95)</f>
       </c>
       <c r="G95" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F95))),"",F95*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F95))),"",F95*$D$55)</f>
       </c>
       <c r="H95" s="145">
         <f>IF(NOT(ISNUMBER(F95)),"",F95*$D$45)</f>
       </c>
       <c r="I95" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H95))),"",H95*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H95))),"",H95*$D$55)</f>
       </c>
       <c r="J95" s="133">
         <f>IF($H$90&gt;0,1-H95/$H$90,0)</f>
@@ -3295,13 +3344,13 @@
         <f>IF(OR(D96="",E96=""),"",E96/D96)</f>
       </c>
       <c r="G96" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F96))),"",F96*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F96))),"",F96*$D$55)</f>
       </c>
       <c r="H96" s="145">
         <f>IF(NOT(ISNUMBER(F96)),"",F96*$D$45)</f>
       </c>
       <c r="I96" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H96))),"",H96*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H96))),"",H96*$D$55)</f>
       </c>
       <c r="J96" s="133">
         <f>IF($H$90&gt;0,1-H96/$H$90,0)</f>
@@ -3325,13 +3374,13 @@
         <f>IF(OR(D97="",E97=""),"",E97/D97)</f>
       </c>
       <c r="G97" s="136">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F97))),"",F97*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F97))),"",F97*$D$55)</f>
       </c>
       <c r="H97" s="145">
         <f>IF(NOT(ISNUMBER(F97)),"",F97*$D$45)</f>
       </c>
       <c r="I97" s="145">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H97))),"",H97*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H97))),"",H97*$D$55)</f>
       </c>
       <c r="J97" s="133">
         <f>IF($H$90&gt;0,1-H97/$H$90,0)</f>
@@ -3355,13 +3404,13 @@
         <f>IF(OR(D98="",E98=""),"",E98/D98)</f>
       </c>
       <c r="G98" s="137">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(F98))),"",F98*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(F98))),"",F98*$D$55)</f>
       </c>
       <c r="H98" s="146">
         <f>IF(NOT(ISNUMBER(F98)),"",F98*$D$45)</f>
       </c>
       <c r="I98" s="146">
-        <f>IF(OR($D$33="",NOT(ISNUMBER(H98))),"",H98*$D$33)</f>
+        <f>IF(OR($D$55="",NOT(ISNUMBER(H98))),"",H98*$D$55)</f>
       </c>
       <c r="J98" s="134">
         <f>IF($H$90&gt;0,1-H98/$H$90,0)</f>
@@ -4120,8 +4169,7 @@
     <mergeCell ref="C37:F37"/>
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="I27:L27"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D56:E56"/>
   </mergeCells>
   <conditionalFormatting sqref="D23:D23">
     <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="不可达"/>
@@ -4130,14 +4178,6 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="J24:J24">
     <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="缺少"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D30:D30">
-    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="不可达"/>
-    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="无效"/>
-    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="缺少"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F35:F35">
-    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="缺少"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D18:D18">
     <cfRule type="expression" dxfId="8" priority="9">
@@ -4213,6 +4253,14 @@
     <cfRule type="expression" dxfId="22" priority="23">
       <formula>$D$7="ETH"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D51:D51">
+    <cfRule type="containsText" dxfId="23" priority="24" operator="containsText" text="不可达"/>
+    <cfRule type="containsText" dxfId="24" priority="25" operator="containsText" text="无效"/>
+    <cfRule type="containsText" dxfId="25" priority="26" operator="containsText" text="缺少"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G55:G55">
+    <cfRule type="containsText" dxfId="26" priority="27" operator="containsText" text="缺少"/>
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="list" sqref="D7">

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R74814a66d1064eec"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Rb96d4fcf946144c7"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R918d13da31044a3f"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Rcab139deb5424cbf"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -164,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="151">
+  <x:cellXfs count="153">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -609,6 +609,12 @@
     </x:xf>
     <x:xf numFmtId="203" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="207" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="0"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1111,7 +1117,7 @@
         <v>Quote</v>
       </c>
       <c r="D7" s="51" t="str">
-        <v>SLV</v>
+        <v>ETH</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="35" t="str">
@@ -1146,7 +1152,7 @@
         <v>内盘地址 / 套</v>
       </c>
       <c r="G8" s="51" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="35" t="str">
@@ -1174,7 +1180,7 @@
         <v>外盘地址数</v>
       </c>
       <c r="G9" s="51" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="35" t="str">
@@ -1196,7 +1202,7 @@
         <v>Holder 地址数</v>
       </c>
       <c r="G10" s="51" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="35" t="str">
@@ -1241,8 +1247,8 @@
       <c r="F12" s="35" t="str">
         <v>资金预留 / Quote</v>
       </c>
-      <c r="G12" s="54" t="n">
-        <v>5</v>
+      <c r="G12" s="152">
+        <f>IF(AND(ISNUMBER($D$55),$D$55&gt;0),ROUNDUP($G$56/$D$55,0),"")</f>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1254,7 +1260,7 @@
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="55" t="str">
-        <v>手动价格只用于 USDT 换算，不改变 Quote 控筹预算。清空覆盖格后恢复自动取价。</v>
+        <v>预留资金 = 10,000 USDT ÷ Quote 价格，向上取整。手动价格会同时调整预留与折算价值；清空后恢复每日价。</v>
       </c>
       <c r="D13" s="55"/>
       <c r="E13" s="55"/>
@@ -2148,8 +2154,12 @@
         <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
       </c>
       <c r="E56" s="107"/>
-      <c r="F56" s="107"/>
-      <c r="G56" s="108"/>
+      <c r="F56" s="107" t="str">
+        <v>预留预算 / USDT</v>
+      </c>
+      <c r="G56" s="111" t="n">
+        <v>10000</v>
+      </c>
       <c r="H56" s="107"/>
       <c r="I56" s="107" t="str">
         <v>洗后外盘 Pool TOKEN</v>
@@ -4662,14 +4672,14 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2501.338633822848</v>
+        <v>2502.962476630463</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.34975868055</v>
+        <v>46283.37613721065</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
         </is>
       </c>
       <c r="V9" s="32" t="inlineStr">
@@ -4730,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>335.40408726191083</v>
+        <v>336.2110724565737</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.349456550925</v>
+        <v>46283.37583913194</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4798,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.7122973158265054</v>
+        <v>2.732284189582491</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.34946334491</v>
+        <v>46283.375841608795</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4871,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.34946857639</v>
+        <v>46283.37585087962</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4941,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.34947450231</v>
+        <v>46283.37585325232</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5011,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.34948023148</v>
+        <v>46283.37585993055</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5081,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.34948679398</v>
+        <v>46283.37586900463</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5151,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.349492430556</v>
+        <v>46283.37587409722</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5221,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.34949822917</v>
+        <v>46283.375878530096</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5286,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>178.02078360371235</v>
+        <v>179.28988634498438</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.349504351856</v>
+        <v>46283.37588267361</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5359,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.3495099537</v>
+        <v>46283.37588900463</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5424,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>86.2530563387189</v>
+        <v>87.38305223166567</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.349514768524</v>
+        <v>46283.37589423611</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5497,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.34952186343</v>
+        <v>46283.37590138889</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5562,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.71738362392947</v>
+        <v>8.747312753461895</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.34952603009</v>
+        <v>46283.37590533565</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5635,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.34953179398</v>
+        <v>46283.37591207176</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5705,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.34953803241</v>
+        <v>46283.37592064815</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5770,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>403.5217829501588</v>
+        <v>405.2187628857725</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.34954460648</v>
+        <v>46283.37592271991</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5843,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.34954983796</v>
+        <v>46283.375929409725</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5908,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.1657433846468</v>
+        <v>349.1618993478548</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.34955539352</v>
+        <v>46283.375934351854</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5976,10 +5986,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.293964988345127</v>
+        <v>28.323678595305676</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.34956188657</v>
+        <v>46283.375940868056</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6049,7 +6059,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.34956761574</v>
+        <v>46283.37594597222</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6119,7 +6129,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.349573368054</v>
+        <v>46283.375954965275</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6189,7 +6199,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.34957922454</v>
+        <v>46283.37595836806</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6254,10 +6264,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1151.6354352136261</v>
+        <v>1153.654455124484</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.34958501157</v>
+        <v>46283.37596337963</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6327,7 +6337,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.34959200231</v>
+        <v>46283.375969201385</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6392,10 +6402,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>683.829203335225</v>
+        <v>685.8934068881586</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.349595995365</v>
+        <v>46283.37597491898</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6465,7 +6475,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.34960244213</v>
+        <v>46283.37598070602</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6535,7 +6545,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.34960841435</v>
+        <v>46283.37598986111</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6605,7 +6615,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.34961388889</v>
+        <v>46283.375992395835</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6670,10 +6680,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>135.54480645106406</v>
+        <v>136.26391663430627</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.34961914352</v>
+        <v>46283.3759987963</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6738,10 +6748,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>995.5031912029489</v>
+        <v>999.0251850547057</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.34962496528</v>
+        <v>46283.37600747685</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6811,7 +6821,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.34963667824</v>
+        <v>46283.376015567126</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6881,7 +6891,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.34964212963</v>
+        <v>46283.37602225695</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6946,10 +6956,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>220.89709984356753</v>
+        <v>221.41510302612983</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.34963069444</v>
+        <v>46283.376013194444</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7019,7 +7029,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.34964872685</v>
+        <v>46283.37602708333</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7089,7 +7099,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.34965340278</v>
+        <v>46283.376033009255</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7154,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>720.5402976320944</v>
+        <v>722.4839966211753</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.34966047454</v>
+        <v>46283.376038703704</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7222,10 +7232,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.68038528633753</v>
+        <v>47.860010969170226</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.34966608796</v>
+        <v>46283.3760452662</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7290,10 +7300,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>154.7410656826332</v>
+        <v>155.09966331853428</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.34967207176</v>
+        <v>46283.3760503588</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7363,7 +7373,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.34967752315</v>
+        <v>46283.376056064815</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7428,10 +7438,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.59605185592197</v>
+        <v>101.78509233719389</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.349683472225</v>
+        <v>46283.376062662035</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7501,7 +7511,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.349689131945</v>
+        <v>46283.37606862269</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7571,7 +7581,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.349695185185</v>
+        <v>46283.376075370375</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7641,7 +7651,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.349700798615</v>
+        <v>46283.376079340276</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7711,7 +7721,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.34970590278</v>
+        <v>46283.37608915509</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7781,7 +7791,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.349711539355</v>
+        <v>46283.37609252315</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7846,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>156.24233725965894</v>
+        <v>155.790240641176</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.34971766204</v>
+        <v>46283.376100173606</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7914,10 +7924,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>764.7167150576538</v>
+        <v>763.808543942736</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.34972400463</v>
+        <v>46283.37610248843</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7982,10 +7992,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>368.3780161797042</v>
+        <v>369.6390182192312</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.34972859954</v>
+        <v>46283.37610829861</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8055,7 +8065,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.34973488426</v>
+        <v>46283.37611453704</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8125,7 +8135,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.34974016204</v>
+        <v>46283.376119884255</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8195,7 +8205,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.34974641204</v>
+        <v>46283.376125717594</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8265,7 +8275,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.34975175926</v>
+        <v>46283.376131516205</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8335,7 +8345,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.34975868055</v>
+        <v>46283.37613721065</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4672,10 +4672,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2502.962476630463</v>
+        <v>2508.4644662557284</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.37613721065</v>
+        <v>46283.38506050926</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.2110724565737</v>
+        <v>336.28085914707805</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.37583913194</v>
+        <v>46283.38475974537</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.732284189582491</v>
+        <v>2.7322486406312394</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.375841608795</v>
+        <v>46283.384765532406</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.37585087962</v>
+        <v>46283.38477241898</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.37585325232</v>
+        <v>46283.38477708333</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.37585993055</v>
+        <v>46283.384782905094</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.37586900463</v>
+        <v>46283.38478868056</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.37587409722</v>
+        <v>46283.384794467594</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.375878530096</v>
+        <v>46283.38480032408</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>179.28988634498438</v>
+        <v>179.77795725882402</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.37588267361</v>
+        <v>46283.38480604167</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.37588900463</v>
+        <v>46283.3848115625</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>87.38305223166567</v>
+        <v>87.38191531630532</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.37589423611</v>
+        <v>46283.384817673614</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.37590138889</v>
+        <v>46283.3848234375</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.747312753461895</v>
+        <v>8.747198944731515</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.37590533565</v>
+        <v>46283.38482923611</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.37591207176</v>
+        <v>46283.38483502315</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.37592064815</v>
+        <v>46283.38484107639</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>405.2187628857725</v>
+        <v>406.5646026679958</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.37592271991</v>
+        <v>46283.38484665509</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.375929409725</v>
+        <v>46283.38485244213</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.1618993478548</v>
+        <v>349.15735650440314</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.375934351854</v>
+        <v>46283.38485789352</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5986,10 +5986,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.323678595305676</v>
+        <v>28.403375978430248</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.375940868056</v>
+        <v>46283.384863969906</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.37594597222</v>
+        <v>46283.38486982638</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.375954965275</v>
+        <v>46283.38487560185</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.37595836806</v>
+        <v>46283.38488144676</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1153.654455124484</v>
+        <v>1152.8788192682578</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.37596337963</v>
+        <v>46283.38488722222</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.375969201385</v>
+        <v>46283.38489300926</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>685.8934068881586</v>
+        <v>686.4449441890677</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.37597491898</v>
+        <v>46283.38489844907</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.37598070602</v>
+        <v>46283.38490456019</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.37598986111</v>
+        <v>46283.384910347224</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.375992395835</v>
+        <v>46283.38491616898</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.26391663430627</v>
+        <v>136.88265442459146</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.3759987963</v>
+        <v>46283.384921944446</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6748,10 +6748,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>999.0251850547057</v>
+        <v>999.1022611609354</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.37600747685</v>
+        <v>46283.38492769676</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.376015567126</v>
+        <v>46283.3849393287</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.37602225695</v>
+        <v>46283.38494510417</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.41510302612983</v>
+        <v>221.46226344281345</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.376013194444</v>
+        <v>46283.384933217596</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.37602708333</v>
+        <v>46283.38495092593</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.376033009255</v>
+        <v>46283.38495668981</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>722.4839966211753</v>
+        <v>722.5346460136693</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.376038703704</v>
+        <v>46283.3849625</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.860010969170226</v>
+        <v>47.899421223667076</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.3760452662</v>
+        <v>46283.38496863426</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7300,10 +7300,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.09966331853428</v>
+        <v>155.6881313320863</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.3760503588</v>
+        <v>46283.38497407408</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.376056064815</v>
+        <v>46283.384979849536</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.78509233719389</v>
+        <v>102.01395748701182</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.376062662035</v>
+        <v>46283.384985648154</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.37606862269</v>
+        <v>46283.38499170139</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.376075370375</v>
+        <v>46283.38499724537</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.376079340276</v>
+        <v>46283.385003020834</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.37608915509</v>
+        <v>46283.38500878472</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.37609252315</v>
+        <v>46283.38501457176</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7856,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>155.790240641176</v>
+        <v>155.6881313320863</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.376100173606</v>
+        <v>46283.38502003472</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>763.808543942736</v>
+        <v>763.6775065879218</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.37610248843</v>
+        <v>46283.38502614583</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7992,10 +7992,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>369.6390182192312</v>
+        <v>369.1237888782468</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.37610829861</v>
+        <v>46283.38503194445</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.37611453704</v>
+        <v>46283.38503773148</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.376119884255</v>
+        <v>46283.38504351852</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.376125717594</v>
+        <v>46283.38504929398</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.376131516205</v>
+        <v>46283.38505509259</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.37613721065</v>
+        <v>46283.38506050926</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4672,10 +4672,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2508.4644662557284</v>
+        <v>2508.6344334500604</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.38506050926</v>
+        <v>46283.396544745374</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.28085914707805</v>
+        <v>337.57106956886383</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.38475974537</v>
+        <v>46283.39623636574</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.7322486406312394</v>
+        <v>2.742201988196522</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.384765532406</v>
+        <v>46283.39624217593</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.38477241898</v>
+        <v>46283.39624799768</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.38477708333</v>
+        <v>46283.39625465278</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.384782905094</v>
+        <v>46283.39626325232</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.38478868056</v>
+        <v>46283.396269074074</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.384794467594</v>
+        <v>46283.3962721412</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.38480032408</v>
+        <v>46283.39627695602</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>179.77795725882402</v>
+        <v>180.60502583574612</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.38480604167</v>
+        <v>46283.396282800924</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.3848115625</v>
+        <v>46283.39628944444</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>87.38191531630532</v>
+        <v>87.38016627351763</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.384817673614</v>
+        <v>46283.396295370374</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.3848234375</v>
+        <v>46283.396300162036</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.747198944731515</v>
+        <v>8.74702386015971</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.38482923611</v>
+        <v>46283.39630600694</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.38483502315</v>
+        <v>46283.39631266204</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.38484107639</v>
+        <v>46283.39631855324</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>406.5646026679958</v>
+        <v>406.98681040875823</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.38484665509</v>
+        <v>46283.39632721065</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.38485244213</v>
+        <v>46283.39633004629</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.15735650440314</v>
+        <v>349.1503677452995</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.38485789352</v>
+        <v>46283.396335011574</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5986,10 +5986,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.403375978430248</v>
+        <v>28.442839600198962</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.384863969906</v>
+        <v>46283.39634148148</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.38486982638</v>
+        <v>46283.396346574074</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.38487560185</v>
+        <v>46283.39635398149</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.38488144676</v>
+        <v>46283.396359108796</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1152.8788192682578</v>
+        <v>1151.8449314799784</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.38488722222</v>
+        <v>46283.39636402778</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.38489300926</v>
+        <v>46283.39637190972</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>686.4449441890677</v>
+        <v>686.1810033456866</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.38489844907</v>
+        <v>46283.396376550925</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.38490456019</v>
+        <v>46283.3963834838</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.384910347224</v>
+        <v>46283.396388009256</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.38491616898</v>
+        <v>46283.39639627315</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.88265442459146</v>
+        <v>136.97999493593355</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.384921944446</v>
+        <v>46283.39639879629</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6748,10 +6748,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>999.1022611609354</v>
+        <v>996.7904227094357</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.38492769676</v>
+        <v>46283.396408622684</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.3849393287</v>
+        <v>46283.39641954861</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.38494510417</v>
+        <v>46283.396422997685</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.46226344281345</v>
+        <v>222.11836104391827</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.384933217596</v>
+        <v>46283.396410393514</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.38495092593</v>
+        <v>46283.39642777778</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.38495668981</v>
+        <v>46283.396433587965</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>722.5346460136693</v>
+        <v>721.6795086454423</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.3849625</v>
+        <v>46283.39644269676</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.899421223667076</v>
+        <v>47.958510684079315</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.38496863426</v>
+        <v>46283.39644585648</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7300,10 +7300,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.6881313320863</v>
+        <v>155.8851757961643</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.38497407408</v>
+        <v>46283.39645097222</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.384979849536</v>
+        <v>46283.39645760416</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.01395748701182</v>
+        <v>102.13101120199521</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.384985648154</v>
+        <v>46283.39646322917</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.38499170139</v>
+        <v>46283.396469085645</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.38499724537</v>
+        <v>46283.396474155095</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.385003020834</v>
+        <v>46283.396479965275</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.38500878472</v>
+        <v>46283.3964868287</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.38501457176</v>
+        <v>46283.39649158565</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7856,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>155.6881313320863</v>
+        <v>156.30551332720174</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.38502003472</v>
+        <v>46283.39649737268</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>763.6775065879218</v>
+        <v>766.2753190812222</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.38502614583</v>
+        <v>46283.39650318287</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7992,10 +7992,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>369.1237888782468</v>
+        <v>369.15643261539014</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.38503194445</v>
+        <v>46283.39650902778</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.38503773148</v>
+        <v>46283.396514803244</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.38504351852</v>
+        <v>46283.3965205787</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.38504929398</v>
+        <v>46283.396526412034</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.38505509259</v>
+        <v>46283.396532199076</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.38506050926</v>
+        <v>46283.39653795139</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4672,10 +4672,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2508.6344334500604</v>
+        <v>2506.0924165801803</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.396544745374</v>
+        <v>46283.39930128472</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>337.57106956886383</v>
+        <v>336.68170213362185</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.39623636574</v>
+        <v>46283.39899443287</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.742201988196522</v>
+        <v>2.732204889345702</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.39624217593</v>
+        <v>46283.39900023148</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.39624799768</v>
+        <v>46283.39900600694</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.39625465278</v>
+        <v>46283.39901180555</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.39626325232</v>
+        <v>46283.399017592594</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.396269074074</v>
+        <v>46283.399023391205</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.3962721412</v>
+        <v>46283.39902916666</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.39627695602</v>
+        <v>46283.399034965274</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>180.60502583574612</v>
+        <v>180.00526424824835</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.396282800924</v>
+        <v>46283.39904076389</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.39628944444</v>
+        <v>46283.3990465625</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>87.38016627351763</v>
+        <v>87.38051607647371</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.396295370374</v>
+        <v>46283.39905234954</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.396300162036</v>
+        <v>46283.39905814815</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.74702386015971</v>
+        <v>8.747058876513346</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.39630600694</v>
+        <v>46283.39906394676</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.39631266204</v>
+        <v>46283.399069722225</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.39631855324</v>
+        <v>46283.39907554398</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>406.98681040875823</v>
+        <v>405.81749471823764</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.39632721065</v>
+        <v>46283.39908135417</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.39633004629</v>
+        <v>46283.39908710648</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.1503677452995</v>
+        <v>349.1517654747381</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.396335011574</v>
+        <v>46283.39909290509</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5986,10 +5986,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.442839600198962</v>
+        <v>28.442953463445</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.39634148148</v>
+        <v>46283.39909869213</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.396346574074</v>
+        <v>46283.39910447916</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.39635398149</v>
+        <v>46283.39911027777</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.396359108796</v>
+        <v>46283.399116064815</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1151.8449314799784</v>
+        <v>1151.8495425808628</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.39636402778</v>
+        <v>46283.39912188658</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.39637190972</v>
+        <v>46283.399127662036</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>686.1810033456866</v>
+        <v>686.1937583629989</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.396376550925</v>
+        <v>46283.39913351852</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.3963834838</v>
+        <v>46283.39913925926</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.396388009256</v>
+        <v>46283.3991452662</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.39639627315</v>
+        <v>46283.399150868056</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.97999493593355</v>
+        <v>136.98054329844186</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.39639879629</v>
+        <v>46283.39915662037</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6748,10 +6748,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>996.7904227094357</v>
+        <v>996.7944130913647</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.396408622684</v>
+        <v>46283.399162430556</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.39641954861</v>
+        <v>46283.39917494213</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.396422997685</v>
+        <v>46283.39917981482</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>222.11836104391827</v>
+        <v>221.5788141029811</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.396410393514</v>
+        <v>46283.39916824074</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.39642777778</v>
+        <v>46283.39918559028</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.396433587965</v>
+        <v>46283.39919138889</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>721.6795086454423</v>
+        <v>721.6823976949398</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.39644269676</v>
+        <v>46283.399197164355</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.958510684079315</v>
+        <v>47.95870267305716</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.39644585648</v>
+        <v>46283.39920347222</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7300,10 +7300,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.8851757961643</v>
+        <v>155.88579984047126</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.39645097222</v>
+        <v>46283.39920873843</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.39645760416</v>
+        <v>46283.39921452547</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.13101120199521</v>
+        <v>102.13142005598519</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.39646322917</v>
+        <v>46283.39922033565</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.396469085645</v>
+        <v>46283.39922611111</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.396474155095</v>
+        <v>46283.39923189815</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.396479965275</v>
+        <v>46283.39923768519</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.3964868287</v>
+        <v>46283.3992434838</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.39649158565</v>
+        <v>46283.39924923611</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7856,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>156.30551332720174</v>
+        <v>155.92583214654226</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.39649737268</v>
+        <v>46283.39925505787</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>766.2753190812222</v>
+        <v>766.4184997292815</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.39650318287</v>
+        <v>46283.399260833336</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7992,10 +7992,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>369.15643261539014</v>
+        <v>369.15791043372</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.39650902778</v>
+        <v>46283.39926659722</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.396514803244</v>
+        <v>46283.39927260417</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.3965205787</v>
+        <v>46283.399278414356</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.396526412034</v>
+        <v>46283.399283935185</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.396532199076</v>
+        <v>46283.39928972222</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.39653795139</v>
+        <v>46283.399295497686</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4672,10 +4672,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2506.0924165801803</v>
+        <v>2505.389473262808</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.39930128472</v>
+        <v>46283.40053702547</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.68170213362185</v>
+        <v>336.7595103936267</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.39899443287</v>
+        <v>46283.400229872685</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.732204889345702</v>
+        <v>2.7322677822592754</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.39900023148</v>
+        <v>46283.4002363426</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.39900600694</v>
+        <v>46283.40024228009</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.39901180555</v>
+        <v>46283.40024722223</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.399017592594</v>
+        <v>46283.40025366898</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.399023391205</v>
+        <v>46283.40025880787</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.39902916666</v>
+        <v>46283.400265324075</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.399034965274</v>
+        <v>46283.40027039352</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>180.00526424824835</v>
+        <v>179.55903399821852</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.39904076389</v>
+        <v>46283.40027729167</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.3990465625</v>
+        <v>46283.40028284722</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>87.38051607647371</v>
+        <v>87.38252749782319</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.39905234954</v>
+        <v>46283.40028884259</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.39905814815</v>
+        <v>46283.400293541665</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.747058876513346</v>
+        <v>8.74726022598757</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.39906394676</v>
+        <v>46283.4003003125</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.399069722225</v>
+        <v>46283.40030594907</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.39907554398</v>
+        <v>46283.40031089121</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>405.81749471823764</v>
+        <v>405.8268362741075</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.39908135417</v>
+        <v>46283.400317326385</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.39908710648</v>
+        <v>46283.40032245371</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.1517654747381</v>
+        <v>349.15980263618803</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.39909290509</v>
+        <v>46283.4003289699</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5986,10 +5986,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.442953463445</v>
+        <v>28.443608194801687</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.39909869213</v>
+        <v>46283.40033402778</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.39910447916</v>
+        <v>46283.400340555556</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.39911027777</v>
+        <v>46283.40034677083</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.399116064815</v>
+        <v>46283.40035214121</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1151.8495425808628</v>
+        <v>1149.734279451945</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.39912188658</v>
+        <v>46283.40035805555</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.399127662036</v>
+        <v>46283.400363865745</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>686.1937583629989</v>
+        <v>684.5481749852378</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.39913351852</v>
+        <v>46283.40036982639</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.39913925926</v>
+        <v>46283.40037487268</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.3991452662</v>
+        <v>46283.400380983796</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.399150868056</v>
+        <v>46283.40038701389</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.98054329844186</v>
+        <v>136.9836964680685</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.39915662037</v>
+        <v>46283.40039193287</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6748,10 +6748,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>996.7944130913647</v>
+        <v>996.8173584074782</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.399162430556</v>
+        <v>46283.400398564816</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.39917494213</v>
+        <v>46283.40041012732</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.39917981482</v>
+        <v>46283.400416122684</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.5788141029811</v>
+        <v>221.66398110431658</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.39916824074</v>
+        <v>46283.40040371528</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.39918559028</v>
+        <v>46283.400421736114</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.39919138889</v>
+        <v>46283.40042670139</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>721.6823976949398</v>
+        <v>721.6990101784481</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.399197164355</v>
+        <v>46283.40043248843</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.95870267305716</v>
+        <v>47.959806639510795</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.39920347222</v>
+        <v>46283.400439097226</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7300,10 +7300,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.88579984047126</v>
+        <v>155.8893881921995</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.39920873843</v>
+        <v>46283.4004447338</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.39921452547</v>
+        <v>46283.40045065972</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.13142005598519</v>
+        <v>102.13377102995487</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.39922033565</v>
+        <v>46283.400456574076</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.39922611111</v>
+        <v>46283.40046225695</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.39923189815</v>
+        <v>46283.400467824074</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.39923768519</v>
+        <v>46283.40047385417</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.3992434838</v>
+        <v>46283.40048011574</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.39924923611</v>
+        <v>46283.40048556713</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7856,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>155.92583214654226</v>
+        <v>156.0495211025151</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.39925505787</v>
+        <v>46283.400491134256</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>766.4184997292815</v>
+        <v>764.964920884334</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.399260833336</v>
+        <v>46283.40049613426</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7992,10 +7992,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>369.15791043372</v>
+        <v>369.16640811873856</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.39926659722</v>
+        <v>46283.40050190972</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.39927260417</v>
+        <v>46283.40050788195</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.399278414356</v>
+        <v>46283.400514560184</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.399283935185</v>
+        <v>46283.40051998843</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.39928972222</v>
+        <v>46283.40052563657</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.399295497686</v>
+        <v>46283.40053158565</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4672,10 +4672,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2505.389473262808</v>
+        <v>2511.6521129932194</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.40053702547</v>
+        <v>46283.42145649306</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.7595103936267</v>
+        <v>335.8070408086671</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.400229872685</v>
+        <v>46283.42114976852</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.7322677822592754</v>
+        <v>2.7322541096404533</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.4002363426</v>
+        <v>46283.42115546296</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.40024228009</v>
+        <v>46283.42116133102</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.40024722223</v>
+        <v>46283.42116710648</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.40025366898</v>
+        <v>46283.42117288194</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.40025880787</v>
+        <v>46283.42117869213</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.400265324075</v>
+        <v>46283.42118469907</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.40027039352</v>
+        <v>46283.42119059028</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>179.55903399821852</v>
+        <v>179.25788775739986</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.40027729167</v>
+        <v>46283.42119611111</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.40028284722</v>
+        <v>46283.42120189815</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>87.38252749782319</v>
+        <v>87.38209022443516</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.40028884259</v>
+        <v>46283.42120758102</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.400293541665</v>
+        <v>46283.42121340278</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.74726022598757</v>
+        <v>8.747216453574199</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.4003003125</v>
+        <v>46283.42121925926</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.40030594907</v>
+        <v>46283.42122496528</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.40031089121</v>
+        <v>46283.42123076389</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>405.8268362741075</v>
+        <v>404.7339054720144</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.400317326385</v>
+        <v>46283.42123659722</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.40032245371</v>
+        <v>46283.42124238426</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.15980263618803</v>
+        <v>349.15805539570147</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.4003289699</v>
+        <v>46283.42124815972</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5986,10 +5986,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.443608194801687</v>
+        <v>28.323366777591513</v>
       </c>
       <c r="T28" s="30">
-        <v>46283.40033402778</v>
+        <v>46283.42125400463</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.400340555556</v>
+        <v>46283.42125974537</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6129,7 +6129,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.40034677083</v>
+        <v>46283.42126587963</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6199,7 +6199,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.40035214121</v>
+        <v>46283.42127136574</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1149.734279451945</v>
+        <v>1151.489979232867</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.40035805555</v>
+        <v>46283.42127712963</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.400363865745</v>
+        <v>46283.42128295139</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6402,10 +6402,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>684.5481749852378</v>
+        <v>685.5255585858333</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.40036982639</v>
+        <v>46283.421288668986</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6475,7 +6475,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.40037487268</v>
+        <v>46283.42129452546</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.400380983796</v>
+        <v>46283.421300277776</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.40038701389</v>
+        <v>46283.42130599537</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.9836964680685</v>
+        <v>136.72279630695326</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.40039193287</v>
+        <v>46283.421311875005</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6748,10 +6748,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>996.8173584074782</v>
+        <v>996.8123702054195</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.400398564816</v>
+        <v>46283.421317719905</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.40041012732</v>
+        <v>46283.42132917824</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.400416122684</v>
+        <v>46283.421335011575</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6956,10 +6956,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.66398110431658</v>
+        <v>221.00232691970874</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.40040371528</v>
+        <v>46283.42132347222</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.400421736114</v>
+        <v>46283.42134072917</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.40042670139</v>
+        <v>46283.42134652778</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7164,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>721.6990101784481</v>
+        <v>720.9347711862287</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.40043248843</v>
+        <v>46283.421352314814</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7232,10 +7232,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.959806639510795</v>
+        <v>47.86949233117321</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.400439097226</v>
+        <v>46283.42135820602</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7300,10 +7300,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.8893881921995</v>
+        <v>155.09795581354618</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.4004447338</v>
+        <v>46283.42136402778</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7373,7 +7373,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.40045065972</v>
+        <v>46283.421369814816</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7438,10 +7438,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.13377102995487</v>
+        <v>101.58380664047839</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.400456574076</v>
+        <v>46283.42137552083</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7511,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.40046225695</v>
+        <v>46283.42138144676</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.400467824074</v>
+        <v>46283.42138712963</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.40047385417</v>
+        <v>46283.42139292824</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.40048011574</v>
+        <v>46283.421398715276</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.40048556713</v>
+        <v>46283.42140450232</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7856,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>156.0495211025151</v>
+        <v>155.83856681762455</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.400491134256</v>
+        <v>46283.42141027778</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7924,10 +7924,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>764.964920884334</v>
+        <v>763.109565391448</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.40049613426</v>
+        <v>46283.42141618055</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7992,10 +7992,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>369.16640811873856</v>
+        <v>368.6241148947882</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.40050190972</v>
+        <v>46283.421421875</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8065,7 +8065,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.40050788195</v>
+        <v>46283.421427685185</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8135,7 +8135,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.400514560184</v>
+        <v>46283.421433414354</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.40051998843</v>
+        <v>46283.42143917824</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8275,7 +8275,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.40052563657</v>
+        <v>46283.421444976855</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.40053158565</v>
+        <v>46283.42145128472</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4672,10 +4672,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2511.6521129932194</v>
+        <v>2629.1017819111953</v>
       </c>
       <c r="T9" s="29">
-        <v>46283.42145649306</v>
+        <v>46284.256953414355</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>335.8070408086671</v>
+        <v>335.5550953977214</v>
       </c>
       <c r="T10" s="30">
-        <v>46283.42114976852</v>
+        <v>46284.2566465162</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.7322541096404533</v>
+        <v>2.700926417761292</v>
       </c>
       <c r="T11" s="30">
-        <v>46283.42115546296</v>
+        <v>46284.25665268518</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46283.42116133102</v>
+        <v>46284.256657777776</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46283.42116710648</v>
+        <v>46284.2566637037</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46283.42117288194</v>
+        <v>46284.25666993055</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46283.42117869213</v>
+        <v>46284.25667564815</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46283.42118469907</v>
+        <v>46284.25668190972</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46283.42119059028</v>
+        <v>46284.256686875</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>179.25788775739986</v>
+        <v>194.6367604088202</v>
       </c>
       <c r="T18" s="30">
-        <v>46283.42119611111</v>
+        <v>46284.25669326389</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46283.42120189815</v>
+        <v>46284.25669886574</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>87.38209022443516</v>
+        <v>91.79148447917636</v>
       </c>
       <c r="T20" s="30">
-        <v>46283.42120758102</v>
+        <v>46284.25670438657</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46283.42121340278</v>
+        <v>46284.256710601854</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.747216453574199</v>
+        <v>8.833029729197115</v>
       </c>
       <c r="T22" s="30">
-        <v>46283.42121925926</v>
+        <v>46284.25671638889</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46283.42122496528</v>
+        <v>46284.25672184028</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46283.42123076389</v>
+        <v>46284.25672791666</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>404.7339054720144</v>
+        <v>403.9685612164972</v>
       </c>
       <c r="T25" s="30">
-        <v>46283.42123659722</v>
+        <v>46284.25673368056</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46283.42124238426</v>
+        <v>46284.256738715274</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.15805539570147</v>
+        <v>351.53057498722063</v>
       </c>
       <c r="T27" s="30">
-        <v>46283.42124815972</v>
+        <v>46284.256745300925</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5985,20 +5985,22 @@
       <c r="R28" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
-      <c r="S28" s="27">
-        <v>28.323366777591513</v>
+      <c r="S28" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T28" s="30">
-        <v>46283.42125400463</v>
+        <v>46284.256750127315</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0xd10e6245961d697d975963682ece9979e9917fbc</t>
+          <t/>
         </is>
       </c>
       <c r="V28" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6061,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46283.42125974537</v>
+        <v>46284.25675688658</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6129,7 +6131,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46283.42126587963</v>
+        <v>46284.25676303241</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6199,7 +6201,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46283.42127136574</v>
+        <v>46284.25676841435</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6264,10 +6266,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1151.489979232867</v>
+        <v>1156.4966783606776</v>
       </c>
       <c r="T32" s="30">
-        <v>46283.42127712963</v>
+        <v>46284.25677363426</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6337,7 +6339,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46283.42128295139</v>
+        <v>46284.2567800926</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6402,10 +6404,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>685.5255585858333</v>
+        <v>668.92944279888</v>
       </c>
       <c r="T34" s="30">
-        <v>46283.421288668986</v>
+        <v>46284.25678516203</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6475,7 +6477,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46283.42129452546</v>
+        <v>46284.25679111111</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6545,7 +6547,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46283.421300277776</v>
+        <v>46284.25679728009</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6615,7 +6617,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46283.42130599537</v>
+        <v>46284.256803159726</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6680,10 +6682,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.72279630695326</v>
+        <v>154.96315236125992</v>
       </c>
       <c r="T38" s="30">
-        <v>46283.421311875005</v>
+        <v>46284.25680851852</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6748,10 +6750,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>996.8123702054195</v>
+        <v>1015.4042836692986</v>
       </c>
       <c r="T39" s="30">
-        <v>46283.421317719905</v>
+        <v>46284.25681479167</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6821,7 +6823,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46283.42132917824</v>
+        <v>46284.2568258449</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6891,7 +6893,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46283.421335011575</v>
+        <v>46284.25683210648</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6956,10 +6958,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.00232691970874</v>
+        <v>222.52632652999978</v>
       </c>
       <c r="T42" s="30">
-        <v>46283.42132347222</v>
+        <v>46284.25681989583</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7029,7 +7031,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46283.42134072917</v>
+        <v>46284.25683820602</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7099,7 +7101,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46283.42134652778</v>
+        <v>46284.256843090276</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7164,10 +7166,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>720.9347711862287</v>
+        <v>723.3781186947123</v>
       </c>
       <c r="T45" s="30">
-        <v>46283.421352314814</v>
+        <v>46284.25684939815</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7232,10 +7234,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.86949233117321</v>
+        <v>48.006466217912745</v>
       </c>
       <c r="T46" s="30">
-        <v>46283.42135820602</v>
+        <v>46284.25685482639</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7300,10 +7302,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.09795581354618</v>
+        <v>152.54232201645164</v>
       </c>
       <c r="T47" s="30">
-        <v>46283.42136402778</v>
+        <v>46284.256861145834</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7373,7 +7375,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46283.421369814816</v>
+        <v>46284.2568662037</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7438,10 +7440,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.58380664047839</v>
+        <v>101.11868370851202</v>
       </c>
       <c r="T49" s="30">
-        <v>46283.42137552083</v>
+        <v>46284.25687215278</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7511,7 +7513,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46283.42138144676</v>
+        <v>46284.25687849537</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7581,7 +7583,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46283.42138712963</v>
+        <v>46284.256884814815</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7651,7 +7653,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46283.42139292824</v>
+        <v>46284.25688956019</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7721,7 +7723,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46283.421398715276</v>
+        <v>46284.25689582176</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7791,7 +7793,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46283.42140450232</v>
+        <v>46284.25690172454</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7856,10 +7858,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>155.83856681762455</v>
+        <v>152.92245240117362</v>
       </c>
       <c r="T55" s="30">
-        <v>46283.42141027778</v>
+        <v>46284.25690637731</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7924,10 +7926,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>763.109565391448</v>
+        <v>764.0720767223157</v>
       </c>
       <c r="T56" s="30">
-        <v>46283.42141618055</v>
+        <v>46284.25691318287</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7992,10 +7994,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>368.6241148947882</v>
+        <v>365.54538206604866</v>
       </c>
       <c r="T57" s="30">
-        <v>46283.421421875</v>
+        <v>46284.256918506944</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8065,7 +8067,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46283.421427685185</v>
+        <v>46284.25692518518</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8135,7 +8137,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46283.421433414354</v>
+        <v>46284.256930393516</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8205,7 +8207,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46283.42143917824</v>
+        <v>46284.25693635417</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8275,7 +8277,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46283.421444976855</v>
+        <v>46284.256941782405</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8345,7 +8347,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46283.42145128472</v>
+        <v>46284.25694795139</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4672,10 +4672,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2629.1017819111953</v>
+        <v>2580.0817123580937</v>
       </c>
       <c r="T9" s="29">
-        <v>46284.256953414355</v>
+        <v>46285.27349457176</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4740,10 +4740,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>335.5550953977214</v>
+        <v>334.9426372843646</v>
       </c>
       <c r="T10" s="30">
-        <v>46284.2566465162</v>
+        <v>46285.27318768518</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4808,10 +4808,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
       <c r="S11" s="27">
-        <v>2.700926417761292</v>
+        <v>2.6810617004333714</v>
       </c>
       <c r="T11" s="30">
-        <v>46284.25665268518</v>
+        <v>46285.27319353009</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46284.256657777776</v>
+        <v>46285.27319930556</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46284.2566637037</v>
+        <v>46285.273205115736</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46284.25666993055</v>
+        <v>46285.27321087963</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46284.25667564815</v>
+        <v>46285.27321663194</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46284.25668190972</v>
+        <v>46285.27322246528</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46284.256686875</v>
+        <v>46285.273228252314</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5296,10 +5296,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>194.6367604088202</v>
+        <v>192.1700993593463</v>
       </c>
       <c r="T18" s="30">
-        <v>46284.25669326389</v>
+        <v>46285.273234050925</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46284.25669886574</v>
+        <v>46285.27323954861</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5434,10 +5434,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>91.79148447917636</v>
+        <v>90.91600273708387</v>
       </c>
       <c r="T20" s="30">
-        <v>46284.25670438657</v>
+        <v>46285.273245625</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46284.256710601854</v>
+        <v>46285.27325148148</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5572,10 +5572,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.833029729197115</v>
+        <v>8.843502026802613</v>
       </c>
       <c r="T22" s="30">
-        <v>46284.25671638889</v>
+        <v>46285.27325719907</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46284.25672184028</v>
+        <v>46285.27326297454</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5715,7 +5715,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46284.25672791666</v>
+        <v>46285.27326883102</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>403.9685612164972</v>
+        <v>400.1284508665432</v>
       </c>
       <c r="T25" s="30">
-        <v>46284.25673368056</v>
+        <v>46285.27327459491</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5853,7 +5853,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46284.256738715274</v>
+        <v>46285.273280092595</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5918,10 +5918,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>351.53057498722063</v>
+        <v>349.5884370210603</v>
       </c>
       <c r="T27" s="30">
-        <v>46284.256745300925</v>
+        <v>46285.273286157404</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -5985,22 +5985,20 @@
       <c r="R28" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
-      <c r="S28" s="27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="S28" s="27">
+        <v>27.690965622386464</v>
       </c>
       <c r="T28" s="30">
-        <v>46284.256750127315</v>
+        <v>46285.273291631944</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
-          <t/>
+          <t>https://dexscreener.com/robinhood/0xd10e6245961d697d975963682ece9979e9917fbc</t>
         </is>
       </c>
       <c r="V28" s="33" t="inlineStr">
         <is>
-          <t>暂无合格池价；可手动输入</t>
+          <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6059,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46284.25675688658</v>
+        <v>46285.273297430555</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6131,7 +6129,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46284.25676303241</v>
+        <v>46285.27330356481</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6201,7 +6199,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46284.25676841435</v>
+        <v>46285.273309027776</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6266,10 +6264,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1156.4966783606776</v>
+        <v>1149.547220699397</v>
       </c>
       <c r="T32" s="30">
-        <v>46284.25677363426</v>
+        <v>46285.27331482639</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6339,7 +6337,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46284.2567800926</v>
+        <v>46285.273321134264</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6404,10 +6402,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>668.92944279888</v>
+        <v>669.7652270299038</v>
       </c>
       <c r="T34" s="30">
-        <v>46284.25678516203</v>
+        <v>46285.273326724535</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6477,7 +6475,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46284.25679111111</v>
+        <v>46285.2733328588</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6547,7 +6545,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46284.25679728009</v>
+        <v>46285.27333861111</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6617,7 +6615,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46284.256803159726</v>
+        <v>46285.273344155095</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6682,10 +6680,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>154.96315236125992</v>
+        <v>154.7412775459082</v>
       </c>
       <c r="T38" s="30">
-        <v>46284.25680851852</v>
+        <v>46285.27334990741</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6750,10 +6748,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1015.4042836692986</v>
+        <v>998.9555864122192</v>
       </c>
       <c r="T39" s="30">
-        <v>46284.25681479167</v>
+        <v>46285.27335563657</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6823,7 +6821,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46284.2568258449</v>
+        <v>46285.27336726852</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6893,7 +6891,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46284.25683210648</v>
+        <v>46285.27337311342</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6958,10 +6956,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>222.52632652999978</v>
+        <v>221.1215641393992</v>
       </c>
       <c r="T42" s="30">
-        <v>46284.25681989583</v>
+        <v>46285.27336118056</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7031,7 +7029,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46284.25683820602</v>
+        <v>46285.27337888889</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7101,7 +7099,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46284.256843090276</v>
+        <v>46285.27338466435</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7166,10 +7164,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>723.3781186947123</v>
+        <v>720.4953161451934</v>
       </c>
       <c r="T45" s="30">
-        <v>46284.25684939815</v>
+        <v>46285.2733905787</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7234,10 +7232,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>48.006466217912745</v>
+        <v>47.33874614347281</v>
       </c>
       <c r="T46" s="30">
-        <v>46284.25685482639</v>
+        <v>46285.27339596065</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7302,10 +7300,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>152.54232201645164</v>
+        <v>150.76970480310203</v>
       </c>
       <c r="T47" s="30">
-        <v>46284.256861145834</v>
+        <v>46285.273402025465</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7375,7 +7373,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46284.2568662037</v>
+        <v>46285.27340775463</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7440,10 +7438,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.11868370851202</v>
+        <v>100.73989299762705</v>
       </c>
       <c r="T49" s="30">
-        <v>46284.25687215278</v>
+        <v>46285.273413599534</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7513,7 +7511,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46284.25687849537</v>
+        <v>46285.273419351855</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7583,7 +7581,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46284.256884814815</v>
+        <v>46285.273425127314</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7653,7 +7651,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46284.25688956019</v>
+        <v>46285.2734309375</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7723,7 +7721,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46284.25689582176</v>
+        <v>46285.27343675926</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7793,7 +7791,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46284.25690172454</v>
+        <v>46285.27344251158</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7858,10 +7856,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>152.92245240117362</v>
+        <v>152.61043373175778</v>
       </c>
       <c r="T55" s="30">
-        <v>46284.25690637731</v>
+        <v>46285.27344795139</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7926,10 +7924,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>764.0720767223157</v>
+        <v>764.0325568925294</v>
       </c>
       <c r="T56" s="30">
-        <v>46284.25691318287</v>
+        <v>46285.27345454861</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -7994,10 +7992,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>365.54538206604866</v>
+        <v>362.95372967695204</v>
       </c>
       <c r="T57" s="30">
-        <v>46284.256918506944</v>
+        <v>46285.27345984954</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8067,7 +8065,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46284.25692518518</v>
+        <v>46285.27346563658</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8137,7 +8135,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46284.256930393516</v>
+        <v>46285.273471423614</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8207,7 +8205,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46284.25693635417</v>
+        <v>46285.273477222225</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8277,7 +8275,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46284.256941782405</v>
+        <v>46285.27348305556</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8347,7 +8345,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46284.25694795139</v>
+        <v>46285.27348880787</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R918d13da31044a3f"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Rcab139deb5424cbf"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R1503447c5fe24ac7"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R121b487aa5444b30"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -164,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="153">
+  <x:cellXfs count="155">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -615,6 +615,12 @@
     </x:xf>
     <x:xf numFmtId="207" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -627,7 +633,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -638,7 +644,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -649,7 +655,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -660,7 +666,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -671,7 +677,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -682,7 +688,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -693,7 +699,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -704,7 +710,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -760,7 +766,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -771,7 +777,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -782,7 +788,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -793,7 +799,7 @@
         <x:color rgb="FF7D2638"/>
       </x:font>
       <x:fill>
-        <x:patternFill patternType="solid">
+        <x:patternFill>
           <x:bgColor rgb="FFFDE8E7"/>
         </x:patternFill>
       </x:fill>
@@ -1522,10 +1528,10 @@
       <c r="A26" s="2"/>
       <c r="B26" s="2"/>
       <c r="C26" s="107" t="str">
-        <v>恢复目标控筹资金</v>
+        <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,$G$50/$J$55-$G$50/$J$56),""))</f>
       </c>
       <c r="E26" s="106">
         <f>$D$7</f>
@@ -1620,7 +1626,7 @@
       <c r="K30" s="106"/>
       <c r="L30" s="106"/>
     </row>
-    <row r="31" customHeight="1" hidden="1">
+    <row r="31" hidden="1" customHeight="1">
       <c r="A31" s="2"/>
       <c r="B31" s="2"/>
       <c r="C31"/>
@@ -1634,7 +1640,7 @@
       <c r="K31" s="106"/>
       <c r="L31" s="106"/>
     </row>
-    <row r="32" customHeight="1" hidden="1">
+    <row r="32" hidden="1" customHeight="1">
       <c r="A32" s="2"/>
       <c r="B32" s="2"/>
       <c r="C32"/>
@@ -1648,7 +1654,7 @@
       <c r="K32" s="106"/>
       <c r="L32" s="106"/>
     </row>
-    <row r="33" customHeight="1" hidden="1">
+    <row r="33" hidden="1" customHeight="1">
       <c r="A33" s="2"/>
       <c r="B33" s="2"/>
       <c r="C33"/>
@@ -1662,7 +1668,7 @@
       <c r="K33" s="106"/>
       <c r="L33" s="106"/>
     </row>
-    <row r="34" customHeight="1" hidden="1">
+    <row r="34" hidden="1" customHeight="1">
       <c r="A34" s="2"/>
       <c r="B34" s="2"/>
       <c r="C34"/>
@@ -1676,7 +1682,7 @@
       <c r="K34" s="106"/>
       <c r="L34" s="106"/>
     </row>
-    <row r="35" customHeight="1" hidden="1">
+    <row r="35" hidden="1" customHeight="1">
       <c r="A35" s="2"/>
       <c r="B35" s="2"/>
       <c r="C35"/>
@@ -1690,11 +1696,11 @@
       <c r="K35" s="106"/>
       <c r="L35" s="106"/>
     </row>
-    <row r="36" ht="30" customHeight="1">
+    <row r="36" ht="36" customHeight="1">
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>Pons 按现有 Quote 洗筹损耗预算承担费用、持仓保持目标的口径，补回资金为 0；不代表免手续费。动态 Snipe Tax 未计入。</v>
+        <v>Pons 外盘买入时 Hook fee 与 Creator Tax 从输出 Meme 扣除，卖出时从输出 Quote 扣除。洗筹后 Meme 持仓会按买入侧费率减少；补回按洗后 TOKEN 缺口与现有 V4 曲线差额估算，不重复计入洗筹损耗。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -1756,7 +1762,7 @@
       <c r="K39" s="8"/>
       <c r="L39" s="8"/>
     </row>
-    <row r="40" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="40" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40" s="107" t="str">
@@ -1776,7 +1782,7 @@
       <c r="K40" s="107"/>
       <c r="L40" s="107"/>
     </row>
-    <row r="41" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="41" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41" s="107" t="str">
@@ -1802,7 +1808,7 @@
       <c r="K41" s="107"/>
       <c r="L41" s="107"/>
     </row>
-    <row r="42" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="42" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42" s="107" t="str">
@@ -1828,7 +1834,7 @@
       <c r="K42" s="107"/>
       <c r="L42" s="107"/>
     </row>
-    <row r="43" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="43" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43" s="107"/>
@@ -1850,7 +1856,7 @@
       <c r="K43" s="107"/>
       <c r="L43" s="107"/>
     </row>
-    <row r="44" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="44" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44" s="107" t="str">
@@ -1876,7 +1882,7 @@
       <c r="K44" s="107"/>
       <c r="L44" s="107"/>
     </row>
-    <row r="45" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="45" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45" s="107" t="str">
@@ -1902,7 +1908,7 @@
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
     </row>
-    <row r="46" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="46" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46" s="107" t="str">
@@ -1928,7 +1934,7 @@
       <c r="K46" s="107"/>
       <c r="L46" s="107"/>
     </row>
-    <row r="47" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="47" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47" s="107" t="str">
@@ -1954,7 +1960,7 @@
       <c r="K47" s="107"/>
       <c r="L47" s="107"/>
     </row>
-    <row r="48" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="48" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48" s="107" t="str">
@@ -1980,7 +1986,7 @@
       <c r="K48" s="107"/>
       <c r="L48" s="107"/>
     </row>
-    <row r="49" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="49" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49" s="107" t="str">
@@ -2006,7 +2012,7 @@
       <c r="K49" s="107"/>
       <c r="L49" s="107"/>
     </row>
-    <row r="50" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="50" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50" s="107"/>
@@ -2024,7 +2030,7 @@
       <c r="K50" s="107"/>
       <c r="L50" s="107"/>
     </row>
-    <row r="51" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="51" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51" s="107" t="str">
@@ -2050,7 +2056,7 @@
       <c r="K51" s="107"/>
       <c r="L51" s="107"/>
     </row>
-    <row r="52" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="52" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52" s="107" t="str">
@@ -2072,7 +2078,7 @@
       <c r="K52" s="107"/>
       <c r="L52" s="107"/>
     </row>
-    <row r="53" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="53" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53" s="107" t="str">
@@ -2094,7 +2100,7 @@
       <c r="K53" s="107"/>
       <c r="L53" s="107"/>
     </row>
-    <row r="54" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="54" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54" s="107" t="str">
@@ -2115,12 +2121,12 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="112">
-        <f>1</f>
+        <f>MAX(0,1-$G$42-$J$7)</f>
       </c>
       <c r="K54" s="107"/>
       <c r="L54" s="107"/>
     </row>
-    <row r="55" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="55" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55" s="107" t="str">
@@ -2140,11 +2146,13 @@
       <c r="I55" s="107" t="str">
         <v>目标外盘 Pool TOKEN</v>
       </c>
-      <c r="J55" s="108"/>
+      <c r="J55" s="108">
+        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
+      </c>
       <c r="K55" s="107"/>
       <c r="L55" s="107"/>
     </row>
-    <row r="56" ht="30" customHeight="1" outlineLevel="1" hidden="1">
+    <row r="56" ht="30" hidden="1" customHeight="1" outlineLevel="1">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56" s="107" t="str">
@@ -2164,7 +2172,9 @@
       <c r="I56" s="107" t="str">
         <v>洗后外盘 Pool TOKEN</v>
       </c>
-      <c r="J56" s="108"/>
+      <c r="J56" s="108">
+        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
+      </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
     </row>
@@ -4492,7 +4502,7 @@
         <v>场景价格覆盖请用控筹模型</v>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="35" t="str">
@@ -4504,25 +4514,27 @@
       </c>
       <c r="F6" s="35"/>
       <c r="G6" s="35"/>
-      <c r="H6" s="35" t="str">
-        <v>外盘成交口径</v>
-      </c>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35" t="str">
-        <v>exact-input；Hook fee 与 Creator Tax 从 Meme 输出端扣除</v>
-      </c>
-      <c r="K6" s="35"/>
-      <c r="L6" s="35"/>
-      <c r="M6" s="35"/>
-      <c r="N6" s="35"/>
-      <c r="O6" s="35"/>
-      <c r="P6" s="35"/>
-      <c r="Q6" s="35"/>
-      <c r="R6" s="35"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
+      <c r="H6" s="153" t="str">
+        <v>外盘扣费依据</v>
+      </c>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153" t="str">
+        <v>V4 Hook 按交易方向从输出币收取；买入输出为 Meme，卖出输出为 Quote。</v>
+      </c>
+      <c r="K6" s="153"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="153"/>
+      <c r="O6" s="153"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="153"/>
+      <c r="R6" s="153" t="str">
+        <v>https://docs.ponsfamily.com/v2</v>
+      </c>
+      <c r="S6" s="153"/>
+      <c r="T6" s="153"/>
+      <c r="U6" s="153"/>
+      <c r="V6" s="153"/>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="2"/>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R1503447c5fe24ac7"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R121b487aa5444b30"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Rf7e4b787ee604d02"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R4dbb6c88067644a8"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1531,7 +1531,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,$G$50/$J$55-$G$50/$J$56),""))</f>
+        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
       </c>
       <c r="E26" s="106">
         <f>$D$7</f>
@@ -1700,7 +1700,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>Pons 外盘买入时 Hook fee 与 Creator Tax 从输出 Meme 扣除，卖出时从输出 Quote 扣除。洗筹后 Meme 持仓会按买入侧费率减少；补回按洗后 TOKEN 缺口与现有 V4 曲线差额估算，不重复计入洗筹损耗。</v>
+        <v>Pons V2 外盘手续费始终按 Quote leg 计收；Hook 某些方向暂存的 Meme 费用会在池内转换回 Quote，属于内部归集路径。按本模型口径不降低 TOKEN 控筹率，因此恢复目标控筹预留为 0。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -2121,7 +2121,7 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="112">
-        <f>MAX(0,1-$G$42-$J$7)</f>
+        <f>1</f>
       </c>
       <c r="K54" s="107"/>
       <c r="L54" s="107"/>
@@ -4519,7 +4519,7 @@
       </c>
       <c r="I6" s="153"/>
       <c r="J6" s="153" t="str">
-        <v>V4 Hook 按交易方向从输出币收取；买入输出为 Meme，卖出输出为 Quote。</v>
+        <v>费用始终按 Quote leg 计收；Hook 暂存的 Meme 费用会转换回 Quote。</v>
       </c>
       <c r="K6" s="153"/>
       <c r="L6" s="153"/>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Rf7e4b787ee604d02"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R4dbb6c88067644a8"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R4da12d0f94ab4c51"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R82fe03f62c564d75"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1903,7 +1903,7 @@
         <v>外盘含费投入 / Quote</v>
       </c>
       <c r="J45" s="108">
-        <f>IF($J$42="","",$G$50/($G$48-MAX(0,($D$52-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF($J$42="","",($J$43-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="K45" s="107"/>
       <c r="L45" s="107"/>
@@ -2107,7 +2107,7 @@
         <v>当前控筹上限</v>
       </c>
       <c r="D54" s="113">
-        <f>MIN(1-$G$51/$D$45,$G$43+(1-$G$42-$J$7)*$G$48/$D$45)</f>
+        <f>1-$G$51/$D$45</f>
       </c>
       <c r="E54" s="107"/>
       <c r="F54" s="107" t="str">
@@ -2147,7 +2147,7 @@
         <v>目标外盘 Pool TOKEN</v>
       </c>
       <c r="J55" s="108">
-        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
+        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)</f>
       </c>
       <c r="K55" s="107"/>
       <c r="L55" s="107"/>
@@ -2173,7 +2173,7 @@
         <v>洗后外盘 Pool TOKEN</v>
       </c>
       <c r="J56" s="108">
-        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)/MAX(0.000000001,1-$G$42-$J$7)</f>
+        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)</f>
       </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
@@ -2680,7 +2680,7 @@
         <f>IF(E73="","",MAX(0,E73-$G$44))</f>
       </c>
       <c r="K73" s="145">
-        <f>IF(D73="","",$G$50/($G$48-MAX(0,(C73-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D73="","",MAX(0,$G$50/D73-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L73" s="148">
         <f>IF(K73="","",$J$41+K73)</f>
@@ -2714,7 +2714,7 @@
         <f>IF(E74="","",MAX(0,E74-$G$44))</f>
       </c>
       <c r="K74" s="145">
-        <f>IF(D74="","",$G$50/($G$48-MAX(0,(C74-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D74="","",MAX(0,$G$50/D74-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L74" s="148">
         <f>IF(K74="","",$J$41+K74)</f>
@@ -2748,7 +2748,7 @@
         <f>IF(E75="","",MAX(0,E75-$G$44))</f>
       </c>
       <c r="K75" s="145">
-        <f>IF(D75="","",$G$50/($G$48-MAX(0,(C75-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D75="","",MAX(0,$G$50/D75-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L75" s="148">
         <f>IF(K75="","",$J$41+K75)</f>
@@ -2782,7 +2782,7 @@
         <f>IF(E76="","",MAX(0,E76-$G$44))</f>
       </c>
       <c r="K76" s="145">
-        <f>IF(D76="","",$G$50/($G$48-MAX(0,(C76-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D76="","",MAX(0,$G$50/D76-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L76" s="148">
         <f>IF(K76="","",$J$41+K76)</f>
@@ -2816,7 +2816,7 @@
         <f>IF(E77="","",MAX(0,E77-$G$44))</f>
       </c>
       <c r="K77" s="145">
-        <f>IF(D77="","",$G$50/($G$48-MAX(0,(C77-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D77="","",MAX(0,$G$50/D77-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L77" s="148">
         <f>IF(K77="","",$J$41+K77)</f>
@@ -2850,7 +2850,7 @@
         <f>IF(E78="","",MAX(0,E78-$G$44))</f>
       </c>
       <c r="K78" s="145">
-        <f>IF(D78="","",$G$50/($G$48-MAX(0,(C78-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D78="","",MAX(0,$G$50/D78-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L78" s="148">
         <f>IF(K78="","",$J$41+K78)</f>
@@ -2884,7 +2884,7 @@
         <f>IF(E79="","",MAX(0,E79-$G$44))</f>
       </c>
       <c r="K79" s="145">
-        <f>IF(D79="","",$G$50/($G$48-MAX(0,(C79-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D79="","",MAX(0,$G$50/D79-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L79" s="148">
         <f>IF(K79="","",$J$41+K79)</f>
@@ -2918,7 +2918,7 @@
         <f>IF(E80="","",MAX(0,E80-$G$44))</f>
       </c>
       <c r="K80" s="145">
-        <f>IF(D80="","",$G$50/($G$48-MAX(0,(C80-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D80="","",MAX(0,$G$50/D80-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L80" s="148">
         <f>IF(K80="","",$J$41+K80)</f>
@@ -2952,7 +2952,7 @@
         <f>IF(E81="","",MAX(0,E81-$G$44))</f>
       </c>
       <c r="K81" s="145">
-        <f>IF(D81="","",$G$50/($G$48-MAX(0,(C81-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D81="","",MAX(0,$G$50/D81-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L81" s="148">
         <f>IF(K81="","",$J$41+K81)</f>
@@ -2986,7 +2986,7 @@
         <f>IF(E82="","",MAX(0,E82-$G$44))</f>
       </c>
       <c r="K82" s="145">
-        <f>IF(D82="","",$G$50/($G$48-MAX(0,(C82-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D82="","",MAX(0,$G$50/D82-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L82" s="148">
         <f>IF(K82="","",$J$41+K82)</f>
@@ -3020,7 +3020,7 @@
         <f>IF(E83="","",MAX(0,E83-$G$44))</f>
       </c>
       <c r="K83" s="145">
-        <f>IF(D83="","",$G$50/($G$48-MAX(0,(C83-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D83="","",MAX(0,$G$50/D83-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L83" s="148">
         <f>IF(K83="","",$J$41+K83)</f>
@@ -3054,7 +3054,7 @@
         <f>IF(E84="","",MAX(0,E84-$G$44))</f>
       </c>
       <c r="K84" s="145">
-        <f>IF(D84="","",$G$50/($G$48-MAX(0,(C84-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D84="","",MAX(0,$G$50/D84-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L84" s="148">
         <f>IF(K84="","",$J$41+K84)</f>
@@ -3088,7 +3088,7 @@
         <f>IF(E85="","",MAX(0,E85-$G$44))</f>
       </c>
       <c r="K85" s="146">
-        <f>IF(D85="","",$G$50/($G$48-MAX(0,(C85-$G$43)*$D$45)/(1-$G$42-$J$7))-$G$44)</f>
+        <f>IF(D85="","",MAX(0,$G$50/D85-$G$44)/MAX(0.000000001,1-$G$42-$J$7))</f>
       </c>
       <c r="L85" s="149">
         <f>IF(K85="","",$J$41+K85)</f>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R4da12d0f94ab4c51"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R82fe03f62c564d75"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R6c70b30a17644365"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R3ed7d1eb6cff4109"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -164,7 +164,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="155">
+  <x:cellXfs count="158">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -621,6 +621,11 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="210" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1123,7 +1128,7 @@
         <v>Quote</v>
       </c>
       <c r="D7" s="51" t="str">
-        <v>ETH</v>
+        <v>USDG</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="35" t="str">
@@ -1393,7 +1398,7 @@
         <v>原生币价格 / USDT</v>
       </c>
       <c r="J19" s="123">
-        <f>IF($D$7="ETH",$D$55,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+        <f>IF($D$7="ETH",$D$55,IF(VLOOKUP("ETH",'Quote参数'!$E$9:$S$63,15,FALSE)&gt;0,VLOOKUP("ETH",'Quote参数'!$E$9:$S$63,15,FALSE),""))</f>
       </c>
       <c r="K19" s="106"/>
       <c r="L19" s="106"/>
@@ -1789,7 +1794,7 @@
         <v>Quote 名称</v>
       </c>
       <c r="D41" s="108">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,2,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,2,FALSE)</f>
       </c>
       <c r="E41" s="107"/>
       <c r="F41" s="107" t="str">
@@ -1815,7 +1820,7 @@
         <v>Quote 合约</v>
       </c>
       <c r="D42" s="109">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,3,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,3,FALSE)</f>
       </c>
       <c r="E42" s="107"/>
       <c r="F42" s="107" t="str">
@@ -1863,14 +1868,14 @@
         <v>Decimals</v>
       </c>
       <c r="D44" s="110">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,4,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,4,FALSE)</f>
       </c>
       <c r="E44" s="107"/>
       <c r="F44" s="107" t="str">
         <v>毕业真实 Quote</v>
       </c>
       <c r="G44" s="108">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,6,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,6,FALSE)</f>
       </c>
       <c r="H44" s="107"/>
       <c r="I44" s="107" t="str">
@@ -1915,14 +1920,14 @@
         <v>协议参数证据</v>
       </c>
       <c r="D46" s="108">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$62,12,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$P$63,12,FALSE)</f>
       </c>
       <c r="E46" s="107"/>
       <c r="F46" s="107" t="str">
         <v>phantom Quote</v>
       </c>
       <c r="G46" s="108">
-        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$62,5,FALSE)</f>
+        <f>VLOOKUP($D$7,'Quote参数'!$E$9:$J$63,5,FALSE)</f>
       </c>
       <c r="H46" s="107"/>
       <c r="I46" s="107" t="str">
@@ -2133,7 +2138,7 @@
         <v>Quote 价格 / USDT</v>
       </c>
       <c r="D55" s="108">
-        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$62,15,FALSE),""))</f>
+        <f>IF($D$9&lt;&gt;"",IF(AND(ISNUMBER($D$9),$D$9&gt;0),$D$9,""),IF(VLOOKUP($D$7,'Quote参数'!$E$9:$S$63,15,FALSE)&gt;0,VLOOKUP($D$7,'Quote参数'!$E$9:$S$63,15,FALSE),""))</f>
       </c>
       <c r="E55" s="107"/>
       <c r="F55" s="107" t="str">
@@ -2159,7 +2164,7 @@
         <v>行情时间 / UTC</v>
       </c>
       <c r="D56" s="150">
-        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$62,16,FALSE))</f>
+        <f>IF(VLOOKUP($D$7,'Quote参数'!$E$9:$T$63,16,FALSE)=0,"",VLOOKUP($D$7,'Quote参数'!$E$9:$T$63,16,FALSE))</f>
       </c>
       <c r="E56" s="107"/>
       <c r="F56" s="107" t="str">
@@ -4284,7 +4289,7 @@
   </conditionalFormatting>
   <dataValidations count="13">
     <dataValidation type="list" sqref="D7">
-      <formula1>'Quote参数'!$E$9:$E$62</formula1>
+      <formula1>'Quote参数'!$E$9:$E$63</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="between" sqref="D8">
       <formula1>0</formula1>
@@ -4414,7 +4419,7 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="6" t="str">
-        <v>ETH + 53 个股票 / ETF Quote。股票类参数为 Robinhood Chain 区块 54,430,299 快照；Factory owner 后续可更新新 Launch 参数。</v>
+        <v>ETH、USDG 与股票 / ETF Quote。USDG 参数取 Factory 区块 68,708,148；已发币以发行时快照为准。</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4549,9 +4554,11 @@
       <c r="F7" s="35"/>
       <c r="G7" s="35"/>
       <c r="H7" s="35" t="str">
-        <v>Snipe 窗口</v>
-      </c>
-      <c r="I7" s="35"/>
+        <v>USDG 参数依据</v>
+      </c>
+      <c r="I7" s="35" t="str">
+        <v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</v>
+      </c>
       <c r="J7" s="35" t="str">
         <v>3 秒（当前 Factory 链上参数）</v>
       </c>
@@ -8367,6 +8374,72 @@
       <c r="V62" s="34" t="inlineStr">
         <is>
           <t>暂无合格池价；可手动输入</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="42" customHeight="1">
+      <c r="C63" t="n">
+        <v>55</v>
+      </c>
+      <c r="D63" t="str">
+        <v>稳定币</v>
+      </c>
+      <c r="E63" t="str">
+        <v>USDG</v>
+      </c>
+      <c r="F63" t="str">
+        <v>Global Dollar</v>
+      </c>
+      <c r="G63" t="str">
+        <v>​0x5fc5360D0400a0Fd4f2af552ADD042D716F1d168</v>
+      </c>
+      <c r="H63" t="n">
+        <v>6</v>
+      </c>
+      <c r="I63" t="n">
+        <v>202.25</v>
+      </c>
+      <c r="J63" t="n">
+        <v>505.625</v>
+      </c>
+      <c r="K63">
+        <f>J63/I63</f>
+      </c>
+      <c r="L63">
+        <f>J63</f>
+      </c>
+      <c r="M63">
+        <f>1000000000*I63*J63/(I63+J63)^2</f>
+      </c>
+      <c r="N63">
+        <f>1000000000*I63^2/(I63+J63)^2</f>
+      </c>
+      <c r="O63">
+        <f>1-N63/1000000000</f>
+      </c>
+      <c r="P63" t="n">
+        <v>68708148</v>
+      </c>
+      <c r="Q63" t="str">
+        <v>Approved / ERC-20</v>
+      </c>
+      <c r="R63" t="str">
+        <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
+      </c>
+      <c r="S63" s="155">
+        <v>1.0003961568781237</v>
+      </c>
+      <c r="T63" s="156">
+        <v>46285.27349457176</v>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</t>
+        </is>
+      </c>
+      <c r="V63" s="157" t="inlineStr">
+        <is>
+          <t>USDG 按 1 USD 估算；本地可手动更新</t>
         </is>
       </c>
     </row>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R6c70b30a17644365"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R3ed7d1eb6cff4109"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Rd7aedc8ed7d34244"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R2337eec321c940d1"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -4419,7 +4419,7 @@
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="6" t="str">
-        <v>ETH、USDG 与股票 / ETF Quote。USDG 参数取 Factory 区块 68,708,148；已发币以发行时快照为准。</v>
+        <v>ETH、USDG 与股票 / ETF Quote。USDG 采用 TRAIN 发行参数快照，外盘 8,090 USDG；新币参数可变。</v>
       </c>
       <c r="D3" s="6"/>
       <c r="E3" s="6"/>
@@ -4557,7 +4557,7 @@
         <v>USDG 参数依据</v>
       </c>
       <c r="I7" s="35" t="str">
-        <v>https://robinhoodchain.blockscout.com/address/0x7eD598BcEf8bd9Edd8C97A195C6d13f40801EC7e?tab=read_contract</v>
+        <v>https://robin.etherscan.io/tx/0x387e3237904e4822075066331564561c373b691fd47ad2d52b4f64fb4f398c84#eventlog</v>
       </c>
       <c r="J7" s="35" t="str">
         <v>3 秒（当前 Factory 链上参数）</v>
@@ -8397,10 +8397,10 @@
         <v>6</v>
       </c>
       <c r="I63" t="n">
-        <v>202.25</v>
+        <v>3236</v>
       </c>
       <c r="J63" t="n">
-        <v>505.625</v>
+        <v>8090</v>
       </c>
       <c r="K63">
         <f>J63/I63</f>
@@ -8418,10 +8418,10 @@
         <f>1-N63/1000000000</f>
       </c>
       <c r="P63" t="n">
-        <v>68708148</v>
+        <v>69045064</v>
       </c>
       <c r="Q63" t="str">
-        <v>Approved / ERC-20</v>
+        <v>已发行实例 / ERC-20</v>
       </c>
       <c r="R63" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Rd7aedc8ed7d34244"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R2337eec321c940d1"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R4174b316770c4864"/>
+    <sheet name="Quote参数" sheetId="2" r:id="Ra03c4c2a547940c6"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1536,7 +1536,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",0)</f>
+        <f>IF($D$51&lt;&gt;"可达","",0)</f>
       </c>
       <c r="E26" s="106">
         <f>$D$7</f>
@@ -1573,7 +1573,7 @@
       <c r="A28" s="2"/>
       <c r="B28" s="2"/>
       <c r="C28" s="107" t="str">
-        <v>补回目标控筹率</v>
+        <v>原目标控筹率</v>
       </c>
       <c r="D28" s="124">
         <f>$D$8</f>
@@ -1705,7 +1705,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>Pons V2 外盘手续费始终按 Quote leg 计收；Hook 某些方向暂存的 Meme 费用会在池内转换回 Quote，属于内部归集路径。按本模型口径不降低 TOKEN 控筹率，因此恢复目标控筹预留为 0。</v>
+        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -2126,7 +2126,7 @@
         <v>洗后持仓保留比例</v>
       </c>
       <c r="J54" s="112">
-        <f>1</f>
+        <f>MAX(0,1-$J$29)*MAX(0,1-$J$30)</f>
       </c>
       <c r="K54" s="107"/>
       <c r="L54" s="107"/>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="I6" s="153"/>
       <c r="J6" s="153" t="str">
-        <v>费用始终按 Quote leg 计收；Hook 暂存的 Meme 费用会转换回 Quote。</v>
+        <v>外盘卖出所得 Quote 用于回买；双边 Hook 与 Creator Tax 降低洗后持币，预留为 0。</v>
       </c>
       <c r="K6" s="153"/>
       <c r="L6" s="153"/>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="R4174b316770c4864"/>
-    <sheet name="Quote参数" sheetId="2" r:id="Ra03c4c2a547940c6"/>
+    <sheet name="控筹模型" sheetId="1" r:id="Rc186d0e49add41d6"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R3b11b162cb2c48f3"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -1536,7 +1536,7 @@
         <v>恢复目标控筹预留</v>
       </c>
       <c r="D26" s="122">
-        <f>IF($D$51&lt;&gt;"可达","",0)</f>
+        <f>IF($D$51&lt;&gt;"可达","",IF(AND($J$55&gt;0,$J$56&gt;0),MAX(0,($G$50/$J$55-$G$50/$J$56)*(1/(1-$G$42-$J$7))),""))</f>
       </c>
       <c r="E26" s="106">
         <f>$D$7</f>
@@ -1705,7 +1705,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>外盘一卖一买：卖出所得 Quote 全额用于回买，不额外补 Quote。洗后控筹按卖出、买入两腿含税费率同价估算；实际成交量、滑点与价格冲击未计入。洗筹损耗另按预算 FDV × 双边费率列示。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>
@@ -2152,7 +2152,7 @@
         <v>目标外盘 Pool TOKEN</v>
       </c>
       <c r="J55" s="108">
-        <f>$G$48-MAX(0,($D$8-$G$43)*$D$45)</f>
+        <f>$G$48-($D$8-$G$43)*$D$45</f>
       </c>
       <c r="K55" s="107"/>
       <c r="L55" s="107"/>
@@ -2178,7 +2178,7 @@
         <v>洗后外盘 Pool TOKEN</v>
       </c>
       <c r="J56" s="108">
-        <f>$G$48-MAX(0,($D$27-$G$43)*$D$45)</f>
+        <f>$G$48-($D$27-$G$43)*$D$45</f>
       </c>
       <c r="K56" s="107"/>
       <c r="L56" s="107"/>
@@ -4524,7 +4524,7 @@
       </c>
       <c r="I6" s="153"/>
       <c r="J6" s="153" t="str">
-        <v>外盘卖出所得 Quote 用于回买；双边 Hook 与 Creator Tax 降低洗后持币，预留为 0。</v>
+        <v>外盘卖出所得 Quote 用于回买；双边 Hook 与 Creator Tax 降低持币。恢复目标按外盘曲线差额及买入费另列。</v>
       </c>
       <c r="K6" s="153"/>
       <c r="L6" s="153"/>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2580.0817123580937</v>
+        <v>2727.8255833609232</v>
       </c>
       <c r="T9" s="29">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>334.9426372843646</v>
+        <v>339.45909396889476</v>
       </c>
       <c r="T10" s="30">
-        <v>46285.27318768518</v>
+        <v>46287.26970171296</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4826,20 +4826,22 @@
       <c r="R11" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
-      <c r="S11" s="27">
-        <v>2.6810617004333714</v>
+      <c r="S11" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T11" s="30">
-        <v>46285.27319353009</v>
+        <v>46287.2697075</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0xcf38764ae8c92222af4358a701871a6235cfc7b7</t>
+          <t/>
         </is>
       </c>
       <c r="V11" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46285.27319930556</v>
+        <v>46287.26971328704</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4970,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46285.273205115736</v>
+        <v>46287.269719097225</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5040,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46285.27321087963</v>
+        <v>46287.269724861115</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5110,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46285.27321663194</v>
+        <v>46287.26973090278</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5180,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46285.27322246528</v>
+        <v>46287.269736469905</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5250,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46285.273228252314</v>
+        <v>46287.26974224537</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5315,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>192.1700993593463</v>
+        <v>195.68559474357525</v>
       </c>
       <c r="T18" s="30">
-        <v>46285.273234050925</v>
+        <v>46287.269748032406</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5388,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46285.27323954861</v>
+        <v>46287.26975383102</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5453,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>90.91600273708387</v>
+        <v>91.72137107946152</v>
       </c>
       <c r="T20" s="30">
-        <v>46285.273245625</v>
+        <v>46287.2697596412</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5526,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46285.27325148148</v>
+        <v>46287.26976541666</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5591,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.843502026802613</v>
+        <v>9.112123124688052</v>
       </c>
       <c r="T22" s="30">
-        <v>46285.27325719907</v>
+        <v>46287.269771203704</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5664,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46285.27326297454</v>
+        <v>46287.26977706018</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5734,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46285.27326883102</v>
+        <v>46287.26978283565</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5799,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>400.1284508665432</v>
+        <v>394.81199119394824</v>
       </c>
       <c r="T25" s="30">
-        <v>46285.27327459491</v>
+        <v>46287.269788715275</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5872,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46285.273280092595</v>
+        <v>46287.269794375</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5937,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.5884370210603</v>
+        <v>353.7224173232363</v>
       </c>
       <c r="T27" s="30">
-        <v>46285.273286157404</v>
+        <v>46287.26980012732</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6004,20 +6006,22 @@
       <c r="R28" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
-      <c r="S28" s="27">
-        <v>27.690965622386464</v>
+      <c r="S28" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T28" s="30">
-        <v>46285.273291631944</v>
+        <v>46287.269805937496</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0xd10e6245961d697d975963682ece9979e9917fbc</t>
+          <t/>
         </is>
       </c>
       <c r="V28" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -6078,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46285.273297430555</v>
+        <v>46287.26981172454</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6148,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46285.27330356481</v>
+        <v>46287.26981751157</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6218,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46285.273309027776</v>
+        <v>46287.269823333336</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6283,10 +6287,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1149.547220699397</v>
+        <v>1163.6911400356285</v>
       </c>
       <c r="T32" s="30">
-        <v>46285.27331482639</v>
+        <v>46287.269829108795</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6356,7 +6360,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46285.273321134264</v>
+        <v>46287.26983491898</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6421,10 +6425,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>669.7652270299038</v>
+        <v>744.0333597728271</v>
       </c>
       <c r="T34" s="30">
-        <v>46285.273326724535</v>
+        <v>46287.26984072917</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6494,7 +6498,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46285.2733328588</v>
+        <v>46287.26984649306</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6564,7 +6568,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46285.27333861111</v>
+        <v>46287.26985232639</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6634,7 +6638,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46285.273344155095</v>
+        <v>46287.269858125</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6699,10 +6703,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>154.7412775459082</v>
+        <v>164.18825586361623</v>
       </c>
       <c r="T38" s="30">
-        <v>46285.27334990741</v>
+        <v>46287.26986392361</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6767,10 +6771,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>998.9555864122192</v>
+        <v>1043.4931339001987</v>
       </c>
       <c r="T39" s="30">
-        <v>46285.27335563657</v>
+        <v>46287.26986969908</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6840,7 +6844,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46285.27336726852</v>
+        <v>46287.26988130787</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6910,7 +6914,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46285.27337311342</v>
+        <v>46287.2698870949</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6975,10 +6979,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>221.1215641393992</v>
+        <v>226.25271688303374</v>
       </c>
       <c r="T42" s="30">
-        <v>46285.27336118056</v>
+        <v>46287.26987550926</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7048,7 +7052,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46285.27337888889</v>
+        <v>46287.26989287037</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7118,7 +7122,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46285.27338466435</v>
+        <v>46287.26989869213</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7183,10 +7187,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>720.4953161451934</v>
+        <v>741.542779467616</v>
       </c>
       <c r="T45" s="30">
-        <v>46285.2733905787</v>
+        <v>46287.26990446759</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7251,10 +7255,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.33874614347281</v>
+        <v>51.080901850131085</v>
       </c>
       <c r="T46" s="30">
-        <v>46285.27339596065</v>
+        <v>46287.26991023148</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7319,10 +7323,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>150.76970480310203</v>
+        <v>157.4966967303382</v>
       </c>
       <c r="T47" s="30">
-        <v>46285.273402025465</v>
+        <v>46287.269916018515</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7392,7 +7396,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46285.27340775463</v>
+        <v>46287.269921770836</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7457,10 +7461,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.73989299762705</v>
+        <v>100.49341496568701</v>
       </c>
       <c r="T49" s="30">
-        <v>46285.273413599534</v>
+        <v>46287.26992755787</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7530,7 +7534,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46285.273419351855</v>
+        <v>46287.26993332176</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7600,7 +7604,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46285.273425127314</v>
+        <v>46287.269939120364</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7670,7 +7674,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46285.2734309375</v>
+        <v>46287.26994489583</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7740,7 +7744,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46285.27343675926</v>
+        <v>46287.269950671296</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7810,7 +7814,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46285.27344251158</v>
+        <v>46287.26995644676</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7875,10 +7879,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>152.61043373175778</v>
+        <v>152.2654778563405</v>
       </c>
       <c r="T55" s="30">
-        <v>46285.27344795139</v>
+        <v>46287.26996224537</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7943,10 +7947,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>764.0325568925294</v>
+        <v>774.3204166570811</v>
       </c>
       <c r="T56" s="30">
-        <v>46285.27345454861</v>
+        <v>46287.26996803241</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8011,10 +8015,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>362.95372967695204</v>
+        <v>375.0876654260443</v>
       </c>
       <c r="T57" s="30">
-        <v>46285.27345984954</v>
+        <v>46287.26997378472</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8084,7 +8088,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46285.27346563658</v>
+        <v>46287.26997954861</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8154,7 +8158,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46285.273471423614</v>
+        <v>46287.26998532407</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8224,7 +8228,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46285.273477222225</v>
+        <v>46287.26999111111</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8294,7 +8298,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46285.27348305556</v>
+        <v>46287.2699969213</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8364,7 +8368,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46285.27348880787</v>
+        <v>46287.27000268518</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8427,10 +8431,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0003961568781237</v>
+        <v>1.0002330543016522</v>
       </c>
       <c r="T63" s="156">
-        <v>46285.27349457176</v>
+        <v>46287.270008506945</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
-    <sheet name="控筹模型" sheetId="1" r:id="Rc186d0e49add41d6"/>
-    <sheet name="Quote参数" sheetId="2" r:id="R3b11b162cb2c48f3"/>
+    <sheet name="控筹模型" sheetId="1" r:id="R29bd439ea94449d8"/>
+    <sheet name="Quote参数" sheetId="2" r:id="R75525efca1a94dae"/>
   </sheets>
   <calcPr calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
 </workbook>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="11">
+  <x:numFmts count="12">
     <x:numFmt numFmtId="200" formatCode="@"/>
     <x:numFmt numFmtId="201" formatCode="0"/>
     <x:numFmt numFmtId="202" formatCode="#,##0.000000"/>
@@ -27,6 +27,7 @@
     <x:numFmt numFmtId="208" formatCode="0.00%"/>
     <x:numFmt numFmtId="209" formatCode="0.000000E+00"/>
     <x:numFmt numFmtId="210" formatCode="0.0000000000"/>
+    <x:numFmt numFmtId="211" formatCode=";;;"/>
   </x:numFmts>
   <x:fonts count="12">
     <x:font>
@@ -164,7 +165,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="158">
+  <x:cellXfs count="159">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -626,6 +627,9 @@
     <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="211" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1348,7 +1352,7 @@
         <v>建议 Quote 资金</v>
       </c>
       <c r="D18" s="121">
-        <f>IF(ISNUMBER($D$26),(IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($D$22="","",SUM($D$22,$D$23,$D$24,$D$25))))+$D$26,"")</f>
+        <f>IF(AND(LEFT($D$51,2)="可达",ISNUMBER($D$22),ISNUMBER($D$23),ISNUMBER($D$25),ISNUMBER($D$26)),SUM($D$22:$D$23,$D$25:$D$26),"")</f>
       </c>
       <c r="E18" s="62">
         <f>$D$7</f>
@@ -1481,15 +1485,11 @@
       <c r="K23" s="106"/>
       <c r="L23" s="106"/>
     </row>
-    <row r="24" ht="20" customHeight="1">
+    <row r="24" customHeight="1" hidden="1">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
-      <c r="C24" s="107" t="str">
-        <v>洗筹损耗</v>
-      </c>
-      <c r="D24" s="122">
-        <f>IF(LEFT($D$51,2)&lt;&gt;"可达","",IF($J$46="","",$J$46*($G$42+$J$7)*2))</f>
-      </c>
+      <c r="C24" s="107"/>
+      <c r="D24" s="158"/>
       <c r="E24" s="106">
         <f>$D$7</f>
       </c>
@@ -1705,7 +1705,7 @@
       <c r="A36" s="2"/>
       <c r="B36" s="2"/>
       <c r="C36" s="115" t="str">
-        <v>外盘一卖一买使用卖出所得 Quote 回买；洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote。洗筹损耗另列；未模拟成交量、滑点与价格冲击。</v>
+        <v>外盘一卖一买使用卖出所得 Quote 回买；手续费仅降低洗后持币，不另列资金。洗后若低于目标，再按外盘曲线差额及买入费预留恢复所需 Quote；未模拟成交量、滑点与价格冲击。</v>
       </c>
       <c r="D36" s="115"/>
       <c r="E36" s="115"/>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2758.198541325769</v>
+        <v>2686.1873966070093</v>
       </c>
       <c r="T9" s="29">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>340.60403355830897</v>
+        <v>336.74859425540046</v>
       </c>
       <c r="T10" s="30">
-        <v>46288.25891674768</v>
+        <v>46289.26581546296</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46288.25892252315</v>
+        <v>46289.26582151621</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46288.25892833334</v>
+        <v>46289.26582662037</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46288.25893412037</v>
+        <v>46289.26583290509</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46288.25893991898</v>
+        <v>46289.26583895834</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46288.25894572916</v>
+        <v>46289.265844814814</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46288.25895150463</v>
+        <v>46289.265850428244</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46288.25895733797</v>
+        <v>46289.265856770835</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>202.15800570507255</v>
+        <v>197.53437098055062</v>
       </c>
       <c r="T18" s="30">
-        <v>46288.258963101856</v>
+        <v>46289.26586221065</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46288.258968912036</v>
+        <v>46289.26586791666</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>95.02436458054115</v>
+        <v>92.81615001010175</v>
       </c>
       <c r="T20" s="30">
-        <v>46288.25897498843</v>
+        <v>46289.26587375</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46288.25898048611</v>
+        <v>46289.26587935185</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.361760010882046</v>
+        <v>9.047574277924358</v>
       </c>
       <c r="T22" s="30">
-        <v>46288.25898627315</v>
+        <v>46289.26588525463</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46288.25899204861</v>
+        <v>46289.26589109954</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46288.258997847224</v>
+        <v>46289.26589609953</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>398.0908410781227</v>
+        <v>395.3887976507912</v>
       </c>
       <c r="T25" s="30">
-        <v>46288.25900363426</v>
+        <v>46289.265902708335</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46288.25900943287</v>
+        <v>46289.265908483794</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>355.09175725036306</v>
+        <v>342.1055263615869</v>
       </c>
       <c r="T27" s="30">
-        <v>46288.259015219905</v>
+        <v>46289.26591423611</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>30.74578020667885</v>
+        <v>28.73499988998086</v>
       </c>
       <c r="T28" s="30">
-        <v>46288.259021018515</v>
+        <v>46289.26591978009</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46288.25902684028</v>
+        <v>46289.26592571759</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46288.25903260417</v>
+        <v>46289.26593152778</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46288.259038414355</v>
+        <v>46289.265937337965</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46288.25904418982</v>
+        <v>46289.265942418984</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46288.259049988425</v>
+        <v>46289.26594888889</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6425,10 +6425,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>739.9591123131149</v>
+        <v>737.2682846815346</v>
       </c>
       <c r="T34" s="30">
-        <v>46288.25905609954</v>
+        <v>46289.265954016206</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46288.259061585646</v>
+        <v>46289.265961122685</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46288.25906737269</v>
+        <v>46289.26596657407</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46288.25907315972</v>
+        <v>46289.26597211806</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6703,10 +6703,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>170.79210891647628</v>
+        <v>162.04719621214093</v>
       </c>
       <c r="T38" s="30">
-        <v>46288.2590789699</v>
+        <v>46289.26597721065</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6771,10 +6771,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1101.617104015555</v>
+        <v>1072.9166875036256</v>
       </c>
       <c r="T39" s="30">
-        <v>46288.25908476851</v>
+        <v>46289.265983715275</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46288.25909634259</v>
+        <v>46289.26599552084</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46288.25910215278</v>
+        <v>46289.2660015625</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6979,10 +6979,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>228.90303377034883</v>
+        <v>225.00915159237707</v>
       </c>
       <c r="T42" s="30">
-        <v>46288.25909057871</v>
+        <v>46289.26598880787</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46288.25910792824</v>
+        <v>46289.26600688657</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46288.25911373843</v>
+        <v>46289.26601197917</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7187,10 +7187,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>746.6403683892571</v>
+        <v>738.9185718314986</v>
       </c>
       <c r="T45" s="30">
-        <v>46288.259119560185</v>
+        <v>46289.266017974536</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7255,10 +7255,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>49.60932655339204</v>
+        <v>48.92851356135968</v>
       </c>
       <c r="T46" s="30">
-        <v>46288.25912530093</v>
+        <v>46289.26602482639</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7323,10 +7323,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.72927710409556</v>
+        <v>151.13629771580256</v>
       </c>
       <c r="T47" s="30">
-        <v>46288.25913107639</v>
+        <v>46289.26603024305</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46288.25913685185</v>
+        <v>46289.26603578704</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7461,10 +7461,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.99898780970823</v>
+        <v>101.50766233324597</v>
       </c>
       <c r="T49" s="30">
-        <v>46288.25914266204</v>
+        <v>46289.26604190972</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46288.25914844908</v>
+        <v>46289.26604731481</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46288.25915422454</v>
+        <v>46289.266053391206</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46288.25916001158</v>
+        <v>46289.266058333335</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46288.25916581019</v>
+        <v>46289.26606476852</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46288.25917158565</v>
+        <v>46289.266071122685</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>154.39902701707922</v>
+        <v>148.54584697737408</v>
       </c>
       <c r="T55" s="30">
-        <v>46288.25917737269</v>
+        <v>46289.266076087966</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7947,10 +7947,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>775.3857725252348</v>
+        <v>767.2064939299438</v>
       </c>
       <c r="T56" s="30">
-        <v>46288.2591831713</v>
+        <v>46289.26608217593</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>378.15809372161965</v>
+        <v>378.0457799657141</v>
       </c>
       <c r="T57" s="30">
-        <v>46288.25918893518</v>
+        <v>46289.266087696764</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46288.259195</v>
+        <v>46289.266094039354</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46288.259200775465</v>
+        <v>46289.266100162036</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46288.259206296294</v>
+        <v>46289.26610519676</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46288.25921207176</v>
+        <v>46289.266110856486</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46288.259217858795</v>
+        <v>46289.26611681713</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8431,10 +8431,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0001880353506458</v>
+        <v>1.000174030281269</v>
       </c>
       <c r="T63" s="156">
-        <v>46288.25922368056</v>
+        <v>46289.26612302083</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2686.1873966070093</v>
+        <v>2673.706614603858</v>
       </c>
       <c r="T9" s="29">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.74859425540046</v>
+        <v>336.1201738716447</v>
       </c>
       <c r="T10" s="30">
-        <v>46289.26581546296</v>
+        <v>46290.26226416667</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46289.26582151621</v>
+        <v>46290.26227013889</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46289.26582662037</v>
+        <v>46290.26227575231</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46289.26583290509</v>
+        <v>46290.26228188658</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46289.26583895834</v>
+        <v>46290.262287708334</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46289.265844814814</v>
+        <v>46290.262293541666</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46289.265850428244</v>
+        <v>46290.26229899305</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46289.265856770835</v>
+        <v>46290.26230534723</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>197.53437098055062</v>
+        <v>199.02622277254463</v>
       </c>
       <c r="T18" s="30">
-        <v>46289.26586221065</v>
+        <v>46290.2623099537</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46289.26586791666</v>
+        <v>46290.26231670139</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>92.81615001010175</v>
+        <v>92.52683988485906</v>
       </c>
       <c r="T20" s="30">
-        <v>46289.26587375</v>
+        <v>46290.26232230324</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46289.26587935185</v>
+        <v>46290.26232800926</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.047574277924358</v>
+        <v>9.11165832181457</v>
       </c>
       <c r="T22" s="30">
-        <v>46289.26588525463</v>
+        <v>46290.26233424769</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46289.26589109954</v>
+        <v>46290.26233929398</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46289.26589609953</v>
+        <v>46290.26234540509</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>395.3887976507912</v>
+        <v>392.0213478853151</v>
       </c>
       <c r="T25" s="30">
-        <v>46289.265902708335</v>
+        <v>46290.26235128472</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46289.265908483794</v>
+        <v>46290.26235662037</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>342.1055263615869</v>
+        <v>342.0522535101389</v>
       </c>
       <c r="T27" s="30">
-        <v>46289.26591423611</v>
+        <v>46290.26236283565</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.73499988998086</v>
+        <v>29.39534995369157</v>
       </c>
       <c r="T28" s="30">
-        <v>46289.26591978009</v>
+        <v>46290.26236862269</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46289.26592571759</v>
+        <v>46290.262374398146</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46289.26593152778</v>
+        <v>46290.262380196764</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46289.265937337965</v>
+        <v>46290.26238590278</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46289.265942418984</v>
+        <v>46290.26239177083</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6360,7 +6360,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46289.26594888889</v>
+        <v>46290.26239751157</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6425,10 +6425,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>737.2682846815346</v>
+        <v>779.671900285852</v>
       </c>
       <c r="T34" s="30">
-        <v>46289.265954016206</v>
+        <v>46290.26240344907</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46289.265961122685</v>
+        <v>46290.26240974537</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6568,7 +6568,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46289.26596657407</v>
+        <v>46290.262415046294</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46289.26597211806</v>
+        <v>46290.26242064815</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6703,10 +6703,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>162.04719621214093</v>
+        <v>161.7394365774571</v>
       </c>
       <c r="T38" s="30">
-        <v>46289.26597721065</v>
+        <v>46290.26242579862</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6771,10 +6771,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1072.9166875036256</v>
+        <v>1080.4866485700397</v>
       </c>
       <c r="T39" s="30">
-        <v>46289.265983715275</v>
+        <v>46290.26243282408</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46289.26599552084</v>
+        <v>46290.262444328706</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6914,7 +6914,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46289.2660015625</v>
+        <v>46290.26244982639</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6979,10 +6979,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>225.00915159237707</v>
+        <v>225.1709811185636</v>
       </c>
       <c r="T42" s="30">
-        <v>46289.26598880787</v>
+        <v>46290.262437314814</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46289.26600688657</v>
+        <v>46290.26245526621</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7122,7 +7122,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46289.26601197917</v>
+        <v>46290.26246114584</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7187,10 +7187,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>738.9185718314986</v>
+        <v>743.8253762184718</v>
       </c>
       <c r="T45" s="30">
-        <v>46289.266017974536</v>
+        <v>46290.26246638889</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7255,10 +7255,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>48.92851356135968</v>
+        <v>48.798881396414146</v>
       </c>
       <c r="T46" s="30">
-        <v>46289.26602482639</v>
+        <v>46290.262473159724</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7323,10 +7323,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>151.13629771580256</v>
+        <v>151.9076471917889</v>
       </c>
       <c r="T47" s="30">
-        <v>46289.26603024305</v>
+        <v>46290.26247868055</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7396,7 +7396,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46289.26603578704</v>
+        <v>46290.26248414352</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7461,10 +7461,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.50766233324597</v>
+        <v>101.2684308544155</v>
       </c>
       <c r="T49" s="30">
-        <v>46289.26604190972</v>
+        <v>46290.26249064815</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7534,7 +7534,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46289.26604731481</v>
+        <v>46290.26249605324</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7604,7 +7604,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46289.266053391206</v>
+        <v>46290.26250199074</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7674,7 +7674,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46289.266058333335</v>
+        <v>46290.26250736111</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46289.26606476852</v>
+        <v>46290.26251299769</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7814,7 +7814,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46289.266071122685</v>
+        <v>46290.2625190625</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7879,10 +7879,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.54584697737408</v>
+        <v>148.60704648245982</v>
       </c>
       <c r="T55" s="30">
-        <v>46289.266076087966</v>
+        <v>46290.262525254635</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7947,10 +7947,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>767.2064939299438</v>
+        <v>769.1499852973241</v>
       </c>
       <c r="T56" s="30">
-        <v>46289.26608217593</v>
+        <v>46290.26253040509</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8015,10 +8015,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>378.0457799657141</v>
+        <v>379.67910159649057</v>
       </c>
       <c r="T57" s="30">
-        <v>46289.266087696764</v>
+        <v>46290.26253623843</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46289.266094039354</v>
+        <v>46290.26254206018</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8158,7 +8158,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46289.266100162036</v>
+        <v>46290.262547997685</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8228,7 +8228,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46289.26610519676</v>
+        <v>46290.26255359954</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46289.266110856486</v>
+        <v>46290.262559780094</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8368,7 +8368,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46289.26611681713</v>
+        <v>46290.26256527778</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8431,10 +8431,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.000174030281269</v>
+        <v>1.0001820331300297</v>
       </c>
       <c r="T63" s="156">
-        <v>46289.26612302083</v>
+        <v>46290.262572581014</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2673.706614603858</v>
+        <v>2685.5680311095375</v>
       </c>
       <c r="T9" s="29">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.1201738716447</v>
+        <v>341.31075331408994</v>
       </c>
       <c r="T10" s="30">
-        <v>46290.26226416667</v>
+        <v>46291.261777326385</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46290.26227013889</v>
+        <v>46291.261783344904</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46290.26227575231</v>
+        <v>46291.26178842592</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46290.26228188658</v>
+        <v>46291.26179460648</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46290.262287708334</v>
+        <v>46291.261800810185</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46290.262293541666</v>
+        <v>46291.26180665509</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46290.26229899305</v>
+        <v>46291.261812303244</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46290.26230534723</v>
+        <v>46291.26181841435</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>199.02622277254463</v>
+        <v>194.9146948156772</v>
       </c>
       <c r="T18" s="30">
-        <v>46290.2623099537</v>
+        <v>46291.26182319444</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46290.26231670139</v>
+        <v>46291.26183018518</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>92.52683988485906</v>
+        <v>87.19552080270289</v>
       </c>
       <c r="T20" s="30">
-        <v>46290.26232230324</v>
+        <v>46291.26183552083</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46290.26232800926</v>
+        <v>46291.26184144676</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.11165832181457</v>
+        <v>9.10162008837573</v>
       </c>
       <c r="T22" s="30">
-        <v>46290.26233424769</v>
+        <v>46291.26184716435</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46290.26233929398</v>
+        <v>46291.261852916665</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46290.26234540509</v>
+        <v>46291.26185809028</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>392.0213478853151</v>
+        <v>392.5298703169164</v>
       </c>
       <c r="T25" s="30">
-        <v>46290.26235128472</v>
+        <v>46291.26186460649</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46290.26235662037</v>
+        <v>46291.261869664355</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>342.0522535101389</v>
+        <v>344.0312375602858</v>
       </c>
       <c r="T27" s="30">
-        <v>46290.26236283565</v>
+        <v>46291.261875972225</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.39534995369157</v>
+        <v>29.195196745020617</v>
       </c>
       <c r="T28" s="30">
-        <v>46290.26236862269</v>
+        <v>46291.26188167824</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46290.262374398146</v>
+        <v>46291.261887581015</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46290.262380196764</v>
+        <v>46291.26189347223</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46290.26238590278</v>
+        <v>46291.261899212965</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6284,22 +6284,20 @@
       <c r="R32" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
-      <c r="S32" s="27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="S32" s="27">
+        <v>1183.6206844818378</v>
       </c>
       <c r="T32" s="30">
-        <v>46290.26239177083</v>
+        <v>46291.261904293984</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
-          <t/>
+          <t>https://dexscreener.com/robinhood/0x666ba98ab094793e276215448f2485fd8e3c3ce5</t>
         </is>
       </c>
       <c r="V32" s="33" t="inlineStr">
         <is>
-          <t>暂无合格池价；可手动输入</t>
+          <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6358,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46290.26239751157</v>
+        <v>46291.261910995374</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6425,10 +6423,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>779.671900285852</v>
+        <v>746.2428312239579</v>
       </c>
       <c r="T34" s="30">
-        <v>46290.26240344907</v>
+        <v>46291.261915856485</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6498,7 +6496,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46290.26240974537</v>
+        <v>46291.2619228588</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6568,7 +6566,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46290.262415046294</v>
+        <v>46291.26192824074</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6638,7 +6636,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46290.26242064815</v>
+        <v>46291.26193393519</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6703,10 +6701,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>161.7394365774571</v>
+        <v>159.49839071354702</v>
       </c>
       <c r="T38" s="30">
-        <v>46290.26242579862</v>
+        <v>46291.261938993055</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6771,10 +6769,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1080.4866485700397</v>
+        <v>1086.0133103692456</v>
       </c>
       <c r="T39" s="30">
-        <v>46290.26243282408</v>
+        <v>46291.26194546296</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6844,7 +6842,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46290.262444328706</v>
+        <v>46291.26195732639</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6914,7 +6912,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46290.26244982639</v>
+        <v>46291.26196309028</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6979,10 +6977,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>225.1709811185636</v>
+        <v>224.9300375466833</v>
       </c>
       <c r="T42" s="30">
-        <v>46290.262437314814</v>
+        <v>46291.26195061343</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7052,7 +7050,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46290.26245526621</v>
+        <v>46291.261973506946</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7122,7 +7120,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46290.26246114584</v>
+        <v>46291.26197475694</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7187,10 +7185,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>743.8253762184718</v>
+        <v>744.4125054259658</v>
       </c>
       <c r="T45" s="30">
-        <v>46290.26246638889</v>
+        <v>46291.26198068287</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7255,10 +7253,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>48.798881396414146</v>
+        <v>46.4982766932514</v>
       </c>
       <c r="T46" s="30">
-        <v>46290.262473159724</v>
+        <v>46291.261986516205</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7323,10 +7321,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>151.9076471917889</v>
+        <v>151.37694509622713</v>
       </c>
       <c r="T47" s="30">
-        <v>46290.26247868055</v>
+        <v>46291.26199190972</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7396,7 +7394,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46290.26248414352</v>
+        <v>46291.2619969213</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7461,10 +7459,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.2684308544155</v>
+        <v>100.56790108639338</v>
       </c>
       <c r="T49" s="30">
-        <v>46290.26249064815</v>
+        <v>46291.26200364583</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7534,7 +7532,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46290.26249605324</v>
+        <v>46291.262009143524</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7604,7 +7602,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46290.26250199074</v>
+        <v>46291.2620150463</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7674,7 +7672,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46290.26250736111</v>
+        <v>46291.26202065972</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7744,7 +7742,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46290.26251299769</v>
+        <v>46291.262026435186</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7814,7 +7812,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46290.2625190625</v>
+        <v>46291.26203196759</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7879,10 +7877,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.60704648245982</v>
+        <v>148.60645194844685</v>
       </c>
       <c r="T55" s="30">
-        <v>46290.262525254635</v>
+        <v>46291.26203877315</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7947,10 +7945,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>769.1499852973241</v>
+        <v>772.297468949473</v>
       </c>
       <c r="T56" s="30">
-        <v>46290.26253040509</v>
+        <v>46291.26204315972</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8015,10 +8013,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>379.67910159649057</v>
+        <v>371.236080022244</v>
       </c>
       <c r="T57" s="30">
-        <v>46290.26253623843</v>
+        <v>46291.2620493287</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8088,7 +8086,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46290.26254206018</v>
+        <v>46291.26205559028</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8158,7 +8156,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46290.262547997685</v>
+        <v>46291.26206121528</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8228,7 +8226,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46290.26255359954</v>
+        <v>46291.262066979165</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8298,7 +8296,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46290.262559780094</v>
+        <v>46291.26207280093</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8368,7 +8366,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46290.26256527778</v>
+        <v>46291.26207788194</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8431,10 +8429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0001820331300297</v>
+        <v>1.0001780316896407</v>
       </c>
       <c r="T63" s="156">
-        <v>46290.262572581014</v>
+        <v>46291.26208503472</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2685.5680311095375</v>
+        <v>2707.200336085702</v>
       </c>
       <c r="T9" s="29">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>341.31075331408994</v>
+        <v>340.4868241401557</v>
       </c>
       <c r="T10" s="30">
-        <v>46291.261777326385</v>
+        <v>46292.28181748843</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46291.261783344904</v>
+        <v>46292.28182361111</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46291.26178842592</v>
+        <v>46292.281829074076</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46291.26179460648</v>
+        <v>46292.28183487269</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46291.261800810185</v>
+        <v>46292.281840648146</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46291.26180665509</v>
+        <v>46292.28184645833</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46291.261812303244</v>
+        <v>46292.28185255787</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46291.26181841435</v>
+        <v>46292.28185804398</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>194.9146948156772</v>
+        <v>197.7704314600223</v>
       </c>
       <c r="T18" s="30">
-        <v>46291.26182319444</v>
+        <v>46292.28186383102</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46291.26183018518</v>
+        <v>46292.281869618055</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>87.19552080270289</v>
+        <v>89.22275180170944</v>
       </c>
       <c r="T20" s="30">
-        <v>46291.26183552083</v>
+        <v>46292.28187543982</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46291.26184144676</v>
+        <v>46292.28188178241</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.10162008837573</v>
+        <v>9.132328743829678</v>
       </c>
       <c r="T22" s="30">
-        <v>46291.26184716435</v>
+        <v>46292.281887094905</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46291.261852916665</v>
+        <v>46292.2818928125</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46291.26185809028</v>
+        <v>46292.28189861111</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>392.5298703169164</v>
+        <v>396.01098280061416</v>
       </c>
       <c r="T25" s="30">
-        <v>46291.26186460649</v>
+        <v>46292.28190439815</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46291.261869664355</v>
+        <v>46292.28191019676</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>344.0312375602858</v>
+        <v>346.938469309674</v>
       </c>
       <c r="T27" s="30">
-        <v>46291.261875972225</v>
+        <v>46292.28191668982</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.195196745020617</v>
+        <v>29.367488709620954</v>
       </c>
       <c r="T28" s="30">
-        <v>46291.26188167824</v>
+        <v>46292.28192178241</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46291.261887581015</v>
+        <v>46292.28192758102</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46291.26189347223</v>
+        <v>46292.28193337963</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46291.261899212965</v>
+        <v>46292.28193916667</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6285,10 +6285,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1183.6206844818378</v>
+        <v>1183.7218490715134</v>
       </c>
       <c r="T32" s="30">
-        <v>46291.261904293984</v>
+        <v>46292.281944953706</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46291.261910995374</v>
+        <v>46292.28195077546</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>746.2428312239579</v>
+        <v>748.4108447654152</v>
       </c>
       <c r="T34" s="30">
-        <v>46291.261915856485</v>
+        <v>46292.281956562496</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46291.2619228588</v>
+        <v>46292.28196236111</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46291.26192824074</v>
+        <v>46292.28196815972</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46291.26193393519</v>
+        <v>46292.28197396991</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6701,10 +6701,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>159.49839071354702</v>
+        <v>160.87102211063822</v>
       </c>
       <c r="T38" s="30">
-        <v>46291.261938993055</v>
+        <v>46292.28197975695</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6769,10 +6769,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1086.0133103692456</v>
+        <v>1092.6586279501273</v>
       </c>
       <c r="T39" s="30">
-        <v>46291.26194546296</v>
+        <v>46292.281985567126</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46291.26195732639</v>
+        <v>46292.2819971412</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46291.26196309028</v>
+        <v>46292.28200295139</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>224.9300375466833</v>
+        <v>224.81732841874677</v>
       </c>
       <c r="T42" s="30">
-        <v>46291.26195061343</v>
+        <v>46292.28199135417</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46291.261973506946</v>
+        <v>46292.282008738424</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46291.26197475694</v>
+        <v>46292.28201451389</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7185,10 +7185,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>744.4125054259658</v>
+        <v>746.4503448379337</v>
       </c>
       <c r="T45" s="30">
-        <v>46291.26198068287</v>
+        <v>46292.2820203125</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7253,10 +7253,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>46.4982766932514</v>
+        <v>46.391829916628744</v>
       </c>
       <c r="T46" s="30">
-        <v>46291.261986516205</v>
+        <v>46292.282026064815</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>151.37694509622713</v>
+        <v>151.95874948111768</v>
       </c>
       <c r="T47" s="30">
-        <v>46291.26199190972</v>
+        <v>46292.28203185185</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46291.2619969213</v>
+        <v>46292.28203763889</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7459,10 +7459,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.56790108639338</v>
+        <v>101.69593246277802</v>
       </c>
       <c r="T49" s="30">
-        <v>46291.26200364583</v>
+        <v>46292.28204342593</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46291.262009143524</v>
+        <v>46292.28204918982</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46291.2620150463</v>
+        <v>46292.28205497685</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46291.26202065972</v>
+        <v>46292.28206076389</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46291.262026435186</v>
+        <v>46292.28206706019</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46291.26203196759</v>
+        <v>46292.28207233796</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.60645194844685</v>
+        <v>148.5678848106267</v>
       </c>
       <c r="T55" s="30">
-        <v>46291.26203877315</v>
+        <v>46292.282078125005</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7945,10 +7945,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>772.297468949473</v>
+        <v>772.0168643003966</v>
       </c>
       <c r="T56" s="30">
-        <v>46291.26204315972</v>
+        <v>46292.28208423611</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>371.236080022244</v>
+        <v>372.90509079815354</v>
       </c>
       <c r="T57" s="30">
-        <v>46291.2620493287</v>
+        <v>46292.282089988425</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46291.26205559028</v>
+        <v>46292.282095497685</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46291.26206121528</v>
+        <v>46292.28210175926</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46291.262066979165</v>
+        <v>46292.282107060186</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46291.26207280093</v>
+        <v>46292.28211363426</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46291.26207788194</v>
+        <v>46292.282118599534</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8429,10 +8429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0001780316896407</v>
+        <v>1.0002550650415856</v>
       </c>
       <c r="T63" s="156">
-        <v>46291.26208503472</v>
+        <v>46292.2821247338</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2707.200336085702</v>
+        <v>2649.7340672949285</v>
       </c>
       <c r="T9" s="29">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>340.4868241401557</v>
+        <v>340.7159626643886</v>
       </c>
       <c r="T10" s="30">
-        <v>46292.28181748843</v>
+        <v>46293.299240381944</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46292.28182361111</v>
+        <v>46293.29924615741</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46292.281829074076</v>
+        <v>46293.299251979166</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46292.28183487269</v>
+        <v>46293.2992577662</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46292.281840648146</v>
+        <v>46293.29926354167</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46292.28184645833</v>
+        <v>46293.29926936343</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46292.28185255787</v>
+        <v>46293.299275150464</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46292.28185804398</v>
+        <v>46293.2992809375</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>197.7704314600223</v>
+        <v>191.42953458525602</v>
       </c>
       <c r="T18" s="30">
-        <v>46292.28186383102</v>
+        <v>46293.299286747686</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46292.281869618055</v>
+        <v>46293.29929252315</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>89.22275180170944</v>
+        <v>86.68695964444942</v>
       </c>
       <c r="T20" s="30">
-        <v>46292.28187543982</v>
+        <v>46293.29929833333</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46292.28188178241</v>
+        <v>46293.29930413194</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.132328743829678</v>
+        <v>9.046813559016854</v>
       </c>
       <c r="T22" s="30">
-        <v>46292.281887094905</v>
+        <v>46293.29931018519</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46292.2818928125</v>
+        <v>46293.29931568287</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46292.28189861111</v>
+        <v>46293.29932146991</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>396.01098280061416</v>
+        <v>384.60961358982644</v>
       </c>
       <c r="T25" s="30">
-        <v>46292.28190439815</v>
+        <v>46293.29932726852</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46292.28191019676</v>
+        <v>46293.2993330787</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>346.938469309674</v>
+        <v>340.7559751082586</v>
       </c>
       <c r="T27" s="30">
-        <v>46292.28191668982</v>
+        <v>46293.29933886574</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.367488709620954</v>
+        <v>28.928996918041513</v>
       </c>
       <c r="T28" s="30">
-        <v>46292.28192178241</v>
+        <v>46293.299344652776</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46292.28192758102</v>
+        <v>46293.29935046296</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46292.28193337963</v>
+        <v>46293.29935628472</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46292.28193916667</v>
+        <v>46293.29936210648</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6285,10 +6285,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1183.7218490715134</v>
+        <v>1185.8087865326117</v>
       </c>
       <c r="T32" s="30">
-        <v>46292.281944953706</v>
+        <v>46293.29936788195</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46292.28195077546</v>
+        <v>46293.29937366898</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>748.4108447654152</v>
+        <v>733.0679841430685</v>
       </c>
       <c r="T34" s="30">
-        <v>46292.281956562496</v>
+        <v>46293.29937946759</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46292.28196236111</v>
+        <v>46293.29938524306</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46292.28196815972</v>
+        <v>46293.29939101852</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46292.28197396991</v>
+        <v>46293.299396828705</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6701,10 +6701,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>160.87102211063822</v>
+        <v>156.94881108024595</v>
       </c>
       <c r="T38" s="30">
-        <v>46292.28197975695</v>
+        <v>46293.29940263889</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6769,10 +6769,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1092.6586279501273</v>
+        <v>1067.6920522282428</v>
       </c>
       <c r="T39" s="30">
-        <v>46292.281985567126</v>
+        <v>46293.29940841435</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46292.2819971412</v>
+        <v>46293.29942028935</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46292.28200295139</v>
+        <v>46293.29942578704</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>224.81732841874677</v>
+        <v>223.4795021251609</v>
       </c>
       <c r="T42" s="30">
-        <v>46292.28199135417</v>
+        <v>46293.29941422454</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46292.282008738424</v>
+        <v>46293.29943157407</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46292.28201451389</v>
+        <v>46293.29943738426</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7185,10 +7185,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>746.4503448379337</v>
+        <v>740.9804449183696</v>
       </c>
       <c r="T45" s="30">
-        <v>46292.2820203125</v>
+        <v>46293.299443171294</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7253,10 +7253,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>46.391829916628744</v>
+        <v>45.22406468411676</v>
       </c>
       <c r="T46" s="30">
-        <v>46292.282026064815</v>
+        <v>46293.299448923615</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>151.95874948111768</v>
+        <v>149.08436523758888</v>
       </c>
       <c r="T47" s="30">
-        <v>46292.28203185185</v>
+        <v>46293.29945472222</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46292.28203763889</v>
+        <v>46293.299460497685</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7459,10 +7459,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.69593246277802</v>
+        <v>100.70131810993219</v>
       </c>
       <c r="T49" s="30">
-        <v>46292.28204342593</v>
+        <v>46293.299466296296</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46292.28204918982</v>
+        <v>46293.29947207176</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46292.28205497685</v>
+        <v>46293.29947791667</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46292.28206076389</v>
+        <v>46293.29948365741</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46292.28206706019</v>
+        <v>46293.2994894213</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46292.28207233796</v>
+        <v>46293.29949520833</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.5678848106267</v>
+        <v>149.0163440830098</v>
       </c>
       <c r="T55" s="30">
-        <v>46292.282078125005</v>
+        <v>46293.2995009838</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7945,10 +7945,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>772.0168643003966</v>
+        <v>769.809410726736</v>
       </c>
       <c r="T56" s="30">
-        <v>46292.28208423611</v>
+        <v>46293.299506793985</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>372.90509079815354</v>
+        <v>370.8053204546614</v>
       </c>
       <c r="T57" s="30">
-        <v>46292.282089988425</v>
+        <v>46293.299512557875</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46292.282095497685</v>
+        <v>46293.299518368054</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46292.28210175926</v>
+        <v>46293.29952414352</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46292.282107060186</v>
+        <v>46293.2995299074</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46292.28211363426</v>
+        <v>46293.299535937505</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46292.282118599534</v>
+        <v>46293.299541458335</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8429,10 +8429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0002550650415856</v>
+        <v>1.0003110967510895</v>
       </c>
       <c r="T63" s="156">
-        <v>46292.2821247338</v>
+        <v>46293.2995472801</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2649.7340672949285</v>
+        <v>2664.683327648073</v>
       </c>
       <c r="T9" s="29">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>340.7159626643886</v>
+        <v>329.55171803241296</v>
       </c>
       <c r="T10" s="30">
-        <v>46293.299240381944</v>
+        <v>46295.29085960648</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46293.29924615741</v>
+        <v>46295.290865497685</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46293.299251979166</v>
+        <v>46295.29087069444</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46293.2992577662</v>
+        <v>46295.29087696759</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46293.29926354167</v>
+        <v>46295.29088311343</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46293.29926936343</v>
+        <v>46295.29088908565</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46293.299275150464</v>
+        <v>46295.29089452547</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46293.2992809375</v>
+        <v>46295.29090085648</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>191.42953458525602</v>
+        <v>189.05408933628502</v>
       </c>
       <c r="T18" s="30">
-        <v>46293.299286747686</v>
+        <v>46295.29090550926</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46293.29929252315</v>
+        <v>46295.290912083336</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>86.68695964444942</v>
+        <v>83.29823810271681</v>
       </c>
       <c r="T20" s="30">
-        <v>46293.29929833333</v>
+        <v>46295.29091789352</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46293.29930413194</v>
+        <v>46295.2909235301</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.046813559016854</v>
+        <v>9.0940828941011</v>
       </c>
       <c r="T22" s="30">
-        <v>46293.29931018519</v>
+        <v>46295.290929375</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46293.29931568287</v>
+        <v>46295.29093516203</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46293.29932146991</v>
+        <v>46295.29094089121</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>384.60961358982644</v>
+        <v>380.61902985111954</v>
       </c>
       <c r="T25" s="30">
-        <v>46293.29932726852</v>
+        <v>46295.290947407404</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46293.2993330787</v>
+        <v>46295.290951979165</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>340.7559751082586</v>
+        <v>337.9045496423288</v>
       </c>
       <c r="T27" s="30">
-        <v>46293.29933886574</v>
+        <v>46295.290958287034</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.928996918041513</v>
+        <v>28.459647820611185</v>
       </c>
       <c r="T28" s="30">
-        <v>46293.299344652776</v>
+        <v>46295.290963761574</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46293.29935046296</v>
+        <v>46295.29096987269</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46293.29935628472</v>
+        <v>46295.290975648146</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46293.29936210648</v>
+        <v>46295.290981377315</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6285,10 +6285,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1185.8087865326117</v>
+        <v>1183.2411187392524</v>
       </c>
       <c r="T32" s="30">
-        <v>46293.29936788195</v>
+        <v>46295.29098722222</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46293.29937366898</v>
+        <v>46295.2909930324</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>733.0679841430685</v>
+        <v>737.0298531202077</v>
       </c>
       <c r="T34" s="30">
-        <v>46293.29937946759</v>
+        <v>46295.29099818287</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46293.29938524306</v>
+        <v>46295.29100511574</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46293.29939101852</v>
+        <v>46295.291010787034</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46293.299396828705</v>
+        <v>46295.29101616898</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6701,10 +6701,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>156.94881108024595</v>
+        <v>154.042220312686</v>
       </c>
       <c r="T38" s="30">
-        <v>46293.29940263889</v>
+        <v>46295.291021296296</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6769,10 +6769,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1067.6920522282428</v>
+        <v>1063.7806216307329</v>
       </c>
       <c r="T39" s="30">
-        <v>46293.29940841435</v>
+        <v>46295.2910277662</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46293.29942028935</v>
+        <v>46295.29103982639</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46293.29942578704</v>
+        <v>46295.29104523148</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>223.4795021251609</v>
+        <v>227.9072605613303</v>
       </c>
       <c r="T42" s="30">
-        <v>46293.29941422454</v>
+        <v>46295.291032870366</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46293.29943157407</v>
+        <v>46295.29105082176</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46293.29943738426</v>
+        <v>46295.29105605324</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7185,10 +7185,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>740.9804449183696</v>
+        <v>735.6693919238621</v>
       </c>
       <c r="T45" s="30">
-        <v>46293.299443171294</v>
+        <v>46295.291062847224</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7253,10 +7253,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>45.22406468411676</v>
+        <v>41.153951189453224</v>
       </c>
       <c r="T46" s="30">
-        <v>46293.299448923615</v>
+        <v>46295.29106887731</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>149.08436523758888</v>
+        <v>145.9594802638094</v>
       </c>
       <c r="T47" s="30">
-        <v>46293.29945472222</v>
+        <v>46295.29107422454</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46293.299460497685</v>
+        <v>46295.29107982639</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7459,10 +7459,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.70131810993219</v>
+        <v>100.79416922336672</v>
       </c>
       <c r="T49" s="30">
-        <v>46293.299466296296</v>
+        <v>46295.2910859375</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46293.29947207176</v>
+        <v>46295.29109141204</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46293.29947791667</v>
+        <v>46295.29109738426</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46293.29948365741</v>
+        <v>46295.29110299768</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46293.2994894213</v>
+        <v>46295.29110873843</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46293.29949520833</v>
+        <v>46295.29111488426</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>149.0163440830098</v>
+        <v>149.18057221398053</v>
       </c>
       <c r="T55" s="30">
-        <v>46293.2995009838</v>
+        <v>46295.29112082176</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7945,10 +7945,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>769.809410726736</v>
+        <v>765.9396535425509</v>
       </c>
       <c r="T56" s="30">
-        <v>46293.299506793985</v>
+        <v>46295.29112609954</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>370.8053204546614</v>
+        <v>353.1967336927218</v>
       </c>
       <c r="T57" s="30">
-        <v>46293.299512557875</v>
+        <v>46295.29113168981</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46293.299518368054</v>
+        <v>46295.29113774306</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46293.29952414352</v>
+        <v>46295.291143703704</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46293.2995299074</v>
+        <v>46295.291149247685</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46293.299535937505</v>
+        <v>46295.29115513889</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46293.299541458335</v>
+        <v>46295.2911608912</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8429,10 +8429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0003110967510895</v>
+        <v>1.0003391149599714</v>
       </c>
       <c r="T63" s="156">
-        <v>46293.2995472801</v>
+        <v>46295.29116716435</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2664.683327648073</v>
+        <v>2693.7966660531224</v>
       </c>
       <c r="T9" s="29">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>329.55171803241296</v>
+        <v>335.38537256816346</v>
       </c>
       <c r="T10" s="30">
-        <v>46295.29085960648</v>
+        <v>46296.3089755787</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46295.290865497685</v>
+        <v>46296.308981145834</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46295.29087069444</v>
+        <v>46296.30898775463</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46295.29087696759</v>
+        <v>46296.30899199074</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46295.29088311343</v>
+        <v>46296.30899842593</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46295.29088908565</v>
+        <v>46296.309004166666</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46295.29089452547</v>
+        <v>46296.309010254634</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46295.29090085648</v>
+        <v>46296.309016134255</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>189.05408933628502</v>
+        <v>188.73492481413606</v>
       </c>
       <c r="T18" s="30">
-        <v>46295.29090550926</v>
+        <v>46296.30902263889</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46295.290912083336</v>
+        <v>46296.30902738426</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>83.29823810271681</v>
+        <v>83.48872011972118</v>
       </c>
       <c r="T20" s="30">
-        <v>46295.29091789352</v>
+        <v>46296.30903349537</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46295.2909235301</v>
+        <v>46296.30903920139</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.0940828941011</v>
+        <v>9.16315212433077</v>
       </c>
       <c r="T22" s="30">
-        <v>46295.290929375</v>
+        <v>46296.309045277776</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46295.29093516203</v>
+        <v>46296.30905106482</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46295.29094089121</v>
+        <v>46296.30905655093</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>380.61902985111954</v>
+        <v>385.252526869243</v>
       </c>
       <c r="T25" s="30">
-        <v>46295.290947407404</v>
+        <v>46296.30906236111</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46295.290951979165</v>
+        <v>46296.309068229166</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>337.9045496423288</v>
+        <v>354.90208631769326</v>
       </c>
       <c r="T27" s="30">
-        <v>46295.290958287034</v>
+        <v>46296.30907376157</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.459647820611185</v>
+        <v>30.460478404571173</v>
       </c>
       <c r="T28" s="30">
-        <v>46295.290963761574</v>
+        <v>46296.30907876157</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46295.29096987269</v>
+        <v>46296.30908543981</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46295.290975648146</v>
+        <v>46296.30909131944</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46295.290981377315</v>
+        <v>46296.30909702546</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6285,10 +6285,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1183.2411187392524</v>
+        <v>1162.119769200605</v>
       </c>
       <c r="T32" s="30">
-        <v>46295.29098722222</v>
+        <v>46296.309102997686</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46295.2909930324</v>
+        <v>46296.30910895833</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>737.0298531202077</v>
+        <v>729.0507934729546</v>
       </c>
       <c r="T34" s="30">
-        <v>46295.29099818287</v>
+        <v>46296.30911351852</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46295.29100511574</v>
+        <v>46296.309120694445</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46295.291010787034</v>
+        <v>46296.30912509259</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46295.29101616898</v>
+        <v>46296.30913165509</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6701,10 +6701,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>154.042220312686</v>
+        <v>155.97365493729842</v>
       </c>
       <c r="T38" s="30">
-        <v>46295.291021296296</v>
+        <v>46296.30913756944</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6769,10 +6769,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1063.7806216307329</v>
+        <v>1060.4647998911626</v>
       </c>
       <c r="T39" s="30">
-        <v>46295.2910277662</v>
+        <v>46296.30914329861</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46295.29103982639</v>
+        <v>46296.309155104165</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46295.29104523148</v>
+        <v>46296.30916075232</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>227.9072605613303</v>
+        <v>232.34992837536115</v>
       </c>
       <c r="T42" s="30">
-        <v>46295.291032870366</v>
+        <v>46296.30914824074</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46295.29105082176</v>
+        <v>46296.30916643519</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46295.29105605324</v>
+        <v>46296.30917141204</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7185,10 +7185,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>735.6693919238621</v>
+        <v>749.1377033699592</v>
       </c>
       <c r="T45" s="30">
-        <v>46295.291062847224</v>
+        <v>46296.3091772338</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7253,10 +7253,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>41.153951189453224</v>
+        <v>42.734700737053544</v>
       </c>
       <c r="T46" s="30">
-        <v>46295.29106887731</v>
+        <v>46296.30918409722</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>145.9594802638094</v>
+        <v>145.7601414886721</v>
       </c>
       <c r="T47" s="30">
-        <v>46295.29107422454</v>
+        <v>46296.30918943287</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46295.29107982639</v>
+        <v>46296.309195254624</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7459,10 +7459,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.79416922336672</v>
+        <v>102.0050897508743</v>
       </c>
       <c r="T49" s="30">
-        <v>46295.2910859375</v>
+        <v>46296.30920167824</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46295.29109141204</v>
+        <v>46296.309208067134</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46295.29109738426</v>
+        <v>46296.30921260417</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46295.29110299768</v>
+        <v>46296.3092187963</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46295.29110873843</v>
+        <v>46296.30922434028</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46295.29111488426</v>
+        <v>46296.309230370374</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>149.18057221398053</v>
+        <v>152.4424401994286</v>
       </c>
       <c r="T55" s="30">
-        <v>46295.29112082176</v>
+        <v>46296.3092350463</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7945,10 +7945,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>765.9396535425509</v>
+        <v>770.4950502973023</v>
       </c>
       <c r="T56" s="30">
-        <v>46295.29112609954</v>
+        <v>46296.30924170138</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>353.1967336927218</v>
+        <v>359.2335763502645</v>
       </c>
       <c r="T57" s="30">
-        <v>46295.29113168981</v>
+        <v>46296.30924662037</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46295.29113774306</v>
+        <v>46296.30925337963</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46295.291143703704</v>
+        <v>46296.30925929398</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46295.291149247685</v>
+        <v>46296.30926479167</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46295.29115513889</v>
+        <v>46296.30927091435</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46295.2911608912</v>
+        <v>46296.30927554398</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8429,10 +8429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0003391149599714</v>
+        <v>1.0003441183767217</v>
       </c>
       <c r="T63" s="156">
-        <v>46295.29116716435</v>
+        <v>46296.30928234954</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2693.7966660531224</v>
+        <v>2729.5370497260674</v>
       </c>
       <c r="T9" s="29">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>335.38537256816346</v>
+        <v>331.3804082637039</v>
       </c>
       <c r="T10" s="30">
-        <v>46296.3089755787</v>
+        <v>46297.29964009259</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46296.308981145834</v>
+        <v>46297.299645879626</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46296.30898775463</v>
+        <v>46297.299651678244</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46296.30899199074</v>
+        <v>46297.29965775463</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46296.30899842593</v>
+        <v>46297.29966326389</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46296.309004166666</v>
+        <v>46297.2996690625</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46296.309010254634</v>
+        <v>46297.299675057875</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46296.309016134255</v>
+        <v>46297.299680613425</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>188.73492481413606</v>
+        <v>193.1885361264463</v>
       </c>
       <c r="T18" s="30">
-        <v>46296.30902263889</v>
+        <v>46297.299686412036</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46296.30902738426</v>
+        <v>46297.2996921875</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5455,10 +5455,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
       <c r="S20" s="27">
-        <v>83.48872011972118</v>
+        <v>83.63534150847707</v>
       </c>
       <c r="T20" s="30">
-        <v>46296.30903349537</v>
+        <v>46297.29969798611</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46296.30903920139</v>
+        <v>46297.29970378472</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>9.16315212433077</v>
+        <v>8.802667208164076</v>
       </c>
       <c r="T22" s="30">
-        <v>46296.309045277776</v>
+        <v>46297.29970960648</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46296.30905106482</v>
+        <v>46297.299715393514</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46296.30905655093</v>
+        <v>46297.299721180556</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>385.252526869243</v>
+        <v>384.566523656668</v>
       </c>
       <c r="T25" s="30">
-        <v>46296.30906236111</v>
+        <v>46297.29972697917</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46296.309068229166</v>
+        <v>46297.299732754625</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>354.90208631769326</v>
+        <v>342.0936543772763</v>
       </c>
       <c r="T27" s="30">
-        <v>46296.30907376157</v>
+        <v>46297.29973854167</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>30.460478404571173</v>
+        <v>29.759016982145592</v>
       </c>
       <c r="T28" s="30">
-        <v>46296.30907876157</v>
+        <v>46297.29974436343</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46296.30908543981</v>
+        <v>46297.299750150465</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46296.30909131944</v>
+        <v>46297.2997559375</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46296.30909702546</v>
+        <v>46297.29976173611</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6285,10 +6285,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
       <c r="S32" s="27">
-        <v>1162.119769200605</v>
+        <v>1153.7195770318406</v>
       </c>
       <c r="T32" s="30">
-        <v>46296.309102997686</v>
+        <v>46297.29976780093</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46296.30910895833</v>
+        <v>46297.29977331019</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6423,10 +6423,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>729.0507934729546</v>
+        <v>729.150932732618</v>
       </c>
       <c r="T34" s="30">
-        <v>46296.30911351852</v>
+        <v>46297.299779085646</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46296.309120694445</v>
+        <v>46297.299785219904</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46296.30912509259</v>
+        <v>46297.299790694444</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46296.30913165509</v>
+        <v>46297.29979646991</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6701,10 +6701,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>155.97365493729842</v>
+        <v>164.16974343226</v>
       </c>
       <c r="T38" s="30">
-        <v>46296.30913756944</v>
+        <v>46297.299802615744</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6769,10 +6769,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1060.4647998911626</v>
+        <v>1092.9211551099984</v>
       </c>
       <c r="T39" s="30">
-        <v>46296.30914329861</v>
+        <v>46297.299808055555</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6842,7 +6842,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46296.309155104165</v>
+        <v>46297.2998196875</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6912,7 +6912,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46296.30916075232</v>
+        <v>46297.29982568287</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6977,10 +6977,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>232.34992837536115</v>
+        <v>232.0303051824703</v>
       </c>
       <c r="T42" s="30">
-        <v>46296.30914824074</v>
+        <v>46297.29981387732</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7050,7 +7050,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46296.30916643519</v>
+        <v>46297.299831226854</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7120,7 +7120,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46296.30917141204</v>
+        <v>46297.29983704861</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7185,10 +7185,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>749.1377033699592</v>
+        <v>746.1760913556809</v>
       </c>
       <c r="T45" s="30">
-        <v>46296.3091772338</v>
+        <v>46297.29984284722</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7253,10 +7253,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>42.734700737053544</v>
+        <v>43.02703719226926</v>
       </c>
       <c r="T46" s="30">
-        <v>46296.30918409722</v>
+        <v>46297.29984859954</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7321,10 +7321,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>145.7601414886721</v>
+        <v>150.16550014654442</v>
       </c>
       <c r="T47" s="30">
-        <v>46296.30918943287</v>
+        <v>46297.29985462963</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46296.309195254624</v>
+        <v>46297.29986016204</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7459,10 +7459,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.0050897508743</v>
+        <v>101.87086687266243</v>
       </c>
       <c r="T49" s="30">
-        <v>46296.30920167824</v>
+        <v>46297.2998659375</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7532,7 +7532,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46296.309208067134</v>
+        <v>46297.299871944444</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46296.30921260417</v>
+        <v>46297.299877777776</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46296.3092187963</v>
+        <v>46297.29988327546</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46296.30922434028</v>
+        <v>46297.29988934028</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7812,7 +7812,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46296.309230370374</v>
+        <v>46297.29989484954</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7877,10 +7877,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>152.4424401994286</v>
+        <v>149.29523645664636</v>
       </c>
       <c r="T55" s="30">
-        <v>46296.3092350463</v>
+        <v>46297.29990063657</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7945,10 +7945,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>770.4950502973023</v>
+        <v>767.3024926552746</v>
       </c>
       <c r="T56" s="30">
-        <v>46296.30924170138</v>
+        <v>46297.299906423614</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8013,10 +8013,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>359.2335763502645</v>
+        <v>356.11210196689603</v>
       </c>
       <c r="T57" s="30">
-        <v>46296.30924662037</v>
+        <v>46297.29991219907</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8086,7 +8086,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46296.30925337963</v>
+        <v>46297.299917986114</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8156,7 +8156,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46296.30925929398</v>
+        <v>46297.299923796294</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8226,7 +8226,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46296.30926479167</v>
+        <v>46297.29992979167</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46296.30927091435</v>
+        <v>46297.299935324074</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8366,7 +8366,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46296.30927554398</v>
+        <v>46297.299941122685</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8429,10 +8429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0003441183767217</v>
+        <v>1.0003030918368265</v>
       </c>
       <c r="T63" s="156">
-        <v>46296.30928234954</v>
+        <v>46297.299946921295</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,14 +4691,14 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2729.5370497260674</v>
+        <v>2679.2227521709956</v>
       </c>
       <c r="T9" s="29">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="V9" s="32" t="inlineStr">
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>331.3804082637039</v>
+        <v>333.6877067108583</v>
       </c>
       <c r="T10" s="30">
-        <v>46297.29964009259</v>
+        <v>46298.280402349534</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46297.299645879626</v>
+        <v>46298.28040855324</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46297.299651678244</v>
+        <v>46298.28041375</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46297.29965775463</v>
+        <v>46298.28042025463</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46297.29966326389</v>
+        <v>46298.280426087964</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46297.2996690625</v>
+        <v>46298.28043305555</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46297.299675057875</v>
+        <v>46298.28043817129</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46297.299680613425</v>
+        <v>46298.28044471065</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>193.1885361264463</v>
+        <v>183.1206926382681</v>
       </c>
       <c r="T18" s="30">
-        <v>46297.299686412036</v>
+        <v>46298.28044858796</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46297.2996921875</v>
+        <v>46298.28045539352</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5454,20 +5454,22 @@
       <c r="R20" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xdF0992E440dD0be65BD8439b609d6D4366bf1CB5</v>
       </c>
-      <c r="S20" s="27">
-        <v>83.63534150847707</v>
+      <c r="S20" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T20" s="30">
-        <v>46297.29969798611</v>
+        <v>46298.2804599537</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x754ddd4bf8e8635b4301a7f4af2ea7a82ab6cea7</t>
+          <t/>
         </is>
       </c>
       <c r="V20" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46297.29970378472</v>
+        <v>46298.28046646991</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.802667208164076</v>
+        <v>8.89100468352924</v>
       </c>
       <c r="T22" s="30">
-        <v>46297.29970960648</v>
+        <v>46298.2804715625</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46297.299715393514</v>
+        <v>46298.28047732639</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46297.299721180556</v>
+        <v>46298.28048388889</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>384.566523656668</v>
+        <v>379.54288834638317</v>
       </c>
       <c r="T25" s="30">
-        <v>46297.29972697917</v>
+        <v>46298.280489791665</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46297.299732754625</v>
+        <v>46298.2804955787</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>342.0936543772763</v>
+        <v>343.3287961539654</v>
       </c>
       <c r="T27" s="30">
-        <v>46297.29973854167</v>
+        <v>46298.280501284724</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.759016982145592</v>
+        <v>29.017278952521636</v>
       </c>
       <c r="T28" s="30">
-        <v>46297.29974436343</v>
+        <v>46298.2805071412</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46297.299750150465</v>
+        <v>46298.2805127199</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46297.2997559375</v>
+        <v>46298.280518541666</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46297.29976173611</v>
+        <v>46298.28052435185</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6284,20 +6286,22 @@
       <c r="R32" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x8005d266423c7ea827372c9c864491e5786600ea</v>
       </c>
-      <c r="S32" s="27">
-        <v>1153.7195770318406</v>
+      <c r="S32" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T32" s="30">
-        <v>46297.29976780093</v>
+        <v>46298.28053015046</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x666ba98ab094793e276215448f2485fd8e3c3ce5</t>
+          <t/>
         </is>
       </c>
       <c r="V32" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46297.29977331019</v>
+        <v>46298.28053591435</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6423,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>729.150932732618</v>
+        <v>727.9322563449671</v>
       </c>
       <c r="T34" s="30">
-        <v>46297.299779085646</v>
+        <v>46298.280541053246</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6496,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46297.299785219904</v>
+        <v>46298.28054907407</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6566,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46297.299790694444</v>
+        <v>46298.28055365741</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6636,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46297.29979646991</v>
+        <v>46298.28055916666</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6701,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>164.16974343226</v>
+        <v>159.9880786528878</v>
       </c>
       <c r="T38" s="30">
-        <v>46297.299802615744</v>
+        <v>46298.28056501157</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6769,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1092.9211551099984</v>
+        <v>1073.5713135584322</v>
       </c>
       <c r="T39" s="30">
-        <v>46297.299808055555</v>
+        <v>46298.28057065972</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6842,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46297.2998196875</v>
+        <v>46298.2805825</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6912,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46297.29982568287</v>
+        <v>46298.28058760417</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6977,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>232.0303051824703</v>
+        <v>234.5365026247966</v>
       </c>
       <c r="T42" s="30">
-        <v>46297.29981387732</v>
+        <v>46298.28057587963</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7050,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46297.299831226854</v>
+        <v>46298.280594525466</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7120,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46297.29983704861</v>
+        <v>46298.28059900463</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7185,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>746.1760913556809</v>
+        <v>750.1847708791094</v>
       </c>
       <c r="T45" s="30">
-        <v>46297.29984284722</v>
+        <v>46298.280605</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7253,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>43.02703719226926</v>
+        <v>43.96496804138868</v>
       </c>
       <c r="T46" s="30">
-        <v>46297.29984859954</v>
+        <v>46298.28061141204</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7321,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>150.16550014654442</v>
+        <v>147.92671571887624</v>
       </c>
       <c r="T47" s="30">
-        <v>46297.29985462963</v>
+        <v>46298.28061724537</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7394,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46297.29986016204</v>
+        <v>46298.280622708335</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7459,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.87086687266243</v>
+        <v>101.09042321782361</v>
       </c>
       <c r="T49" s="30">
-        <v>46297.2998659375</v>
+        <v>46298.28062870371</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7532,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46297.299871944444</v>
+        <v>46298.28063435185</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7602,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46297.299877777776</v>
+        <v>46298.28064030092</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7672,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46297.29988327546</v>
+        <v>46298.28064653935</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7742,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46297.29988934028</v>
+        <v>46298.280651712965</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7812,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46297.29989484954</v>
+        <v>46298.28065673611</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7877,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>149.29523645664636</v>
+        <v>159.1009784105604</v>
       </c>
       <c r="T55" s="30">
-        <v>46297.29990063657</v>
+        <v>46298.28066383102</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7945,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>767.3024926552746</v>
+        <v>771.8572198658449</v>
       </c>
       <c r="T56" s="30">
-        <v>46297.299906423614</v>
+        <v>46298.280669189815</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8013,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>356.11210196689603</v>
+        <v>371.16194129936684</v>
       </c>
       <c r="T57" s="30">
-        <v>46297.29991219907</v>
+        <v>46298.28067377315</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8086,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46297.299917986114</v>
+        <v>46298.28068065972</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8156,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46297.299923796294</v>
+        <v>46298.28068568287</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8226,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46297.29992979167</v>
+        <v>46298.28069252315</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8296,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46297.299935324074</v>
+        <v>46298.28069694444</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8366,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46297.299941122685</v>
+        <v>46298.280704317134</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8429,14 +8433,14 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0003030918368265</v>
+        <v>1.0001130127704432</v>
       </c>
       <c r="T63" s="156">
-        <v>46297.299946921295</v>
+        <v>46298.28070979167</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether&amp;vs_currencies=usd</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="V63" s="157" t="inlineStr">

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2679.2227521709956</v>
+        <v>2695.7437467309787</v>
       </c>
       <c r="T9" s="29">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>333.6877067108583</v>
+        <v>333.54768445781</v>
       </c>
       <c r="T10" s="30">
-        <v>46298.280402349534</v>
+        <v>46299.29654232639</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46298.28040855324</v>
+        <v>46299.29654877315</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46298.28041375</v>
+        <v>46299.29655388889</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46298.28042025463</v>
+        <v>46299.2965596875</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46298.280426087964</v>
+        <v>46299.296565798606</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46298.28043305555</v>
+        <v>46299.29657128472</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46298.28043817129</v>
+        <v>46299.2965774537</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46298.28044471065</v>
+        <v>46299.29658318287</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>183.1206926382681</v>
+        <v>184.3453006599548</v>
       </c>
       <c r="T18" s="30">
-        <v>46298.28044858796</v>
+        <v>46299.296588668985</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46298.28045539352</v>
+        <v>46299.29659508102</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46298.2804599537</v>
+        <v>46299.29660056713</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46298.28046646991</v>
+        <v>46299.29660633102</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.89100468352924</v>
+        <v>8.920740421454981</v>
       </c>
       <c r="T22" s="30">
-        <v>46298.2804715625</v>
+        <v>46299.29661221065</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46298.28047732639</v>
+        <v>46299.29661796296</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46298.28048388889</v>
+        <v>46299.29662372685</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>379.54288834638317</v>
+        <v>381.99170531154084</v>
       </c>
       <c r="T25" s="30">
-        <v>46298.280489791665</v>
+        <v>46299.296629502314</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46298.2804955787</v>
+        <v>46299.29663532407</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>343.3287961539654</v>
+        <v>345.5186780502782</v>
       </c>
       <c r="T27" s="30">
-        <v>46298.280501284724</v>
+        <v>46299.29664112269</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.017278952521636</v>
+        <v>29.08041367433497</v>
       </c>
       <c r="T28" s="30">
-        <v>46298.2805071412</v>
+        <v>46299.2966466088</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46298.2805127199</v>
+        <v>46299.29665273148</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46298.280518541666</v>
+        <v>46299.296659224536</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46298.28052435185</v>
+        <v>46299.296664270834</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46298.28053015046</v>
+        <v>46299.29666975695</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46298.28053591435</v>
+        <v>46299.29667619213</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>727.9322563449671</v>
+        <v>732.0407593830289</v>
       </c>
       <c r="T34" s="30">
-        <v>46298.280541053246</v>
+        <v>46299.29668167824</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46298.28054907407</v>
+        <v>46299.29668811343</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46298.28055365741</v>
+        <v>46299.29669350694</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46298.28055916666</v>
+        <v>46299.29669905092</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>159.9880786528878</v>
+        <v>162.64349941045108</v>
       </c>
       <c r="T38" s="30">
-        <v>46298.28056501157</v>
+        <v>46299.29670482639</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1073.5713135584322</v>
+        <v>1077.2294100410336</v>
       </c>
       <c r="T39" s="30">
-        <v>46298.28057065972</v>
+        <v>46299.296710613424</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46298.2805825</v>
+        <v>46299.29672189814</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46298.28058760417</v>
+        <v>46299.29672796297</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>234.5365026247966</v>
+        <v>234.84949250787818</v>
       </c>
       <c r="T42" s="30">
-        <v>46298.28057587963</v>
+        <v>46299.29671611111</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46298.280594525466</v>
+        <v>46299.296733773146</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46298.28059900463</v>
+        <v>46299.29673957176</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>750.1847708791094</v>
+        <v>752.3824477431627</v>
       </c>
       <c r="T45" s="30">
-        <v>46298.280605</v>
+        <v>46299.296745416665</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>43.96496804138868</v>
+        <v>44.22367056465687</v>
       </c>
       <c r="T46" s="30">
-        <v>46298.28061141204</v>
+        <v>46299.29675115741</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>147.92671571887624</v>
+        <v>148.28230743151684</v>
       </c>
       <c r="T47" s="30">
-        <v>46298.28061724537</v>
+        <v>46299.2967569676</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46298.280622708335</v>
+        <v>46299.296762743055</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.09042321782361</v>
+        <v>101.63843599018719</v>
       </c>
       <c r="T49" s="30">
-        <v>46298.28062870371</v>
+        <v>46299.29676855324</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46298.28063435185</v>
+        <v>46299.296774305556</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46298.28064030092</v>
+        <v>46299.29678013889</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46298.28064653935</v>
+        <v>46299.296785914354</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46298.280651712965</v>
+        <v>46299.29679137732</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46298.28065673611</v>
+        <v>46299.296797511575</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>159.1009784105604</v>
+        <v>159.06120207977264</v>
       </c>
       <c r="T55" s="30">
-        <v>46298.28066383102</v>
+        <v>46299.296803310186</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>771.8572198658449</v>
+        <v>772.6541302928143</v>
       </c>
       <c r="T56" s="30">
-        <v>46298.280669189815</v>
+        <v>46299.29680878472</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>371.16194129936684</v>
+        <v>371.6608478503716</v>
       </c>
       <c r="T57" s="30">
-        <v>46298.28067377315</v>
+        <v>46299.29681453704</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46298.28068065972</v>
+        <v>46299.296820613425</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46298.28068568287</v>
+        <v>46299.296826412035</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46298.28069252315</v>
+        <v>46299.296832210646</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46298.28069694444</v>
+        <v>46299.29683798611</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46298.280704317134</v>
+        <v>46299.29684346065</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0001130127704432</v>
+        <v>1.0000830068895719</v>
       </c>
       <c r="T63" s="156">
-        <v>46298.28070979167</v>
+        <v>46299.296849583334</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2695.7437467309787</v>
+        <v>2727.264543220299</v>
       </c>
       <c r="T9" s="29">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>333.54768445781</v>
+        <v>332.4507590572226</v>
       </c>
       <c r="T10" s="30">
-        <v>46299.29654232639</v>
+        <v>46300.3049999537</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46299.29654877315</v>
+        <v>46300.305005752314</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46299.29655388889</v>
+        <v>46300.305011550925</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46299.2965596875</v>
+        <v>46300.30501732639</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46299.296565798606</v>
+        <v>46300.305023113426</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46299.29657128472</v>
+        <v>46300.30502893519</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46299.2965774537</v>
+        <v>46300.30503491899</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46299.29658318287</v>
+        <v>46300.30504049769</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>184.3453006599548</v>
+        <v>186.98104582551036</v>
       </c>
       <c r="T18" s="30">
-        <v>46299.296588668985</v>
+        <v>46300.30504629629</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46299.29659508102</v>
+        <v>46300.305052118056</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46299.29660056713</v>
+        <v>46300.305057881946</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46299.29660633102</v>
+        <v>46300.30506366898</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.920740421454981</v>
+        <v>8.952444017216699</v>
       </c>
       <c r="T22" s="30">
-        <v>46299.29661221065</v>
+        <v>46300.305069456015</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46299.29661796296</v>
+        <v>46300.30507524306</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46299.29662372685</v>
+        <v>46300.30508103009</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>381.99170531154084</v>
+        <v>382.4344045924537</v>
       </c>
       <c r="T25" s="30">
-        <v>46299.296629502314</v>
+        <v>46300.3050868287</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46299.29663532407</v>
+        <v>46300.30509262731</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>345.5186780502782</v>
+        <v>346.87469679222426</v>
       </c>
       <c r="T27" s="30">
-        <v>46299.29664112269</v>
+        <v>46300.30509840278</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.08041367433497</v>
+        <v>29.378020199514467</v>
       </c>
       <c r="T28" s="30">
-        <v>46299.2966466088</v>
+        <v>46300.305104189814</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46299.29665273148</v>
+        <v>46300.305110023146</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46299.296659224536</v>
+        <v>46300.30511583333</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46299.296664270834</v>
+        <v>46300.30512159722</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46299.29666975695</v>
+        <v>46300.30512745371</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46299.29667619213</v>
+        <v>46300.305133194444</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>732.0407593830289</v>
+        <v>728.6289156939844</v>
       </c>
       <c r="T34" s="30">
-        <v>46299.29668167824</v>
+        <v>46300.305138993055</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46299.29668811343</v>
+        <v>46300.305144756945</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46299.29669350694</v>
+        <v>46300.30515054398</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46299.29669905092</v>
+        <v>46300.30515637732</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>162.64349941045108</v>
+        <v>164.75497810902377</v>
       </c>
       <c r="T38" s="30">
-        <v>46299.29670482639</v>
+        <v>46300.305162372686</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1077.2294100410336</v>
+        <v>1078.0142979033276</v>
       </c>
       <c r="T39" s="30">
-        <v>46299.296710613424</v>
+        <v>46300.30516793982</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46299.29672189814</v>
+        <v>46300.30517953704</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46299.29672796297</v>
+        <v>46300.30518533565</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>234.84949250787818</v>
+        <v>235.57431178711786</v>
       </c>
       <c r="T42" s="30">
-        <v>46299.29671611111</v>
+        <v>46300.305173773144</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46299.296733773146</v>
+        <v>46300.30519109954</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46299.29673957176</v>
+        <v>46300.3051969213</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>752.3824477431627</v>
+        <v>751.2750981017819</v>
       </c>
       <c r="T45" s="30">
-        <v>46299.296745416665</v>
+        <v>46300.30520270833</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>44.22367056465687</v>
+        <v>44.41212450999122</v>
       </c>
       <c r="T46" s="30">
-        <v>46299.29675115741</v>
+        <v>46300.30520847222</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>148.28230743151684</v>
+        <v>146.57001361371655</v>
       </c>
       <c r="T47" s="30">
-        <v>46299.2967569676</v>
+        <v>46300.30521425926</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46299.296762743055</v>
+        <v>46300.3052200463</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.63843599018719</v>
+        <v>101.96783721956093</v>
       </c>
       <c r="T49" s="30">
-        <v>46299.29676855324</v>
+        <v>46300.30522584491</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46299.296774305556</v>
+        <v>46300.30523186343</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46299.29678013889</v>
+        <v>46300.30523762732</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46299.296785914354</v>
+        <v>46300.30524320602</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46299.29679137732</v>
+        <v>46300.30524898148</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46299.296797511575</v>
+        <v>46300.30525474537</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>159.06120207977264</v>
+        <v>160.15372196609675</v>
       </c>
       <c r="T55" s="30">
-        <v>46299.296803310186</v>
+        <v>46300.30526055556</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>772.6541302928143</v>
+        <v>770.2502783259829</v>
       </c>
       <c r="T56" s="30">
-        <v>46299.29680878472</v>
+        <v>46300.30526631945</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>371.6608478503716</v>
+        <v>373.27190322958165</v>
       </c>
       <c r="T57" s="30">
-        <v>46299.29681453704</v>
+        <v>46300.30527211806</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46299.296820613425</v>
+        <v>46300.30527788194</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46299.296826412035</v>
+        <v>46300.305283657406</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46299.296832210646</v>
+        <v>46300.30528945602</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46299.29683798611</v>
+        <v>46300.30529523148</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46299.29684346065</v>
+        <v>46300.30530100694</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0000830068895719</v>
+        <v>1.000273074549352</v>
       </c>
       <c r="T63" s="156">
-        <v>46299.296849583334</v>
+        <v>46300.30530678241</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2727.264543220299</v>
+        <v>2704.849577773577</v>
       </c>
       <c r="T9" s="29">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>332.4507590572226</v>
+        <v>332.970267618439</v>
       </c>
       <c r="T10" s="30">
-        <v>46300.3049999537</v>
+        <v>46301.32320273148</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46300.305005752314</v>
+        <v>46301.32320947917</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46300.305011550925</v>
+        <v>46301.32321513889</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46300.30501732639</v>
+        <v>46301.32322099537</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46300.305023113426</v>
+        <v>46301.32322715278</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46300.30502893519</v>
+        <v>46301.323232546296</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46300.30503491899</v>
+        <v>46301.32323829861</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46300.30504049769</v>
+        <v>46301.32324415509</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>186.98104582551036</v>
+        <v>187.2138857133141</v>
       </c>
       <c r="T18" s="30">
-        <v>46300.30504629629</v>
+        <v>46301.32324984954</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46300.305052118056</v>
+        <v>46301.32325584491</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46300.305057881946</v>
+        <v>46301.32326068287</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46300.30506366898</v>
+        <v>46301.32326722222</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.952444017216699</v>
+        <v>8.651565933433952</v>
       </c>
       <c r="T22" s="30">
-        <v>46300.305069456015</v>
+        <v>46301.32327190972</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46300.30507524306</v>
+        <v>46301.323278020835</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46300.30508103009</v>
+        <v>46301.323284618054</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>382.4344045924537</v>
+        <v>378.71854805719835</v>
       </c>
       <c r="T25" s="30">
-        <v>46300.3050868287</v>
+        <v>46301.32328984954</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46300.30509262731</v>
+        <v>46301.323295648144</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>346.87469679222426</v>
+        <v>345.0524544942635</v>
       </c>
       <c r="T27" s="30">
-        <v>46300.30509840278</v>
+        <v>46301.32330130787</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.378020199514467</v>
+        <v>29.605358569901153</v>
       </c>
       <c r="T28" s="30">
-        <v>46300.305104189814</v>
+        <v>46301.323308136576</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46300.305110023146</v>
+        <v>46301.32331436343</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46300.30511583333</v>
+        <v>46301.3233193287</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46300.30512159722</v>
+        <v>46301.32332505787</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46300.30512745371</v>
+        <v>46301.323330162035</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46300.305133194444</v>
+        <v>46301.323336678244</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>728.6289156939844</v>
+        <v>746.1790584095721</v>
       </c>
       <c r="T34" s="30">
-        <v>46300.305138993055</v>
+        <v>46301.32334243055</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46300.305144756945</v>
+        <v>46301.32334833333</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46300.30515054398</v>
+        <v>46301.32335415509</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46300.30515637732</v>
+        <v>46301.32335979166</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>164.75497810902377</v>
+        <v>163.17953549592477</v>
       </c>
       <c r="T38" s="30">
-        <v>46300.305162372686</v>
+        <v>46301.32336642361</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1078.0142979033276</v>
+        <v>1065.6228777408712</v>
       </c>
       <c r="T39" s="30">
-        <v>46300.30516793982</v>
+        <v>46301.3233712963</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46300.30517953704</v>
+        <v>46301.32338311343</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46300.30518533565</v>
+        <v>46301.32338765046</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>235.57431178711786</v>
+        <v>240.21347863963376</v>
       </c>
       <c r="T42" s="30">
-        <v>46300.305173773144</v>
+        <v>46301.32337650463</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46300.30519109954</v>
+        <v>46301.32339452546</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46300.3051969213</v>
+        <v>46301.3233996875</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>751.2750981017819</v>
+        <v>759.1384040511332</v>
       </c>
       <c r="T45" s="30">
-        <v>46300.30520270833</v>
+        <v>46301.323406261574</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>44.41212450999122</v>
+        <v>44.60807406140511</v>
       </c>
       <c r="T46" s="30">
-        <v>46300.30520847222</v>
+        <v>46301.32341146991</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,14 +7325,14 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>146.57001361371655</v>
+        <v>150.18718388028233</v>
       </c>
       <c r="T47" s="30">
-        <v>46300.30521425926</v>
+        <v>46301.32341716435</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0xa541143f20d7b0643123064abf25f423e375b531</t>
+          <t>https://dexscreener.com/robinhood/0x714187eed11d8fc9500ff6798734c8bb63a8a19b</t>
         </is>
       </c>
       <c r="V47" s="33" t="inlineStr">
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46300.3052200463</v>
+        <v>46301.32342371528</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.96783721956093</v>
+        <v>101.00828249913233</v>
       </c>
       <c r="T49" s="30">
-        <v>46300.30522584491</v>
+        <v>46301.32342875</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46300.30523186343</v>
+        <v>46301.32343503473</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46300.30523762732</v>
+        <v>46301.32344118055</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46300.30524320602</v>
+        <v>46301.323446875</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46300.30524898148</v>
+        <v>46301.32345239584</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46300.30525474537</v>
+        <v>46301.32345754629</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>160.15372196609675</v>
+        <v>173.52140737473482</v>
       </c>
       <c r="T55" s="30">
-        <v>46300.30526055556</v>
+        <v>46301.323463472225</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>770.2502783259829</v>
+        <v>777.0306425463009</v>
       </c>
       <c r="T56" s="30">
-        <v>46300.30526631945</v>
+        <v>46301.323469016206</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>373.27190322958165</v>
+        <v>381.2190006391157</v>
       </c>
       <c r="T57" s="30">
-        <v>46300.30527211806</v>
+        <v>46301.32347440972</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46300.30527788194</v>
+        <v>46301.32348184028</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46300.305283657406</v>
+        <v>46301.32348601852</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46300.30528945602</v>
+        <v>46301.323492905096</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46300.30529523148</v>
+        <v>46301.32349791667</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46300.30530100694</v>
+        <v>46301.323504513886</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.000273074549352</v>
+        <v>1.0001810327669307</v>
       </c>
       <c r="T63" s="156">
-        <v>46300.30530678241</v>
+        <v>46301.32351050926</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4698,7 +4698,7 @@
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="V9" s="32" t="inlineStr">
@@ -8440,7 +8440,7 @@
       </c>
       <c r="U63" t="inlineStr">
         <is>
-          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
+          <t>https://api.coingecko.com/api/v3/simple/price?ids=tether,ethereum,binancecoin,solana,hyperliquid,aster-2,myx-finance&amp;vs_currencies=usd&amp;include_last_updated_at=true</t>
         </is>
       </c>
       <c r="V63" s="157" t="inlineStr">

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2704.849577773577</v>
+        <v>2617.743395358373</v>
       </c>
       <c r="T9" s="29">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>332.970267618439</v>
+        <v>333.80506368359727</v>
       </c>
       <c r="T10" s="30">
-        <v>46301.32320273148</v>
+        <v>46302.30944957176</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46301.32320947917</v>
+        <v>46302.30945534722</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46301.32321513889</v>
+        <v>46302.30946113426</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46301.32322099537</v>
+        <v>46302.30946693287</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46301.32322715278</v>
+        <v>46302.30947274306</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46301.323232546296</v>
+        <v>46302.30947853009</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46301.32323829861</v>
+        <v>46302.30948430555</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46301.32324415509</v>
+        <v>46302.309490625</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>187.2138857133141</v>
+        <v>183.41476099273402</v>
       </c>
       <c r="T18" s="30">
-        <v>46301.32324984954</v>
+        <v>46302.30949622685</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46301.32325584491</v>
+        <v>46302.30950171296</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46301.32326068287</v>
+        <v>46302.30950751157</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46301.32326722222</v>
+        <v>46302.30951329861</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.651565933433952</v>
+        <v>8.631165207302987</v>
       </c>
       <c r="T22" s="30">
-        <v>46301.32327190972</v>
+        <v>46302.3095191088</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46301.323278020835</v>
+        <v>46302.30952490741</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46301.323284618054</v>
+        <v>46302.309530694445</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>378.71854805719835</v>
+        <v>377.9110179874283</v>
       </c>
       <c r="T25" s="30">
-        <v>46301.32328984954</v>
+        <v>46302.309536493056</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46301.323295648144</v>
+        <v>46302.30954229167</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5940,20 +5940,22 @@
       <c r="R27" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
-      <c r="S27" s="27">
-        <v>345.0524544942635</v>
+      <c r="S27" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T27" s="30">
-        <v>46301.32330130787</v>
+        <v>46302.309548425925</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x8c2b4303fa0b99d07a5d3e9411497a277e65b673</t>
+          <t/>
         </is>
       </c>
       <c r="V27" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -6009,10 +6011,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.605358569901153</v>
+        <v>29.033919579143184</v>
       </c>
       <c r="T28" s="30">
-        <v>46301.323308136576</v>
+        <v>46302.30955388889</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6084,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46301.32331436343</v>
+        <v>46302.309559664354</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6154,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46301.3233193287</v>
+        <v>46302.30956545139</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6224,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46301.32332505787</v>
+        <v>46302.30957125</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6294,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46301.323330162035</v>
+        <v>46302.309577037035</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6364,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46301.323336678244</v>
+        <v>46302.309583368056</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>746.1790584095721</v>
+        <v>739.5398378781136</v>
       </c>
       <c r="T34" s="30">
-        <v>46301.32334243055</v>
+        <v>46302.30958862268</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6502,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46301.32334833333</v>
+        <v>46302.309594432874</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6572,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46301.32335415509</v>
+        <v>46302.309600243054</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6642,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46301.32335979166</v>
+        <v>46302.309606041665</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6707,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>163.17953549592477</v>
+        <v>160.82171093097568</v>
       </c>
       <c r="T38" s="30">
-        <v>46301.32336642361</v>
+        <v>46302.3096118287</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6775,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1065.6228777408712</v>
+        <v>1033.5895345871693</v>
       </c>
       <c r="T39" s="30">
-        <v>46301.3233712963</v>
+        <v>46302.309617604165</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46301.32338311343</v>
+        <v>46302.30962920139</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46301.32338765046</v>
+        <v>46302.309635000005</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>240.21347863963376</v>
+        <v>240.09641301575712</v>
       </c>
       <c r="T42" s="30">
-        <v>46301.32337650463</v>
+        <v>46302.30962371528</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46301.32339452546</v>
+        <v>46302.30964131944</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46301.3233996875</v>
+        <v>46302.309646574075</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>759.1384040511332</v>
+        <v>759.9425922499538</v>
       </c>
       <c r="T45" s="30">
-        <v>46301.323406261574</v>
+        <v>46302.309652916665</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>44.60807406140511</v>
+        <v>45.45613657843809</v>
       </c>
       <c r="T46" s="30">
-        <v>46301.32341146991</v>
+        <v>46302.309658136575</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>150.18718388028233</v>
+        <v>149.03411960614685</v>
       </c>
       <c r="T47" s="30">
-        <v>46301.32341716435</v>
+        <v>46302.309663935186</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46301.32342371528</v>
+        <v>46302.30966974537</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.00828249913233</v>
+        <v>100.60358148350028</v>
       </c>
       <c r="T49" s="30">
-        <v>46301.32342875</v>
+        <v>46302.30967550926</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46301.32343503473</v>
+        <v>46302.30968128472</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46301.32344118055</v>
+        <v>46302.30968706019</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46301.323446875</v>
+        <v>46302.30969284722</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46301.32345239584</v>
+        <v>46302.30969863426</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46301.32345754629</v>
+        <v>46302.30970442129</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>173.52140737473482</v>
+        <v>168.60276137278535</v>
       </c>
       <c r="T55" s="30">
-        <v>46301.323463472225</v>
+        <v>46302.30971018519</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>777.0306425463009</v>
+        <v>780.2353317697889</v>
       </c>
       <c r="T56" s="30">
-        <v>46301.323469016206</v>
+        <v>46302.309715972224</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>381.2190006391157</v>
+        <v>378.7811354532862</v>
       </c>
       <c r="T57" s="30">
-        <v>46301.32347440972</v>
+        <v>46302.30972175926</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46301.32348184028</v>
+        <v>46302.30972935185</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46301.32348601852</v>
+        <v>46302.30973332176</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46301.323492905096</v>
+        <v>46302.309739097225</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46301.32349791667</v>
+        <v>46302.30974486111</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46301.323504513886</v>
+        <v>46302.309750636574</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0001810327669307</v>
+        <v>1.0001350182274606</v>
       </c>
       <c r="T63" s="156">
-        <v>46301.32351050926</v>
+        <v>46302.30975677083</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2617.743395358373</v>
+        <v>2573.9239713479265</v>
       </c>
       <c r="T9" s="29">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>333.80506368359727</v>
+        <v>337.039078923276</v>
       </c>
       <c r="T10" s="30">
-        <v>46302.30944957176</v>
+        <v>46303.320533935184</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46302.30945534722</v>
+        <v>46303.32053993056</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46302.30946113426</v>
+        <v>46303.32054548611</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46302.30946693287</v>
+        <v>46303.32055127315</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46302.30947274306</v>
+        <v>46303.320557060186</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46302.30947853009</v>
+        <v>46303.32056290509</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46302.30948430555</v>
+        <v>46303.320568333336</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46302.309490625</v>
+        <v>46303.32057445602</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>183.41476099273402</v>
+        <v>177.91981301510148</v>
       </c>
       <c r="T18" s="30">
-        <v>46302.30949622685</v>
+        <v>46303.32058054398</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46302.30950171296</v>
+        <v>46303.32058627315</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46302.30950751157</v>
+        <v>46303.32059152777</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46302.30951329861</v>
+        <v>46303.32059730324</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.631165207302987</v>
+        <v>8.234619621607722</v>
       </c>
       <c r="T22" s="30">
-        <v>46302.3095191088</v>
+        <v>46303.320603148146</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46302.30952490741</v>
+        <v>46303.32060922454</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46302.309530694445</v>
+        <v>46303.320615069446</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>377.9110179874283</v>
+        <v>379.1527046673184</v>
       </c>
       <c r="T25" s="30">
-        <v>46302.309536493056</v>
+        <v>46303.320620451384</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46302.30954229167</v>
+        <v>46303.320626574074</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="T27" s="30">
-        <v>46302.309548425925</v>
+        <v>46303.32063203704</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.033919579143184</v>
+        <v>29.566586855225783</v>
       </c>
       <c r="T28" s="30">
-        <v>46302.30955388889</v>
+        <v>46303.320637812496</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46302.309559664354</v>
+        <v>46303.320643935185</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46302.30956545139</v>
+        <v>46303.320649409725</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46302.30957125</v>
+        <v>46303.32065548611</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46302.309577037035</v>
+        <v>46303.3206609838</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46302.309583368056</v>
+        <v>46303.320667858796</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>739.5398378781136</v>
+        <v>723.2357352474739</v>
       </c>
       <c r="T34" s="30">
-        <v>46302.30958862268</v>
+        <v>46303.3206728588</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46302.309594432874</v>
+        <v>46303.32067869213</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46302.309600243054</v>
+        <v>46303.320684502316</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46302.309606041665</v>
+        <v>46303.32069032407</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6707,10 +6707,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>160.82171093097568</v>
+        <v>152.4054994852112</v>
       </c>
       <c r="T38" s="30">
-        <v>46302.3096118287</v>
+        <v>46303.320696076386</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1033.5895345871693</v>
+        <v>1086.1493297740033</v>
       </c>
       <c r="T39" s="30">
-        <v>46302.309617604165</v>
+        <v>46303.32070152778</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46302.30962920139</v>
+        <v>46303.32071309028</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46302.309635000005</v>
+        <v>46303.32071891204</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>240.09641301575712</v>
+        <v>236.34258819197572</v>
       </c>
       <c r="T42" s="30">
-        <v>46302.30962371528</v>
+        <v>46303.32070762732</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46302.30964131944</v>
+        <v>46303.3207247338</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46302.309646574075</v>
+        <v>46303.32073047454</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>759.9425922499538</v>
+        <v>756.7145168439495</v>
       </c>
       <c r="T45" s="30">
-        <v>46302.309652916665</v>
+        <v>46303.32073655092</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>45.45613657843809</v>
+        <v>46.56612359533698</v>
       </c>
       <c r="T46" s="30">
-        <v>46302.309658136575</v>
+        <v>46303.32074201389</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>149.03411960614685</v>
+        <v>151.9752581198052</v>
       </c>
       <c r="T47" s="30">
-        <v>46302.309663935186</v>
+        <v>46303.32074811343</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46302.30966974537</v>
+        <v>46303.32075386574</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.60358148350028</v>
+        <v>100.94663106002467</v>
       </c>
       <c r="T49" s="30">
-        <v>46302.30967550926</v>
+        <v>46303.320759699076</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46302.30968128472</v>
+        <v>46303.32076553241</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46302.30968706019</v>
+        <v>46303.32077125</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46302.30969284722</v>
+        <v>46303.32077767361</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46302.30969863426</v>
+        <v>46303.32078357639</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46302.30970442129</v>
+        <v>46303.32078865741</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>168.60276137278535</v>
+        <v>167.33387430348427</v>
       </c>
       <c r="T55" s="30">
-        <v>46302.30971018519</v>
+        <v>46303.32079440972</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>780.2353317697889</v>
+        <v>776.8858329522863</v>
       </c>
       <c r="T56" s="30">
-        <v>46302.309715972224</v>
+        <v>46303.32079987269</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>378.7811354532862</v>
+        <v>376.9114473219476</v>
       </c>
       <c r="T57" s="30">
-        <v>46302.30972175926</v>
+        <v>46303.3208059838</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46302.30972935185</v>
+        <v>46303.32081145833</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46302.30973332176</v>
+        <v>46303.320817280095</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46302.309739097225</v>
+        <v>46303.320823043985</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46302.30974486111</v>
+        <v>46303.320828819444</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46302.309750636574</v>
+        <v>46303.320834606486</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0001350182274606</v>
+        <v>1.0005613148976575</v>
       </c>
       <c r="T63" s="156">
-        <v>46302.30975677083</v>
+        <v>46303.32084079861</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2573.9239713479265</v>
+        <v>2502.464158378589</v>
       </c>
       <c r="T9" s="29">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>337.039078923276</v>
+        <v>337.82735781180736</v>
       </c>
       <c r="T10" s="30">
-        <v>46303.320533935184</v>
+        <v>46304.31786243056</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46303.32053993056</v>
+        <v>46304.317868391205</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46303.32054548611</v>
+        <v>46304.31787373842</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46303.32055127315</v>
+        <v>46304.31787991898</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46303.320557060186</v>
+        <v>46304.3178853125</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46303.32056290509</v>
+        <v>46304.317891122686</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46303.320568333336</v>
+        <v>46304.31789724537</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46303.32057445602</v>
+        <v>46304.31790223379</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>177.91981301510148</v>
+        <v>175.6782314497657</v>
       </c>
       <c r="T18" s="30">
-        <v>46303.32058054398</v>
+        <v>46304.31790792824</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46303.32058627315</v>
+        <v>46304.31791424769</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46303.32059152777</v>
+        <v>46304.31791932871</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46303.32059730324</v>
+        <v>46304.31792603009</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.234619621607722</v>
+        <v>8.235542520116038</v>
       </c>
       <c r="T22" s="30">
-        <v>46303.320603148146</v>
+        <v>46304.31793149306</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46303.32060922454</v>
+        <v>46304.317937314816</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46303.320615069446</v>
+        <v>46304.31794331018</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>379.1527046673184</v>
+        <v>385.48943438934407</v>
       </c>
       <c r="T25" s="30">
-        <v>46303.320620451384</v>
+        <v>46304.31794828703</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46303.320626574074</v>
+        <v>46304.3179540625</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="T27" s="30">
-        <v>46303.32063203704</v>
+        <v>46304.31795984953</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.566586855225783</v>
+        <v>28.479166479040398</v>
       </c>
       <c r="T28" s="30">
-        <v>46303.320637812496</v>
+        <v>46304.317965625</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46303.320643935185</v>
+        <v>46304.31797159722</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46303.320649409725</v>
+        <v>46304.317978101855</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46303.32065548611</v>
+        <v>46304.317983182875</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46303.3206609838</v>
+        <v>46304.317989710646</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46303.320667858796</v>
+        <v>46304.317995682875</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>723.2357352474739</v>
+        <v>724.1373444328033</v>
       </c>
       <c r="T34" s="30">
-        <v>46303.3206728588</v>
+        <v>46304.31800057871</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46303.32067869213</v>
+        <v>46304.318006469905</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46303.320684502316</v>
+        <v>46304.318011979165</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46303.32069032407</v>
+        <v>46304.318017986116</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6707,10 +6707,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>152.4054994852112</v>
+        <v>153.71344915127884</v>
       </c>
       <c r="T38" s="30">
-        <v>46303.320696076386</v>
+        <v>46304.31802357639</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1086.1493297740033</v>
+        <v>1045.9539269928662</v>
       </c>
       <c r="T39" s="30">
-        <v>46303.32070152778</v>
+        <v>46304.31802949074</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46303.32071309028</v>
+        <v>46304.31804135416</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46303.32071891204</v>
+        <v>46304.31804805556</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>236.34258819197572</v>
+        <v>233.93743989705072</v>
       </c>
       <c r="T42" s="30">
-        <v>46303.32070762732</v>
+        <v>46304.318035972225</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46303.3207247338</v>
+        <v>46304.31805273148</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46303.32073047454</v>
+        <v>46304.31805834491</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>756.7145168439495</v>
+        <v>753.7272584449335</v>
       </c>
       <c r="T45" s="30">
-        <v>46303.32073655092</v>
+        <v>46304.3180641088</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>46.56612359533698</v>
+        <v>45.740783547327354</v>
       </c>
       <c r="T46" s="30">
-        <v>46303.32074201389</v>
+        <v>46304.31807079861</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>151.9752581198052</v>
+        <v>156.69545604191623</v>
       </c>
       <c r="T47" s="30">
-        <v>46303.32074811343</v>
+        <v>46304.3180756713</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46303.32075386574</v>
+        <v>46304.3180816088</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.94663106002467</v>
+        <v>102.05868549533837</v>
       </c>
       <c r="T49" s="30">
-        <v>46303.320759699076</v>
+        <v>46304.31808748843</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46303.32076553241</v>
+        <v>46304.31809320601</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46303.32077125</v>
+        <v>46304.31809884259</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46303.32077767361</v>
+        <v>46304.318104791666</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46303.32078357639</v>
+        <v>46304.318110532404</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46303.32078865741</v>
+        <v>46304.31811671296</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>167.33387430348427</v>
+        <v>166.62213669799775</v>
       </c>
       <c r="T55" s="30">
-        <v>46303.32079440972</v>
+        <v>46304.318122233795</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>776.8858329522863</v>
+        <v>777.9635694822616</v>
       </c>
       <c r="T56" s="30">
-        <v>46303.32079987269</v>
+        <v>46304.31812773148</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>376.9114473219476</v>
+        <v>379.3953330591488</v>
       </c>
       <c r="T57" s="30">
-        <v>46303.3208059838</v>
+        <v>46304.3181344213</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46303.32081145833</v>
+        <v>46304.31813949074</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46303.320817280095</v>
+        <v>46304.31814575232</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46303.320823043985</v>
+        <v>46304.31815100695</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46303.320828819444</v>
+        <v>46304.3181571875</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46303.320834606486</v>
+        <v>46304.31816472222</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0005613148976575</v>
+        <v>1.0006734532340265</v>
       </c>
       <c r="T63" s="156">
-        <v>46303.32084079861</v>
+        <v>46304.31816902778</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2502.464158378589</v>
+        <v>2492.967260609154</v>
       </c>
       <c r="T9" s="29">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>337.82735781180736</v>
+        <v>336.78090177181997</v>
       </c>
       <c r="T10" s="30">
-        <v>46304.31786243056</v>
+        <v>46305.308619097224</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46304.317868391205</v>
+        <v>46305.308624687495</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46304.31787373842</v>
+        <v>46305.30863047454</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46304.31787991898</v>
+        <v>46305.308636469905</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46304.3178853125</v>
+        <v>46305.30864204861</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46304.317891122686</v>
+        <v>46305.30864802084</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46304.31789724537</v>
+        <v>46305.30865361111</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46304.31790223379</v>
+        <v>46305.30865962963</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>175.6782314497657</v>
+        <v>180.81470695668273</v>
       </c>
       <c r="T18" s="30">
-        <v>46304.31790792824</v>
+        <v>46305.308665752316</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46304.31791424769</v>
+        <v>46305.30867068287</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46304.31791932871</v>
+        <v>46305.30867677083</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46304.31792603009</v>
+        <v>46305.30868229167</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.235542520116038</v>
+        <v>8.12605391016307</v>
       </c>
       <c r="T22" s="30">
-        <v>46304.31793149306</v>
+        <v>46305.308688680554</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46304.317937314816</v>
+        <v>46305.30869416667</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46304.31794331018</v>
+        <v>46305.30869994213</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>385.48943438934407</v>
+        <v>383.78592051078056</v>
       </c>
       <c r="T25" s="30">
-        <v>46304.31794828703</v>
+        <v>46305.30870541666</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46304.3179540625</v>
+        <v>46305.30871174769</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5940,22 +5940,20 @@
       <c r="R27" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
-      <c r="S27" s="27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="S27" s="27">
+        <v>351.79208510340203</v>
       </c>
       <c r="T27" s="30">
-        <v>46304.31795984953</v>
+        <v>46305.308717314816</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
-          <t/>
+          <t>https://dexscreener.com/robinhood/0x8c2b4303fa0b99d07a5d3e9411497a277e65b673</t>
         </is>
       </c>
       <c r="V27" s="33" t="inlineStr">
         <is>
-          <t>暂无合格池价；可手动输入</t>
+          <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
@@ -6010,20 +6008,22 @@
       <c r="R28" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
-      <c r="S28" s="27">
-        <v>28.479166479040398</v>
+      <c r="S28" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T28" s="30">
-        <v>46304.317965625</v>
+        <v>46305.308723125</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0xd10e6245961d697d975963682ece9979e9917fbc</t>
+          <t/>
         </is>
       </c>
       <c r="V28" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46304.31797159722</v>
+        <v>46305.30872891204</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46304.317978101855</v>
+        <v>46305.30873472222</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46304.317983182875</v>
+        <v>46305.30874050926</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46304.317989710646</v>
+        <v>46305.30874628472</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46304.317995682875</v>
+        <v>46305.308752048615</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>724.1373444328033</v>
+        <v>719.4760096271723</v>
       </c>
       <c r="T34" s="30">
-        <v>46304.31800057871</v>
+        <v>46305.30875752315</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46304.318006469905</v>
+        <v>46305.308763333334</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46304.318011979165</v>
+        <v>46305.30876943287</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46304.318017986116</v>
+        <v>46305.308774930556</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6707,10 +6707,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>153.71344915127884</v>
+        <v>156.08628428178994</v>
       </c>
       <c r="T38" s="30">
-        <v>46304.31802357639</v>
+        <v>46305.30878103009</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1045.9539269928662</v>
+        <v>1030.8880115686186</v>
       </c>
       <c r="T39" s="30">
-        <v>46304.31802949074</v>
+        <v>46305.308786828704</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46304.31804135416</v>
+        <v>46305.308798391205</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46304.31804805556</v>
+        <v>46305.30880420139</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>233.93743989705072</v>
+        <v>230.5317461508824</v>
       </c>
       <c r="T42" s="30">
-        <v>46304.318035972225</v>
+        <v>46305.308792615746</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46304.31805273148</v>
+        <v>46305.30881001157</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46304.31805834491</v>
+        <v>46305.30881579861</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>753.7272584449335</v>
+        <v>754.2419102231162</v>
       </c>
       <c r="T45" s="30">
-        <v>46304.3180641088</v>
+        <v>46305.30882128472</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>45.740783547327354</v>
+        <v>48.13385972549549</v>
       </c>
       <c r="T46" s="30">
-        <v>46304.31807079861</v>
+        <v>46305.30882739583</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>156.69545604191623</v>
+        <v>159.43878189250992</v>
       </c>
       <c r="T47" s="30">
-        <v>46304.3180756713</v>
+        <v>46305.30883314815</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46304.3180816088</v>
+        <v>46305.308838923615</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.05868549533837</v>
+        <v>101.24542784374358</v>
       </c>
       <c r="T49" s="30">
-        <v>46304.31808748843</v>
+        <v>46305.308845057865</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46304.31809320601</v>
+        <v>46305.30885050926</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46304.31809884259</v>
+        <v>46305.30885712963</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46304.318104791666</v>
+        <v>46305.30886211805</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46304.318110532404</v>
+        <v>46305.308867569445</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46304.31811671296</v>
+        <v>46305.30887388889</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>166.62213669799775</v>
+        <v>163.1575523765205</v>
       </c>
       <c r="T55" s="30">
-        <v>46304.318122233795</v>
+        <v>46305.30887915509</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>777.9635694822616</v>
+        <v>781.16196566442</v>
       </c>
       <c r="T56" s="30">
-        <v>46304.31812773148</v>
+        <v>46305.3088853125</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>379.3953330591488</v>
+        <v>383.34259022972117</v>
       </c>
       <c r="T57" s="30">
-        <v>46304.3181344213</v>
+        <v>46305.308891064815</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46304.31813949074</v>
+        <v>46305.30889684027</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46304.31814575232</v>
+        <v>46305.30890232639</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46304.31815100695</v>
+        <v>46305.308908113424</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46304.3181571875</v>
+        <v>46305.30891422454</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46304.31816472222</v>
+        <v>46305.30891966435</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0006734532340265</v>
+        <v>1.0007455554388018</v>
       </c>
       <c r="T63" s="156">
-        <v>46304.31816902778</v>
+        <v>46305.308925798614</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2492.967260609154</v>
+        <v>2500.62304391734</v>
       </c>
       <c r="T9" s="29">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.78090177181997</v>
+        <v>336.60385516555954</v>
       </c>
       <c r="T10" s="30">
-        <v>46305.308619097224</v>
+        <v>46306.31189152778</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46305.308624687495</v>
+        <v>46306.3118972338</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46305.30863047454</v>
+        <v>46306.31190300926</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46305.308636469905</v>
+        <v>46306.31190876157</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46305.30864204861</v>
+        <v>46306.31191458333</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46305.30864802084</v>
+        <v>46306.31192034722</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46305.30865361111</v>
+        <v>46306.31192621528</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46305.30865962963</v>
+        <v>46306.31193193287</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>180.81470695668273</v>
+        <v>180.7477928231346</v>
       </c>
       <c r="T18" s="30">
-        <v>46305.308665752316</v>
+        <v>46306.3119378125</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46305.30867068287</v>
+        <v>46306.31194353009</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46305.30867677083</v>
+        <v>46306.311949351846</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46305.30868229167</v>
+        <v>46306.31195523148</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.12605391016307</v>
+        <v>8.090062624671338</v>
       </c>
       <c r="T22" s="30">
-        <v>46305.308688680554</v>
+        <v>46306.31196111111</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46305.30869416667</v>
+        <v>46306.31196671296</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46305.30869994213</v>
+        <v>46306.31197246528</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>383.78592051078056</v>
+        <v>385.2563287750206</v>
       </c>
       <c r="T25" s="30">
-        <v>46305.30870541666</v>
+        <v>46306.31197826389</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46305.30871174769</v>
+        <v>46306.311984050924</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>351.79208510340203</v>
+        <v>352.9581324496285</v>
       </c>
       <c r="T27" s="30">
-        <v>46305.308717314816</v>
+        <v>46306.31198987269</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6014,7 +6014,7 @@
         </is>
       </c>
       <c r="T28" s="30">
-        <v>46305.308723125</v>
+        <v>46306.31199556713</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46305.30872891204</v>
+        <v>46306.312001412036</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46305.30873472222</v>
+        <v>46306.312007395834</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46305.30874050926</v>
+        <v>46306.31201299768</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46305.30874628472</v>
+        <v>46306.31201894676</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46305.308752048615</v>
+        <v>46306.312024803236</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>719.4760096271723</v>
+        <v>718.727449063032</v>
       </c>
       <c r="T34" s="30">
-        <v>46305.30875752315</v>
+        <v>46306.31203032407</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46305.308763333334</v>
+        <v>46306.312036157404</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46305.30876943287</v>
+        <v>46306.31204221065</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46305.308774930556</v>
+        <v>46306.31204777778</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6707,10 +6707,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>156.08628428178994</v>
+        <v>156.30645553568263</v>
       </c>
       <c r="T38" s="30">
-        <v>46305.30878103009</v>
+        <v>46306.31205359954</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6775,10 +6775,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1030.8880115686186</v>
+        <v>1035.2838027598095</v>
       </c>
       <c r="T39" s="30">
-        <v>46305.308786828704</v>
+        <v>46306.31205920139</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46305.308798391205</v>
+        <v>46306.31207078703</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46305.30880420139</v>
+        <v>46306.31207690972</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>230.5317461508824</v>
+        <v>230.80148970050854</v>
       </c>
       <c r="T42" s="30">
-        <v>46305.308792615746</v>
+        <v>46306.312065046295</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46305.30881001157</v>
+        <v>46306.3120825</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46305.30881579861</v>
+        <v>46306.31208827547</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>754.2419102231162</v>
+        <v>749.8045793978142</v>
       </c>
       <c r="T45" s="30">
-        <v>46305.30882128472</v>
+        <v>46306.312094050925</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>48.13385972549549</v>
+        <v>48.13001750528211</v>
       </c>
       <c r="T46" s="30">
-        <v>46305.30882739583</v>
+        <v>46306.31209982639</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>159.43878189250992</v>
+        <v>160.0797496214195</v>
       </c>
       <c r="T47" s="30">
-        <v>46305.30883314815</v>
+        <v>46306.31210553241</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46305.308838923615</v>
+        <v>46306.31211143518</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.24542784374358</v>
+        <v>101.67876556233593</v>
       </c>
       <c r="T49" s="30">
-        <v>46305.308845057865</v>
+        <v>46306.312117152775</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46305.30885050926</v>
+        <v>46306.31212314815</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46305.30885712963</v>
+        <v>46306.312128784724</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46305.30886211805</v>
+        <v>46306.31213439815</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46305.308867569445</v>
+        <v>46306.31214028935</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46305.30887388889</v>
+        <v>46306.312146041666</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>163.1575523765205</v>
+        <v>163.7429475932489</v>
       </c>
       <c r="T55" s="30">
-        <v>46305.30887915509</v>
+        <v>46306.312151805556</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>781.16196566442</v>
+        <v>780.7786197350287</v>
       </c>
       <c r="T56" s="30">
-        <v>46305.3088853125</v>
+        <v>46306.31215759259</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>383.34259022972117</v>
+        <v>382.2937424371476</v>
       </c>
       <c r="T57" s="30">
-        <v>46305.308891064815</v>
+        <v>46306.3121633912</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46305.30889684027</v>
+        <v>46306.31216920139</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46305.30890232639</v>
+        <v>46306.31217511574</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46305.308908113424</v>
+        <v>46306.31218099537</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46305.30891422454</v>
+        <v>46306.31218653935</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46305.30891966435</v>
+        <v>46306.31219240741</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0007455554388018</v>
+        <v>1.00087376279492</v>
       </c>
       <c r="T63" s="156">
-        <v>46305.308925798614</v>
+        <v>46306.312198148145</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2500.62304391734</v>
+        <v>2566.294900854111</v>
       </c>
       <c r="T9" s="29">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>336.60385516555954</v>
+        <v>338.33791160679885</v>
       </c>
       <c r="T10" s="30">
-        <v>46306.31189152778</v>
+        <v>46307.317547094906</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46306.3118972338</v>
+        <v>46307.31755280092</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46306.31190300926</v>
+        <v>46307.31755789352</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46306.31190876157</v>
+        <v>46307.31756393519</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46306.31191458333</v>
+        <v>46307.31757006944</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46306.31192034722</v>
+        <v>46307.31757585648</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46306.31192621528</v>
+        <v>46307.31758173611</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46306.31193193287</v>
+        <v>46307.31758703704</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>180.7477928231346</v>
+        <v>184.3718258554867</v>
       </c>
       <c r="T18" s="30">
-        <v>46306.3119378125</v>
+        <v>46307.31759335648</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46306.31194353009</v>
+        <v>46307.31759902778</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46306.311949351846</v>
+        <v>46307.31760480324</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46306.31195523148</v>
+        <v>46307.31761099537</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.090062624671338</v>
+        <v>8.135817109233102</v>
       </c>
       <c r="T22" s="30">
-        <v>46306.31196111111</v>
+        <v>46307.31761637731</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46306.31196671296</v>
+        <v>46307.31762226852</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46306.31197246528</v>
+        <v>46307.31762804398</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>385.2563287750206</v>
+        <v>386.8365881605348</v>
       </c>
       <c r="T25" s="30">
-        <v>46306.31197826389</v>
+        <v>46307.31763384259</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46306.311984050924</v>
+        <v>46307.31763953704</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>352.9581324496285</v>
+        <v>356.57495109002934</v>
       </c>
       <c r="T27" s="30">
-        <v>46306.31198987269</v>
+        <v>46307.31764538194</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6008,22 +6008,20 @@
       <c r="R28" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
-      <c r="S28" s="27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="S28" s="27">
+        <v>31.21231680651666</v>
       </c>
       <c r="T28" s="30">
-        <v>46306.31199556713</v>
+        <v>46307.31765074074</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
-          <t/>
+          <t>https://dexscreener.com/robinhood/0xd10e6245961d697d975963682ece9979e9917fbc</t>
         </is>
       </c>
       <c r="V28" s="33" t="inlineStr">
         <is>
-          <t>暂无合格池价；可手动输入</t>
+          <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
@@ -6084,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46306.312001412036</v>
+        <v>46307.31765697917</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6154,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46306.312007395834</v>
+        <v>46307.31766284722</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6224,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46306.31201299768</v>
+        <v>46307.31766851852</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6294,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46306.31201894676</v>
+        <v>46307.317674351856</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46306.312024803236</v>
+        <v>46307.317680347216</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6429,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>718.727449063032</v>
+        <v>722.3464777315781</v>
       </c>
       <c r="T34" s="30">
-        <v>46306.31203032407</v>
+        <v>46307.31768543981</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6502,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46306.312036157404</v>
+        <v>46307.31769125</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6572,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46306.31204221065</v>
+        <v>46307.31769736111</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6642,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46306.31204777778</v>
+        <v>46307.31770331018</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6707,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>156.30645553568263</v>
+        <v>158.8535803099216</v>
       </c>
       <c r="T38" s="30">
-        <v>46306.31205359954</v>
+        <v>46307.3177083912</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6775,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1035.2838027598095</v>
+        <v>1027.0643510109728</v>
       </c>
       <c r="T39" s="30">
-        <v>46306.31205920139</v>
+        <v>46307.317714895835</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46306.31207078703</v>
+        <v>46307.3177259838</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46306.31207690972</v>
+        <v>46307.31773230324</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>230.80148970050854</v>
+        <v>230.05448895960612</v>
       </c>
       <c r="T42" s="30">
-        <v>46306.312065046295</v>
+        <v>46307.31771962963</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46306.3120825</v>
+        <v>46307.317737997684</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46306.31208827547</v>
+        <v>46307.31774384259</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>749.8045793978142</v>
+        <v>752.9483580760243</v>
       </c>
       <c r="T45" s="30">
-        <v>46306.312094050925</v>
+        <v>46307.31774957176</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>48.13001750528211</v>
+        <v>48.46465222634183</v>
       </c>
       <c r="T46" s="30">
-        <v>46306.31209982639</v>
+        <v>46307.31775498843</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>160.0797496214195</v>
+        <v>160.6048324552055</v>
       </c>
       <c r="T47" s="30">
-        <v>46306.31210553241</v>
+        <v>46307.31776111111</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46306.31211143518</v>
+        <v>46307.31776712963</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.67876556233593</v>
+        <v>101.95289632086941</v>
       </c>
       <c r="T49" s="30">
-        <v>46306.312117152775</v>
+        <v>46307.31777230324</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46306.31212314815</v>
+        <v>46307.317778564815</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46306.312128784724</v>
+        <v>46307.317784212966</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46306.31213439815</v>
+        <v>46307.317790138884</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46306.31214028935</v>
+        <v>46307.31779594908</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46306.312146041666</v>
+        <v>46307.31780201389</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>163.7429475932489</v>
+        <v>164.4675943299459</v>
       </c>
       <c r="T55" s="30">
-        <v>46306.312151805556</v>
+        <v>46307.317807060186</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>780.7786197350287</v>
+        <v>782.5695372191117</v>
       </c>
       <c r="T56" s="30">
-        <v>46306.31215759259</v>
+        <v>46307.3178135301</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>382.2937424371476</v>
+        <v>383.4041339557784</v>
       </c>
       <c r="T57" s="30">
-        <v>46306.3121633912</v>
+        <v>46307.317819351854</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46306.31216920139</v>
+        <v>46307.31782487268</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46306.31217511574</v>
+        <v>46307.31783061343</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46306.31218099537</v>
+        <v>46307.31783642361</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46306.31218653935</v>
+        <v>46307.31784215278</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46306.31219240741</v>
+        <v>46307.31784795139</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.00087376279492</v>
+        <v>1.0007155115907875</v>
       </c>
       <c r="T63" s="156">
-        <v>46306.312198148145</v>
+        <v>46307.317853402776</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2566.294900854111</v>
+        <v>2534.8972198314686</v>
       </c>
       <c r="T9" s="29">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>338.33791160679885</v>
+        <v>342.8974600188147</v>
       </c>
       <c r="T10" s="30">
-        <v>46307.317547094906</v>
+        <v>46308.330837141206</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46307.31755280092</v>
+        <v>46308.33084329861</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46307.31755789352</v>
+        <v>46308.33084840278</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46307.31756393519</v>
+        <v>46308.33085443287</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46307.31757006944</v>
+        <v>46308.330859988426</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46307.31757585648</v>
+        <v>46308.330865682874</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46307.31758173611</v>
+        <v>46308.33087168982</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46307.31758703704</v>
+        <v>46308.330877569446</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>184.3718258554867</v>
+        <v>182.1515782310202</v>
       </c>
       <c r="T18" s="30">
-        <v>46307.31759335648</v>
+        <v>46308.33088314815</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46307.31759902778</v>
+        <v>46308.33088944444</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46307.31760480324</v>
+        <v>46308.330895439816</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46307.31761099537</v>
+        <v>46308.33090148148</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>8.135817109233102</v>
+        <v>7.976221452733132</v>
       </c>
       <c r="T22" s="30">
-        <v>46307.31761637731</v>
+        <v>46308.3309066088</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46307.31762226852</v>
+        <v>46308.330912812504</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46307.31762804398</v>
+        <v>46308.330918831016</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>386.8365881605348</v>
+        <v>387.32711514981685</v>
       </c>
       <c r="T25" s="30">
-        <v>46307.31763384259</v>
+        <v>46308.330923611116</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46307.31763953704</v>
+        <v>46308.33092931713</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>356.57495109002934</v>
+        <v>354.03614819559255</v>
       </c>
       <c r="T27" s="30">
-        <v>46307.31764538194</v>
+        <v>46308.330935868056</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>31.21231680651666</v>
+        <v>30.42373050979764</v>
       </c>
       <c r="T28" s="30">
-        <v>46307.31765074074</v>
+        <v>46308.33094087963</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46307.31765697917</v>
+        <v>46308.33094678241</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46307.31766284722</v>
+        <v>46308.330953599536</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46307.31766851852</v>
+        <v>46308.33095909723</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46307.317674351856</v>
+        <v>46308.33096486111</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46307.317680347216</v>
+        <v>46308.33097224537</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>722.3464777315781</v>
+        <v>738.9163547567102</v>
       </c>
       <c r="T34" s="30">
-        <v>46307.31768543981</v>
+        <v>46308.33097574074</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46307.31769125</v>
+        <v>46308.33098119213</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46307.31769736111</v>
+        <v>46308.330987835645</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46307.31770331018</v>
+        <v>46308.3309934375</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>158.8535803099216</v>
+        <v>154.1622465523108</v>
       </c>
       <c r="T38" s="30">
-        <v>46307.3177083912</v>
+        <v>46308.33100005787</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>1027.0643510109728</v>
+        <v>962.8710394107404</v>
       </c>
       <c r="T39" s="30">
-        <v>46307.317714895835</v>
+        <v>46308.331004733795</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46307.3177259838</v>
+        <v>46308.33101648148</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46307.31773230324</v>
+        <v>46308.331022847226</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>230.05448895960612</v>
+        <v>224.8453793959288</v>
       </c>
       <c r="T42" s="30">
-        <v>46307.31771962963</v>
+        <v>46308.33101052084</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46307.317737997684</v>
+        <v>46308.33102848379</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46307.31774384259</v>
+        <v>46308.331033622686</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>752.9483580760243</v>
+        <v>743.2697504053162</v>
       </c>
       <c r="T45" s="30">
-        <v>46307.31774957176</v>
+        <v>46308.33103934027</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>48.46465222634183</v>
+        <v>49.498608914953664</v>
       </c>
       <c r="T46" s="30">
-        <v>46307.31775498843</v>
+        <v>46308.3310456713</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>160.6048324552055</v>
+        <v>156.60214967674784</v>
       </c>
       <c r="T47" s="30">
-        <v>46307.31776111111</v>
+        <v>46308.33105152778</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46307.31776712963</v>
+        <v>46308.331057476855</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.95289632086941</v>
+        <v>102.14467284481896</v>
       </c>
       <c r="T49" s="30">
-        <v>46307.31777230324</v>
+        <v>46308.3310621875</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46307.317778564815</v>
+        <v>46308.33106935185</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46307.317784212966</v>
+        <v>46308.331074050926</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46307.317790138884</v>
+        <v>46308.331080185184</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46307.31779594908</v>
+        <v>46308.33108677083</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46307.31780201389</v>
+        <v>46308.331091851855</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>164.4675943299459</v>
+        <v>162.82700506394988</v>
       </c>
       <c r="T55" s="30">
-        <v>46307.317807060186</v>
+        <v>46308.33109756944</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>782.5695372191117</v>
+        <v>780.1785392606233</v>
       </c>
       <c r="T56" s="30">
-        <v>46307.3178135301</v>
+        <v>46308.331103749995</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>383.4041339557784</v>
+        <v>375.06254878805464</v>
       </c>
       <c r="T57" s="30">
-        <v>46307.317819351854</v>
+        <v>46308.33110959491</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46307.31782487268</v>
+        <v>46308.33111557871</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46307.31783061343</v>
+        <v>46308.331120856485</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46307.31783642361</v>
+        <v>46308.33112726852</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46307.31784215278</v>
+        <v>46308.331132430554</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46307.31784795139</v>
+        <v>46308.331138483794</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0007155115907875</v>
+        <v>1.0007806088749225</v>
       </c>
       <c r="T63" s="156">
-        <v>46307.317853402776</v>
+        <v>46308.3311437963</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2534.8972198314686</v>
+        <v>2506.62482287105</v>
       </c>
       <c r="T9" s="29">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>342.8974600188147</v>
+        <v>342.7295070811551</v>
       </c>
       <c r="T10" s="30">
-        <v>46308.330837141206</v>
+        <v>46309.26569613426</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46308.33084329861</v>
+        <v>46309.26570200231</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46308.33084840278</v>
+        <v>46309.26570802083</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46308.33085443287</v>
+        <v>46309.26571346065</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46308.330859988426</v>
+        <v>46309.26571925926</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46308.330865682874</v>
+        <v>46309.26572502315</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46308.33087168982</v>
+        <v>46309.26573083334</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46308.330877569446</v>
+        <v>46309.265736643516</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>182.1515782310202</v>
+        <v>181.9924905331081</v>
       </c>
       <c r="T18" s="30">
-        <v>46308.33088314815</v>
+        <v>46309.265742615746</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46308.33088944444</v>
+        <v>46309.26574819445</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46308.330895439816</v>
+        <v>46309.2657540625</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46308.33090148148</v>
+        <v>46309.26575983797</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>7.976221452733132</v>
+        <v>7.745638825064647</v>
       </c>
       <c r="T22" s="30">
-        <v>46308.3309066088</v>
+        <v>46309.265765682874</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46308.330912812504</v>
+        <v>46309.265771377315</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46308.330918831016</v>
+        <v>46309.26577738426</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>387.32711514981685</v>
+        <v>382.0281164687893</v>
       </c>
       <c r="T25" s="30">
-        <v>46308.330923611116</v>
+        <v>46309.26578310185</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46308.33092931713</v>
+        <v>46309.26578883102</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>354.03614819559255</v>
+        <v>353.35724407368565</v>
       </c>
       <c r="T27" s="30">
-        <v>46308.330935868056</v>
+        <v>46309.26579453704</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>30.42373050979764</v>
+        <v>29.601549928347833</v>
       </c>
       <c r="T28" s="30">
-        <v>46308.33094087963</v>
+        <v>46309.265800393514</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46308.33094678241</v>
+        <v>46309.26580622685</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46308.330953599536</v>
+        <v>46309.26581232639</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46308.33095909723</v>
+        <v>46309.26581778935</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46308.33096486111</v>
+        <v>46309.26582369213</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46308.33097224537</v>
+        <v>46309.26582945602</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>738.9163547567102</v>
+        <v>766.5280324075927</v>
       </c>
       <c r="T34" s="30">
-        <v>46308.33097574074</v>
+        <v>46309.26583506945</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46308.33098119213</v>
+        <v>46309.2658409838</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46308.330987835645</v>
+        <v>46309.265846759256</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46308.3309934375</v>
+        <v>46309.265852557866</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>154.1622465523108</v>
+        <v>152.98137043767863</v>
       </c>
       <c r="T38" s="30">
-        <v>46308.33100005787</v>
+        <v>46309.26585829861</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>962.8710394107404</v>
+        <v>950.7371366354705</v>
       </c>
       <c r="T39" s="30">
-        <v>46308.331004733795</v>
+        <v>46309.26586413194</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46308.33101648148</v>
+        <v>46309.26587565972</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46308.331022847226</v>
+        <v>46309.265881643514</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>224.8453793959288</v>
+        <v>228.6864837601774</v>
       </c>
       <c r="T42" s="30">
-        <v>46308.33101052084</v>
+        <v>46309.26586987269</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46308.33102848379</v>
+        <v>46309.265887187496</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46308.331033622686</v>
+        <v>46309.265893055555</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>743.2697504053162</v>
+        <v>742.5205549640137</v>
       </c>
       <c r="T45" s="30">
-        <v>46308.33103934027</v>
+        <v>46309.265898958336</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>49.498608914953664</v>
+        <v>49.57609139453522</v>
       </c>
       <c r="T46" s="30">
-        <v>46308.3310456713</v>
+        <v>46309.26590460648</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>156.60214967674784</v>
+        <v>155.78341032271493</v>
       </c>
       <c r="T47" s="30">
-        <v>46308.33105152778</v>
+        <v>46309.26591059028</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46308.331057476855</v>
+        <v>46309.265916145836</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.14467284481896</v>
+        <v>101.60396768847721</v>
       </c>
       <c r="T49" s="30">
-        <v>46308.3310621875</v>
+        <v>46309.265922060185</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46308.33106935185</v>
+        <v>46309.26592773148</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46308.331074050926</v>
+        <v>46309.265933703704</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46308.331080185184</v>
+        <v>46309.26593930556</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46308.33108677083</v>
+        <v>46309.26594515046</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46308.331091851855</v>
+        <v>46309.26595091435</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>162.82700506394988</v>
+        <v>157.5046633949515</v>
       </c>
       <c r="T55" s="30">
-        <v>46308.33109756944</v>
+        <v>46309.26595664352</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>780.1785392606233</v>
+        <v>780.8984941037075</v>
       </c>
       <c r="T56" s="30">
-        <v>46308.331103749995</v>
+        <v>46309.26596253472</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>375.06254878805464</v>
+        <v>374.92294390316147</v>
       </c>
       <c r="T57" s="30">
-        <v>46308.33110959491</v>
+        <v>46309.26596834491</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46308.33111557871</v>
+        <v>46309.26597408565</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46308.331120856485</v>
+        <v>46309.26597988426</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46308.33112726852</v>
+        <v>46309.26598564815</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46308.331132430554</v>
+        <v>46309.26599140046</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46308.331138483794</v>
+        <v>46309.26599721065</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0007806088749225</v>
+        <v>1.0007285303701094</v>
       </c>
       <c r="T63" s="156">
-        <v>46308.3311437963</v>
+        <v>46309.266003055556</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2506.62482287105</v>
+        <v>2349.7953631665714</v>
       </c>
       <c r="T9" s="29">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>342.7295070811551</v>
+        <v>346.19607701831774</v>
       </c>
       <c r="T10" s="30">
-        <v>46309.26569613426</v>
+        <v>46310.25333003472</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46309.26570200231</v>
+        <v>46310.25333579861</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46309.26570802083</v>
+        <v>46310.25334159723</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46309.26571346065</v>
+        <v>46310.25334739583</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46309.26571925926</v>
+        <v>46310.25335319444</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46309.26572502315</v>
+        <v>46310.25335899305</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46309.26573083334</v>
+        <v>46310.25336476852</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46309.265736643516</v>
+        <v>46310.253370543986</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>181.9924905331081</v>
+        <v>169.7449771641509</v>
       </c>
       <c r="T18" s="30">
-        <v>46309.265742615746</v>
+        <v>46310.25337636574</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46309.26574819445</v>
+        <v>46310.25338216435</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46309.2657540625</v>
+        <v>46310.25338795139</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46309.26575983797</v>
+        <v>46310.25339377315</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>7.745638825064647</v>
+        <v>7.176552192151434</v>
       </c>
       <c r="T22" s="30">
-        <v>46309.265765682874</v>
+        <v>46310.25339953703</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46309.265771377315</v>
+        <v>46310.25340533565</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46309.26577738426</v>
+        <v>46310.253411122685</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>382.0281164687893</v>
+        <v>377.78491762979604</v>
       </c>
       <c r="T25" s="30">
-        <v>46309.26578310185</v>
+        <v>46310.25341695602</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46309.26578883102</v>
+        <v>46310.25342270834</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>353.35724407368565</v>
+        <v>340.45083160925924</v>
       </c>
       <c r="T27" s="30">
-        <v>46309.26579453704</v>
+        <v>46310.25342850694</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.601549928347833</v>
+        <v>27.91548683948445</v>
       </c>
       <c r="T28" s="30">
-        <v>46309.265800393514</v>
+        <v>46310.25343428241</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46309.26580622685</v>
+        <v>46310.25344006945</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46309.26581232639</v>
+        <v>46310.253445856484</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46309.26581778935</v>
+        <v>46310.253451979166</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46309.26582369213</v>
+        <v>46310.253457789346</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46309.26582945602</v>
+        <v>46310.25346356481</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>766.5280324075927</v>
+        <v>727.4942022066148</v>
       </c>
       <c r="T34" s="30">
-        <v>46309.26583506945</v>
+        <v>46310.25346936342</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46309.2658409838</v>
+        <v>46310.253475185185</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46309.265846759256</v>
+        <v>46310.25348136574</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46309.265852557866</v>
+        <v>46310.253486747686</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>152.98137043767863</v>
+        <v>139.15404764550033</v>
       </c>
       <c r="T38" s="30">
-        <v>46309.26585829861</v>
+        <v>46310.25349258102</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>950.7371366354705</v>
+        <v>876.059842636327</v>
       </c>
       <c r="T39" s="30">
-        <v>46309.26586413194</v>
+        <v>46310.25349836805</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46309.26587565972</v>
+        <v>46310.25350996528</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46309.265881643514</v>
+        <v>46310.25351590278</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>228.6864837601774</v>
+        <v>218.82979159973056</v>
       </c>
       <c r="T42" s="30">
-        <v>46309.26586987269</v>
+        <v>46310.25350415509</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46309.265887187496</v>
+        <v>46310.2535215162</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46309.265893055555</v>
+        <v>46310.253527291665</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>742.5205549640137</v>
+        <v>721.0983628052413</v>
       </c>
       <c r="T45" s="30">
-        <v>46309.265898958336</v>
+        <v>46310.2535330787</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>49.57609139453522</v>
+        <v>47.03294107520166</v>
       </c>
       <c r="T46" s="30">
-        <v>46309.26590460648</v>
+        <v>46310.253538888894</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.78341032271493</v>
+        <v>146.3836482708713</v>
       </c>
       <c r="T47" s="30">
-        <v>46309.26591059028</v>
+        <v>46310.25354471065</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46309.265916145836</v>
+        <v>46310.253550636575</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.60396768847721</v>
+        <v>100.71195001035947</v>
       </c>
       <c r="T49" s="30">
-        <v>46309.265922060185</v>
+        <v>46310.253556261574</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46309.26592773148</v>
+        <v>46310.25356200231</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46309.265933703704</v>
+        <v>46310.25356784723</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46309.26593930556</v>
+        <v>46310.253573622686</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46309.26594515046</v>
+        <v>46310.253579421296</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46309.26595091435</v>
+        <v>46310.25358520833</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>157.5046633949515</v>
+        <v>148.9159602717281</v>
       </c>
       <c r="T55" s="30">
-        <v>46309.26595664352</v>
+        <v>46310.25359100694</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>780.8984941037075</v>
+        <v>768.3515049239957</v>
       </c>
       <c r="T56" s="30">
-        <v>46309.26596253472</v>
+        <v>46310.25359678241</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>374.92294390316147</v>
+        <v>361.421978266157</v>
       </c>
       <c r="T57" s="30">
-        <v>46309.26596834491</v>
+        <v>46310.25360260416</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46309.26597408565</v>
+        <v>46310.25360833333</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46309.26597988426</v>
+        <v>46310.253614166664</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46309.26598564815</v>
+        <v>46310.253619918985</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46309.26599140046</v>
+        <v>46310.253625983794</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46309.26599721065</v>
+        <v>46310.2536314699</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0007285303701094</v>
+        <v>1.000913834330744</v>
       </c>
       <c r="T63" s="156">
-        <v>46309.266003055556</v>
+        <v>46310.25363732639</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2349.7953631665714</v>
+        <v>2446.998889033459</v>
       </c>
       <c r="T9" s="29">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>346.19607701831774</v>
+        <v>341.82738982915134</v>
       </c>
       <c r="T10" s="30">
-        <v>46310.25333003472</v>
+        <v>46311.25135605324</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46310.25333579861</v>
+        <v>46311.25136068287</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46310.25334159723</v>
+        <v>46311.25136646991</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46310.25334739583</v>
+        <v>46311.25137319444</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46310.25335319444</v>
+        <v>46311.25137798611</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46310.25335899305</v>
+        <v>46311.25138451389</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46310.25336476852</v>
+        <v>46311.251390335645</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46310.253370543986</v>
+        <v>46311.251395011575</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>169.7449771641509</v>
+        <v>182.16378249076698</v>
       </c>
       <c r="T18" s="30">
-        <v>46310.25337636574</v>
+        <v>46311.25140116898</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46310.25338216435</v>
+        <v>46311.25140690972</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46310.25338795139</v>
+        <v>46311.25141341435</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46310.25339377315</v>
+        <v>46311.25141857639</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>7.176552192151434</v>
+        <v>7.426461021088347</v>
       </c>
       <c r="T22" s="30">
-        <v>46310.25339953703</v>
+        <v>46311.251424594906</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46310.25340533565</v>
+        <v>46311.25143076389</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46310.253411122685</v>
+        <v>46311.25143657407</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>377.78491762979604</v>
+        <v>382.60286449210815</v>
       </c>
       <c r="T25" s="30">
-        <v>46310.25341695602</v>
+        <v>46311.25144170139</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46310.25342270834</v>
+        <v>46311.25144741898</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>340.45083160925924</v>
+        <v>349.309098916057</v>
       </c>
       <c r="T27" s="30">
-        <v>46310.25342850694</v>
+        <v>46311.25145326389</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>27.91548683948445</v>
+        <v>29.295487073754167</v>
       </c>
       <c r="T28" s="30">
-        <v>46310.25343428241</v>
+        <v>46311.251458645835</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46310.25344006945</v>
+        <v>46311.25146486111</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46310.253445856484</v>
+        <v>46311.25147134259</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46310.253451979166</v>
+        <v>46311.251477233796</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46310.253457789346</v>
+        <v>46311.25148182871</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46310.25346356481</v>
+        <v>46311.25148868056</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>727.4942022066148</v>
+        <v>737.2013651877132</v>
       </c>
       <c r="T34" s="30">
-        <v>46310.25346936342</v>
+        <v>46311.2514937963</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46310.253475185185</v>
+        <v>46311.25149917824</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46310.25348136574</v>
+        <v>46311.25150601852</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46310.253486747686</v>
+        <v>46311.25151188657</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>139.15404764550033</v>
+        <v>148.0588111657142</v>
       </c>
       <c r="T38" s="30">
-        <v>46310.25349258102</v>
+        <v>46311.251516932876</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>876.059842636327</v>
+        <v>927.0365217739434</v>
       </c>
       <c r="T39" s="30">
-        <v>46310.25349836805</v>
+        <v>46311.25152340278</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46310.25350996528</v>
+        <v>46311.25153483797</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46310.25351590278</v>
+        <v>46311.251540729165</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>218.82979159973056</v>
+        <v>219.330817811496</v>
       </c>
       <c r="T42" s="30">
-        <v>46310.25350415509</v>
+        <v>46311.25152851852</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46310.2535215162</v>
+        <v>46311.25154660879</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46310.253527291665</v>
+        <v>46311.251551678244</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>721.0983628052413</v>
+        <v>730.7657662166084</v>
       </c>
       <c r="T45" s="30">
-        <v>46310.2535330787</v>
+        <v>46311.25155738426</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>47.03294107520166</v>
+        <v>51.22456537187353</v>
       </c>
       <c r="T46" s="30">
-        <v>46310.253538888894</v>
+        <v>46311.251563680555</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>146.3836482708713</v>
+        <v>159.4186942640097</v>
       </c>
       <c r="T47" s="30">
-        <v>46310.25354471065</v>
+        <v>46311.251568935186</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46310.253550636575</v>
+        <v>46311.25157505787</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.71195001035947</v>
+        <v>101.30813808012971</v>
       </c>
       <c r="T49" s="30">
-        <v>46310.253556261574</v>
+        <v>46311.25158077546</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46310.25356200231</v>
+        <v>46311.25158704861</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46310.25356784723</v>
+        <v>46311.25159273148</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46310.253573622686</v>
+        <v>46311.25159865741</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46310.253579421296</v>
+        <v>46311.25160378472</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46310.25358520833</v>
+        <v>46311.251610300926</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.9159602717281</v>
+        <v>152.4526337913985</v>
       </c>
       <c r="T55" s="30">
-        <v>46310.25359100694</v>
+        <v>46311.25161550926</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>768.3515049239957</v>
+        <v>774.9942449931441</v>
       </c>
       <c r="T56" s="30">
-        <v>46310.25359678241</v>
+        <v>46311.251621145835</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>361.421978266157</v>
+        <v>375.56674306646784</v>
       </c>
       <c r="T57" s="30">
-        <v>46310.25360260416</v>
+        <v>46311.251627094905</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46310.25360833333</v>
+        <v>46311.2516334375</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46310.253614166664</v>
+        <v>46311.251639155096</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46310.253619918985</v>
+        <v>46311.251645717595</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46310.253625983794</v>
+        <v>46311.25165060185</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46310.2536314699</v>
+        <v>46311.251656458335</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.000913834330744</v>
+        <v>1.0008707575590765</v>
       </c>
       <c r="T63" s="156">
-        <v>46310.25363732639</v>
+        <v>46311.251661828705</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2446.998889033459</v>
+        <v>2427.3814683974124</v>
       </c>
       <c r="T9" s="29">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>341.82738982915134</v>
+        <v>343.199329698194</v>
       </c>
       <c r="T10" s="30">
-        <v>46311.25135605324</v>
+        <v>46312.24195334491</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46311.25136068287</v>
+        <v>46312.24195913195</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46311.25136646991</v>
+        <v>46312.24196490741</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46311.25137319444</v>
+        <v>46312.24197072916</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46311.25137798611</v>
+        <v>46312.241977337966</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46311.25138451389</v>
+        <v>46312.24198252315</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46311.251390335645</v>
+        <v>46312.24198805555</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46311.251395011575</v>
+        <v>46312.24199482639</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>182.16378249076698</v>
+        <v>173.56171911991856</v>
       </c>
       <c r="T18" s="30">
-        <v>46311.25140116898</v>
+        <v>46312.242000578706</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46311.25140690972</v>
+        <v>46312.242006238426</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46311.25141341435</v>
+        <v>46312.242012013885</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46311.25141857639</v>
+        <v>46312.24201770833</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>7.426461021088347</v>
+        <v>7.014043703757835</v>
       </c>
       <c r="T22" s="30">
-        <v>46311.251424594906</v>
+        <v>46312.24202355324</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46311.25143076389</v>
+        <v>46312.242029444446</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46311.25143657407</v>
+        <v>46312.24203508101</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>382.60286449210815</v>
+        <v>382.81080291064745</v>
       </c>
       <c r="T25" s="30">
-        <v>46311.25144170139</v>
+        <v>46312.24204105324</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46311.25144741898</v>
+        <v>46312.24204697917</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>349.309098916057</v>
+        <v>342.3874796912367</v>
       </c>
       <c r="T27" s="30">
-        <v>46311.25145326389</v>
+        <v>46312.24205248843</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.295487073754167</v>
+        <v>28.12945153575794</v>
       </c>
       <c r="T28" s="30">
-        <v>46311.251458645835</v>
+        <v>46312.242057557865</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46311.25146486111</v>
+        <v>46312.24206402778</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46311.25147134259</v>
+        <v>46312.242069224536</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46311.251477233796</v>
+        <v>46312.24207561343</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46311.25148182871</v>
+        <v>46312.242081446755</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46311.25148868056</v>
+        <v>46312.242087280094</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>737.2013651877132</v>
+        <v>709.552901888277</v>
       </c>
       <c r="T34" s="30">
-        <v>46311.2514937963</v>
+        <v>46312.24209231482</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46311.25149917824</v>
+        <v>46312.24209940972</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46311.25150601852</v>
+        <v>46312.24210471065</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46311.25151188657</v>
+        <v>46312.24210978009</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>148.0588111657142</v>
+        <v>137.1756228771524</v>
       </c>
       <c r="T38" s="30">
-        <v>46311.251516932876</v>
+        <v>46312.24211550926</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6773,10 +6773,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
       <c r="S39" s="27">
-        <v>927.0365217739434</v>
+        <v>878.109380521406</v>
       </c>
       <c r="T39" s="30">
-        <v>46311.25152340278</v>
+        <v>46312.24212196759</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46311.25153483797</v>
+        <v>46312.242133796295</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46311.251540729165</v>
+        <v>46312.242139375</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>219.330817811496</v>
+        <v>214.79489025009184</v>
       </c>
       <c r="T42" s="30">
-        <v>46311.25152851852</v>
+        <v>46312.242127129626</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46311.25154660879</v>
+        <v>46312.24214512732</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46311.251551678244</v>
+        <v>46312.24215091435</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>730.7657662166084</v>
+        <v>711.0344530723668</v>
       </c>
       <c r="T45" s="30">
-        <v>46311.25155738426</v>
+        <v>46312.24215677083</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>51.22456537187353</v>
+        <v>49.67200659090067</v>
       </c>
       <c r="T46" s="30">
-        <v>46311.251563680555</v>
+        <v>46312.2421628125</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7325,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>159.4186942640097</v>
+        <v>156.06339837810188</v>
       </c>
       <c r="T47" s="30">
-        <v>46311.251568935186</v>
+        <v>46312.24216834491</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46311.25157505787</v>
+        <v>46312.242174120365</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7463,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.30813808012971</v>
+        <v>101.83662294422261</v>
       </c>
       <c r="T49" s="30">
-        <v>46311.25158077546</v>
+        <v>46312.24218016204</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46311.25158704861</v>
+        <v>46312.242185625</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46311.25159273148</v>
+        <v>46312.24219096065</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7676,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46311.25159865741</v>
+        <v>46312.24219722222</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46311.25160378472</v>
+        <v>46312.24220302083</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7816,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46311.251610300926</v>
+        <v>46312.24220898148</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7881,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>152.4526337913985</v>
+        <v>145.95281259478676</v>
       </c>
       <c r="T55" s="30">
-        <v>46311.25161550926</v>
+        <v>46312.24221428241</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7949,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>774.9942449931441</v>
+        <v>763.7196144363148</v>
       </c>
       <c r="T56" s="30">
-        <v>46311.251621145835</v>
+        <v>46312.24221972222</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8017,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>375.56674306646784</v>
+        <v>352.69927614212077</v>
       </c>
       <c r="T57" s="30">
-        <v>46311.251627094905</v>
+        <v>46312.24222591435</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46311.2516334375</v>
+        <v>46312.242231979166</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46311.251639155096</v>
+        <v>46312.24223751158</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46311.251645717595</v>
+        <v>46312.24224288194</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8300,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46311.25165060185</v>
+        <v>46312.24224939815</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46311.251656458335</v>
+        <v>46312.24225538194</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8433,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0008707575590765</v>
+        <v>1.0010480973579339</v>
       </c>
       <c r="T63" s="156">
-        <v>46311.251661828705</v>
+        <v>46312.24226126158</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2427.3814683974124</v>
+        <v>2412.0898753599427</v>
       </c>
       <c r="T9" s="29">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>343.199329698194</v>
+        <v>342.9828538599583</v>
       </c>
       <c r="T10" s="30">
-        <v>46312.24195334491</v>
+        <v>46313.25849086806</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46312.24195913195</v>
+        <v>46313.25849767361</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46312.24196490741</v>
+        <v>46313.25850315972</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46312.24197072916</v>
+        <v>46313.2585090625</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46312.241977337966</v>
+        <v>46313.258514560184</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46312.24198252315</v>
+        <v>46313.258520324074</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46312.24198805555</v>
+        <v>46313.258525763886</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46312.24199482639</v>
+        <v>46313.2585321875</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>173.56171911991856</v>
+        <v>173.01277027615384</v>
       </c>
       <c r="T18" s="30">
-        <v>46312.242000578706</v>
+        <v>46313.25853792824</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46312.242006238426</v>
+        <v>46313.25854349537</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46312.242012013885</v>
+        <v>46313.258549687496</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46312.24201770833</v>
+        <v>46313.25855521991</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>7.014043703757835</v>
+        <v>7.015094328291881</v>
       </c>
       <c r="T22" s="30">
-        <v>46312.24202355324</v>
+        <v>46313.2585603125</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46312.242029444446</v>
+        <v>46313.258567083336</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46312.24203508101</v>
+        <v>46313.25857269676</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>382.81080291064745</v>
+        <v>382.5878250495187</v>
       </c>
       <c r="T25" s="30">
-        <v>46312.24204105324</v>
+        <v>46313.258578182875</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46312.24204697917</v>
+        <v>46313.2585833912</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>342.3874796912367</v>
+        <v>342.15212032224457</v>
       </c>
       <c r="T27" s="30">
-        <v>46312.24205248843</v>
+        <v>46313.25858914352</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.12945153575794</v>
+        <v>27.77452490549155</v>
       </c>
       <c r="T28" s="30">
-        <v>46312.242057557865</v>
+        <v>46313.25859489583</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46312.24206402778</v>
+        <v>46313.25860164352</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46312.242069224536</v>
+        <v>46313.258607488424</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46312.24207561343</v>
+        <v>46313.25861315972</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46312.242081446755</v>
+        <v>46313.25861827546</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46312.242087280094</v>
+        <v>46313.258624780094</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>709.552901888277</v>
+        <v>705.718149125678</v>
       </c>
       <c r="T34" s="30">
-        <v>46312.24209231482</v>
+        <v>46313.258629791664</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46312.24209940972</v>
+        <v>46313.25863630787</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46312.24210471065</v>
+        <v>46313.25864125</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46312.24210978009</v>
+        <v>46313.25864789352</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>137.1756228771524</v>
+        <v>136.36040623870878</v>
       </c>
       <c r="T38" s="30">
-        <v>46312.24211550926</v>
+        <v>46313.25865285879</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6772,20 +6772,22 @@
       <c r="R39" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0xfF080c8ce2E5feadaCa0Da81314Ae59D232d4afD</v>
       </c>
-      <c r="S39" s="27">
-        <v>878.109380521406</v>
+      <c r="S39" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T39" s="30">
-        <v>46312.24212196759</v>
+        <v>46313.258659548614</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x301f48ec369bb3bfa0bc04d44a79037aa0ee2340</t>
+          <t/>
         </is>
       </c>
       <c r="V39" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46312.242133796295</v>
+        <v>46313.25867141204</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46312.242139375</v>
+        <v>46313.25867697917</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>214.79489025009184</v>
+        <v>213.42845732782047</v>
       </c>
       <c r="T42" s="30">
-        <v>46312.242127129626</v>
+        <v>46313.258664444445</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46312.24214512732</v>
+        <v>46313.258682893524</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46312.24215091435</v>
+        <v>46313.2586883912</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>711.0344530723668</v>
+        <v>706.313674975003</v>
       </c>
       <c r="T45" s="30">
-        <v>46312.24215677083</v>
+        <v>46313.25869400463</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>49.67200659090067</v>
+        <v>49.693879695771365</v>
       </c>
       <c r="T46" s="30">
-        <v>46312.2421628125</v>
+        <v>46313.25870006944</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>156.06339837810188</v>
+        <v>154.73663244645022</v>
       </c>
       <c r="T47" s="30">
-        <v>46312.24216834491</v>
+        <v>46313.25870557871</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7398,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46312.242174120365</v>
+        <v>46313.258711898154</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7463,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.83662294422261</v>
+        <v>102.28031351683536</v>
       </c>
       <c r="T49" s="30">
-        <v>46312.24218016204</v>
+        <v>46313.25871740741</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7536,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46312.242185625</v>
+        <v>46313.258723101855</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7606,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46312.24219096065</v>
+        <v>46313.25872863426</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7676,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46312.24219722222</v>
+        <v>46313.25873475694</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7746,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46312.24220302083</v>
+        <v>46313.25874107639</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7816,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46312.24220898148</v>
+        <v>46313.25874640046</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7881,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>145.95281259478676</v>
+        <v>144.6076885890241</v>
       </c>
       <c r="T55" s="30">
-        <v>46312.24221428241</v>
+        <v>46313.25875212963</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7949,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>763.7196144363148</v>
+        <v>762.413210865194</v>
       </c>
       <c r="T56" s="30">
-        <v>46312.24221972222</v>
+        <v>46313.2587570949</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8017,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>352.69927614212077</v>
+        <v>350.119155214054</v>
       </c>
       <c r="T57" s="30">
-        <v>46312.24222591435</v>
+        <v>46313.2587628125</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8090,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46312.242231979166</v>
+        <v>46313.25876951389</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8160,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46312.24223751158</v>
+        <v>46313.25877541667</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8230,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46312.24224288194</v>
+        <v>46313.25878092593</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8300,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46312.24224939815</v>
+        <v>46313.25878685185</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8370,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46312.24225538194</v>
+        <v>46313.258792569446</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8433,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0010480973579339</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="T63" s="156">
-        <v>46312.24226126158</v>
+        <v>46313.258798449075</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2412.0898753599427</v>
+        <v>2431.997550380802</v>
       </c>
       <c r="T9" s="29">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>342.9828538599583</v>
+        <v>344.81792464819245</v>
       </c>
       <c r="T10" s="30">
-        <v>46313.25849086806</v>
+        <v>46314.26811681713</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46313.25849767361</v>
+        <v>46314.268123344904</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46313.25850315972</v>
+        <v>46314.26812824074</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46313.2585090625</v>
+        <v>46314.2681353588</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46313.258514560184</v>
+        <v>46314.26814075231</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46313.258520324074</v>
+        <v>46314.26814642361</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46313.258525763886</v>
+        <v>46314.26815157408</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46313.2585321875</v>
+        <v>46314.268158125</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>173.01277027615384</v>
+        <v>176.68678996816897</v>
       </c>
       <c r="T18" s="30">
-        <v>46313.25853792824</v>
+        <v>46314.26816309027</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46313.25854349537</v>
+        <v>46314.26816939815</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46313.258549687496</v>
+        <v>46314.268175694444</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46313.25855521991</v>
+        <v>46314.26818115741</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>7.015094328291881</v>
+        <v>7.077678345386301</v>
       </c>
       <c r="T22" s="30">
-        <v>46313.2585603125</v>
+        <v>46314.26818695602</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46313.258567083336</v>
+        <v>46314.268192951386</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46313.25857269676</v>
+        <v>46314.268198437494</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>382.5878250495187</v>
+        <v>385.7249642013371</v>
       </c>
       <c r="T25" s="30">
-        <v>46313.258578182875</v>
+        <v>46314.268204444445</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46313.2585833912</v>
+        <v>46314.26820921296</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>342.15212032224457</v>
+        <v>345.2181892230765</v>
       </c>
       <c r="T27" s="30">
-        <v>46313.25858914352</v>
+        <v>46314.26821524306</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>27.77452490549155</v>
+        <v>28.28869882992658</v>
       </c>
       <c r="T28" s="30">
-        <v>46313.25859489583</v>
+        <v>46314.26822175926</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46313.25860164352</v>
+        <v>46314.26822751157</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46313.258607488424</v>
+        <v>46314.26823371528</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46313.25861315972</v>
+        <v>46314.2682390162</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46313.25861827546</v>
+        <v>46314.26824496528</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46313.258624780094</v>
+        <v>46314.268250636575</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>705.718149125678</v>
+        <v>720.547281753239</v>
       </c>
       <c r="T34" s="30">
-        <v>46313.258629791664</v>
+        <v>46314.268255636576</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46313.25863630787</v>
+        <v>46314.26826211806</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46313.25864125</v>
+        <v>46314.26826806713</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46313.25864789352</v>
+        <v>46314.26827385417</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.36040623870878</v>
+        <v>139.56225064767813</v>
       </c>
       <c r="T38" s="30">
-        <v>46313.25865285879</v>
+        <v>46314.26827875</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46313.258659548614</v>
+        <v>46314.26828447916</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46313.25867141204</v>
+        <v>46314.26829611111</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46313.25867697917</v>
+        <v>46314.26830251157</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>213.42845732782047</v>
+        <v>218.4143718998258</v>
       </c>
       <c r="T42" s="30">
-        <v>46313.258664444445</v>
+        <v>46314.26829127315</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46313.258682893524</v>
+        <v>46314.26830855324</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46313.2586883912</v>
+        <v>46314.26831429398</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>706.313674975003</v>
+        <v>721.9472071038957</v>
       </c>
       <c r="T45" s="30">
-        <v>46313.25869400463</v>
+        <v>46314.26831918981</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>49.693879695771365</v>
+        <v>50.00305201738349</v>
       </c>
       <c r="T46" s="30">
-        <v>46313.25870006944</v>
+        <v>46314.268325868055</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>154.73663244645022</v>
+        <v>158.35467243848183</v>
       </c>
       <c r="T47" s="30">
-        <v>46313.25870557871</v>
+        <v>46314.26833146991</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46313.258711898154</v>
+        <v>46314.268337500005</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.28031351683536</v>
+        <v>101.87734092234967</v>
       </c>
       <c r="T49" s="30">
-        <v>46313.25871740741</v>
+        <v>46314.268342361116</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46313.258723101855</v>
+        <v>46314.26835085648</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46313.25872863426</v>
+        <v>46314.26835457176</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46313.25873475694</v>
+        <v>46314.268360891205</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46313.25874107639</v>
+        <v>46314.26836637731</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46313.25874640046</v>
+        <v>46314.26837131944</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>144.6076885890241</v>
+        <v>148.40809775261448</v>
       </c>
       <c r="T55" s="30">
-        <v>46313.25875212963</v>
+        <v>46314.268378252316</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>762.413210865194</v>
+        <v>771.6090335711906</v>
       </c>
       <c r="T56" s="30">
-        <v>46313.2587570949</v>
+        <v>46314.26838291666</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>350.119155214054</v>
+        <v>358.5069731092252</v>
       </c>
       <c r="T57" s="30">
-        <v>46313.2587628125</v>
+        <v>46314.268388715274</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46313.25876951389</v>
+        <v>46314.26839540509</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46313.25877541667</v>
+        <v>46314.26840123843</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46313.25878092593</v>
+        <v>46314.26840689815</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46313.25878685185</v>
+        <v>46314.26841285879</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46313.258792569446</v>
+        <v>46314.26841777778</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.000883780378074</v>
+        <v>1.0006614372099958</v>
       </c>
       <c r="T63" s="156">
-        <v>46313.258798449075</v>
+        <v>46314.268424375005</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2431.997550380802</v>
+        <v>2394.194799658141</v>
       </c>
       <c r="T9" s="29">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>344.81792464819245</v>
+        <v>343.76057051244845</v>
       </c>
       <c r="T10" s="30">
-        <v>46314.26811681713</v>
+        <v>46315.25977709491</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46314.268123344904</v>
+        <v>46315.25978210648</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46314.26812824074</v>
+        <v>46315.25978784722</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46314.2681353588</v>
+        <v>46315.25979398148</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46314.26814075231</v>
+        <v>46315.25979974537</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46314.26814642361</v>
+        <v>46315.259805960646</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46314.26815157408</v>
+        <v>46315.25981106482</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46314.268158125</v>
+        <v>46315.259817314814</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>176.68678996816897</v>
+        <v>168.50772885847474</v>
       </c>
       <c r="T18" s="30">
-        <v>46314.26816309027</v>
+        <v>46315.25982346065</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46314.26816939815</v>
+        <v>46315.259829201386</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46314.268175694444</v>
+        <v>46315.25983454861</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46314.26818115741</v>
+        <v>46315.25983993056</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>7.077678345386301</v>
+        <v>6.454892808749032</v>
       </c>
       <c r="T22" s="30">
-        <v>46314.26818695602</v>
+        <v>46315.25984627315</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46314.268192951386</v>
+        <v>46315.25985236111</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46314.268198437494</v>
+        <v>46315.25985826389</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>385.7249642013371</v>
+        <v>378.1666503209433</v>
       </c>
       <c r="T25" s="30">
-        <v>46314.268204444445</v>
+        <v>46315.25986403935</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46314.26820921296</v>
+        <v>46315.259869166664</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>345.2181892230765</v>
+        <v>346.792868994698</v>
       </c>
       <c r="T27" s="30">
-        <v>46314.26821524306</v>
+        <v>46315.2598746875</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.28869882992658</v>
+        <v>28.34148284399575</v>
       </c>
       <c r="T28" s="30">
-        <v>46314.26822175926</v>
+        <v>46315.259880949074</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46314.26822751157</v>
+        <v>46315.25988626157</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46314.26823371528</v>
+        <v>46315.25989203704</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46314.2682390162</v>
+        <v>46315.25989857639</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46314.26824496528</v>
+        <v>46315.25990361111</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46314.268250636575</v>
+        <v>46315.259909432876</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>720.547281753239</v>
+        <v>703.0128837658946</v>
       </c>
       <c r="T34" s="30">
-        <v>46314.268255636576</v>
+        <v>46315.25991620371</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46314.26826211806</v>
+        <v>46315.2599219213</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46314.26826806713</v>
+        <v>46315.25992699074</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46314.26827385417</v>
+        <v>46315.259932650464</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>139.56225064767813</v>
+        <v>136.90377305997947</v>
       </c>
       <c r="T38" s="30">
-        <v>46314.26827875</v>
+        <v>46315.25993835648</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46314.26828447916</v>
+        <v>46315.25994416667</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46314.26829611111</v>
+        <v>46315.259956145834</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46314.26830251157</v>
+        <v>46315.25996207176</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>218.4143718998258</v>
+        <v>216.89440595971746</v>
       </c>
       <c r="T42" s="30">
-        <v>46314.26829127315</v>
+        <v>46315.25995063657</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46314.26830855324</v>
+        <v>46315.259967962964</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46314.26831429398</v>
+        <v>46315.259973113425</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>721.9472071038957</v>
+        <v>714.8918880511428</v>
       </c>
       <c r="T45" s="30">
-        <v>46314.26831918981</v>
+        <v>46315.25997905093</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>50.00305201738349</v>
+        <v>50.51829286599242</v>
       </c>
       <c r="T46" s="30">
-        <v>46314.268325868055</v>
+        <v>46315.259985069446</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>158.35467243848183</v>
+        <v>154.28694950772686</v>
       </c>
       <c r="T47" s="30">
-        <v>46314.26833146991</v>
+        <v>46315.259990555554</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46314.268337500005</v>
+        <v>46315.25999626157</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.87734092234967</v>
+        <v>101.71710156298475</v>
       </c>
       <c r="T49" s="30">
-        <v>46314.268342361116</v>
+        <v>46315.26000238426</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46314.26835085648</v>
+        <v>46315.26000877315</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46314.26835457176</v>
+        <v>46315.26001380787</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46314.268360891205</v>
+        <v>46315.26001939815</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46314.26836637731</v>
+        <v>46315.260025173615</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46314.26837131944</v>
+        <v>46315.26003190972</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.40809775261448</v>
+        <v>147.3817153402279</v>
       </c>
       <c r="T55" s="30">
-        <v>46314.268378252316</v>
+        <v>46315.260037175925</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>771.6090335711906</v>
+        <v>768.4124566421348</v>
       </c>
       <c r="T56" s="30">
-        <v>46314.26838291666</v>
+        <v>46315.260042581016</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>358.5069731092252</v>
+        <v>365.2368495319452</v>
       </c>
       <c r="T57" s="30">
-        <v>46314.268388715274</v>
+        <v>46315.26004893519</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46314.26839540509</v>
+        <v>46315.26005413195</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46314.26840123843</v>
+        <v>46315.26006045139</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46314.26840689815</v>
+        <v>46315.260066469906</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46314.26841285879</v>
+        <v>46315.260074108795</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46314.26841777778</v>
+        <v>46315.260077314815</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0006614372099958</v>
+        <v>1.00075857499985</v>
       </c>
       <c r="T63" s="156">
-        <v>46314.268424375005</v>
+        <v>46315.2600841088</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2394.194799658141</v>
+        <v>2439.1916170961113</v>
       </c>
       <c r="T9" s="29">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>343.76057051244845</v>
+        <v>338.2408433350249</v>
       </c>
       <c r="T10" s="30">
-        <v>46315.25977709491</v>
+        <v>46316.25937076389</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46315.25978210648</v>
+        <v>46316.25937671296</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46315.25978784722</v>
+        <v>46316.25938186343</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46315.25979398148</v>
+        <v>46316.25938859954</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46315.25979974537</v>
+        <v>46316.25939436343</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46315.259805960646</v>
+        <v>46316.25939997685</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46315.25981106482</v>
+        <v>46316.25940498843</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46315.259817314814</v>
+        <v>46316.259411851854</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>168.50772885847474</v>
+        <v>172.35839736718043</v>
       </c>
       <c r="T18" s="30">
-        <v>46315.25982346065</v>
+        <v>46316.25941658565</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46315.259829201386</v>
+        <v>46316.259423206015</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46315.25983454861</v>
+        <v>46316.259428935184</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46315.25983993056</v>
+        <v>46316.25943399306</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.454892808749032</v>
+        <v>6.495969796242747</v>
       </c>
       <c r="T22" s="30">
-        <v>46315.25984627315</v>
+        <v>46316.2594405787</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46315.25985236111</v>
+        <v>46316.25944634259</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46315.25985826389</v>
+        <v>46316.25945197917</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>378.1666503209433</v>
+        <v>379.06836382635646</v>
       </c>
       <c r="T25" s="30">
-        <v>46315.25986403935</v>
+        <v>46316.259457893524</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46315.259869166664</v>
+        <v>46316.25946306713</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>346.792868994698</v>
+        <v>343.1753781725406</v>
       </c>
       <c r="T27" s="30">
-        <v>46315.2598746875</v>
+        <v>46316.259469386576</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.34148284399575</v>
+        <v>29.447061849840004</v>
       </c>
       <c r="T28" s="30">
-        <v>46315.259880949074</v>
+        <v>46316.25947482639</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46315.25988626157</v>
+        <v>46316.2594809838</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46315.25989203704</v>
+        <v>46316.25948674769</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46315.25989857639</v>
+        <v>46316.25949251157</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46315.25990361111</v>
+        <v>46316.25949833333</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46315.259909432876</v>
+        <v>46316.25950415509</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>703.0128837658946</v>
+        <v>699.1825487623125</v>
       </c>
       <c r="T34" s="30">
-        <v>46315.25991620371</v>
+        <v>46316.25950918981</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46315.2599219213</v>
+        <v>46316.2595159838</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46315.25992699074</v>
+        <v>46316.259521527776</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46315.259932650464</v>
+        <v>46316.259527511575</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.90377305997947</v>
+        <v>144.36266929308033</v>
       </c>
       <c r="T38" s="30">
-        <v>46315.25993835648</v>
+        <v>46316.25953239583</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46315.25994416667</v>
+        <v>46316.25953885417</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46315.259956145834</v>
+        <v>46316.25955076389</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46315.25996207176</v>
+        <v>46316.25955645833</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>216.89440595971746</v>
+        <v>220.84295467534662</v>
       </c>
       <c r="T42" s="30">
-        <v>46315.25995063657</v>
+        <v>46316.25954398148</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46315.259967962964</v>
+        <v>46316.25956196759</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46315.259973113425</v>
+        <v>46316.25956709491</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>714.8918880511428</v>
+        <v>721.503061313347</v>
       </c>
       <c r="T45" s="30">
-        <v>46315.25997905093</v>
+        <v>46316.25957368055</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>50.51829286599242</v>
+        <v>52.10688622844394</v>
       </c>
       <c r="T46" s="30">
-        <v>46315.259985069446</v>
+        <v>46316.259579722224</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>154.28694950772686</v>
+        <v>155.69308194230499</v>
       </c>
       <c r="T47" s="30">
-        <v>46315.259990555554</v>
+        <v>46316.25958527778</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46315.25999626157</v>
+        <v>46316.2595902199</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.71710156298475</v>
+        <v>101.65341949251362</v>
       </c>
       <c r="T49" s="30">
-        <v>46315.26000238426</v>
+        <v>46316.25959695602</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46315.26000877315</v>
+        <v>46316.25960251158</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46315.26001380787</v>
+        <v>46316.25960848379</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46315.26001939815</v>
+        <v>46316.25961440972</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46315.260025173615</v>
+        <v>46316.25961988426</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46315.26003190972</v>
+        <v>46316.259625833336</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>147.3817153402279</v>
+        <v>161.51843544217135</v>
       </c>
       <c r="T55" s="30">
-        <v>46315.260037175925</v>
+        <v>46316.25963172454</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>768.4124566421348</v>
+        <v>772.760166593099</v>
       </c>
       <c r="T56" s="30">
-        <v>46315.260042581016</v>
+        <v>46316.25963649306</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>365.2368495319452</v>
+        <v>379.80904451190645</v>
       </c>
       <c r="T57" s="30">
-        <v>46315.26004893519</v>
+        <v>46316.25964277778</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46315.26005413195</v>
+        <v>46316.259648784726</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46315.26006045139</v>
+        <v>46316.25965460648</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46315.260066469906</v>
+        <v>46316.25966053241</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46315.260074108795</v>
+        <v>46316.2596662037</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46315.260077314815</v>
+        <v>46316.259671921296</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.00075857499985</v>
+        <v>1.0009198453378656</v>
       </c>
       <c r="T63" s="156">
-        <v>46315.2600841088</v>
+        <v>46316.25967806713</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2439.1916170961113</v>
+        <v>2439.945559714188</v>
       </c>
       <c r="T9" s="29">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>338.2408433350249</v>
+        <v>344.1046374316995</v>
       </c>
       <c r="T10" s="30">
-        <v>46316.25937076389</v>
+        <v>46317.26181047454</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46316.25937671296</v>
+        <v>46317.26181625</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46316.25938186343</v>
+        <v>46317.26182208333</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46316.25938859954</v>
+        <v>46317.26182802083</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46316.25939436343</v>
+        <v>46317.26183354167</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46316.25939997685</v>
+        <v>46317.26183947917</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46316.25940498843</v>
+        <v>46317.26184513889</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46316.259411851854</v>
+        <v>46317.2618512037</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>172.35839736718043</v>
+        <v>172.16840461941837</v>
       </c>
       <c r="T18" s="30">
-        <v>46316.25941658565</v>
+        <v>46317.261856666664</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46316.259423206015</v>
+        <v>46317.2618625</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46316.259428935184</v>
+        <v>46317.26186833333</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46316.25943399306</v>
+        <v>46317.26187405093</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.495969796242747</v>
+        <v>6.544843183956127</v>
       </c>
       <c r="T22" s="30">
-        <v>46316.2594405787</v>
+        <v>46317.261879907404</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46316.25944634259</v>
+        <v>46317.261885671294</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46316.25945197917</v>
+        <v>46317.26189144676</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>379.06836382635646</v>
+        <v>374.3189960570822</v>
       </c>
       <c r="T25" s="30">
-        <v>46316.259457893524</v>
+        <v>46317.261897233795</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46316.25946306713</v>
+        <v>46317.26190309028</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>343.1753781725406</v>
+        <v>330.01421051578166</v>
       </c>
       <c r="T27" s="30">
-        <v>46316.259469386576</v>
+        <v>46317.26190880787</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>29.447061849840004</v>
+        <v>28.801312971598982</v>
       </c>
       <c r="T28" s="30">
-        <v>46316.25947482639</v>
+        <v>46317.26191469907</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46316.2594809838</v>
+        <v>46317.26192072917</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46316.25948674769</v>
+        <v>46317.2619262963</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46316.25949251157</v>
+        <v>46317.26193201389</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46316.25949833333</v>
+        <v>46317.26193774305</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46316.25950415509</v>
+        <v>46317.26194350694</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>699.1825487623125</v>
+        <v>705.3519604507336</v>
       </c>
       <c r="T34" s="30">
-        <v>46316.25950918981</v>
+        <v>46317.261949328706</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46316.2595159838</v>
+        <v>46317.26195533565</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46316.259521527776</v>
+        <v>46317.26196091435</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46316.259527511575</v>
+        <v>46317.261966736114</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>144.36266929308033</v>
+        <v>148.4298380801793</v>
       </c>
       <c r="T38" s="30">
-        <v>46316.25953239583</v>
+        <v>46317.26197251157</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46316.25953885417</v>
+        <v>46317.261978333336</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46316.25955076389</v>
+        <v>46317.261989907405</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46316.25955645833</v>
+        <v>46317.261995740744</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>220.84295467534662</v>
+        <v>218.2615135200048</v>
       </c>
       <c r="T42" s="30">
-        <v>46316.25954398148</v>
+        <v>46317.26198413195</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46316.25956196759</v>
+        <v>46317.262001435185</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46316.25956709491</v>
+        <v>46317.26200729166</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>721.503061313347</v>
+        <v>716.2200028020735</v>
       </c>
       <c r="T45" s="30">
-        <v>46316.25957368055</v>
+        <v>46317.26201319444</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>52.10688622844394</v>
+        <v>51.94844184696675</v>
       </c>
       <c r="T46" s="30">
-        <v>46316.259579722224</v>
+        <v>46317.26201914352</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>155.69308194230499</v>
+        <v>151.6121930228369</v>
       </c>
       <c r="T47" s="30">
-        <v>46316.25958527778</v>
+        <v>46317.2620246875</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46316.2595902199</v>
+        <v>46317.262030543985</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>101.65341949251362</v>
+        <v>100.5243880471549</v>
       </c>
       <c r="T49" s="30">
-        <v>46316.25959695602</v>
+        <v>46317.26203614583</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46316.25960251158</v>
+        <v>46317.26204203704</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46316.25960848379</v>
+        <v>46317.262047766206</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46316.25961440972</v>
+        <v>46317.262053576385</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46316.25961988426</v>
+        <v>46317.26205949074</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46316.259625833336</v>
+        <v>46317.26206519676</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>161.51843544217135</v>
+        <v>156.28565138202268</v>
       </c>
       <c r="T55" s="30">
-        <v>46316.25963172454</v>
+        <v>46317.262070902776</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>772.760166593099</v>
+        <v>770.0798590957309</v>
       </c>
       <c r="T56" s="30">
-        <v>46316.25963649306</v>
+        <v>46317.262076782405</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>379.80904451190645</v>
+        <v>368.47266977563396</v>
       </c>
       <c r="T57" s="30">
-        <v>46316.25964277778</v>
+        <v>46317.26208260417</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46316.259648784726</v>
+        <v>46317.26208825232</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46316.25965460648</v>
+        <v>46317.262094212965</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46316.25966053241</v>
+        <v>46317.26209994213</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46316.2596662037</v>
+        <v>46317.26210570602</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46316.259671921296</v>
+        <v>46317.26211157408</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0009198453378656</v>
+        <v>1.000740548005524</v>
       </c>
       <c r="T63" s="156">
-        <v>46316.25967806713</v>
+        <v>46317.26211732638</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2439.945559714188</v>
+        <v>2404.773203741192</v>
       </c>
       <c r="T9" s="29">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>344.1046374316995</v>
+        <v>346.53683424340176</v>
       </c>
       <c r="T10" s="30">
-        <v>46317.26181047454</v>
+        <v>46318.257669108796</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46317.26181625</v>
+        <v>46318.25767515046</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46317.26182208333</v>
+        <v>46318.25768016204</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46317.26182802083</v>
+        <v>46318.25768646991</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46317.26183354167</v>
+        <v>46318.25769193287</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46317.26183947917</v>
+        <v>46318.25769828704</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46317.26184513889</v>
+        <v>46318.25770405093</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46317.2618512037</v>
+        <v>46318.25771027778</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>172.16840461941837</v>
+        <v>169.72926215376853</v>
       </c>
       <c r="T18" s="30">
-        <v>46317.261856666664</v>
+        <v>46318.257714942134</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46317.2618625</v>
+        <v>46318.25772083333</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46317.26186833333</v>
+        <v>46318.25772688658</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46317.26187405093</v>
+        <v>46318.257732997685</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.544843183956127</v>
+        <v>6.627781014911506</v>
       </c>
       <c r="T22" s="30">
-        <v>46317.261879907404</v>
+        <v>46318.25773887731</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46317.261885671294</v>
+        <v>46318.257744780094</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46317.26189144676</v>
+        <v>46318.25775034722</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>374.3189960570822</v>
+        <v>369.03324502966484</v>
       </c>
       <c r="T25" s="30">
-        <v>46317.261897233795</v>
+        <v>46318.25775559028</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46317.26190309028</v>
+        <v>46318.25776241898</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>330.01421051578166</v>
+        <v>326.6534911986672</v>
       </c>
       <c r="T27" s="30">
-        <v>46317.26190880787</v>
+        <v>46318.257766979164</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.801312971598982</v>
+        <v>28.92395672519538</v>
       </c>
       <c r="T28" s="30">
-        <v>46317.26191469907</v>
+        <v>46318.257773125</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46317.26192072917</v>
+        <v>46318.25777934028</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46317.2619262963</v>
+        <v>46318.257784444446</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46317.26193201389</v>
+        <v>46318.257790868054</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46317.26193774305</v>
+        <v>46318.25779664352</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46317.26194350694</v>
+        <v>46318.2578024074</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>705.3519604507336</v>
+        <v>646.6091191058302</v>
       </c>
       <c r="T34" s="30">
-        <v>46317.261949328706</v>
+        <v>46318.2578075</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46317.26195533565</v>
+        <v>46318.257813819444</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46317.26196091435</v>
+        <v>46318.25781989583</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46317.261966736114</v>
+        <v>46318.25782490741</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>148.4298380801793</v>
+        <v>146.4218993097897</v>
       </c>
       <c r="T38" s="30">
-        <v>46317.26197251157</v>
+        <v>46318.257830787035</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46317.261978333336</v>
+        <v>46318.257837233796</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46317.261989907405</v>
+        <v>46318.25784912037</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46317.261995740744</v>
+        <v>46318.257854641204</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>218.2615135200048</v>
+        <v>214.03127271416645</v>
       </c>
       <c r="T42" s="30">
-        <v>46317.26198413195</v>
+        <v>46318.257842314815</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46317.262001435185</v>
+        <v>46318.2578603125</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46317.26200729166</v>
+        <v>46318.25786543982</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>716.2200028020735</v>
+        <v>707.5106174649037</v>
       </c>
       <c r="T45" s="30">
-        <v>46317.26201319444</v>
+        <v>46318.257871423615</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>51.94844184696675</v>
+        <v>53.76311790041509</v>
       </c>
       <c r="T46" s="30">
-        <v>46317.26201914352</v>
+        <v>46318.25787736111</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>151.6121930228369</v>
+        <v>149.27024326559382</v>
       </c>
       <c r="T47" s="30">
-        <v>46317.2620246875</v>
+        <v>46318.25788361111</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46317.262030543985</v>
+        <v>46318.25788927083</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>100.5243880471549</v>
+        <v>102.42024136336059</v>
       </c>
       <c r="T49" s="30">
-        <v>46317.26203614583</v>
+        <v>46318.2578947338</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46317.26204203704</v>
+        <v>46318.25790082176</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46317.262047766206</v>
+        <v>46318.257906087965</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46317.262053576385</v>
+        <v>46318.257911712964</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46317.26205949074</v>
+        <v>46318.25791748843</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46317.26206519676</v>
+        <v>46318.257923668985</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>156.28565138202268</v>
+        <v>148.2940972701952</v>
       </c>
       <c r="T55" s="30">
-        <v>46317.262070902776</v>
+        <v>46318.25792940972</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>770.0798590957309</v>
+        <v>765.4886837146811</v>
       </c>
       <c r="T56" s="30">
-        <v>46317.262076782405</v>
+        <v>46318.25793482639</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>368.47266977563396</v>
+        <v>376.53605332660544</v>
       </c>
       <c r="T57" s="30">
-        <v>46317.26208260417</v>
+        <v>46318.25794109954</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46317.26208825232</v>
+        <v>46318.25794638889</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46317.262094212965</v>
+        <v>46318.257952604166</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46317.26209994213</v>
+        <v>46318.25795795139</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46317.26210570602</v>
+        <v>46318.25796418981</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46317.26211157408</v>
+        <v>46318.257970543986</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.000740548005524</v>
+        <v>1.001175379895998</v>
       </c>
       <c r="T63" s="156">
-        <v>46317.26211732638</v>
+        <v>46318.25797636574</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2404.773203741192</v>
+        <v>2376.823895153428</v>
       </c>
       <c r="T9" s="29">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>346.53683424340176</v>
+        <v>347.9538543766477</v>
       </c>
       <c r="T10" s="30">
-        <v>46318.257669108796</v>
+        <v>46319.2544030787</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46318.25767515046</v>
+        <v>46319.25440885417</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46318.25768016204</v>
+        <v>46319.25441465278</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46318.25768646991</v>
+        <v>46319.25442041666</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46318.25769193287</v>
+        <v>46319.254426238425</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46318.25769828704</v>
+        <v>46319.25443260417</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46318.25770405093</v>
+        <v>46319.25443868055</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46318.25771027778</v>
+        <v>46319.25444446759</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>169.72926215376853</v>
+        <v>164.06798932637236</v>
       </c>
       <c r="T18" s="30">
-        <v>46318.257714942134</v>
+        <v>46319.25444938657</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46318.25772083333</v>
+        <v>46319.25445581019</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46318.25772688658</v>
+        <v>46319.25446096065</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46318.257732997685</v>
+        <v>46319.254467569444</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.627781014911506</v>
+        <v>6.395768983623228</v>
       </c>
       <c r="T22" s="30">
-        <v>46318.25773887731</v>
+        <v>46319.254472546294</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46318.257744780094</v>
+        <v>46319.25447915509</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46318.25775034722</v>
+        <v>46319.25448503472</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>369.03324502966484</v>
+        <v>365.4996807120022</v>
       </c>
       <c r="T25" s="30">
-        <v>46318.25775559028</v>
+        <v>46319.25448989584</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46318.25776241898</v>
+        <v>46319.25449568287</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>326.6534911986672</v>
+        <v>321.3288386124284</v>
       </c>
       <c r="T27" s="30">
-        <v>46318.257766979164</v>
+        <v>46319.25450225695</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.92395672519538</v>
+        <v>27.83510726675461</v>
       </c>
       <c r="T28" s="30">
-        <v>46318.257773125</v>
+        <v>46319.25450725695</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46318.25777934028</v>
+        <v>46319.254513900465</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46318.257784444446</v>
+        <v>46319.25451989583</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46318.257790868054</v>
+        <v>46319.25452549768</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46318.25779664352</v>
+        <v>46319.25453140046</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46318.2578024074</v>
+        <v>46319.25453709491</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>646.6091191058302</v>
+        <v>640.6778914580952</v>
       </c>
       <c r="T34" s="30">
-        <v>46318.2578075</v>
+        <v>46319.25454300926</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46318.257813819444</v>
+        <v>46319.25454774306</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46318.25781989583</v>
+        <v>46319.25455417824</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46318.25782490741</v>
+        <v>46319.25455936343</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>146.4218993097897</v>
+        <v>146.3820365970105</v>
       </c>
       <c r="T38" s="30">
-        <v>46318.257830787035</v>
+        <v>46319.2545659375</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46318.257837233796</v>
+        <v>46319.25457172454</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46318.25784912037</v>
+        <v>46319.254583333335</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46318.257854641204</v>
+        <v>46319.254589282406</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>214.03127271416645</v>
+        <v>211.47074661344533</v>
       </c>
       <c r="T42" s="30">
-        <v>46318.257842314815</v>
+        <v>46319.254577893524</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46318.2578603125</v>
+        <v>46319.254594895836</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46318.25786543982</v>
+        <v>46319.25460068287</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>707.5106174649037</v>
+        <v>704.8657889416253</v>
       </c>
       <c r="T45" s="30">
-        <v>46318.257871423615</v>
+        <v>46319.2546062963</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>53.76311790041509</v>
+        <v>52.98779499108195</v>
       </c>
       <c r="T46" s="30">
-        <v>46318.25787736111</v>
+        <v>46319.254611446755</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>149.27024326559382</v>
+        <v>144.7505650096387</v>
       </c>
       <c r="T47" s="30">
-        <v>46318.25788361111</v>
+        <v>46319.25461783565</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46318.25788927083</v>
+        <v>46319.254623796296</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7465,10 +7465,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
       <c r="S49" s="27">
-        <v>102.42024136336059</v>
+        <v>101.45150926135373</v>
       </c>
       <c r="T49" s="30">
-        <v>46318.2578947338</v>
+        <v>46319.25462982639</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46318.25790082176</v>
+        <v>46319.25463541667</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46318.257906087965</v>
+        <v>46319.254640335654</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46318.257911712964</v>
+        <v>46319.25464694444</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46318.25791748843</v>
+        <v>46319.25465189815</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46318.257923668985</v>
+        <v>46319.254658784725</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.2940972701952</v>
+        <v>147.50304774906965</v>
       </c>
       <c r="T55" s="30">
-        <v>46318.25792940972</v>
+        <v>46319.254663506945</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>765.4886837146811</v>
+        <v>762.9782063421205</v>
       </c>
       <c r="T56" s="30">
-        <v>46318.25793482639</v>
+        <v>46319.254669305556</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>376.53605332660544</v>
+        <v>371.7853503860482</v>
       </c>
       <c r="T57" s="30">
-        <v>46318.25794109954</v>
+        <v>46319.254675069446</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46318.25794638889</v>
+        <v>46319.25468173611</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46318.257952604166</v>
+        <v>46319.25468721065</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46318.25795795139</v>
+        <v>46319.25469328704</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46318.25796418981</v>
+        <v>46319.254699398145</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46318.257970543986</v>
+        <v>46319.254704872685</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.001175379895998</v>
+        <v>1.0009028143385332</v>
       </c>
       <c r="T63" s="156">
-        <v>46318.25797636574</v>
+        <v>46319.254710682864</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2376.823895153428</v>
+        <v>2351.7566010787523</v>
       </c>
       <c r="T9" s="29">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>347.9538543766477</v>
+        <v>346.8562740900215</v>
       </c>
       <c r="T10" s="30">
-        <v>46319.2544030787</v>
+        <v>46320.268408703705</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46319.25440885417</v>
+        <v>46320.268414513885</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46319.25441465278</v>
+        <v>46320.26842030093</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46319.25442041666</v>
+        <v>46320.268426111106</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46319.254426238425</v>
+        <v>46320.26843214121</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46319.25443260417</v>
+        <v>46320.26843793981</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46319.25443868055</v>
+        <v>46320.268443726854</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46319.25444446759</v>
+        <v>46320.268449270836</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>164.06798932637236</v>
+        <v>164.39516092709863</v>
       </c>
       <c r="T18" s="30">
-        <v>46319.25444938657</v>
+        <v>46320.26845508102</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46319.25445581019</v>
+        <v>46320.26846091435</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46319.25446096065</v>
+        <v>46320.26846663195</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46319.254467569444</v>
+        <v>46320.26847247685</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.395768983623228</v>
+        <v>6.36562084320455</v>
       </c>
       <c r="T22" s="30">
-        <v>46319.254472546294</v>
+        <v>46320.26847850695</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46319.25447915509</v>
+        <v>46320.268484016204</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46319.25448503472</v>
+        <v>46320.26848980324</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>365.4996807120022</v>
+        <v>367.4844888036136</v>
       </c>
       <c r="T25" s="30">
-        <v>46319.25448989584</v>
+        <v>46320.26849560185</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46319.25449568287</v>
+        <v>46320.268501412036</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>321.3288386124284</v>
+        <v>323.5456908450161</v>
       </c>
       <c r="T27" s="30">
-        <v>46319.25450225695</v>
+        <v>46320.268507175926</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>27.83510726675461</v>
+        <v>27.944675148155824</v>
       </c>
       <c r="T28" s="30">
-        <v>46319.25450725695</v>
+        <v>46320.26851304398</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46319.254513900465</v>
+        <v>46320.2685187963</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46319.25451989583</v>
+        <v>46320.268524583335</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46319.25452549768</v>
+        <v>46320.26853037037</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46319.25453140046</v>
+        <v>46320.268536435186</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46319.25453709491</v>
+        <v>46320.26854201389</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>640.6778914580952</v>
+        <v>641.8467506808512</v>
       </c>
       <c r="T34" s="30">
-        <v>46319.25454300926</v>
+        <v>46320.2685477662</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46319.25454774306</v>
+        <v>46320.268553587965</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46319.25455417824</v>
+        <v>46320.26855935185</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46319.25455936343</v>
+        <v>46320.26856513889</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>146.3820365970105</v>
+        <v>145.9588816925345</v>
       </c>
       <c r="T38" s="30">
-        <v>46319.2545659375</v>
+        <v>46320.268570949076</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46319.25457172454</v>
+        <v>46320.26857666667</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46319.254583333335</v>
+        <v>46320.268588252315</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46319.254589282406</v>
+        <v>46320.26859402778</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>211.47074661344533</v>
+        <v>212.6677856547331</v>
       </c>
       <c r="T42" s="30">
-        <v>46319.254577893524</v>
+        <v>46320.2685825</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46319.254594895836</v>
+        <v>46320.26859987268</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46319.25460068287</v>
+        <v>46320.268605682875</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>704.8657889416253</v>
+        <v>705.3828530592513</v>
       </c>
       <c r="T45" s="30">
-        <v>46319.2546062963</v>
+        <v>46320.26861140046</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>52.98779499108195</v>
+        <v>52.57642498326022</v>
       </c>
       <c r="T46" s="30">
-        <v>46319.254611446755</v>
+        <v>46320.26861737268</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>144.7505650096387</v>
+        <v>144.8078653450997</v>
       </c>
       <c r="T47" s="30">
-        <v>46319.25461783565</v>
+        <v>46320.268622986114</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46319.254623796296</v>
+        <v>46320.26862876157</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7464,20 +7464,22 @@
       <c r="R49" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x92fd66527192e3e61d4ddd13322aa222de86f9b5</v>
       </c>
-      <c r="S49" s="27">
-        <v>101.45150926135373</v>
+      <c r="S49" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T49" s="30">
-        <v>46319.25462982639</v>
+        <v>46320.268634687505</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x7f310e3d05e575bd449e4484ef5da15863ea43b1</t>
+          <t/>
         </is>
       </c>
       <c r="V49" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7540,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46319.25463541667</v>
+        <v>46320.2686403125</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7610,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46319.254640335654</v>
+        <v>46320.26864607639</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7680,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46319.25464694444</v>
+        <v>46320.26865182871</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7750,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46319.25465189815</v>
+        <v>46320.26865766203</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7820,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46319.254658784725</v>
+        <v>46320.268663414354</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7885,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>147.50304774906965</v>
+        <v>147.8905873886642</v>
       </c>
       <c r="T55" s="30">
-        <v>46319.254663506945</v>
+        <v>46320.268669178244</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7953,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>762.9782063421205</v>
+        <v>763.3640504565532</v>
       </c>
       <c r="T56" s="30">
-        <v>46319.254669305556</v>
+        <v>46320.268675</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8021,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>371.7853503860482</v>
+        <v>371.7982978970431</v>
       </c>
       <c r="T57" s="30">
-        <v>46319.254675069446</v>
+        <v>46320.268680775465</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8094,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46319.25468173611</v>
+        <v>46320.2686866088</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8164,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46319.25468721065</v>
+        <v>46320.268692349535</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8234,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46319.25469328704</v>
+        <v>46320.26869813658</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8304,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46319.254699398145</v>
+        <v>46320.26870395833</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8374,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46319.254704872685</v>
+        <v>46320.26870971065</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8437,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0009028143385332</v>
+        <v>1.000883780378074</v>
       </c>
       <c r="T63" s="156">
-        <v>46319.254710682864</v>
+        <v>46320.2687155324</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2351.7566010787523</v>
+        <v>2315.08480512333</v>
       </c>
       <c r="T9" s="29">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>346.8562740900215</v>
+        <v>346.2050332716266</v>
       </c>
       <c r="T10" s="30">
-        <v>46320.268408703705</v>
+        <v>46321.274956469904</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46320.268414513885</v>
+        <v>46321.274963125004</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46320.26842030093</v>
+        <v>46321.27496899306</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46320.268426111106</v>
+        <v>46321.27497421296</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46320.26843214121</v>
+        <v>46321.27498023148</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46320.26843793981</v>
+        <v>46321.274986041666</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46320.268443726854</v>
+        <v>46321.27499143519</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46320.268449270836</v>
+        <v>46321.27499783565</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>164.39516092709863</v>
+        <v>162.20543353179568</v>
       </c>
       <c r="T18" s="30">
-        <v>46320.26845508102</v>
+        <v>46321.27500366898</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46320.26846091435</v>
+        <v>46321.275009398145</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46320.26846663195</v>
+        <v>46321.275015023144</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46320.26847247685</v>
+        <v>46321.275020995374</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.36562084320455</v>
+        <v>6.354130184620003</v>
       </c>
       <c r="T22" s="30">
-        <v>46320.26847850695</v>
+        <v>46321.275026944444</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46320.268484016204</v>
+        <v>46321.27503297454</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46320.26848980324</v>
+        <v>46321.27503866898</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>367.4844888036136</v>
+        <v>368.17931655576126</v>
       </c>
       <c r="T25" s="30">
-        <v>46320.26849560185</v>
+        <v>46321.27504395833</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46320.268501412036</v>
+        <v>46321.2750497338</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5940,20 +5940,22 @@
       <c r="R27" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
-      <c r="S27" s="27">
-        <v>323.5456908450161</v>
+      <c r="S27" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T27" s="30">
-        <v>46320.268507175926</v>
+        <v>46321.27505577546</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x8c2b4303fa0b99d07a5d3e9411497a277e65b673</t>
+          <t/>
         </is>
       </c>
       <c r="V27" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -6009,10 +6011,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>27.944675148155824</v>
+        <v>27.50788012207935</v>
       </c>
       <c r="T28" s="30">
-        <v>46320.26851304398</v>
+        <v>46321.2750615625</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6084,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46320.2685187963</v>
+        <v>46321.27506759259</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6154,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46320.268524583335</v>
+        <v>46321.275073136574</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6224,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46320.26853037037</v>
+        <v>46321.27507894676</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6294,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46320.268536435186</v>
+        <v>46321.27508472223</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6364,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46320.26854201389</v>
+        <v>46321.2750905787</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>641.8467506808512</v>
+        <v>641.8271876719867</v>
       </c>
       <c r="T34" s="30">
-        <v>46320.2685477662</v>
+        <v>46321.275095474535</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6502,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46320.268553587965</v>
+        <v>46321.27510226852</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6572,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46320.26855935185</v>
+        <v>46321.27510766204</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6642,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46320.26856513889</v>
+        <v>46321.27511376157</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6707,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>145.9588816925345</v>
+        <v>143.16705858808228</v>
       </c>
       <c r="T38" s="30">
-        <v>46320.268570949076</v>
+        <v>46321.27511954861</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6780,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46320.26857666667</v>
+        <v>46321.27512533565</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6850,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46320.268588252315</v>
+        <v>46321.275136840275</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6920,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46320.26859402778</v>
+        <v>46321.275142719904</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6985,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>212.6677856547331</v>
+        <v>211.77765547605944</v>
       </c>
       <c r="T42" s="30">
-        <v>46320.2685825</v>
+        <v>46321.27513109954</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7058,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46320.26859987268</v>
+        <v>46321.27514863426</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7128,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46320.268605682875</v>
+        <v>46321.275154282404</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7193,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>705.3828530592513</v>
+        <v>703.7574423375194</v>
       </c>
       <c r="T45" s="30">
-        <v>46320.26861140046</v>
+        <v>46321.275159143515</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7261,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>52.57642498326022</v>
+        <v>52.93440736478711</v>
       </c>
       <c r="T46" s="30">
-        <v>46320.26861737268</v>
+        <v>46321.27516576389</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7329,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>144.8078653450997</v>
+        <v>144.76409666283084</v>
       </c>
       <c r="T47" s="30">
-        <v>46320.268622986114</v>
+        <v>46321.275171319445</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7402,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46320.26862876157</v>
+        <v>46321.27517731482</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7470,7 +7472,7 @@
         </is>
       </c>
       <c r="T49" s="30">
-        <v>46320.268634687505</v>
+        <v>46321.275183125</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7540,7 +7542,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46320.2686403125</v>
+        <v>46321.275188935186</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7610,7 +7612,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46320.26864607639</v>
+        <v>46321.27519446759</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7680,7 +7682,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46320.26865182871</v>
+        <v>46321.27520055556</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7750,7 +7752,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46320.26865766203</v>
+        <v>46321.27520631945</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7820,7 +7822,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46320.268663414354</v>
+        <v>46321.27521223379</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7885,10 +7887,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>147.8905873886642</v>
+        <v>148.1963276129484</v>
       </c>
       <c r="T55" s="30">
-        <v>46320.268669178244</v>
+        <v>46321.27521731482</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7953,10 +7955,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>763.3640504565532</v>
+        <v>762.7457847600941</v>
       </c>
       <c r="T56" s="30">
-        <v>46320.268675</v>
+        <v>46321.27522291667</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8021,10 +8023,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>371.7982978970431</v>
+        <v>374.7535898333917</v>
       </c>
       <c r="T57" s="30">
-        <v>46320.268680775465</v>
+        <v>46321.27522916667</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8094,7 +8096,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46320.2686866088</v>
+        <v>46321.27523528935</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8164,7 +8166,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46320.268692349535</v>
+        <v>46321.275241145835</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8234,7 +8236,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46320.26869813658</v>
+        <v>46321.275246817124</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8304,7 +8306,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46320.26870395833</v>
+        <v>46321.27525278935</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8374,7 +8376,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46320.26870971065</v>
+        <v>46321.2752583912</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8437,10 +8439,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.000883780378074</v>
+        <v>1.0006504227748036</v>
       </c>
       <c r="T63" s="156">
-        <v>46320.2687155324</v>
+        <v>46321.27526412037</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2315.08480512333</v>
+        <v>2308.7791323503643</v>
       </c>
       <c r="T9" s="29">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>346.2050332716266</v>
+        <v>343.1847197536736</v>
       </c>
       <c r="T10" s="30">
-        <v>46321.274956469904</v>
+        <v>46322.271636481484</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46321.274963125004</v>
+        <v>46322.271642141204</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46321.27496899306</v>
+        <v>46322.271647939815</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46321.27497421296</v>
+        <v>46322.27165385417</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46321.27498023148</v>
+        <v>46322.27165959491</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46321.274986041666</v>
+        <v>46322.271665671295</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46321.27499143519</v>
+        <v>46322.27167094907</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46321.27499783565</v>
+        <v>46322.27167693287</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>162.20543353179568</v>
+        <v>159.77169749918642</v>
       </c>
       <c r="T18" s="30">
-        <v>46321.27500366898</v>
+        <v>46322.27168277778</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46321.275009398145</v>
+        <v>46322.271688553235</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46321.275015023144</v>
+        <v>46322.27169428241</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46321.275020995374</v>
+        <v>46322.271700150464</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.354130184620003</v>
+        <v>6.128119758680252</v>
       </c>
       <c r="T22" s="30">
-        <v>46321.275026944444</v>
+        <v>46322.27170582176</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46321.27503297454</v>
+        <v>46322.27171190972</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46321.27503866898</v>
+        <v>46322.27171768519</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>368.17931655576126</v>
+        <v>368.0476631536786</v>
       </c>
       <c r="T25" s="30">
-        <v>46321.27504395833</v>
+        <v>46322.27172326389</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46321.2750497338</v>
+        <v>46322.27172908565</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5946,7 +5946,7 @@
         </is>
       </c>
       <c r="T27" s="30">
-        <v>46321.27505577546</v>
+        <v>46322.27173486111</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6011,10 +6011,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>27.50788012207935</v>
+        <v>27.53648584374296</v>
       </c>
       <c r="T28" s="30">
-        <v>46321.2750615625</v>
+        <v>46322.271740578704</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46321.27506759259</v>
+        <v>46322.27174640046</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6154,7 +6154,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46321.275073136574</v>
+        <v>46322.27175224537</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46321.27507894676</v>
+        <v>46322.2717580787</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6294,7 +6294,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46321.27508472223</v>
+        <v>46322.27176386574</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46321.2750905787</v>
+        <v>46322.27176991898</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6429,10 +6429,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>641.8271876719867</v>
+        <v>631.2063484116454</v>
       </c>
       <c r="T34" s="30">
-        <v>46321.275095474535</v>
+        <v>46322.27177547454</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46321.27510226852</v>
+        <v>46322.27178125</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6572,7 +6572,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46321.27510766204</v>
+        <v>46322.27178746527</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46321.27511376157</v>
+        <v>46322.27179288195</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6707,10 +6707,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>143.16705858808228</v>
+        <v>140.9968207875435</v>
       </c>
       <c r="T38" s="30">
-        <v>46321.27511954861</v>
+        <v>46322.27179861111</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46321.27512533565</v>
+        <v>46322.2718043287</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46321.275136840275</v>
+        <v>46322.27181636574</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6920,7 +6920,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46321.275142719904</v>
+        <v>46322.27182171296</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6985,10 +6985,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>211.77765547605944</v>
+        <v>215.34733521916542</v>
       </c>
       <c r="T42" s="30">
-        <v>46321.27513109954</v>
+        <v>46322.271810266204</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7058,7 +7058,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46321.27514863426</v>
+        <v>46322.2718275463</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46321.275154282404</v>
+        <v>46322.27183336805</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7193,10 +7193,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>703.7574423375194</v>
+        <v>709.9106315868527</v>
       </c>
       <c r="T45" s="30">
-        <v>46321.275159143515</v>
+        <v>46322.271839120374</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7261,10 +7261,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>52.93440736478711</v>
+        <v>54.342003154179295</v>
       </c>
       <c r="T46" s="30">
-        <v>46321.27516576389</v>
+        <v>46322.27184496528</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7329,10 +7329,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>144.76409666283084</v>
+        <v>138.06293338673743</v>
       </c>
       <c r="T47" s="30">
-        <v>46321.275171319445</v>
+        <v>46322.27185065972</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46321.27517731482</v>
+        <v>46322.27185646991</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         </is>
       </c>
       <c r="T49" s="30">
-        <v>46321.275183125</v>
+        <v>46322.271862256945</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7542,7 +7542,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46321.275188935186</v>
+        <v>46322.27186800926</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7612,7 +7612,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46321.27519446759</v>
+        <v>46322.271873854166</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7682,7 +7682,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46321.27520055556</v>
+        <v>46322.27187967592</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7752,7 +7752,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46321.27520631945</v>
+        <v>46322.27188543981</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7822,7 +7822,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46321.27521223379</v>
+        <v>46322.27189118055</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7887,10 +7887,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>148.1963276129484</v>
+        <v>147.0448344055874</v>
       </c>
       <c r="T55" s="30">
-        <v>46321.27521731482</v>
+        <v>46322.271896921295</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7955,10 +7955,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>762.7457847600941</v>
+        <v>766.966230255088</v>
       </c>
       <c r="T56" s="30">
-        <v>46321.27522291667</v>
+        <v>46322.27190284722</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8023,10 +8023,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>374.7535898333917</v>
+        <v>392.4600095126042</v>
       </c>
       <c r="T57" s="30">
-        <v>46321.27522916667</v>
+        <v>46322.27190856481</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46321.27523528935</v>
+        <v>46322.271914363424</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46321.275241145835</v>
+        <v>46322.271920162035</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46321.275246817124</v>
+        <v>46322.271925914356</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46321.27525278935</v>
+        <v>46322.27193166666</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8376,7 +8376,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46321.2752583912</v>
+        <v>46322.271937488425</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8439,10 +8439,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0006504227748036</v>
+        <v>1.0013267579542895</v>
       </c>
       <c r="T63" s="156">
-        <v>46321.27526412037</v>
+        <v>46322.271943217595</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2308.7791323503643</v>
+        <v>2351.981144260624</v>
       </c>
       <c r="T9" s="29">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>343.1847197536736</v>
+        <v>346.9668312405318</v>
       </c>
       <c r="T10" s="30">
-        <v>46322.271636481484</v>
+        <v>46323.29176969908</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46322.271642141204</v>
+        <v>46323.291775474536</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46322.271647939815</v>
+        <v>46323.29178127315</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46322.27165385417</v>
+        <v>46323.29178706018</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46322.27165959491</v>
+        <v>46323.29179285879</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46322.271665671295</v>
+        <v>46323.2917986574</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46322.27167094907</v>
+        <v>46323.291804444445</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46322.27167693287</v>
+        <v>46323.29181023148</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>159.77169749918642</v>
+        <v>159.33059722190237</v>
       </c>
       <c r="T18" s="30">
-        <v>46322.27168277778</v>
+        <v>46323.29181607639</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46322.271688553235</v>
+        <v>46323.29182184028</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46322.27169428241</v>
+        <v>46323.291828229165</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46322.271700150464</v>
+        <v>46323.291833460644</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.128119758680252</v>
+        <v>6.358004727952492</v>
       </c>
       <c r="T22" s="30">
-        <v>46322.27170582176</v>
+        <v>46323.291839537036</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46322.27171190972</v>
+        <v>46323.29184554398</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46322.27171768519</v>
+        <v>46323.29185079861</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>368.0476631536786</v>
+        <v>372.5390266345329</v>
       </c>
       <c r="T25" s="30">
-        <v>46322.27172326389</v>
+        <v>46323.29185663194</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46322.27172908565</v>
+        <v>46323.291862673614</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5940,22 +5940,20 @@
       <c r="R27" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
-      <c r="S27" s="27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="S27" s="27">
+        <v>324.4204453406839</v>
       </c>
       <c r="T27" s="30">
-        <v>46322.27173486111</v>
+        <v>46323.29186818287</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
-          <t/>
+          <t>https://dexscreener.com/robinhood/0x8c2b4303fa0b99d07a5d3e9411497a277e65b673</t>
         </is>
       </c>
       <c r="V27" s="33" t="inlineStr">
         <is>
-          <t>暂无合格池价；可手动输入</t>
+          <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
@@ -6011,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>27.53648584374296</v>
+        <v>28.13141745457531</v>
       </c>
       <c r="T28" s="30">
-        <v>46322.271740578704</v>
+        <v>46323.291873981485</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6084,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46322.27174640046</v>
+        <v>46323.291879756944</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6154,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46322.27175224537</v>
+        <v>46323.291885555554</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6224,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46322.2717580787</v>
+        <v>46323.29189137732</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6294,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46322.27176386574</v>
+        <v>46323.29189716435</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6364,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46322.27176991898</v>
+        <v>46323.291903530095</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6429,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>631.2063484116454</v>
+        <v>622.1332657816191</v>
       </c>
       <c r="T34" s="30">
-        <v>46322.27177547454</v>
+        <v>46323.29190875</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6502,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46322.27178125</v>
+        <v>46323.29191454861</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6572,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46322.27178746527</v>
+        <v>46323.2919206713</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6642,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46322.27179288195</v>
+        <v>46323.29192613426</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6707,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>140.9968207875435</v>
+        <v>141.87862518911308</v>
       </c>
       <c r="T38" s="30">
-        <v>46322.27179861111</v>
+        <v>46323.29193194445</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6780,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46322.2718043287</v>
+        <v>46323.29193806713</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6850,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46322.27181636574</v>
+        <v>46323.29194929398</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6920,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46322.27182171296</v>
+        <v>46323.29195508102</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6985,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>215.34733521916542</v>
+        <v>219.29609378207164</v>
       </c>
       <c r="T42" s="30">
-        <v>46322.271810266204</v>
+        <v>46323.29194351852</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7058,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46322.2718275463</v>
+        <v>46323.29196091435</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7128,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46322.27183336805</v>
+        <v>46323.291966655095</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7193,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>709.9106315868527</v>
+        <v>723.9774876569602</v>
       </c>
       <c r="T45" s="30">
-        <v>46322.271839120374</v>
+        <v>46323.291972453706</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7261,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>54.342003154179295</v>
+        <v>54.40850030188007</v>
       </c>
       <c r="T46" s="30">
-        <v>46322.27184496528</v>
+        <v>46323.29197881944</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7329,14 +7327,14 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>138.06293338673743</v>
+        <v>138.10387277582478</v>
       </c>
       <c r="T47" s="30">
-        <v>46322.27185065972</v>
+        <v>46323.291984027775</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x714187eed11d8fc9500ff6798734c8bb63a8a19b</t>
+          <t>https://dexscreener.com/robinhood/0xa541143f20d7b0643123064abf25f423e375b531</t>
         </is>
       </c>
       <c r="V47" s="33" t="inlineStr">
@@ -7402,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46322.27185646991</v>
+        <v>46323.29198981482</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7472,7 +7470,7 @@
         </is>
       </c>
       <c r="T49" s="30">
-        <v>46322.271862256945</v>
+        <v>46323.29199564815</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7542,7 +7540,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46322.27186800926</v>
+        <v>46323.29200141204</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7612,7 +7610,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46322.271873854166</v>
+        <v>46323.29200717593</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7682,7 +7680,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46322.27187967592</v>
+        <v>46323.29201302084</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7752,7 +7750,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46322.27188543981</v>
+        <v>46323.2920190625</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7822,7 +7820,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46322.27189118055</v>
+        <v>46323.292024571754</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7887,10 +7885,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>147.0448344055874</v>
+        <v>150.1790754559991</v>
       </c>
       <c r="T55" s="30">
-        <v>46322.271896921295</v>
+        <v>46323.29203048611</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7955,10 +7953,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>766.966230255088</v>
+        <v>772.0920639084608</v>
       </c>
       <c r="T56" s="30">
-        <v>46322.27190284722</v>
+        <v>46323.29203618056</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8023,10 +8021,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>392.4600095126042</v>
+        <v>412.42924842376556</v>
       </c>
       <c r="T57" s="30">
-        <v>46322.27190856481</v>
+        <v>46323.29204190972</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8096,7 +8094,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46322.271914363424</v>
+        <v>46323.29204825231</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8166,7 +8164,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46322.271920162035</v>
+        <v>46323.29205350694</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8236,7 +8234,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46322.271925914356</v>
+        <v>46323.29205962963</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8306,7 +8304,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46322.27193166666</v>
+        <v>46323.29206513889</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8376,7 +8374,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46322.271937488425</v>
+        <v>46323.29207084491</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8439,10 +8437,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0013267579542895</v>
+        <v>1.0012605870791327</v>
       </c>
       <c r="T63" s="156">
-        <v>46322.271943217595</v>
+        <v>46323.29207699074</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2351.981144260624</v>
+        <v>2310.6600183991904</v>
       </c>
       <c r="T9" s="29">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>346.9668312405318</v>
+        <v>346.97189168302543</v>
       </c>
       <c r="T10" s="30">
-        <v>46323.29176969908</v>
+        <v>46324.307033530094</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4826,22 +4826,20 @@
       <c r="R11" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
-      <c r="S11" s="27" t="inlineStr">
-        <is>
-          <t/>
-        </is>
+      <c r="S11" s="27">
+        <v>2.9731009442848895</v>
       </c>
       <c r="T11" s="30">
-        <v>46323.291775474536</v>
+        <v>46324.30703883102</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
-          <t/>
+          <t>https://dexscreener.com/robinhood/0xcf38764ae8c92222af4358a701871a6235cfc7b7</t>
         </is>
       </c>
       <c r="V11" s="33" t="inlineStr">
         <is>
-          <t>暂无合格池价；可手动输入</t>
+          <t>每日 Quote 代币池价；本地可手动更新</t>
         </is>
       </c>
     </row>
@@ -4902,7 +4900,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46323.29178127315</v>
+        <v>46324.30704530093</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4970,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46323.29178706018</v>
+        <v>46324.307051435186</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5040,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46323.29179285879</v>
+        <v>46324.30705736111</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5110,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46323.2917986574</v>
+        <v>46324.30706280092</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5180,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46323.291804444445</v>
+        <v>46324.307068518516</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5250,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46323.29181023148</v>
+        <v>46324.30707454861</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5315,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>159.33059722190237</v>
+        <v>158.20700991133754</v>
       </c>
       <c r="T18" s="30">
-        <v>46323.29181607639</v>
+        <v>46324.307080266204</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5388,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46323.29182184028</v>
+        <v>46324.307085925924</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5458,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46323.291828229165</v>
+        <v>46324.307091724535</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5528,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46323.291833460644</v>
+        <v>46324.30709761574</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5593,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>6.358004727952492</v>
+        <v>5.926181006790082</v>
       </c>
       <c r="T22" s="30">
-        <v>46323.291839537036</v>
+        <v>46324.30710254629</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5666,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46323.29184554398</v>
+        <v>46324.30710924768</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5736,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46323.29185079861</v>
+        <v>46324.30711482639</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5801,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>372.5390266345329</v>
+        <v>369.97588484789634</v>
       </c>
       <c r="T25" s="30">
-        <v>46323.29185663194</v>
+        <v>46324.307121053236</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5874,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46323.291862673614</v>
+        <v>46324.30712586806</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5939,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>324.4204453406839</v>
+        <v>292.8354273507268</v>
       </c>
       <c r="T27" s="30">
-        <v>46323.29186818287</v>
+        <v>46324.307132291666</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6007,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.13141745457531</v>
+        <v>28.860101085432106</v>
       </c>
       <c r="T28" s="30">
-        <v>46323.291873981485</v>
+        <v>46324.30713775463</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6080,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46323.291879756944</v>
+        <v>46324.30714376158</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6150,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46323.291885555554</v>
+        <v>46324.30714962963</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6220,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46323.29189137732</v>
+        <v>46324.3071554051</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6290,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46323.29189716435</v>
+        <v>46324.30716113426</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6360,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46323.291903530095</v>
+        <v>46324.307166921295</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6425,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>622.1332657816191</v>
+        <v>616.9334616004493</v>
       </c>
       <c r="T34" s="30">
-        <v>46323.29190875</v>
+        <v>46324.30717276621</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6498,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46323.29191454861</v>
+        <v>46324.30717888889</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6568,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46323.2919206713</v>
+        <v>46324.30718465278</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6638,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46323.29192613426</v>
+        <v>46324.30719011574</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6703,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>141.87862518911308</v>
+        <v>141.23030320624412</v>
       </c>
       <c r="T38" s="30">
-        <v>46323.29193194445</v>
+        <v>46324.3071959375</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6776,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46323.29193806713</v>
+        <v>46324.307201689815</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6846,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46323.29194929398</v>
+        <v>46324.30721356481</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6916,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46323.29195508102</v>
+        <v>46324.30721898148</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6981,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>219.29609378207164</v>
+        <v>213.40257888978206</v>
       </c>
       <c r="T42" s="30">
-        <v>46323.29194351852</v>
+        <v>46324.30720753472</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7054,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46323.29196091435</v>
+        <v>46324.30722486111</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7124,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46323.291966655095</v>
+        <v>46324.30723005787</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7189,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>723.9774876569602</v>
+        <v>715.946732441937</v>
       </c>
       <c r="T45" s="30">
-        <v>46323.291972453706</v>
+        <v>46324.3072359838</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7257,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>54.40850030188007</v>
+        <v>52.7650339303894</v>
       </c>
       <c r="T46" s="30">
-        <v>46323.29197881944</v>
+        <v>46324.30724202546</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,14 +7325,14 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>138.10387277582478</v>
+        <v>132.91863413540324</v>
       </c>
       <c r="T47" s="30">
-        <v>46323.291984027775</v>
+        <v>46324.307247592595</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0xa541143f20d7b0643123064abf25f423e375b531</t>
+          <t>https://dexscreener.com/robinhood/0x714187eed11d8fc9500ff6798734c8bb63a8a19b</t>
         </is>
       </c>
       <c r="V47" s="33" t="inlineStr">
@@ -7400,7 +7398,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46323.29198981482</v>
+        <v>46324.307253831015</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7470,7 +7468,7 @@
         </is>
       </c>
       <c r="T49" s="30">
-        <v>46323.29199564815</v>
+        <v>46324.30725993055</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7540,7 +7538,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46323.29200141204</v>
+        <v>46324.30726553241</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7610,7 +7608,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46323.29200717593</v>
+        <v>46324.30727074074</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7680,7 +7678,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46323.29201302084</v>
+        <v>46324.30727631944</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7750,7 +7748,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46323.2920190625</v>
+        <v>46324.307282141206</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7820,7 +7818,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46323.292024571754</v>
+        <v>46324.30728840278</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7885,10 +7883,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>150.1790754559991</v>
+        <v>143.26943001550617</v>
       </c>
       <c r="T55" s="30">
-        <v>46323.29203048611</v>
+        <v>46324.307294074075</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7953,10 +7951,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>772.0920639084608</v>
+        <v>772.1153162748747</v>
       </c>
       <c r="T56" s="30">
-        <v>46323.29203618056</v>
+        <v>46324.307300162036</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8021,10 +8019,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>412.42924842376556</v>
+        <v>401.1283768971037</v>
       </c>
       <c r="T57" s="30">
-        <v>46323.29204190972</v>
+        <v>46324.30730583333</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8094,7 +8092,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46323.29204825231</v>
+        <v>46324.30731179398</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8164,7 +8162,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46323.29205350694</v>
+        <v>46324.30731732639</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8234,7 +8232,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46323.29205962963</v>
+        <v>46324.30732274306</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8304,7 +8302,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46323.29206513889</v>
+        <v>46324.30732898148</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8374,7 +8372,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46323.29207084491</v>
+        <v>46324.30733427084</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8437,10 +8435,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0012605870791327</v>
+        <v>1.0010440889848111</v>
       </c>
       <c r="T63" s="156">
-        <v>46323.29207699074</v>
+        <v>46324.307340983796</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2310.6600183991904</v>
+        <v>2249.665085375695</v>
       </c>
       <c r="T9" s="29">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>346.97189168302543</v>
+        <v>350.97450643897145</v>
       </c>
       <c r="T10" s="30">
-        <v>46324.307033530094</v>
+        <v>46325.30876709491</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4826,20 +4826,22 @@
       <c r="R11" s="33" t="str">
         <v>https://robinhoodchain.blockscout.com/address/0x05a3d1cd21d0c88145e82600e62e7e496e0f222b</v>
       </c>
-      <c r="S11" s="27">
-        <v>2.9731009442848895</v>
+      <c r="S11" s="27" t="inlineStr">
+        <is>
+          <t/>
+        </is>
       </c>
       <c r="T11" s="30">
-        <v>46324.30703883102</v>
+        <v>46325.30877523148</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0xcf38764ae8c92222af4358a701871a6235cfc7b7</t>
+          <t/>
         </is>
       </c>
       <c r="V11" s="33" t="inlineStr">
         <is>
-          <t>每日 Quote 代币池价；本地可手动更新</t>
+          <t>暂无合格池价；可手动输入</t>
         </is>
       </c>
     </row>
@@ -4900,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46324.30704530093</v>
+        <v>46325.30877840278</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4970,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46324.307051435186</v>
+        <v>46325.3087844676</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5040,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46324.30705736111</v>
+        <v>46325.308789953706</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5110,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46324.30706280092</v>
+        <v>46325.3087960301</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5180,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46324.307068518516</v>
+        <v>46325.30880186342</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5250,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46324.30707454861</v>
+        <v>46325.30880733796</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5315,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>158.20700991133754</v>
+        <v>154.49126018010298</v>
       </c>
       <c r="T18" s="30">
-        <v>46324.307080266204</v>
+        <v>46325.308813449075</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5388,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46324.307085925924</v>
+        <v>46325.308818935184</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5458,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46324.307091724535</v>
+        <v>46325.30882472222</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5528,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46324.30709761574</v>
+        <v>46325.30883055556</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5593,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>5.926181006790082</v>
+        <v>5.6770281608631485</v>
       </c>
       <c r="T22" s="30">
-        <v>46324.30710254629</v>
+        <v>46325.308836840275</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5666,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46324.30710924768</v>
+        <v>46325.30884208333</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5736,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46324.30711482639</v>
+        <v>46325.30884813658</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5801,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>369.97588484789634</v>
+        <v>368.4701660655892</v>
       </c>
       <c r="T25" s="30">
-        <v>46324.307121053236</v>
+        <v>46325.308853981485</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5874,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46324.30712586806</v>
+        <v>46325.30885974537</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5939,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>292.8354273507268</v>
+        <v>284.20184188024774</v>
       </c>
       <c r="T27" s="30">
-        <v>46324.307132291666</v>
+        <v>46325.30886556713</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6007,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.860101085432106</v>
+        <v>28.925810152969376</v>
       </c>
       <c r="T28" s="30">
-        <v>46324.30713775463</v>
+        <v>46325.30887127315</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6080,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46324.30714376158</v>
+        <v>46325.308877083335</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6150,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46324.30714962963</v>
+        <v>46325.308882604164</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6220,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46324.3071554051</v>
+        <v>46325.308888645835</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6290,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46324.30716113426</v>
+        <v>46325.30889453703</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6360,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46324.307166921295</v>
+        <v>46325.30890034722</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6425,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>616.9334616004493</v>
+        <v>619.226602533937</v>
       </c>
       <c r="T34" s="30">
-        <v>46324.30717276621</v>
+        <v>46325.3089062963</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6498,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46324.30717888889</v>
+        <v>46325.30891157407</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6568,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46324.30718465278</v>
+        <v>46325.30891760417</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6638,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46324.30719011574</v>
+        <v>46325.30892354166</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6703,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>141.23030320624412</v>
+        <v>136.90949395351444</v>
       </c>
       <c r="T38" s="30">
-        <v>46324.3071959375</v>
+        <v>46325.30892928241</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6776,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46324.307201689815</v>
+        <v>46325.308934733795</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6846,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46324.30721356481</v>
+        <v>46325.30894635417</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6916,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46324.30721898148</v>
+        <v>46325.30895241898</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6981,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>213.40257888978206</v>
+        <v>209.2490503243015</v>
       </c>
       <c r="T42" s="30">
-        <v>46324.30720753472</v>
+        <v>46325.30894083333</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7054,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46324.30722486111</v>
+        <v>46325.308958263886</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7124,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46324.30723005787</v>
+        <v>46325.308964004624</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7189,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>715.946732441937</v>
+        <v>704.0916654818666</v>
       </c>
       <c r="T45" s="30">
-        <v>46324.3072359838</v>
+        <v>46325.30896949075</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7257,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>52.7650339303894</v>
+        <v>43.84427921767148</v>
       </c>
       <c r="T46" s="30">
-        <v>46324.30724202546</v>
+        <v>46325.30897554398</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7325,14 +7327,14 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>132.91863413540324</v>
+        <v>106.53188647545662</v>
       </c>
       <c r="T47" s="30">
-        <v>46324.307247592595</v>
+        <v>46325.30898134259</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
-          <t>https://dexscreener.com/robinhood/0x714187eed11d8fc9500ff6798734c8bb63a8a19b</t>
+          <t>https://dexscreener.com/robinhood/0xa541143f20d7b0643123064abf25f423e375b531</t>
         </is>
       </c>
       <c r="V47" s="33" t="inlineStr">
@@ -7398,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46324.307253831015</v>
+        <v>46325.308987372686</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7468,7 +7470,7 @@
         </is>
       </c>
       <c r="T49" s="30">
-        <v>46324.30725993055</v>
+        <v>46325.30899284722</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7538,7 +7540,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46324.30726553241</v>
+        <v>46325.3089987037</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7608,7 +7610,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46324.30727074074</v>
+        <v>46325.309004525465</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7678,7 +7680,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46324.30727631944</v>
+        <v>46325.30901038195</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7748,7 +7750,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46324.307282141206</v>
+        <v>46325.309016342595</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7818,7 +7820,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46324.30728840278</v>
+        <v>46325.30902184028</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7883,10 +7885,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>143.26943001550617</v>
+        <v>140.204573261698</v>
       </c>
       <c r="T55" s="30">
-        <v>46324.307294074075</v>
+        <v>46325.30902763889</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7951,10 +7953,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>772.1153162748747</v>
+        <v>765.1472522983454</v>
       </c>
       <c r="T56" s="30">
-        <v>46324.307300162036</v>
+        <v>46325.3090334375</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8019,10 +8021,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>401.1283768971037</v>
+        <v>396.7211407722761</v>
       </c>
       <c r="T57" s="30">
-        <v>46324.30730583333</v>
+        <v>46325.30903917824</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8092,7 +8094,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46324.30731179398</v>
+        <v>46325.30904506944</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8162,7 +8164,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46324.30731732639</v>
+        <v>46325.30905083333</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8232,7 +8234,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46324.30732274306</v>
+        <v>46325.3090562963</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8302,7 +8304,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46324.30732898148</v>
+        <v>46325.30906238426</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8372,7 +8374,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46324.30733427084</v>
+        <v>46325.3090683912</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8435,10 +8437,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0010440889848111</v>
+        <v>1.0012395345437652</v>
       </c>
       <c r="T63" s="156">
-        <v>46324.307340983796</v>
+        <v>46325.30907396991</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>

--- a/excel/latest/PonsV2_股票Quote控筹模型.xlsx
+++ b/excel/latest/PonsV2_股票Quote控筹模型.xlsx
@@ -4691,10 +4691,10 @@
         <v>https://www.ponsfamily.com/launchpad/0x177c73569bB399AD42235067172ceB9c5c7fEd49</v>
       </c>
       <c r="S9" s="26">
-        <v>2249.665085375695</v>
+        <v>2244.0889324799714</v>
       </c>
       <c r="T9" s="29">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="U9" s="32" t="inlineStr">
         <is>
@@ -4759,10 +4759,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xaF3D76f1834A1d425780943C99Ea8A608f8a93f9</v>
       </c>
       <c r="S10" s="27">
-        <v>350.97450643897145</v>
+        <v>345.41151038096046</v>
       </c>
       <c r="T10" s="30">
-        <v>46325.30876709491</v>
+        <v>46326.30089288195</v>
       </c>
       <c r="U10" s="33" t="inlineStr">
         <is>
@@ -4832,7 +4832,7 @@
         </is>
       </c>
       <c r="T11" s="30">
-        <v>46325.30877523148</v>
+        <v>46326.30089863426</v>
       </c>
       <c r="U11" s="33" t="inlineStr">
         <is>
@@ -4902,7 +4902,7 @@
         </is>
       </c>
       <c r="T12" s="30">
-        <v>46325.30877840278</v>
+        <v>46326.30090443287</v>
       </c>
       <c r="U12" s="33" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         </is>
       </c>
       <c r="T13" s="30">
-        <v>46325.3087844676</v>
+        <v>46326.30091027777</v>
       </c>
       <c r="U13" s="33" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         </is>
       </c>
       <c r="T14" s="30">
-        <v>46325.308789953706</v>
+        <v>46326.30091592593</v>
       </c>
       <c r="U14" s="33" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="T15" s="30">
-        <v>46325.3087960301</v>
+        <v>46326.300921724534</v>
       </c>
       <c r="U15" s="33" t="inlineStr">
         <is>
@@ -5182,7 +5182,7 @@
         </is>
       </c>
       <c r="T16" s="30">
-        <v>46325.30880186342</v>
+        <v>46326.300927638884</v>
       </c>
       <c r="U16" s="33" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         </is>
       </c>
       <c r="T17" s="30">
-        <v>46325.30880733796</v>
+        <v>46326.300933402774</v>
       </c>
       <c r="U17" s="33" t="inlineStr">
         <is>
@@ -5317,10 +5317,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x6330D8C3178a418788dF01a47479c0ce7CCF450b</v>
       </c>
       <c r="S18" s="27">
-        <v>154.49126018010298</v>
+        <v>145.59866291027186</v>
       </c>
       <c r="T18" s="30">
-        <v>46325.308813449075</v>
+        <v>46326.30093927083</v>
       </c>
       <c r="U18" s="33" t="inlineStr">
         <is>
@@ -5390,7 +5390,7 @@
         </is>
       </c>
       <c r="T19" s="30">
-        <v>46325.308818935184</v>
+        <v>46326.30094498843</v>
       </c>
       <c r="U19" s="33" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         </is>
       </c>
       <c r="T20" s="30">
-        <v>46325.30882472222</v>
+        <v>46326.30095074074</v>
       </c>
       <c r="U20" s="33" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         </is>
       </c>
       <c r="T21" s="30">
-        <v>46325.30883055556</v>
+        <v>46326.30095660879</v>
       </c>
       <c r="U21" s="33" t="inlineStr">
         <is>
@@ -5595,10 +5595,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x1D11f0496982706C5e14A514D4E79F2e6BdE4516</v>
       </c>
       <c r="S22" s="27">
-        <v>5.6770281608631485</v>
+        <v>5.664616662580003</v>
       </c>
       <c r="T22" s="30">
-        <v>46325.308836840275</v>
+        <v>46326.3009625</v>
       </c>
       <c r="U22" s="33" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         </is>
       </c>
       <c r="T23" s="30">
-        <v>46325.30884208333</v>
+        <v>46326.300968067124</v>
       </c>
       <c r="U23" s="33" t="inlineStr">
         <is>
@@ -5738,7 +5738,7 @@
         </is>
       </c>
       <c r="T24" s="30">
-        <v>46325.30884813658</v>
+        <v>46326.300974178244</v>
       </c>
       <c r="U24" s="33" t="inlineStr">
         <is>
@@ -5803,10 +5803,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xC9a981FEE1F9DEc688bb123ccDeCc63D0deBFC4e</v>
       </c>
       <c r="S25" s="27">
-        <v>368.4701660655892</v>
+        <v>358.7223587223587</v>
       </c>
       <c r="T25" s="30">
-        <v>46325.308853981485</v>
+        <v>46326.30097966435</v>
       </c>
       <c r="U25" s="33" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="T26" s="30">
-        <v>46325.30885974537</v>
+        <v>46326.300985497684</v>
       </c>
       <c r="U26" s="33" t="inlineStr">
         <is>
@@ -5941,10 +5941,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x2e0847E8910a9732eB3fb1bb4b70a580ADAD4FE3</v>
       </c>
       <c r="S27" s="27">
-        <v>284.20184188024774</v>
+        <v>281.66956069196397</v>
       </c>
       <c r="T27" s="30">
-        <v>46325.30886556713</v>
+        <v>46326.300991296295</v>
       </c>
       <c r="U27" s="33" t="inlineStr">
         <is>
@@ -6009,10 +6009,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xCceE82fE024c36fA15E1005edE3E9e4787e23D09</v>
       </c>
       <c r="S28" s="27">
-        <v>28.925810152969376</v>
+        <v>27.552455251029592</v>
       </c>
       <c r="T28" s="30">
-        <v>46325.30887127315</v>
+        <v>46326.30099730324</v>
       </c>
       <c r="U28" s="33" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="T29" s="30">
-        <v>46325.308877083335</v>
+        <v>46326.301002858796</v>
       </c>
       <c r="U29" s="33" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         </is>
       </c>
       <c r="T30" s="30">
-        <v>46325.308882604164</v>
+        <v>46326.30100864583</v>
       </c>
       <c r="U30" s="33" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         </is>
       </c>
       <c r="T31" s="30">
-        <v>46325.308888645835</v>
+        <v>46326.30101445602</v>
       </c>
       <c r="U31" s="33" t="inlineStr">
         <is>
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="T32" s="30">
-        <v>46325.30889453703</v>
+        <v>46326.30102017361</v>
       </c>
       <c r="U32" s="33" t="inlineStr">
         <is>
@@ -6362,7 +6362,7 @@
         </is>
       </c>
       <c r="T33" s="30">
-        <v>46325.30890034722</v>
+        <v>46326.30102600694</v>
       </c>
       <c r="U33" s="33" t="inlineStr">
         <is>
@@ -6427,10 +6427,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xc0D6457C16Cc70d6790Dd43521C899C87ce02f35</v>
       </c>
       <c r="S34" s="27">
-        <v>619.226602533937</v>
+        <v>615.4115604217437</v>
       </c>
       <c r="T34" s="30">
-        <v>46325.3089062963</v>
+        <v>46326.30103180555</v>
       </c>
       <c r="U34" s="33" t="inlineStr">
         <is>
@@ -6500,7 +6500,7 @@
         </is>
       </c>
       <c r="T35" s="30">
-        <v>46325.30891157407</v>
+        <v>46326.30103759259</v>
       </c>
       <c r="U35" s="33" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         </is>
       </c>
       <c r="T36" s="30">
-        <v>46325.30891760417</v>
+        <v>46326.301043437496</v>
       </c>
       <c r="U36" s="33" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         </is>
       </c>
       <c r="T37" s="30">
-        <v>46325.30892354166</v>
+        <v>46326.30104917824</v>
       </c>
       <c r="U37" s="33" t="inlineStr">
         <is>
@@ -6705,10 +6705,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xec262a75e413fAfD0dF80480274532C79D42da09</v>
       </c>
       <c r="S38" s="27">
-        <v>136.90949395351444</v>
+        <v>132.0476188093296</v>
       </c>
       <c r="T38" s="30">
-        <v>46325.30892928241</v>
+        <v>46326.30105498843</v>
       </c>
       <c r="U38" s="33" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         </is>
       </c>
       <c r="T39" s="30">
-        <v>46325.308934733795</v>
+        <v>46326.301060694444</v>
       </c>
       <c r="U39" s="33" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         </is>
       </c>
       <c r="T40" s="30">
-        <v>46325.30894635417</v>
+        <v>46326.30107234954</v>
       </c>
       <c r="U40" s="33" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         </is>
       </c>
       <c r="T41" s="30">
-        <v>46325.30895241898</v>
+        <v>46326.301078171295</v>
       </c>
       <c r="U41" s="33" t="inlineStr">
         <is>
@@ -6983,10 +6983,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xd0601CE157Db5bdC3162BbaC2a2C8aF5320D9EEC</v>
       </c>
       <c r="S42" s="27">
-        <v>209.2490503243015</v>
+        <v>204.28649349219614</v>
       </c>
       <c r="T42" s="30">
-        <v>46325.30894083333</v>
+        <v>46326.3010665625</v>
       </c>
       <c r="U42" s="33" t="inlineStr">
         <is>
@@ -7056,7 +7056,7 @@
         </is>
       </c>
       <c r="T43" s="30">
-        <v>46325.308958263886</v>
+        <v>46326.30108386574</v>
       </c>
       <c r="U43" s="33" t="inlineStr">
         <is>
@@ -7126,7 +7126,7 @@
         </is>
       </c>
       <c r="T44" s="30">
-        <v>46325.308964004624</v>
+        <v>46326.30108972222</v>
       </c>
       <c r="U44" s="33" t="inlineStr">
         <is>
@@ -7191,10 +7191,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xD5f3879160bc7c32ebb4dC785F8a4F505888de68</v>
       </c>
       <c r="S45" s="27">
-        <v>704.0916654818666</v>
+        <v>695.3066749400762</v>
       </c>
       <c r="T45" s="30">
-        <v>46325.30896949075</v>
+        <v>46326.30109548611</v>
       </c>
       <c r="U45" s="33" t="inlineStr">
         <is>
@@ -7259,10 +7259,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0xF0C4BF4C582cb3836e98394b1d4e7B7281101bE8</v>
       </c>
       <c r="S46" s="27">
-        <v>43.84427921767148</v>
+        <v>43.26526118786811</v>
       </c>
       <c r="T46" s="30">
-        <v>46325.30897554398</v>
+        <v>46326.30110131944</v>
       </c>
       <c r="U46" s="33" t="inlineStr">
         <is>
@@ -7327,10 +7327,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x05b37Fb53A299a1b874A619e1c4C404D52C36F4C</v>
       </c>
       <c r="S47" s="27">
-        <v>106.53188647545662</v>
+        <v>92.30522876144057</v>
       </c>
       <c r="T47" s="30">
-        <v>46325.30898134259</v>
+        <v>46326.30110704861</v>
       </c>
       <c r="U47" s="33" t="inlineStr">
         <is>
@@ -7400,7 +7400,7 @@
         </is>
       </c>
       <c r="T48" s="30">
-        <v>46325.308987372686</v>
+        <v>46326.30111283565</v>
       </c>
       <c r="U48" s="33" t="inlineStr">
         <is>
@@ -7470,7 +7470,7 @@
         </is>
       </c>
       <c r="T49" s="30">
-        <v>46325.30899284722</v>
+        <v>46326.30111861111</v>
       </c>
       <c r="U49" s="33" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         </is>
       </c>
       <c r="T50" s="30">
-        <v>46325.3089987037</v>
+        <v>46326.30112445602</v>
       </c>
       <c r="U50" s="33" t="inlineStr">
         <is>
@@ -7610,7 +7610,7 @@
         </is>
       </c>
       <c r="T51" s="30">
-        <v>46325.309004525465</v>
+        <v>46326.30113024305</v>
       </c>
       <c r="U51" s="33" t="inlineStr">
         <is>
@@ -7680,7 +7680,7 @@
         </is>
       </c>
       <c r="T52" s="30">
-        <v>46325.30901038195</v>
+        <v>46326.30113597222</v>
       </c>
       <c r="U52" s="33" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         </is>
       </c>
       <c r="T53" s="30">
-        <v>46325.309016342595</v>
+        <v>46326.301141793985</v>
       </c>
       <c r="U53" s="33" t="inlineStr">
         <is>
@@ -7820,7 +7820,7 @@
         </is>
       </c>
       <c r="T54" s="30">
-        <v>46325.30902184028</v>
+        <v>46326.30114753472</v>
       </c>
       <c r="U54" s="33" t="inlineStr">
         <is>
@@ -7885,10 +7885,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x4a0E65A3EcceC6dBe60AE065F2e7bb85Fae35eEa</v>
       </c>
       <c r="S55" s="27">
-        <v>140.204573261698</v>
+        <v>136.80149321697183</v>
       </c>
       <c r="T55" s="30">
-        <v>46325.30902763889</v>
+        <v>46326.30115337963</v>
       </c>
       <c r="U55" s="33" t="inlineStr">
         <is>
@@ -7953,10 +7953,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x117cc2133c37B721F49dE2A7a74833232B3B4C0C</v>
       </c>
       <c r="S56" s="27">
-        <v>765.1472522983454</v>
+        <v>757.3972787822075</v>
       </c>
       <c r="T56" s="30">
-        <v>46325.3090334375</v>
+        <v>46326.30115912037</v>
       </c>
       <c r="U56" s="33" t="inlineStr">
         <is>
@@ -8021,10 +8021,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x322F0929c4625eD5bAd873c95208D54E1c003b2d</v>
       </c>
       <c r="S57" s="27">
-        <v>396.7211407722761</v>
+        <v>400.17614355699897</v>
       </c>
       <c r="T57" s="30">
-        <v>46325.30903917824</v>
+        <v>46326.301164895835</v>
       </c>
       <c r="U57" s="33" t="inlineStr">
         <is>
@@ -8094,7 +8094,7 @@
         </is>
       </c>
       <c r="T58" s="30">
-        <v>46325.30904506944</v>
+        <v>46326.30117070602</v>
       </c>
       <c r="U58" s="33" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         </is>
       </c>
       <c r="T59" s="30">
-        <v>46325.30905083333</v>
+        <v>46326.301176493056</v>
       </c>
       <c r="U59" s="33" t="inlineStr">
         <is>
@@ -8234,7 +8234,7 @@
         </is>
       </c>
       <c r="T60" s="30">
-        <v>46325.3090562963</v>
+        <v>46326.3011822801</v>
       </c>
       <c r="U60" s="33" t="inlineStr">
         <is>
@@ -8304,7 +8304,7 @@
         </is>
       </c>
       <c r="T61" s="30">
-        <v>46325.30906238426</v>
+        <v>46326.301188020836</v>
       </c>
       <c r="U61" s="33" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         </is>
       </c>
       <c r="T62" s="31">
-        <v>46325.3090683912</v>
+        <v>46326.301193784726</v>
       </c>
       <c r="U62" s="34" t="inlineStr">
         <is>
@@ -8437,10 +8437,10 @@
         <v>https://robinhoodchain.blockscout.com/address/0x5fc5360d0400a0fd4f2af552add042d716f1d168</v>
       </c>
       <c r="S63" s="155">
-        <v>1.0012395345437652</v>
+        <v>1.000815664766785</v>
       </c>
       <c r="T63" s="156">
-        <v>46325.30907396991</v>
+        <v>46326.301199664354</v>
       </c>
       <c r="U63" t="inlineStr">
         <is>
